--- a/leads-adept/leads-adept.xlsx
+++ b/leads-adept/leads-adept.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Verworfen" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$I$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$I$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -544,27 +544,27 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Anja Hollenhorst</t>
+          <t>Wolfgang Heidel</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführerin (lt. Impressum; auf der Website Ansprechpartnerin Kundenservice)</t>
+          <t>Geschäftsleitung</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>anja@hti-spedition.de</t>
+          <t>wolfgang.heidel@bayern-express-spedition.de</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>+49 251 74787-0 (Zentrale, Durchwahlen 11-21)</t>
+          <t>+49 89 329892-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>HTI Spedition und Logistik GmbH</t>
+          <t>Bayern Express Spedition GmbH</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -574,44 +574,44 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Münster (NRW)</t>
+          <t>Garching bei München, weiterer Standort Pilsting-Ganacker, Bayern</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Familiengeführte Spedition (Familie Hollenhorst) mit Fernverkehr, Luft-/Seefracht inkl. Zollabwicklung, Lager und Status Reglementierter Beauftragter. Zoll-, Fracht- und Dispositionsprozesse mit hohem Dokumentenaufkommen — gutes Feld für Prozessautomatisierung und Systemanbindung.</t>
+          <t>Familiengeführte bayerische Spedition (Familie Heidel) mit Fernverkehr, Nahverkehrsdisposition, Stückgut-/VTL-Systemverkehr und eigener Abwicklung an zwei Standorten.</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>https://hti-spedition.de/ | https://hti-spedition.de/impressum/</t>
+          <t>https://www.bayern-express-spedition.de/mitarbeiter.php</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Florian Meyer</t>
+          <t>Jens Haverland</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführung / Logistik- und Lagerleitung</t>
+          <t>Geschäftsführer</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>florian.meyer@rdllogistik.de</t>
+          <t>jhaverland@cargomar.de</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>+49 (0)2151 36806-16</t>
+          <t>+49 421 5590-10 (Zentrale)</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>RDL Logistik Rheinische Distributions- und Lagerlogistik GmbH</t>
+          <t>Cargomar GmbH Internationale Spedition / Cargomar Air &amp; Sea GmbH</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,44 +621,44 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Krefeld (Niederrhein, NRW), zweiter Standort Willich</t>
+          <t>Bremen</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Inhabergeführter Lager- und Distributionslogistiker am Niederrhein (seit 2000) mit Lagerlogistik, Distribution und Fuhrpark an zwei Standorten. Geschäftsführung leitet operativ Lager und Abrechnung selbst — Digitalisierung von Lagerverwaltung, Disposition und Abrechnung ist unmittelbar chef-relevant.</t>
+          <t>Inhabergeführte Bremer Spedition mit See-/Luftfracht, Import/Export sowie eigener Lagerlogistik (Teamleitung Lagerlogistik im Haus).</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>https://rdllogistik.de/ueber-uns/ | https://rdllogistik.de/ | https://rdllogistik.de/impressum/</t>
+          <t>https://www.cargomar.de/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Michael Hoeper</t>
+          <t>Dr. Rimbert J. Kelber</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer</t>
+          <t>Niederlassungsleitung</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>hoeper@hoeper-spedition.de</t>
+          <t>rimbert.kelber@koester-hapke-sped.com</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>02862-418327-10</t>
+          <t>+49 5132 822-100</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Richard Hoeper GmbH &amp; Co. KG (Hoeper Spedition)</t>
+          <t>Carl Köster &amp; Louis Hapke GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -668,44 +668,44 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Südlohn-Oeding (Westmünsterland, NRW)</t>
+          <t>Sehnde-Höver bei Hannover, Niedersachsen</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Familienunternehmen in zweiter Generation mit Transporten, eigenem Fuhrpark, Lagerlogistik und Palettenmanagement im Westmünsterland. Kleinerer, aber voll ausgebauter Betrieb mit Dispo-, QM- und Projektmanagement-Funktionen; Hinweis: liegt vermutlich unterhalb der 50-Mitarbeiter-Schwelle.</t>
+          <t>Mittelständische, inhabergeführte Spedition seit 1854 mit nationalen/internationalen Stückgutverkehren, Messelogistik und eigener Lagerlogistik (eigene Lagerleitung).</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>https://hoeper-spedition.de/team/ | https://hoeper-spedition.de/ | https://hoeper-spedition.de/impressum/</t>
+          <t>https://koester-hapke-sped.com/ansprechpartner/ | https://koester-hapke-sped.com/wir-ueber-uns/ | https://koester-hapke-sped.com/kontakt/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Bernd Häger</t>
+          <t>Anja Hollenhorst</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer</t>
+          <t>Geschäftsführerin (lt. Impressum; auf der Website Ansprechpartnerin Kundenservice)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>bhaeger@spedition-haeger.de</t>
+          <t>anja@hti-spedition.de</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>02904 9740-0</t>
+          <t>+49 251 74787-0 (Zentrale, Durchwahlen 11-21)</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Spedition Häger GmbH &amp; Co. KG / Häger Transporte u. Logistik GmbH &amp; Co. KG</t>
+          <t>HTI Spedition und Logistik GmbH</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -715,44 +715,44 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Bestwig (Sauerland, NRW)</t>
+          <t>Münster (NRW)</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Familiengeführte Sauerland-Spedition mit Transport-, Lager- und Kontraktlogistik über zwei Schwestergesellschaften. Zwei-Firmen-Struktur und gewachsene Dispositions-/Lagerprozesse sprechen für manuelle Abläufe mit Digitalisierungs- und Systemintegrationsbedarf.</t>
+          <t>Familiengeführte Spedition (Familie Hollenhorst) mit Fernverkehr, Luft-/Seefracht inkl. Zollabwicklung, Lager und Status Reglementierter Beauftragter. Zoll-, Fracht- und Dispositionsprozesse mit hohem Dokumentenaufkommen — gutes Feld für Prozessautomatisierung und Systemanbindung.</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>https://www.spedition-haeger.de/kontakt/</t>
+          <t>https://hti-spedition.de/ | https://hti-spedition.de/impressum/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Theodor Schulz</t>
+          <t>Peter Plank</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer (Disposition &amp; Kundenbetreuung)</t>
+          <t>Vorsitzender Geschäftsführer / Inhaber</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>ts@schulz-spedition.de</t>
+          <t>peterplank@hellmold-plank.de</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>+49 251 26333-211</t>
+          <t>+49 641 95201-16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Theodor Schulz GmbH &amp; Co. KG (Schulz Spedition)</t>
+          <t>Hellmold &amp; Plank GmbH &amp; Co. KG Spedition</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -762,69 +762,915 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Münster (NRW)</t>
+          <t>Gießen (Europastr. 7+9, 35394), Hessen</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Inhabergeführte Münsteraner Spedition mit Transport, Lagerung/Lagerverwaltung, Palettenmanagement und Abrechnung als eigene Abteilungen. Geschäftsführung sitzt selbst in der Disposition — kurze Entscheidungswege, viele manuell getriebene Dispo- und Abrechnungsprozesse als Digitalisierungsansatz.</t>
+          <t>1904 gegründete, inhabergeführte hessische Spedition (seit 1996 im Alleinbesitz der Familie Plank) mit Systemverkehren, Fernverkehr und Lagerlogistik; zweite Generation (Niklas Plank) in der Geschäftsführung.</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>https://www.schulz-spedition.de/ | https://www.schulz-spedition.de/#unternehmen</t>
+          <t>https://www.hellmold-plank.de/de/kontakt | https://www.hellmold-plank.de/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>Ingo Kaiser</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführung (Management)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>ingo.kaiser@ikg-spedition.de</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>+49 7223 281689-19</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>IKG Spedition GmbH</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Baden-Baden / Sinzheim, Baden-Württemberg</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Familiengeführte Spedition (Ingo und Kristina Kaiser) mit intermodalen Transporten Richtung Italien/Frankreich/Schweiz, eigenem Lager und Fuhrpark sowie Niederlassung in Busto Arsizio.</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ikg-spedition.de/team/ | https://www.ikg-spedition.de/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Joachim Berends</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführer</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>j.berends@bentheimer-eisenbahn.de</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>+49 5921 8034-0</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Kraftverkehr Emsland GmbH</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Nordhorn, Niedersachsen</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführer der Kraftverkehr Emsland GmbH (Spedition/Logistiklager der Bentheimer Eisenbahn-Gruppe). Hinweis: die auf der Ansprechpartner-Seite genannte E-Mail läuft über die Domain der Muttergesellschaft.</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kraftverkehr-emsland.de/kontakt/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Marco Oppermann</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Speditionsleitung &amp; Prokurist</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>marco.oppermann@kraftverkehr-emsland.de</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>+49 5921 8034-96</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Kraftverkehr Emsland GmbH</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Nordhorn, Niedersachsen</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Mittelständische Spedition mit Sammelgut, Ladungsverkehren und eigenem Warehousing-Bereich; Prokurist und Speditionsleiter mit Entscheidungsbefugnis über Prozesse/IT-Themen.</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kraftverkehr-emsland.de/kontakt/ | https://www.kraftverkehr-emsland.de/spedition-logistiklager/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Florian Meyer</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführung / Logistik- und Lagerleitung</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>florian.meyer@rdllogistik.de</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>+49 (0)2151 36806-16</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>RDL Logistik Rheinische Distributions- und Lagerlogistik GmbH</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Krefeld (Niederrhein, NRW), zweiter Standort Willich</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Inhabergeführter Lager- und Distributionslogistiker am Niederrhein (seit 2000) mit Lagerlogistik, Distribution und Fuhrpark an zwei Standorten. Geschäftsführung leitet operativ Lager und Abrechnung selbst — Digitalisierung von Lagerverwaltung, Disposition und Abrechnung ist unmittelbar chef-relevant.</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>https://rdllogistik.de/ueber-uns/ | https://rdllogistik.de/ | https://rdllogistik.de/impressum/</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Michael Hoeper</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführer</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>hoeper@hoeper-spedition.de</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>02862-418327-10</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Richard Hoeper GmbH &amp; Co. KG (Hoeper Spedition)</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Südlohn-Oeding (Westmünsterland, NRW)</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Familienunternehmen in zweiter Generation mit Transporten, eigenem Fuhrpark, Lagerlogistik und Palettenmanagement im Westmünsterland. Kleinerer, aber voll ausgebauter Betrieb mit Dispo-, QM- und Projektmanagement-Funktionen; Hinweis: liegt vermutlich unterhalb der 50-Mitarbeiter-Schwelle.</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>https://hoeper-spedition.de/team/ | https://hoeper-spedition.de/ | https://hoeper-spedition.de/impressum/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Tanja Meininghaus</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführerin</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>tanja.meininghaus@sitra-spedition.de</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>+49 40 751006-0 (Zentrale)</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>SITRA Spedition GmbH</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Hamburg</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Inhabergeführte Hamburger Spedition mit nationalen Stückgut-/Ladungsverkehren, internationalem Geschäft und eigener Disposition; bewusst als persönlich erreichbare Alternative zu Konzernen positioniert.</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>https://sitra-spedition.de/team/ | https://sitra-spedition.de/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Sandra Aleksanderek</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführung</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>sandra.aleksanderek@sander-logistics.de</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>+49 40 73354-128</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Sander Logistics GmbH</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Hamburg (Altenwerder), weitere Standorte Itzehoe und Rostock</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Mittelständisches, familiengeführtes Logistikunternehmen mit Sammelgut, Komplettladungen, Seefracht sowie Lager-, Beschaffungs- und Kontraktlogistik an fünf Standorten.</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>https://sander-logistics.de/ihre-ansprechpartner/ | https://sander-logistics.de/kontakt/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Frank Blodt</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführer</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>frankblodt@spedition-blodt.de</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>+49 6131 25007-0</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Spedition Blodt GmbH</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Mainz, Rheinland-Pfalz</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Familiengeführte Spedition in Mainz mit Transport, Lagerlogistik und Projektmanagement; Geschäftsführung und Lagerlogistik liegen in der Familie Blodt.</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>https://spedition-blodt.de/unser-team/</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Miriam Blodt</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführerin</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>miriamblodt@spedition-blodt.de</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>+49 6131 25007-0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Spedition Blodt GmbH</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Mainz, Rheinland-Pfalz</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Zweite Geschäftsführerin des inhabergeführten Mainzer Speditions- und Lagerlogistikbetriebs.</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>https://spedition-blodt.de/unser-team/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Bernd Häger</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführer</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>bhaeger@spedition-haeger.de</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>02904 9740-0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Spedition Häger GmbH &amp; Co. KG / Häger Transporte u. Logistik GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Bestwig (Sauerland, NRW)</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Familiengeführte Sauerland-Spedition mit Transport-, Lager- und Kontraktlogistik über zwei Schwestergesellschaften. Zwei-Firmen-Struktur und gewachsene Dispositions-/Lagerprozesse sprechen für manuelle Abläufe mit Digitalisierungs- und Systemintegrationsbedarf.</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.spedition-haeger.de/kontakt/</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Nicole Körtge</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Leitung Auftragsmanagement/Logistik</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>nicolekoertge@spedition-wagner.net</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>+49 2642 9022922</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Spedition Wagner GmbH</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Remagen (Am Römerhof 60, 53424), Rheinland-Pfalz</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Familiengeführter Logistikdienstleister mit Kontraktlogistik für die Getränkeindustrie (u. a. Krombacher), Lagerlogistik, Displaybau und eigenem Fuhrpark. Geschäftsführung (Arlt/Gaßner/Kröhl) ohne öffentliche E-Mail – Bereichsleitung Logistik als Entscheidungsträger.</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>https://spedition-wagner.net/unternehmen/team/</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Matthias Schork</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführer</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>m.schork@wuest.com</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>+49 9141 8684-140</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Spedition Wüst (Wüst GmbH &amp; Co. KG)</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Weißenburg i. Bay., weiteres Logistikzentrum Ansbach, Bayern</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Mittelständische bayerische Spedition mit Stückgut- und Ladungsverkehren sowie zwei eigenen Logistikzentren (Lagerung, Kommissionierung, Value Added Services).</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wuest.com/kontakt/ | https://www.wuest.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Michael Müller</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Logistikleiter</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>m.mueller@wuest.com</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>+49 9141 8684-106</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Spedition Wüst (Wüst GmbH &amp; Co. KG)</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Weißenburg i. Bay., Bayern</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Verantwortlicher für die Logistikzentren Weißenburg und Ansbach – direkter Entscheider für Lager-/Kontraktlogistikprozesse.</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wuest.com/kontakt/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Ralf Greinert</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführer</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>ralf.greinert@teamlogistic.de</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>+49 2602 1309-0 (Zentrale)</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>TEAM Logistic GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Montabaur (Westerwaldstr. 2a, 56410), Rheinland-Pfalz</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Familiengeführte Spedition im Westerwald (Familie Greinert) mit eigener Disposition, Werkstatt und Verwaltung; Transporte national/international.</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>https://teamlogistic.de/ansprechpartner/ | https://teamlogistic.de/impressum/</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Uwe Diel</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführer</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>uwe.diel@teamlogistic.de</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>+49 2602 1309-0 (Zentrale)</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>TEAM Logistic GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Montabaur, Rheinland-Pfalz</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Zweiter Geschäftsführer der Team Logistic GmbH &amp; Co. KG, mittelständische Spedition mit eigenem Fuhrpark.</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>https://teamlogistic.de/ansprechpartner/</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Theodor Schulz</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführer (Disposition &amp; Kundenbetreuung)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>ts@schulz-spedition.de</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>+49 251 26333-211</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Theodor Schulz GmbH &amp; Co. KG (Schulz Spedition)</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Münster (NRW)</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Inhabergeführte Münsteraner Spedition mit Transport, Lagerung/Lagerverwaltung, Palettenmanagement und Abrechnung als eigene Abteilungen. Geschäftsführung sitzt selbst in der Disposition — kurze Entscheidungswege, viele manuell getriebene Dispo- und Abrechnungsprozesse als Digitalisierungsansatz.</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.schulz-spedition.de/ | https://www.schulz-spedition.de/#unternehmen</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
           <t>Christian Vetten</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Geschäftsführer (Ansprechpartner Transporte/Lagerlogistik)</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>christian.vetten@vetten-gruppe.de</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>02162 5302-379</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Vetten Gruppe (Gebr. Vetten GmbH &amp; Co. KG)</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Logistik &amp; Supply Chain</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>Mönchengladbach (Niederrhein, NRW)</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Familienbetrieb seit 1931 mit Transport, Lagerlogistik, Textil- und Kontraktlogistik auf &gt;100.000 qm Lagerfläche. Gewachsene Gruppenstruktur mit mehreren Standorten, Variantenvielfalt (Textilaufbereitung, Kontraktlogistik) und vorhandener Logistik-IT (ecovium/SPEDION im Einsatz) — viel Potenzial für Prozessdigitalisierung und Schnittstellen-/ERP-Themen.</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I24" s="2" t="inlineStr">
         <is>
           <t>https://vetten-gruppe.de/kontakt/ | https://vetten-gruppe.de/ | https://vetten-gruppe.de/impressum/ | https://vetten-gruppe.de/die-vetten-gruppe/</t>
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Andreas Koch</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführer</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>a.koch@eckhardt-logistik.de</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>+49 711 80000-0 (Zentrale)</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Walter Eckhardt GmbH Spedition + Logistik</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Korntal-Münchingen (Raum Stuttgart), Baden-Württemberg</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Inhabergeführte Spedition seit 1987 mit Stückgut, Gefahrgut- und Pflanzentransporten sowie eigenem Lager-/Kommissionierzentrum (seit 2019). Eigene Bereiche für Umschlag, Lagerlogistik und Disposition.</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>https://eckhardt-logistik.de/kontakt/ansprechpartner | https://eckhardt-logistik.de/</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Marc Eckhardt</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Gesellschafter (Inhaberfamilie)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>m.eckhardt@eckhardt-logistik.de</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>+49 711 80000-0 (Zentrale)</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Walter Eckhardt GmbH Spedition + Logistik</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Korntal-Münchingen (Raum Stuttgart), Baden-Württemberg</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Gesellschafter und Namensträger des familiengeführten Speditions- und Logistikunternehmens; zweiter Entscheidungsträger neben der Geschäftsführung.</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>https://eckhardt-logistik.de/kontakt/ansprechpartner | https://eckhardt-logistik.de/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I8"/>
+  <autoFilter ref="A1:I26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -893,10 +1739,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5">
@@ -919,10 +1765,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -936,7 +1782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -970,12 +1816,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Kraftverkehr Münsterland C. Weilke GmbH &amp; Co. KG</t>
+          <t>Hermann Ritter GmbH &amp; Co. KG (Ritter Spedition)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Greven</t>
+          <t>Feilitzsch-Zedtwitz, Bayern</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -985,19 +1831,19 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>nur info@weilke.de auf Website, keine Ansprechpartner-/Teamseite mit Personen-E-Mails gefunden</t>
+          <t>nur 40 Mitarbeiter (unter Zielgröße) und nur info@-Adresse</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Richter Spedition GmbH</t>
+          <t>Metzger Spedition GmbH</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Schwerte</t>
+          <t>Neu-Kupfer, Baden-Württemberg</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1007,19 +1853,19 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>nur info@richter-spedition.de, keine Personenseite; Geschäftsführung nicht mit E-Mail veröffentlicht</t>
+          <t>nur info@metzger-spedition.de, keine Personen auf der Website</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Gustav Mäuler GmbH &amp; Co. KG</t>
+          <t>Rüdinger Spedition GmbH</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Remscheid</t>
+          <t>Krautheim, Baden-Württemberg</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1029,19 +1875,19 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>nur info@ und verkauf@ (Funktionsadressen), keine namentlichen Ansprechpartner auf Homepage und Kontaktseite</t>
+          <t>Ansprechpartner mit Namen/Positionen, aber E-Mail-Adressen verschleiert; auch per curl keine Adresse im Quelltext</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Spedition Zobel</t>
+          <t>ZUFALL logistics group (Friedrich Zufall GmbH &amp; Co. KG)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Wetter (Ruhr)</t>
+          <t>Göttingen, Niedersachsen</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1051,19 +1897,19 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Ansprechpartner-Seite nennt nur Personalmanagement; keine E-Mail der Geschäftsführer Philip/Christian Zobel veröffentlicht</t>
+          <t>nur standortbezogene Sammeladressen (goettingen@, kassel@ …), keine persönliche E-Mail der Geschäftsführung</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LLS-Service GmbH</t>
+          <t>Heinrich Koch Internationale Spedition GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Gladbeck</t>
+          <t>Osnabrück, Niedersachsen</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1073,19 +1919,19 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>nur info@lls.services, keine namentlichen Entscheidungsträger auf der Website</t>
+          <t>auf der Kontaktseite nur info@koch-international.de, keine Ansprechpartner-Seite mit Personen-E-Mails</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Emmerich &amp; Rosenberger GmbH &amp; Co. KG (EMRO)</t>
+          <t>Döderlein Spedition GmbH</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Duisburg</t>
+          <t>Nördlingen, Bayern</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1095,19 +1941,19 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>nur info@emro.de, keine Ansprechpartner-Seite mit persönlichen E-Mails gefunden</t>
+          <t>nur info@doederlein.de, keine Ansprechpartner-/Teamseite</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NW Logistik</t>
+          <t>Elflein Spedition &amp; Transport GmbH</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ahlen</t>
+          <t>Bamberg, Bayern</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1117,19 +1963,19 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Website nicht erreichbar (DNS-Fehler), keine Daten verifizierbar</t>
+          <t>Geschäftsführer mit Durchwahl gelistet, aber E-Mail-Links leer ('#') – keine wörtliche Adresse auf der Seite</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Emons Spedition GmbH</t>
+          <t>Spedicam GmbH</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Neufahrn (Raum München), Bayern</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1139,27 +1985,555 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Konzernähnliche Größe (&gt;3.000 Mitarbeiter, 100 Standorte) — außerhalb Mittelstands-Zielprofil</t>
+          <t>nur Funktionsadressen (Gf@, Sl@, Vl@ …), keine personenbezogenen E-Mails</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Wiedmann &amp; Winz GmbH</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Geislingen an der Steige, Baden-Württemberg</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>nur Funktionsadressen (mail@, offer@, anfrage@), keine Ansprechpartner-Seite</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>BKV Logistik GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Rheinstetten, Baden-Württemberg</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>nur Funktionsadressen (kontakt@, transportlogistik@, kontraktlogistik@)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>BECK Spedition + Logistik GmbH</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Filderstadt, Baden-Württemberg</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>nur info@becksped.de, keine Personen auf der Kontaktseite</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Abt Spedition &amp; Service</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Schwäbisch Gmünd, Baden-Württemberg</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Ansprechpartner Jochen Abt genannt, aber nur info@abt-spedition.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Honold Contract Logistics GmbH</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Neu-Ulm, Bayern</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Geschäftsführer namentlich genannt, aber nur Sammeladresse kontraktlogistik@honold.net</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>LTG Logistik und Transport GmbH</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Hamburg</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>keine E-Mail-Adressen auf der Kontaktseite</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>RM Logistik GmbH</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Grasberg / Bremen</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Geschäftsführung (Familie Meyer) mit Telefon, aber keine E-Mail-Adressen auf der Seite</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Spedition Bode GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Bad Oldesloe/Bargteheide, Schleswig-Holstein</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>persönliche GF-Adresse vorhanden, aber Standort außerhalb der definierten Zielregionen</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Finsterwalder Transport &amp; Logistik GmbH</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Türkheim, Bayern</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>nur standortbezogene Sammeladressen (sales.tu@ …)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Noerpel-Gruppe</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ulm / Hamburg / Hannover</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>über 1.000 Mitarbeiter, außerhalb der Zielgröße; nur info@noerpel.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Rudolph Logistik Gruppe</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Gudensberg, Hessen</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ca. 4.500 Mitarbeiter an 42 Standorten – Konzerngröße, außerhalb Zielprofil</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>LOXXESS AG</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Tegernsee, Bayern</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Kontraktlogistiker deutlich über 1.000 Mitarbeitern – außerhalb Zielgröße</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Spedition König</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Esslingen, Baden-Württemberg</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>nur info@koenig-sped.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Spedition Kübler GmbH</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Michelfeld/Schwäbisch Hall, Baden-Württemberg</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>nur info@kuebler-spedition.de, keine personenbezogenen E-Mails</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>E3 Spedition (E3 Gruppe)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Homberg (Hessen) u. a.</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Ansprechpartner nur über JavaScript-Filter, keine E-Mails im Seitenquelltext</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Carl Köster &amp; Louis Hapke – Kontaktseite</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Sehnde-Höver, Niedersachsen</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Hinweis: /kontakt/ enthält nur info@; verwertbare Daten ausschließlich auf /ansprechpartner/ (siehe Lead)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Kraftverkehr Münsterland C. Weilke GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Greven</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>nur info@weilke.de auf Website, keine Ansprechpartner-/Teamseite mit Personen-E-Mails gefunden</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Richter Spedition GmbH</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Schwerte</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>nur info@richter-spedition.de, keine Personenseite; Geschäftsführung nicht mit E-Mail veröffentlicht</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Gustav Mäuler GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Remscheid</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>nur info@ und verkauf@ (Funktionsadressen), keine namentlichen Ansprechpartner auf Homepage und Kontaktseite</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Spedition Zobel</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Wetter (Ruhr)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Ansprechpartner-Seite nennt nur Personalmanagement; keine E-Mail der Geschäftsführer Philip/Christian Zobel veröffentlicht</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>LLS-Service GmbH</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Gladbeck</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>nur info@lls.services, keine namentlichen Entscheidungsträger auf der Website</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Emmerich &amp; Rosenberger GmbH &amp; Co. KG (EMRO)</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Duisburg</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>nur info@emro.de, keine Ansprechpartner-Seite mit persönlichen E-Mails gefunden</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>NW Logistik</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Ahlen</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Website nicht erreichbar (DNS-Fehler), keine Daten verifizierbar</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Emons Spedition GmbH</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Köln</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Konzernähnliche Größe (&gt;3.000 Mitarbeiter, 100 Standorte) — außerhalb Mittelstands-Zielprofil</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>TEAM Logistic (Greinert/Diel)</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>Raum Montabaur (RLP)</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Logistik &amp; Supply Chain</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
         <is>
           <t>persönliche GF-E-Mails vorhanden, aber außerhalb Zielregion und Größe nicht verifiziert — nachqualifizierbar</t>
         </is>

--- a/leads-adept/leads-adept.xlsx
+++ b/leads-adept/leads-adept.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Verworfen" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$I$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$I$77</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -497,101 +497,101 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Hubertus Beumer</t>
+          <t>Christian Jordan</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer</t>
+          <t>Geschäftsleitung</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>hubertus.beumer@b-logistik.de</t>
+          <t>c.jordan@dreckshage.de</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>+49 2524 911-0 (Zentrale, keine Durchwahl veröffentlicht)</t>
+          <t>0521 9259-101</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>B Logistik GmbH</t>
+          <t>August Dreckshage GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Maschinenbau &amp; Fertigung</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Ennigerloh (Münsterland, NRW)</t>
+          <t>Bielefeld (Ostwestfalen-Lippe)</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Mittelständischer, inhabergeführter Kontraktlogistiker mit 65.000 qm Logistikfläche an drei Standorten (u. a. Pharma-Logistik-Centrum, Retail/E-Commerce, Nahrungsmittel). Branchenmix mit hohen Compliance-Anforderungen (Pharma/GDP) und kundenindividuellen Value-Added-Services — klassisches Umfeld für manuelle Prozesse und ERP-/LVS-Integration.</t>
+          <t>Bielefelder Familienunternehmen für Antriebs- und Lineartechnik, technische Walzen, Profile und Systeme sowie Werkstoffe – Zulieferer und Fertigungspartner des Maschinenbaus.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>https://www.b-logistik.de/kontakt | https://www.b-logistik.de/ | https://www.b-logistik.de/ueber-uns/unser-team</t>
+          <t>https://dreckshage.de/de/kontakt/ansprechpartner | https://dreckshage.de/en/contact/contact-partner (Zitat: 'Geschäftsleitung | Christian Jordan | Telefon 0521 9259-101 | E-Mail | c.jordan@dreckshage.de')</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Wolfgang Heidel</t>
+          <t>Markus Bürger</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsleitung</t>
+          <t>Geschäftsführung</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>wolfgang.heidel@bayern-express-spedition.de</t>
+          <t>m.buerger@blechwerk.de</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>+49 89 329892-10</t>
+          <t>+49 (0) 5222 / 91793-0</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Bayern Express Spedition GmbH</t>
+          <t>Blechwerk Bürger GmbH</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Maschinenbau &amp; Fertigung</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Garching bei München, weiterer Standort Pilsting-Ganacker, Bayern</t>
+          <t>Bad Salzuflen (Ostwestfalen-Lippe)</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Familiengeführte bayerische Spedition (Familie Heidel) mit Fernverkehr, Nahverkehrsdisposition, Stückgut-/VTL-Systemverkehr und eigener Abwicklung an zwei Standorten.</t>
+          <t>Inhabergeführter Betrieb der metallverarbeitenden Fertigung (Blechbearbeitung, Laserschneiden, Kanten, Schweißbaugruppen) für Maschinenbau-Kunden in OWL.</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>https://www.bayern-express-spedition.de/mitarbeiter.php</t>
+          <t>https://blechwerk.de/unternehmen/ansprechpartner/ | https://blechwerk.de/ (Zitat u. a.: '40 Mitarbeitern mit mehr als 20 Jahren Erfahrung in der Metall- und Blechv...', Standort 32107 Bad Salzuflen)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Jens Haverland</t>
+          <t>Holger Krebs</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -601,467 +601,467 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>jhaverland@cargomar.de</t>
+          <t>krebs@ctechnik.de</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>+49 421 5590-10 (Zentrale)</t>
+          <t>+49 2154 89102-0</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Cargomar GmbH Internationale Spedition / Cargomar Air &amp; Sea GmbH</t>
+          <t>C-Technik Maschinen- und Anlagenbau GmbH</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Maschinenbau &amp; Fertigung</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Bremen</t>
+          <t>Willich (Niederrhein); zweiter Standort Hagen</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Inhabergeführte Bremer Spedition mit See-/Luftfracht, Import/Export sowie eigener Lagerlogistik (Teamleitung Lagerlogistik im Haus).</t>
+          <t>Inhabergeführter Sondermaschinen- und Anlagenbauer mit Konstruktion, Kalkulation und Projektmanagement; Sitz 47877 Willich, weiterer Standort im Raum Hagen.</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>https://www.cargomar.de/</t>
+          <t>https://ctechnik.de/kontakt/ | https://ctechnik.de/ (Adresse 47877 Willich) | Zweiter Geschäftsführer auf derselben Seite: 'Mirko Krebs | Geschäftsführer | T. +49 2154 89102 – 211 | mkrebs@ctechnik.de'</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Dr. Rimbert J. Kelber</t>
+          <t>Dirk Haßmann</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Niederlassungsleitung</t>
+          <t>Leiter Einkauf (Bereichsleiter Einkauf/Supply Chain)</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>rimbert.kelber@koester-hapke-sped.com</t>
+          <t>Dirk.Hassmann@flaco.de</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>+49 5132 822-100</t>
+          <t>+49 (0) 5241 603-62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Carl Köster &amp; Louis Hapke GmbH &amp; Co. KG</t>
+          <t>FLACO-Geräte GmbH</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Maschinenbau &amp; Fertigung</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Sehnde-Höver bei Hannover, Niedersachsen</t>
+          <t>Gütersloh (Ostwestfalen-Lippe)</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Mittelständische, inhabergeführte Spedition seit 1854 mit nationalen/internationalen Stückgutverkehren, Messelogistik und eigener Lagerlogistik (eigene Lagerleitung).</t>
+          <t>Hersteller von Fluid-, Tank- und Werkstatttechnik sowie Fluidsystemen für Fertigungsbetriebe. Geschäftsführer Thomas Voigt ist auf der Kontaktseite genannt, jedoch ohne persönliche E-Mail – daher der Einkaufsleiter als Entscheider hinterlegt.</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>https://koester-hapke-sped.com/ansprechpartner/ | https://koester-hapke-sped.com/wir-ueber-uns/ | https://koester-hapke-sped.com/kontakt/</t>
+          <t>https://flaco.de/de/kontakt-beratung.html | https://flaco.de/de/kontakt-beratung.html (Zitat zur Geschäftsführung ohne E-Mail: 'Thomas Voigt | Geschäftsführer | Tel. +49 (0) 5241 - 603 - 0')</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Anja Hollenhorst</t>
+          <t>Frederic Lanz</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführerin (lt. Impressum; auf der Website Ansprechpartnerin Kundenservice)</t>
+          <t>CEO / Vice Chairman of the Board</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>anja@hti-spedition.de</t>
+          <t>lanz@kemper.eu</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>+49 251 74787-0 (Zentrale, Durchwahlen 11-21)</t>
+          <t>+49 (0) 2564 68-119</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>HTI Spedition und Logistik GmbH</t>
+          <t>KEMPER GmbH</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Maschinenbau &amp; Fertigung</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Münster (NRW)</t>
+          <t>Vreden (Münsterland, NRW)</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Familiengeführte Spedition (Familie Hollenhorst) mit Fernverkehr, Luft-/Seefracht inkl. Zollabwicklung, Lager und Status Reglementierter Beauftragter. Zoll-, Fracht- und Dispositionsprozesse mit hohem Dokumentenaufkommen — gutes Feld für Prozessautomatisierung und Systemanbindung.</t>
+          <t>Familiengeführter Hersteller von Absaug- und Filteranlagen sowie Schweißrauchabsaugung für die metallverarbeitende Fertigung. Sitz 48691 Vreden.</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>https://hti-spedition.de/ | https://hti-spedition.de/impressum/</t>
+          <t>https://kemper.eu/Unternehmen/Kontakt/ | https://kemper.eu/Unternehmen/ (Adresse 48691 Vreden)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Peter Plank</t>
+          <t>Dr. Sascha Falkenberg</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Vorsitzender Geschäftsführer / Inhaber</t>
+          <t>Managing Director / Member of the Board (Geschäftsführer)</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>peterplank@hellmold-plank.de</t>
+          <t>s.falkenberg@minda.com</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>+49 641 95201-16</t>
+          <t>+49 (0) 5721 / 9789-20</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Hellmold &amp; Plank GmbH &amp; Co. KG Spedition</t>
+          <t>MINDA Industrieanlagen GmbH</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Maschinenbau &amp; Fertigung</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Gießen (Europastr. 7+9, 35394), Hessen</t>
+          <t>Minden (Ostwestfalen-Lippe)</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1904 gegründete, inhabergeführte hessische Spedition (seit 1996 im Alleinbesitz der Familie Plank) mit Systemverkehren, Fernverkehr und Lagerlogistik; zweite Generation (Niklas Plank) in der Geschäftsführung.</t>
+          <t>Anlagenbauer für Material- und Fördertechnik in der Wellpappen-, Holzwerkstoff- und Reifenindustrie mit Hauptsitz Minden.</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>https://www.hellmold-plank.de/de/kontakt | https://www.hellmold-plank.de/</t>
+          <t>https://minda.com/en/contact/general-management | https://minda.com/en/contact/management (Produktionsleitung Minden: 'Dirk Juras | Head of Production | +49 (0) 571 / 3997 - 0 | d.juras@minda.com')</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Ingo Kaiser</t>
+          <t>Olaf Clemens</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführung (Management)</t>
+          <t>Geschäftsführender Gesellschafter</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>ingo.kaiser@ikg-spedition.de</t>
+          <t>olaf.clemens@sn-packaging.de</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>+49 7223 281689-19</t>
+          <t>+49 2267 699-0</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>IKG Spedition GmbH</t>
+          <t>SN Maschinenbau GmbH</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Maschinenbau &amp; Fertigung</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Baden-Baden / Sinzheim, Baden-Württemberg</t>
+          <t>Wipperfürth (Bergisches Land / Rheinland)</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Familiengeführte Spedition (Ingo und Kristina Kaiser) mit intermodalen Transporten Richtung Italien/Frankreich/Schweiz, eigenem Lager und Fuhrpark sowie Niederlassung in Busto Arsizio.</t>
+          <t>Familiengeführter Hersteller von Beutelverpackungsmaschinen (Form-, Füll- und Verschließmaschinen) mit Firmensitz und Entwicklung in Wipperfürth. International tätig über die Marke SN Packaging.</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>https://www.ikg-spedition.de/team/ | https://www.ikg-spedition.de/</t>
+          <t>https://sn-maschinenbau.de/service-kontakt/kontakt-sales/beratung-vertrieb | https://sn-maschinenbau.de/unternehmen/ (Zitat: 'An unserem Firmensitz in Wipperfürth entwickeln täglich rund 300 Mitarbeiterinnen und Mitarbeiter führende Beutelverpackungslösung...', 51688 Wipperfürth)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Joachim Berends</t>
+          <t>Roland Mertens</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer</t>
+          <t>Geschäftsleitung Sales (Chief Sales Officer)</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>j.berends@bentheimer-eisenbahn.de</t>
+          <t>rmertens@schoellerwerk.de</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>+49 5921 8034-0</t>
+          <t>+49 2482 81 129</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Kraftverkehr Emsland GmbH</t>
+          <t>Schoeller Werk GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Maschinenbau &amp; Fertigung</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Nordhorn, Niedersachsen</t>
+          <t>Hellenthal (Eifel, NRW)</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer der Kraftverkehr Emsland GmbH (Spedition/Logistiklager der Bentheimer Eisenbahn-Gruppe). Hinweis: die auf der Ansprechpartner-Seite genannte E-Mail läuft über die Domain der Muttergesellschaft.</t>
+          <t>Metallverarbeitende Fertigung: Hersteller längsnahtgeschweißter Edelstahlrohre für Industrie und Automotive. Teil der familiengeführten Schoeller-Gruppe.</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>https://www.kraftverkehr-emsland.de/kontakt/</t>
+          <t>https://schoellerwerk.de/kontakt/ | https://www.schoellerwerk.de/en/contact/ (englische Fassung derselben Ansprechpartner-Tabelle: 'Roland Mertens | Chief Sales Officer')</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Marco Oppermann</t>
+          <t>Andreas Sommer</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Speditionsleitung &amp; Prokurist</t>
+          <t>Geschäftsführer (Werkzeugmachermeister)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>marco.oppermann@kraftverkehr-emsland.de</t>
+          <t>asommer@oelfke.de</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>+49 5921 8034-96</t>
+          <t>+49 2351 676950</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Kraftverkehr Emsland GmbH</t>
+          <t>Ulrich Oelfke Formenbau GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Maschinenbau &amp; Fertigung</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Nordhorn, Niedersachsen</t>
+          <t>Lüdenscheid (Sauerland / Märkischer Kreis)</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Mittelständische Spedition mit Sammelgut, Ladungsverkehren und eigenem Warehousing-Bereich; Prokurist und Speditionsleiter mit Entscheidungsbefugnis über Prozesse/IT-Themen.</t>
+          <t>Inhabergeführter Werkzeug- und Formenbaubetrieb für Spritzgießwerkzeuge in Lüdenscheid, Kerkhagen 15.</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>https://www.kraftverkehr-emsland.de/kontakt/ | https://www.kraftverkehr-emsland.de/spedition-logistiklager/</t>
+          <t>https://oelfke.de/kontakt/ | https://oelfke.de/impressum/ (Zitat: 'Ulrich Oelfke | Formenbau GmbH &amp; Co. KG | Geschäftsführer | Andreas Sommer | Kerkhagen 15 | 58513 Lüdenscheid') | Weiterer Entscheider: 'Julian Sommer | Geschäftsleitung | Feinwerkmechanikermeister | jsommer@oelfke.de' (https://oelfke.de/kontakt/)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Florian Meyer</t>
+          <t>Ulrich Rotte</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführung / Logistik- und Lagerleitung</t>
+          <t>Geschäftsführender Gesellschafter</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>florian.meyer@rdllogistik.de</t>
+          <t>rotte@ulrich-rotte.de</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>+49 (0)2151 36806-16</t>
+          <t>+49 5258 9789-0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>RDL Logistik Rheinische Distributions- und Lagerlogistik GmbH</t>
+          <t>Ulrich Rotte Anlagenbau &amp; Fördertechnik GmbH</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Maschinenbau &amp; Fertigung</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Krefeld (Niederrhein, NRW), zweiter Standort Willich</t>
+          <t>Salzkotten / Kreis Paderborn (Ostwestfalen-Lippe)</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Inhabergeführter Lager- und Distributionslogistiker am Niederrhein (seit 2000) mit Lagerlogistik, Distribution und Fuhrpark an zwei Standorten. Geschäftsführung leitet operativ Lager und Abrechnung selbst — Digitalisierung von Lagerverwaltung, Disposition und Abrechnung ist unmittelbar chef-relevant.</t>
+          <t>1994 gegründetes Familienunternehmen für Anlagenbau und Fördertechnik, u. a. für Holztechnik, technische Laminate und Industrieautomation.</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>https://rdllogistik.de/ueber-uns/ | https://rdllogistik.de/ | https://rdllogistik.de/impressum/</t>
+          <t>https://www.ulrich-rotte.de/ueber-uns/ | https://www.ulrich-rotte.de/ueber-uns/ (Zitat: 'Gegründet 1994 von Ulrich und Brigitte Rotte haben wir inzwischen 90 Mitarbeiter und einen Jahresumsatz von 16 Millionen...', 33154 Salzkotten) | Zweiter Entscheider auf derselben Seite: 'Benedikt Rotte | Geschäftsführender Gesellschafter | +49 5258 9789-0 | benedikt.rotte@ulrich-rotte.de'</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Michael Hoeper</t>
+          <t>Dipl.-Ing. Norbert Felder</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer</t>
+          <t>Geschäftsführer / Konstruktion &amp; Entwicklung</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>hoeper@hoeper-spedition.de</t>
+          <t>felder@weidmann-mb.de</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>02862-418327-10</t>
+          <t>+49 2241 2014101</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Richard Hoeper GmbH &amp; Co. KG (Hoeper Spedition)</t>
+          <t>WEIDMANN Maschinenbau GmbH</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Maschinenbau &amp; Fertigung</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Südlohn-Oeding (Westmünsterland, NRW)</t>
+          <t>Troisdorf (Raum Köln/Bonn, Rheinland)</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Familienunternehmen in zweiter Generation mit Transporten, eigenem Fuhrpark, Lagerlogistik und Palettenmanagement im Westmünsterland. Kleinerer, aber voll ausgebauter Betrieb mit Dispo-, QM- und Projektmanagement-Funktionen; Hinweis: liegt vermutlich unterhalb der 50-Mitarbeiter-Schwelle.</t>
+          <t>Sondermaschinenbauer für automatisierte Produktions- und Montageanlagen (u. a. Montageautomaten) mit Sitz 53842 Troisdorf.</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>https://hoeper-spedition.de/team/ | https://hoeper-spedition.de/ | https://hoeper-spedition.de/impressum/</t>
+          <t>https://weidmann-maschinenbau.de/ansprechpartner.php | https://weidmann-maschinenbau.de/unternehmen.php (Standort 53842 Troisdorf)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Tanja Meininghaus</t>
+          <t>Dominic Scheumann</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführerin</t>
+          <t>Geschäftsführer</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>tanja.meininghaus@sitra-spedition.de</t>
+          <t>d.scheumann@wibra-formenbau.de</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>+49 40 751006-0 (Zentrale)</t>
+          <t>+49 (0) 2351 / 36824-10</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>SITRA Spedition GmbH</t>
+          <t>WIBRA Formenbau GmbH</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Maschinenbau &amp; Fertigung</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Hamburg</t>
+          <t>Lüdenscheid (Sauerland / Märkischer Kreis)</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Inhabergeführte Hamburger Spedition mit nationalen Stückgut-/Ladungsverkehren, internationalem Geschäft und eigener Disposition; bewusst als persönlich erreichbare Alternative zu Konzernen positioniert.</t>
+          <t>Werkzeug- und Formenbauer in Lüdenscheid (58511) mit eigener Konstruktion und Betriebsleitung; zwei geschäftsführende Gesellschafter.</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>https://sitra-spedition.de/team/ | https://sitra-spedition.de/</t>
+          <t>https://wibraformenbau.de/kontakt/ | https://wibraformenbau.de/kontakt/ (zweiter Geschäftsführer: 'Sebastian Scholz | Geschäftsführer | Telefon: +49 (0) 23 51 / 36824 12 | E-Mail: s.scholz@wibra-formenbau.de'; Betriebsleiter: 'Jürgen Manz | Betriebsleiter | j.manz@wibra-formenbau.de')</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Sandra Aleksanderek</t>
+          <t>Christoph Dahlmann</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1071,17 +1071,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>sandra.aleksanderek@sander-logistics.de</t>
+          <t>c.dahlmann@als-arnsberg.de</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>+49 40 73354-128</t>
+          <t>02932 9306-15</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Sander Logistics GmbH</t>
+          <t>A.L.S. Allgemeine Land- und Seespedition GmbH</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Hamburg (Altenwerder), weitere Standorte Itzehoe und Rostock</t>
+          <t>Arnsberg (Sauerland)</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Mittelständisches, familiengeführtes Logistikunternehmen mit Sammelgut, Komplettladungen, Seefracht sowie Lager-, Beschaffungs- und Kontraktlogistik an fünf Standorten.</t>
+          <t>Mittelständische Spedition mit nationalen und internationalen Verkehren, Überseeverkehr, Zollabwicklung und Logistikzentrum. Klare Leitungsstruktur mit vier Prokuristen (Vertrieb, Disposition, Marketing, kaufmännische Logistikleitung).</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>https://sander-logistics.de/ihre-ansprechpartner/ | https://sander-logistics.de/kontakt/</t>
+          <t>https://www.als-arnsberg.de/ansprechpartner | https://www.regiomanager.de/suedwestfalen/ranking/mobilitaet-logistik/spedition-und-logistik/hochsauerlandkreis/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Frank Blodt</t>
+          <t>René Fröhlich</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1118,17 +1118,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>frankblodt@spedition-blodt.de</t>
+          <t>r.froehlich@lrp24.de</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>+49 6131 25007-0</t>
+          <t>+49 341 222 8 66 55 (Zentrale)</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Spedition Blodt GmbH</t>
+          <t>ALN Logistik GmbH</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1138,44 +1138,44 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Mainz, Rheinland-Pfalz</t>
+          <t>Leipzig (Sachsen)</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Familiengeführte Spedition in Mainz mit Transport, Lagerlogistik und Projektmanagement; Geschäftsführung und Lagerlogistik liegen in der Familie Blodt.</t>
+          <t>Spedition für Transport-, Sonder- und Lagerlogistik mit Sitz Brahestraße 10, 04347 Leipzig und Lagerstandorten in Leipzig und Berlin.</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>https://spedition-blodt.de/unser-team/</t>
+          <t>https://aln-logistik.de/logistik-experten/ansprechpartner/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Miriam Blodt</t>
+          <t>Hubertus Beumer</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführerin</t>
+          <t>Geschäftsführer</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>miriamblodt@spedition-blodt.de</t>
+          <t>hubertus.beumer@b-logistik.de</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>+49 6131 25007-0</t>
+          <t>+49 2524 911-0 (Zentrale, keine Durchwahl veröffentlicht)</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Spedition Blodt GmbH</t>
+          <t>B Logistik GmbH</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1185,24 +1185,24 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Mainz, Rheinland-Pfalz</t>
+          <t>Ennigerloh (Münsterland, NRW)</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Zweite Geschäftsführerin des inhabergeführten Mainzer Speditions- und Lagerlogistikbetriebs.</t>
+          <t>Mittelständischer, inhabergeführter Kontraktlogistiker mit 65.000 qm Logistikfläche an drei Standorten (u. a. Pharma-Logistik-Centrum, Retail/E-Commerce, Nahrungsmittel). Branchenmix mit hohen Compliance-Anforderungen (Pharma/GDP) und kundenindividuellen Value-Added-Services — klassisches Umfeld für manuelle Prozesse und ERP-/LVS-Integration.</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>https://spedition-blodt.de/unser-team/</t>
+          <t>https://www.b-logistik.de/kontakt | https://www.b-logistik.de/ | https://www.b-logistik.de/ueber-uns/unser-team</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Bernd Häger</t>
+          <t>Jan Feldberg</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>bhaeger@spedition-haeger.de</t>
+          <t>jan.feldberg@btg-feldberg.de</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>02904 9740-0</t>
+          <t>+49 (0) 2871 9970 260</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Spedition Häger GmbH &amp; Co. KG / Häger Transporte u. Logistik GmbH &amp; Co. KG</t>
+          <t>BTG Feldberg &amp; Sohn GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1232,44 +1232,44 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Bestwig (Sauerland, NRW)</t>
+          <t>Bocholt (Westmünsterland)</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Familiengeführte Sauerland-Spedition mit Transport-, Lager- und Kontraktlogistik über zwei Schwestergesellschaften. Zwei-Firmen-Struktur und gewachsene Dispositions-/Lagerprozesse sprechen für manuelle Abläufe mit Digitalisierungs- und Systemintegrationsbedarf.</t>
+          <t>Familiengeführte Spedition (Geschäftsführer Jan und Jörg Feldberg) mit Stückgut, Luft- und Seefracht, Logistikzentrum, Umzugslogistik sowie eigenem Projektmanagement und QM.</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>https://www.spedition-haeger.de/kontakt/</t>
+          <t>https://www.btg-feldberg.de/ansprechpartner | https://www.regiomanager.de/ranking/mobilitaet-logistik/spedition-und-logistik/muensterland/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Nicole Körtge</t>
+          <t>Mathias Ronneberger</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Leitung Auftragsmanagement/Logistik</t>
+          <t>Geschäftsführer (Shipping – Chartering &amp; Brokerage), Mitinhaber</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>nicolekoertge@spedition-wagner.net</t>
+          <t>ronneberger@balticlloyd.com</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>+49 2642 9022922</t>
+          <t>+49 381 666 139 14</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Spedition Wagner GmbH</t>
+          <t>Baltic Lloyd Schiffahrt-Spedition-Logistik GmbH</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1279,44 +1279,44 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Remagen (Am Römerhof 60, 53424), Rheinland-Pfalz</t>
+          <t>Rostock (Mecklenburg-Vorpommern)</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Familiengeführter Logistikdienstleister mit Kontraktlogistik für die Getränkeindustrie (u. a. Krombacher), Lagerlogistik, Displaybau und eigenem Fuhrpark. Geschäftsführung (Arlt/Gaßner/Kröhl) ohne öffentliche E-Mail – Bereichsleitung Logistik als Entscheidungsträger.</t>
+          <t>Im Rostocker Überseehafen (Am Skandinavienkai 2-3) ansässige Spedition für Schifffahrt, Hafenumschlag, Lagerung und Landverkehre; seit einer Nachfolgeregelung inhabergeführt durch drei langjährige Mitarbeiter.</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>https://spedition-wagner.net/unternehmen/team/</t>
+          <t>https://balticlloyd.com/dasteam/ | https://www.mbg-mv.de/rostocker-logistikunternehmen-auf-erfolgskurs-dreifache-nachfolgeregelung-sichert-zukunft</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Matthias Schork</t>
+          <t>Ronny Oldag</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer</t>
+          <t>Geschäftsführer (Cargo Handling, Storage), Mitinhaber</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>m.schork@wuest.com</t>
+          <t>oldag@balticlloyd.com</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>+49 9141 8684-140</t>
+          <t>+49 381 666 139 12</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Spedition Wüst (Wüst GmbH &amp; Co. KG)</t>
+          <t>Baltic Lloyd Schiffahrt-Spedition-Logistik GmbH</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1326,44 +1326,44 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Weißenburg i. Bay., weiteres Logistikzentrum Ansbach, Bayern</t>
+          <t>Rostock (Mecklenburg-Vorpommern)</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Mittelständische bayerische Spedition mit Stückgut- und Ladungsverkehren sowie zwei eigenen Logistikzentren (Lagerung, Kommissionierung, Value Added Services).</t>
+          <t>Geschäftsführer mit Zuständigkeit für Umschlag und Lagerung im Rostocker Überseehafen; dritter Geschäftsführer Wolfgang Nuß.</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>https://www.wuest.com/kontakt/ | https://www.wuest.com/</t>
+          <t>https://balticlloyd.com/dasteam/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Michael Müller</t>
+          <t>Wolfgang Heidel</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Logistikleiter</t>
+          <t>Geschäftsleitung</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>m.mueller@wuest.com</t>
+          <t>wolfgang.heidel@bayern-express-spedition.de</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>+49 9141 8684-106</t>
+          <t>+49 89 329892-10</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Spedition Wüst (Wüst GmbH &amp; Co. KG)</t>
+          <t>Bayern Express Spedition GmbH</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1373,24 +1373,24 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Weißenburg i. Bay., Bayern</t>
+          <t>Garching bei München, weiterer Standort Pilsting-Ganacker, Bayern</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Verantwortlicher für die Logistikzentren Weißenburg und Ansbach – direkter Entscheider für Lager-/Kontraktlogistikprozesse.</t>
+          <t>Familiengeführte bayerische Spedition (Familie Heidel) mit Fernverkehr, Nahverkehrsdisposition, Stückgut-/VTL-Systemverkehr und eigener Abwicklung an zwei Standorten.</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>https://www.wuest.com/kontakt/</t>
+          <t>https://www.bayern-express-spedition.de/mitarbeiter.php</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Ralf Greinert</t>
+          <t>Christian Messing</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1400,17 +1400,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>ralf.greinert@teamlogistic.de</t>
+          <t>c.messing@spedition-messing.de</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>+49 2602 1309-0 (Zentrale)</t>
+          <t>02541 9487-10</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>TEAM Logistic GmbH &amp; Co. KG</t>
+          <t>Bernhard Messing GmbH &amp; Co. KG (Spedition Messing)</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1420,44 +1420,44 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Montabaur (Westerwaldstr. 2a, 56410), Rheinland-Pfalz</t>
+          <t>Coesfeld</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Familiengeführte Spedition im Westerwald (Familie Greinert) mit eigener Disposition, Werkstatt und Verwaltung; Transporte national/international.</t>
+          <t>Familiengeführte Spedition mit Sammelgut, Fernverkehr, Tourendisposition, eigener Lagerlogistik und Bereich Bio &amp; Frische (Lebensmittellogistik). Mehrere Familienmitglieder (Christian, Andreas, Esther Meßing) im Unternehmen.</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>https://teamlogistic.de/ansprechpartner/ | https://teamlogistic.de/impressum/</t>
+          <t>https://www.spedition-messing.de/ansprechpartner | https://www.regiomanager.de/ranking/mobilitaet-logistik/spedition-und-logistik/kreis-coesfeld/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Uwe Diel</t>
+          <t>Tim Bönders</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer</t>
+          <t>Geschäftsführender Gesellschafter (4. Generation)</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>uwe.diel@teamlogistic.de</t>
+          <t>tboenders@bk-group.de</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>+49 2602 1309-0 (Zentrale)</t>
+          <t>nicht öffentlich</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>TEAM Logistic GmbH &amp; Co. KG</t>
+          <t>Bönders GmbH (B+K Group)</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1467,44 +1467,44 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Montabaur, Rheinland-Pfalz</t>
+          <t>Krefeld</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Zweiter Geschäftsführer der Team Logistic GmbH &amp; Co. KG, mittelständische Spedition mit eigenem Fuhrpark.</t>
+          <t>Inhabergeführter Logistikdienstleister aus Krefeld (seit über 70 Jahren, 4. Generation) mit Kontraktlogistik, Ersatzteillogistik, Warehousing und Distribution für ausgewählte Schlüsselbranchen.</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>https://teamlogistic.de/ansprechpartner/</t>
+          <t>https://www.boenders.de/about/management/ | https://www.regiomanager.de/niederrhein/ranking/mobilitaet-logistik/spedition-und-logistik/krefeld/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Theodor Schulz</t>
+          <t>Norman Lippe</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer (Disposition &amp; Kundenbetreuung)</t>
+          <t>Geschäftsführer</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>ts@schulz-spedition.de</t>
+          <t>norman.lippe@cargotrans.de</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>+49 251 26333-211</t>
+          <t>+49 2361 3061-0 (Zentrale Recklinghausen)</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Theodor Schulz GmbH &amp; Co. KG (Schulz Spedition)</t>
+          <t>CARGOTRANS GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1514,44 +1514,44 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Münster (NRW)</t>
+          <t>Recklinghausen (Hauptsitz), Verwaltung Dortmund, NL Hamburg</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Inhabergeführte Münsteraner Spedition mit Transport, Lagerung/Lagerverwaltung, Palettenmanagement und Abrechnung als eigene Abteilungen. Geschäftsführung sitzt selbst in der Disposition — kurze Entscheidungswege, viele manuell getriebene Dispo- und Abrechnungsprozesse als Digitalisierungsansatz.</t>
+          <t>Mittelständische Spedition im nördlichen Ruhrgebiet mit Road-/Intermodal-Verkehren, Warehousing und Zollservice; vollständige Ansprechpartnerliste inkl. Dispositions- und Lagerleitung öffentlich.</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>https://www.schulz-spedition.de/ | https://www.schulz-spedition.de/#unternehmen</t>
+          <t>https://www.cargotrans.de/kontakt | https://www.regiomanager.de/ranking/mobilitaet-logistik/spedition-und-logistik/dortmund/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Christian Vetten</t>
+          <t>Jens Haverland</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer (Ansprechpartner Transporte/Lagerlogistik)</t>
+          <t>Geschäftsführer</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>christian.vetten@vetten-gruppe.de</t>
+          <t>jhaverland@cargomar.de</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>02162 5302-379</t>
+          <t>+49 421 5590-10 (Zentrale)</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Vetten Gruppe (Gebr. Vetten GmbH &amp; Co. KG)</t>
+          <t>Cargomar GmbH Internationale Spedition / Cargomar Air &amp; Sea GmbH</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1561,44 +1561,44 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Mönchengladbach (Niederrhein, NRW)</t>
+          <t>Bremen</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Familienbetrieb seit 1931 mit Transport, Lagerlogistik, Textil- und Kontraktlogistik auf &gt;100.000 qm Lagerfläche. Gewachsene Gruppenstruktur mit mehreren Standorten, Variantenvielfalt (Textilaufbereitung, Kontraktlogistik) und vorhandener Logistik-IT (ecovium/SPEDION im Einsatz) — viel Potenzial für Prozessdigitalisierung und Schnittstellen-/ERP-Themen.</t>
+          <t>Inhabergeführte Bremer Spedition mit See-/Luftfracht, Import/Export sowie eigener Lagerlogistik (Teamleitung Lagerlogistik im Haus).</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>https://vetten-gruppe.de/kontakt/ | https://vetten-gruppe.de/ | https://vetten-gruppe.de/impressum/ | https://vetten-gruppe.de/die-vetten-gruppe/</t>
+          <t>https://www.cargomar.de/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Andreas Koch</t>
+          <t>Dr. Rimbert J. Kelber</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer</t>
+          <t>Niederlassungsleitung</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>a.koch@eckhardt-logistik.de</t>
+          <t>rimbert.kelber@koester-hapke-sped.com</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>+49 711 80000-0 (Zentrale)</t>
+          <t>+49 5132 822-100</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Walter Eckhardt GmbH Spedition + Logistik</t>
+          <t>Carl Köster &amp; Louis Hapke GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1608,69 +1608,2466 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Korntal-Münchingen (Raum Stuttgart), Baden-Württemberg</t>
+          <t>Sehnde-Höver bei Hannover, Niedersachsen</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Inhabergeführte Spedition seit 1987 mit Stückgut, Gefahrgut- und Pflanzentransporten sowie eigenem Lager-/Kommissionierzentrum (seit 2019). Eigene Bereiche für Umschlag, Lagerlogistik und Disposition.</t>
+          <t>Mittelständische, inhabergeführte Spedition seit 1854 mit nationalen/internationalen Stückgutverkehren, Messelogistik und eigener Lagerlogistik (eigene Lagerleitung).</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>https://eckhardt-logistik.de/kontakt/ansprechpartner | https://eckhardt-logistik.de/</t>
+          <t>https://koester-hapke-sped.com/ansprechpartner/ | https://koester-hapke-sped.com/wir-ueber-uns/ | https://koester-hapke-sped.com/kontakt/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>Andreas Grimmeißen</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>CEO – Geschäftsführer</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>andreas.grimmeissen@ewo-logistics.com</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>+49 7191 969 93 10</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>E.W.O Logistics GmbH</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Backnang bei Stuttgart (Baden-Württemberg)</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Inhabergeführte Speditions- und Logistikgesellschaft im Raum Stuttgart/Backnang, Familienunternehmen (Geschäftsführung, Verkaufs- und Dispositionsleitung sämtlich Familie Grimmeißen).</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ewo-logistics.com/ewo-logistics-backnang-stuttgart-badenwuerttemberg-deutschland/</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Doris Grimmeißen</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>CEO – Geschäftsführerin</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>doris.grimmeissen@ewo-logistics.com</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>+49 7191 969 93 20</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>E.W.O Logistics GmbH</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Backnang bei Stuttgart (Baden-Württemberg)</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Zweite Geschäftsführerin des inhabergeführten Logistikunternehmens im Rems-Murr-Kreis.</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ewo-logistics.com/ewo-logistics-backnang-stuttgart-badenwuerttemberg-deutschland/</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Anja Hollenhorst</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführerin (lt. Impressum; auf der Website Ansprechpartnerin Kundenservice)</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>anja@hti-spedition.de</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>+49 251 74787-0 (Zentrale, Durchwahlen 11-21)</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>HTI Spedition und Logistik GmbH</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Münster (NRW)</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Familiengeführte Spedition (Familie Hollenhorst) mit Fernverkehr, Luft-/Seefracht inkl. Zollabwicklung, Lager und Status Reglementierter Beauftragter. Zoll-, Fracht- und Dispositionsprozesse mit hohem Dokumentenaufkommen — gutes Feld für Prozessautomatisierung und Systemanbindung.</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>https://hti-spedition.de/ | https://hti-spedition.de/impressum/</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Klaus Hüttemann</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführer / geschäftsführender Gesellschafter (2. Generation)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>k.huettemann@huelog.de</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>+49 2065 909116</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>HUETTEMANN Logistik GmbH (HUETTEMANN Group)</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Duisburg</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Inhabergeführte Logistikgruppe aus Duisburg mit Kontraktlogistik, Lagerlogistik, Hafenumschlag und Transport. Klaus Hüttemann führt die Gruppe in zweiter Generation als geschäftsführender Gesellschafter.</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.huettemann-logistik.de/unternehmensgruppe/management/ | https://www.regiomanager.de/revier/ranking/mobilitaet-logistik/spedition-und-logistik/duisburg/</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Hanjo Heinen</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführer</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>hanjo.heinen@heinen-ht.de</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>nicht öffentlich</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Heinen Transport GmbH (Heinen Gruppe: HT, HLS, HHL, HSK, HHV, HG)</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Meerbusch (Hauptsitz), Logistikzentrum Duisburg</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Familiengeführte Transport- und Logistikgruppe im Rheinland mit Logistikzentrum in Duisburg, Speditions-, Lager- und Kontraktlogistikgesellschaften. Weitere Entscheider: Pascal Heinen (Prokurist / Leitung Logistik, pascal.heinen@heinen-ht.de), Sabine Heinen (Prokuristin, sabine.heinen@heinen-ht.de).</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.heinen-transport-gmbh.de/ansprechpartner | https://www.heinen-transport-gmbh.de/impressum</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Ludger Henke</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführung</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>l.henke@henke-spedition.de</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>+49 5250 9850-0</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Heinrich Henke Güterfernverkehr und Spedition GmbH &amp; Co.</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Delbrück (Kreis Paderborn)</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Familienspedition in dritter Generation mit Fernverkehr, Disposition und Lagerlogistik im Raum Paderborn. Mehrere Familienmitglieder (Ludger, Ludgerus, Regina Henke) im Unternehmen tätig.</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.henke-spedition.de/kontakt | https://www.regiomanager.de/ostwestfalen/ranking/mobilitaet-logistik/spedition-und-logistik/kreis-paderborn/</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Bernd Specht</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführer</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>b.specht@wichmann-transporte.de</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>+49 5481/808-51</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Heinrich Wichmann Transporte GmbH</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Lengerich (Kreis Steinfurt)</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Mittelständisches Transportunternehmen mit eigener Werkstatt, Disposition und Fuhrparkmanagement im nördlichen Münsterland.</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wichmann-transporte.de/kontakt | https://www.regiomanager.de/muensterland/ranking/mobilitaet-logistik/spedition-und-logistik/kreis-steinfurt/</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Peter Plank</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Vorsitzender Geschäftsführer / Inhaber</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>peterplank@hellmold-plank.de</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>+49 641 95201-16</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Hellmold &amp; Plank GmbH &amp; Co. KG Spedition</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Gießen (Europastr. 7+9, 35394), Hessen</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>1904 gegründete, inhabergeführte hessische Spedition (seit 1996 im Alleinbesitz der Familie Plank) mit Systemverkehren, Fernverkehr und Lagerlogistik; zweite Generation (Niklas Plank) in der Geschäftsführung.</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hellmold-plank.de/de/kontakt | https://www.hellmold-plank.de/</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Oliver Hüer</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführer</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>oliver@hueer.com</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>0251 87189-130</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Hüer Transport und Logistik GmbH</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Münster</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Inhabergeführte Spedition in Münster mit Nahverkehr, Kurierdienst und Logistikdienstleistungen. Familienstruktur: Oliver Hüer (GF) und Patrycja Hüer (Prokuristin).</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hueer.com/kontakt | https://www.hueer.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Ingo Kaiser</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführung (Management)</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>ingo.kaiser@ikg-spedition.de</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>+49 7223 281689-19</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>IKG Spedition GmbH</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Baden-Baden / Sinzheim, Baden-Württemberg</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>Familiengeführte Spedition (Ingo und Kristina Kaiser) mit intermodalen Transporten Richtung Italien/Frankreich/Schweiz, eigenem Lager und Fuhrpark sowie Niederlassung in Busto Arsizio.</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ikg-spedition.de/team/ | https://www.ikg-spedition.de/</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Joachim Berends</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführer</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>j.berends@bentheimer-eisenbahn.de</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>+49 5921 8034-0</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Kraftverkehr Emsland GmbH</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Nordhorn, Niedersachsen</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführer der Kraftverkehr Emsland GmbH (Spedition/Logistiklager der Bentheimer Eisenbahn-Gruppe). Hinweis: die auf der Ansprechpartner-Seite genannte E-Mail läuft über die Domain der Muttergesellschaft.</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kraftverkehr-emsland.de/kontakt/</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Marco Oppermann</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Speditionsleitung &amp; Prokurist</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>marco.oppermann@kraftverkehr-emsland.de</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>+49 5921 8034-96</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Kraftverkehr Emsland GmbH</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Nordhorn, Niedersachsen</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Mittelständische Spedition mit Sammelgut, Ladungsverkehren und eigenem Warehousing-Bereich; Prokurist und Speditionsleiter mit Entscheidungsbefugnis über Prozesse/IT-Themen.</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kraftverkehr-emsland.de/kontakt/ | https://www.kraftverkehr-emsland.de/spedition-logistiklager/</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Lena Milde</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Standort-/Niederlassungsleitung Magdeburg</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>lena.milde@krage-gerloff.de</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>+49 39424 951 0 (Zentrale Schwanebeck)</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Krage &amp; Gerloff Logistik GmbH</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Magdeburg (Sachsen-Anhalt)</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>1995 gegründeter Logistikdienstleister mit Hauptsitz Schwanebeck und Logistikstandort Tucheimer Straße 5, 39126 Magdeburg; Lager- und Transportlogistik.</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.krage-gerloff.de/magdeburg</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Andreas Köhler</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführer</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>a.koehler@koehler-transport.de</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>+49 221 96640-10</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>KÖHLER GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Köln</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Inhabergeführtes Familienunternehmen in Köln mit Transport, Lager und eigener Werkstatt. Etwas unterhalb der Zielgröße, aber klar mittelständisch und inhabergeführt.</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.koehler-transport.com/ansprechpartner | https://www.koehler-transport.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Alexander Schwarz</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Business Development Manager &amp; Lager Management</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>a.schwarz@lkt-thiele.com</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>+49 36373 129831-20</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>LOGISTIK KONTOR GmbH (LKT Thiele)</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Buttstädt (Thüringen)</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Verantwortlich für Geschäftsentwicklung und Lagermanagement – Bereichsleiter-Ebene für Lager-/Distributionslogistik bei der Thüringer Spedition.</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lkt-thiele.com/unternehmen/team/</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Stephan Voigt</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführer</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>s.voigt@lkt-thiele.com</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>+49 36373 129831-13</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>LOGISTIK KONTOR GmbH (LKT Thiele)</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Buttstädt (Thüringen)</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Seit 2004 tätige mittelständische Spedition mit Sitz Vor dem Lohe 5, 99628 Buttstädt und Niederlassung Wiebelsheim; nationale/internationale Transporte, Lagerung, Charterverkehr.</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lkt-thiele.com/unternehmen/team/ | https://www.lkt-thiele.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>David Liedhegener</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführender Gesellschafter</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>d.liedhegener@liedhegener-logistik.de</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>02933 - 9 22 22 10</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Liedhegener-Logistik GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Sundern (Sauerland)</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Inhabergeführter Logistikdienstleister mit Transport, Verladung und Lagerlogistik im Sauerland. Familie Liedhegener (David und Sandra Liedhegener) in Geschäftsführung und Verwaltung.</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.liedhegener-logistik.de/kontakt | https://www.regiomanager.de/suedwestfalen/ranking/mobilitaet-logistik/spedition-und-logistik/hochsauerlandkreis/</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Jakob Riesen</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführer</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>j.riesen@mbi-spedition.de</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>+49 (521) 93 803 - 0</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>MBI Internationale Spedition GmbH</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Bielefeld</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>Familiengeführte internationale Spedition mit Kontraktlogistik, Lagerung, Kommissionierung und Zollabwicklung. Zwei Geschäftsführer aus der Familie Riesen (Jakob und Peter Riesen).</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mbi-spedition.de/unser-team/ | https://www.mbi-spedition.de/</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Christof Mielke</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführung</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>mielke@mielke-logistik.de</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>0271 / 37514-0</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Mielke Logistik GmbH</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Freudenberg (Siegerland)</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Familiengeführte Spedition mit Schwer-/Spezialtransport, Disposition national und international sowie Lagerstandorten (u. a. Außenlager Netphen). Zweite Generation (Tim Christopher Mielke) bereits in der Geschäftsführung.</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mielke-logistik.de/ansprechpartner | https://www.regiomanager.de/suedwestfalen/ranking/mobilitaet-logistik/spedition-und-logistik/kreis-siegen-wittgenstein/</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>René Langen</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsleitung</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>r.langen@speditionlangen.de</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>+49 2166 9539-0</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Paul Langen GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Mönchengladbach</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>Familienunternehmen seit 1883 mit Spedition, Lagerlogistik und Möbel-/Sperrgutlogistik, europaweite Distribution ab Mönchengladbach.</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.speditionlangen.de/kontakt | https://www.regiomanager.de/ranking/mobilitaet-logistik/spedition-und-logistik/moenchengladbach/</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Benjamin Peelen</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführer (Peelen Logistik GmbH)</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>benjamin.peelen@peelen.de</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>+49 2843 9597-114 (Peelen Logistik GmbH, Rheinberg)</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Peelen Transporte GmbH / Peelen Logistik GmbH</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Duisburg (Betriebshof) / Rheinberg (Logistikzentrum Niederrhein)</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>Familiengeführte Transport- und Logistikgruppe am Niederrhein mit eigenem Fuhrpark, Warehouse (LZN Rheinberg) und Kontraktlogistik.</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.peelen.de/kontakt | https://www.regiomanager.de/revier/ranking/mobilitaet-logistik/spedition-und-logistik/duisburg/</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Florian Meyer</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführung / Logistik- und Lagerleitung</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>florian.meyer@rdllogistik.de</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>+49 (0)2151 36806-16</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>RDL Logistik Rheinische Distributions- und Lagerlogistik GmbH</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Krefeld (Niederrhein, NRW), zweiter Standort Willich</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>Inhabergeführter Lager- und Distributionslogistiker am Niederrhein (seit 2000) mit Lagerlogistik, Distribution und Fuhrpark an zwei Standorten. Geschäftsführung leitet operativ Lager und Abrechnung selbst — Digitalisierung von Lagerverwaltung, Disposition und Abrechnung ist unmittelbar chef-relevant.</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>https://rdllogistik.de/ueber-uns/ | https://rdllogistik.de/ | https://rdllogistik.de/impressum/</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Udo Feldmann</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Leitung Disposition Landmaschinen &amp; Prokurist</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>feldmann@reiling-logistik.de</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>05247/9837-14</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Reiling Logistik GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Harsewinkel (Kreis Gütersloh)</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>Inhabergeführte Logistikgruppe (Geschäftsführer Christian Reiling und Carsten Mannefeld) mit Schüttgut-, Landmaschinen- und Kommunallogistik. Persönliche E-Mail der Geschäftsführer nicht eindeutig belegt, daher Prokurist als Ansprechpartner.</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reiling-logistik.de | https://www.regiomanager.de/ostwestfalen/ranking/mobilitaet-logistik/spedition-und-logistik/kreis-guetersloh/</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Michael Hoeper</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführer</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>hoeper@hoeper-spedition.de</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>02862-418327-10</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Richard Hoeper GmbH &amp; Co. KG (Hoeper Spedition)</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>Südlohn-Oeding (Westmünsterland, NRW)</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>Familienunternehmen in zweiter Generation mit Transporten, eigenem Fuhrpark, Lagerlogistik und Palettenmanagement im Westmünsterland. Kleinerer, aber voll ausgebauter Betrieb mit Dispo-, QM- und Projektmanagement-Funktionen; Hinweis: liegt vermutlich unterhalb der 50-Mitarbeiter-Schwelle.</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>https://hoeper-spedition.de/team/ | https://hoeper-spedition.de/ | https://hoeper-spedition.de/impressum/</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Tanja Meininghaus</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführerin</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>tanja.meininghaus@sitra-spedition.de</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>+49 40 751006-0 (Zentrale)</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>SITRA Spedition GmbH</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Hamburg</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>Inhabergeführte Hamburger Spedition mit nationalen Stückgut-/Ladungsverkehren, internationalem Geschäft und eigener Disposition; bewusst als persönlich erreichbare Alternative zu Konzernen positioniert.</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>https://sitra-spedition.de/team/ | https://sitra-spedition.de/</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Mike Forker</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführender Gesellschafter</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>forker@sachsenland-gmbh.de</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>+49 351 799010</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Sachsenland Transport &amp; Logistik GmbH</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>Dresden (Sachsen)</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>Selbstbeschreibung: 'Wir sind ein mittelständisches, inhabergeführtes Transport- und Logistikunternehmen'. Sitz Magdeburger Straße 58, 01067 Dresden, weitere Standorte Duisburg, Vilnius, Kiew; Transport, Lager, Zoll, Air &amp; Sea.</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sachsenland-gmbh.de/kontakt-dresden/ | https://www.sachsenland-gmbh.de/</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Sandra Aleksanderek</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführung</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>sandra.aleksanderek@sander-logistics.de</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>+49 40 73354-128</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Sander Logistics GmbH</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>Hamburg (Altenwerder), weitere Standorte Itzehoe und Rostock</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>Mittelständisches, familiengeführtes Logistikunternehmen mit Sammelgut, Komplettladungen, Seefracht sowie Lager-, Beschaffungs- und Kontraktlogistik an fünf Standorten.</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>https://sander-logistics.de/ihre-ansprechpartner/ | https://sander-logistics.de/kontakt/</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Markus Baur</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführer / Leiter Finanz- und Lohnbuchhaltung</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>m.baur@spedition-baur.de</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>+49 7371 9515 20</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Spedition Anton Baur GmbH</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>Ertingen (Baden-Württemberg)</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>Familiengeführte Spedition in 88521 Ertingen mit Niederlassung Stuttgart (A. Baur Mineralöl-Abfertigungsspedition). Schwerpunkte Fernverkehr, Schüttgut-/Kipper-/Schubbodentransporte, Kran- und Baustofflogistik sowie Mineralöltransporte.</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>https://www.spedition-baur.de/team</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Thomas Baur</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführer / Abrechnung Baustoff- und Holztransporte</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>t.baur@spedition-baur.de</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>+49 7371 9515 10</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Spedition Anton Baur GmbH</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Ertingen (Baden-Württemberg)</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>Zweiter Geschäftsführer des inhabergeführten Familienbetriebs (Zentrale Industriestraße 8, 88521 Ertingen). Zusätzlich Prokuristen Adrian und Tobias Baur im Unternehmen.</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.spedition-baur.de/team</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Frank Blodt</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführer</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>frankblodt@spedition-blodt.de</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>+49 6131 25007-0</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Spedition Blodt GmbH</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>Mainz, Rheinland-Pfalz</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>Familiengeführte Spedition in Mainz mit Transport, Lagerlogistik und Projektmanagement; Geschäftsführung und Lagerlogistik liegen in der Familie Blodt.</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>https://spedition-blodt.de/unser-team/</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Miriam Blodt</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführerin</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>miriamblodt@spedition-blodt.de</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>+49 6131 25007-0</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Spedition Blodt GmbH</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Mainz, Rheinland-Pfalz</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>Zweite Geschäftsführerin des inhabergeführten Mainzer Speditions- und Lagerlogistikbetriebs.</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>https://spedition-blodt.de/unser-team/</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Bernd Häger</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführer</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>bhaeger@spedition-haeger.de</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>02904 9740-0</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Spedition Häger GmbH &amp; Co. KG / Häger Transporte u. Logistik GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>Bestwig (Sauerland, NRW)</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>Familiengeführte Sauerland-Spedition mit Transport-, Lager- und Kontraktlogistik über zwei Schwestergesellschaften. Zwei-Firmen-Struktur und gewachsene Dispositions-/Lagerprozesse sprechen für manuelle Abläufe mit Digitalisierungs- und Systemintegrationsbedarf.</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>https://www.spedition-haeger.de/kontakt/</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Gregor Roes</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführer</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>g.roes@spedition-hoevelmann.de</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>+49 2851 962-121</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Spedition Hövelmann GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Rees (Niederrhein)</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>Familiengeführte Niederrhein-Spedition mit Transport-, Lager- und Kontraktlogistik. Weitere Entscheider: Markus Hövelmann (Gesellschafter, m.hoevelmann@spedition-hoevelmann.de), Ricarda Hövelmann (Gesellschafterin, r.hoevelmann@spedition-hoevelmann.de), Jörg Möllenbeck (Prokurist, j.moellenbeck@spedition-hoevelmann.de).</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.spedition-hoevelmann.de/kontakt</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Verena Wiechers</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsleitung</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>v.wiechers@wiechers-spedition.de</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>+49 234 94338-27</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Spedition Josef Wiechers GmbH (WIECHERS Spedition + Logistik)</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>Bochum (Hauptsitz), Standort Duisburg</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>Familiengeführte Spedition aus Bochum mit Standort Duisburg, Schwerpunkt Transport-, Lager- und Distributionslogistik im Ruhrgebiet. Zusätzlicher Ansprechpartner: Markus Koch (Speditionsleitung, Prokurist), m.koch@wiechers-spedition.de.</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wiechers-spedition.de/kontakt | https://www.regiomanager.de/ranking/mobilitaet-logistik/spedition-und-logistik/bochum/</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Christine Kollmannsberger</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsleitung / Geschäftsführerin</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>C.Kollmannsberger@spedition-kollmannsberger.de</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>+49 8456 966-212</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Spedition Kollmannsberger KG</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>Großmehring bei Ingolstadt (Bayern)</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>Zweite Person der Geschäftsleitung des Familienunternehmens; Dispositionsleitung Helmut Atzmüller ebenfalls mit persönlicher Adresse gelistet.</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.spedition-kollmannsberger.de/spedition-ansprechpartner</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Ludwig Kollmannsberger</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsleitung / Geschäftsführer</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>L.Kollmannsberger@spedition-kollmannsberger.de</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>+49 8456 966-211</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Spedition Kollmannsberger KG</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>Großmehring bei Ingolstadt (Bayern)</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>Familiengeführte Spedition im InTerPark Ingolstadt (Dieselstraße 6, 85098 Großmehring) mit Transport-, Lager- und Distributionslogistik für den Raum Ingolstadt/Oberbayern.</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>https://www.spedition-kollmannsberger.de/spedition-ansprechpartner | https://www.spedition-kollmannsberger.de/</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Jürgen Frömberg</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführer</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>jFroemberg@spedition-maier.de</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>+49 7731 828-201</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Spedition Maier GmbH</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>Singen (Hohentwiel), Baden-Württemberg</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>Mittelständische Spedition mit Standorten Singen, Pfullendorf und Ramsen (CH). Sammelgut, Charterverkehr, Zollabwicklung sowie eigene Lagerlogistik mit mehreren Betriebs- und Standortleitern.</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.spedition-maier.de/team/</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Thomas Marizzi</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsleitung – Speditionsleitung</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>tMarizzi@spedition-maier.de</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>+49 7731 828-188</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Spedition Maier GmbH</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>Singen (Hohentwiel), Baden-Württemberg</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>Mitglied der Geschäftsleitung mit Verantwortung für den Speditionsbereich; kaufmännische Leitung Jochen Sigg (jsigg@spedition-maier.de) ebenfalls auf derselben Seite belegt.</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.spedition-maier.de/team/</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Nicole Körtge</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Leitung Auftragsmanagement/Logistik</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>nicolekoertge@spedition-wagner.net</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>+49 2642 9022922</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Spedition Wagner GmbH</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>Remagen (Am Römerhof 60, 53424), Rheinland-Pfalz</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>Familiengeführter Logistikdienstleister mit Kontraktlogistik für die Getränkeindustrie (u. a. Krombacher), Lagerlogistik, Displaybau und eigenem Fuhrpark. Geschäftsführung (Arlt/Gaßner/Kröhl) ohne öffentliche E-Mail – Bereichsleitung Logistik als Entscheidungsträger.</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>https://spedition-wagner.net/unternehmen/team/</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Matthias Schork</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführer</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>m.schork@wuest.com</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>+49 9141 8684-140</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Spedition Wüst (Wüst GmbH &amp; Co. KG)</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>Weißenburg i. Bay., weiteres Logistikzentrum Ansbach, Bayern</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>Mittelständische bayerische Spedition mit Stückgut- und Ladungsverkehren sowie zwei eigenen Logistikzentren (Lagerung, Kommissionierung, Value Added Services).</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wuest.com/kontakt/ | https://www.wuest.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Michael Müller</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Logistikleiter</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>m.mueller@wuest.com</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>+49 9141 8684-106</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Spedition Wüst (Wüst GmbH &amp; Co. KG)</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>Weißenburg i. Bay., Bayern</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>Verantwortlicher für die Logistikzentren Weißenburg und Ansbach – direkter Entscheider für Lager-/Kontraktlogistikprozesse.</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wuest.com/kontakt/</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Bernd Stratkötter</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführer, Auftragsmanagement &amp; Disposition</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>bs@stratkoetter.de</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>02523 / 9200-12</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>Stratkötter Logistik + Transport GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>Wadersloh (Kreis Warendorf)</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>Familienbetrieb mit drei Geschäftsführern aus der Familie Stratkötter (Werner, Bernd, Thomas), Schwerpunkt Auftragsmanagement, Disposition und Lagerlogistik im Münsterland.</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>https://www.stratkoetter.de/ansprechpartner | https://www.regiomanager.de/muensterland/ranking/mobilitaet-logistik/spedition-und-logistik/kreis-warendorf/</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Ralf Greinert</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführer</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>ralf.greinert@teamlogistic.de</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>+49 2602 1309-0 (Zentrale)</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>TEAM Logistic GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>Montabaur (Westerwaldstr. 2a, 56410), Rheinland-Pfalz</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>Familiengeführte Spedition im Westerwald (Familie Greinert) mit eigener Disposition, Werkstatt und Verwaltung; Transporte national/international.</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>https://teamlogistic.de/ansprechpartner/ | https://teamlogistic.de/impressum/</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Uwe Diel</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführer</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>uwe.diel@teamlogistic.de</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>+49 2602 1309-0 (Zentrale)</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>TEAM Logistic GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>Montabaur, Rheinland-Pfalz</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>Zweiter Geschäftsführer der Team Logistic GmbH &amp; Co. KG, mittelständische Spedition mit eigenem Fuhrpark.</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>https://teamlogistic.de/ansprechpartner/</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Manuel Keller</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Bereichsleiter / Mitglied der Geschäftsleitung</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Manuel.Keller@teamlog.de</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>+49 6021 1507-121</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>TEAMLOG (Team Log GmbH &amp; Co. KG)</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>Aschaffenburg (Bayern)</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>Inhabergeführter Kontrakt- und Lagerlogistiker mit Zentrale Germanenstraße 30, 63741 Aschaffenburg und 15 Standorten im Rhein-Main-Gebiet.</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>https://teamlog.de/kontakt/ | https://teamlog.de/</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Theodor Schulz</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführer (Disposition &amp; Kundenbetreuung)</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>ts@schulz-spedition.de</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>+49 251 26333-211</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Theodor Schulz GmbH &amp; Co. KG (Schulz Spedition)</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>Münster (NRW)</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>Inhabergeführte Münsteraner Spedition mit Transport, Lagerung/Lagerverwaltung, Palettenmanagement und Abrechnung als eigene Abteilungen. Geschäftsführung sitzt selbst in der Disposition — kurze Entscheidungswege, viele manuell getriebene Dispo- und Abrechnungsprozesse als Digitalisierungsansatz.</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.schulz-spedition.de/ | https://www.schulz-spedition.de/#unternehmen</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Christian Vetten</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführer (Ansprechpartner Transporte/Lagerlogistik)</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>christian.vetten@vetten-gruppe.de</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>02162 5302-379</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Vetten Gruppe (Gebr. Vetten GmbH &amp; Co. KG)</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Mönchengladbach (Niederrhein, NRW)</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>Familienbetrieb seit 1931 mit Transport, Lagerlogistik, Textil- und Kontraktlogistik auf &gt;100.000 qm Lagerfläche. Gewachsene Gruppenstruktur mit mehreren Standorten, Variantenvielfalt (Textilaufbereitung, Kontraktlogistik) und vorhandener Logistik-IT (ecovium/SPEDION im Einsatz) — viel Potenzial für Prozessdigitalisierung und Schnittstellen-/ERP-Themen.</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>https://vetten-gruppe.de/kontakt/ | https://vetten-gruppe.de/ | https://vetten-gruppe.de/impressum/ | https://vetten-gruppe.de/die-vetten-gruppe/</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Dirk Schröder</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführer</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>dirk.schroeder@westfalia-intralog.com</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>+49 (0) 5221 - 1809 - 690</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>WESTFALIA intralog GmbH</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>Herford (OWL)</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>Kontraktlogistiker mit Standorten in Herford und Bremerhaven, Schwerpunkt Lager- und Value-Added-Services für Industriekunden.</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.westfalia-intralog.de/kontakt | https://www.regiomanager.de/ostwestfalen-lippe/ranking/mobilitaet-logistik/spedition-und-logistik/kreis-herford/</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Andreas Koch</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführer</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>a.koch@eckhardt-logistik.de</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>+49 711 80000-0 (Zentrale)</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Walter Eckhardt GmbH Spedition + Logistik</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>Korntal-Münchingen (Raum Stuttgart), Baden-Württemberg</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>Inhabergeführte Spedition seit 1987 mit Stückgut, Gefahrgut- und Pflanzentransporten sowie eigenem Lager-/Kommissionierzentrum (seit 2019). Eigene Bereiche für Umschlag, Lagerlogistik und Disposition.</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>https://eckhardt-logistik.de/kontakt/ansprechpartner | https://eckhardt-logistik.de/</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
           <t>Marc Eckhardt</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>Gesellschafter (Inhaberfamilie)</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
         <is>
           <t>m.eckhardt@eckhardt-logistik.de</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>+49 711 80000-0 (Zentrale)</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>Walter Eckhardt GmbH Spedition + Logistik</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Logistik &amp; Supply Chain</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
         <is>
           <t>Korntal-Münchingen (Raum Stuttgart), Baden-Württemberg</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>Gesellschafter und Namensträger des familiengeführten Speditions- und Logistikunternehmens; zweiter Entscheidungsträger neben der Geschäftsführung.</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="I75" s="2" t="inlineStr">
         <is>
           <t>https://eckhardt-logistik.de/kontakt/ansprechpartner | https://eckhardt-logistik.de/</t>
         </is>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Dirk Valerius</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführender Gesellschafter</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>d.valerius@werneke.de</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>02922 / 8060 - 260</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Werneke Logistic GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>Werl (Kreis Soest / Südwestfalen)</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>Inhabergeführter Logistikdienstleister mit Stückgut, Sammelgut, Charterverkehr und vier Lagerstandorten (Kontraktlogistik). Familie Werneke weiterhin im Unternehmen aktiv.</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.werneke.de/ansprechpartner | https://www.regiomanager.de/suedwestfalen/ranking/mobilitaet-logistik/spedition-und-logistik/kreis-soest/</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Jörg Küpper</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführer</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>j.kuepper@d-log.de</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>+49 201 2897960</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>d-log GmbH</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>Essen</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>Inhabergeführter Logistikdienstleister aus Essen (Schacht Neu-Cöln) mit Transport-, Lager- und Distributionslogistik im Ruhrgebiet.</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>https://www.d-log.de/impressum | https://www.regiomanager.de/ranking/mobilitaet-logistik/spedition-und-logistik/essen/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I26"/>
+  <autoFilter ref="A1:I77"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1726,10 +4123,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4">
@@ -1739,10 +4136,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25</v>
+        <v>64</v>
       </c>
       <c r="C4" t="n">
-        <v>33</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5">
@@ -1765,10 +4162,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25</v>
+        <v>76</v>
       </c>
       <c r="C6" t="n">
-        <v>33</v>
+        <v>191</v>
       </c>
     </row>
   </sheetData>
@@ -1782,7 +4179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -2539,6 +4936,3482 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>TEAM Logistic GmbH</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Raum Montabaur (Vorwahl 02602)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Persönliche E-Mails vorhanden, aber Standort außerhalb Ruhrgebiet/Rheinland/Niederrhein</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Spedition Schiffers GmbH</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Mönchengladbach</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Website nicht erreichbar (DNS-Fehler, auch per curl); E-Mails nicht auf einer gecrawlten Seite verifizierbar</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>meta4log GmbH</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Essen</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Nur info@meta4log.de auf der Website; keine persönliche E-Mail des Geschäftsführers (Bernd Jungclaus)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Rheinkraft International GmbH (RKI)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Duisburg</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Nur info@rki-logistics.com, keine Personen auf Kontaktseite</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Windgätter u. Sohn GmbH</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Dortmund</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Ansprechpartner mit Durchwahl, aber nur Sammeladresse dispo@windgaetter-transporte.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hoff Transport und Logistik GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Krefeld</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Nur info@/order@/karriere@; keine Personen genannt</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>AXTRA GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Essen</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Nur info@axtra.de, keine Ansprechpartnerseite</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Meinolf Jacobi Spedition GmbH</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Bochum</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Keine E-Mail-Adresse auf der Website auffindbar</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Johs. Stelten GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Krefeld</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Nur info@steltenkg.de; keine persönliche E-Mail der Geschäftsführung</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Spedition Minor GmbH</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Gelsenkirchen</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Nur info@spedition-minor.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Hubert Kläsener GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Gelsenkirchen</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail auf Website/Kontaktseite</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Scheren Logistik GmbH</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Düsseldorf</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Team-Seite nennt Personen nur mit Vornamen/Initial, nur info@scheren.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>MSG Speditionsgesellschaft mbH</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Mönchengladbach</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Nur Funktionsadressen (Management@, National@, Sea@ etc.), keine Personenzuordnung</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Graf-Transporte Internationale Spedition GmbH</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Bochum</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Keine E-Mail-Adressen auf der Website auffindbar</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Curt Richter SE</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Köln</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Keine persönlichen E-Mails auf gecrawlten Seiten</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Deußen Logistik GmbH</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Köln</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Keine erreichbare Firmenwebsite mit persönlichen E-Mails gefunden</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>HEUEL LOGISTICS</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Dortmund/Arnsberg</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Nur Funktionsadressen (angebot@, info@)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>LOXX Logistics</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Duisburg</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Persönliche E-Mails vorhanden, aber inzwischen Teil der Rhenus-Gruppe (Konzern) – ausgeschlossen</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Hendricks Unternehmensgruppe</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Neuss</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Nur Funktionsadressen (automotive@hendricks.group)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>TechnoCargo Logistik GmbH u. Co. KG</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Neuss</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Nur bewerbung@technocargo.de; Konzernstruktur (Bertschi-nahe Geschäftsführung)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>NEUFRA Speditions-Gesellschaft mbH</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Neuss</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Keine persönlichen E-Mails auffindbar</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Bodenheim Spedition GmbH</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Krefeld</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Kontaktseite enthält nur Platzhalter (email@example.org)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Spedition Kronenberg GmbH</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Bochum</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Nur Sammeladresse DispoKronenberg@aol.com; zudem unter 50 MA</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>GATE 41 Logistics GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Mönchengladbach</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Website enthält nur Platzhalter-Adresse, keine echten E-Mails</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Die Richrath's GmbH</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Düsseldorf</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Nur support@die-richraths.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Sägewerk Transporte GmbH</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Düsseldorf</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Keine persönlichen E-Mails auf der Website</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Wilhelm Rotthege</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Essen/Düsseldorf</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Nur Standort-Sammeladressen (essen@, duesseldorf@)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Spedition Buerhaus / GDS Logistik / OFL Olympia Food Logistics / BM Spedition / A. Siepmann / Joachim Schultz / LOGIFLEX / P+M Logistik / Rosenbaum / Guckuk / ABC-Logistik / VCK Logistics</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>diverse (Dortmund, Bochum, Duisburg, MG, Köln, Düsseldorf)</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Sammelposten: keine erreichbare Website mit persönlichen E-Mails der Entscheidungsträger gefunden</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Emons, DSV, DB Schenker, Rhenus, Kühne+Nagel, Dachser, DHL, BLG, Yusen, Kintetsu</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>diverse</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Konzerne bzw. laut Vorgabe ausgeschlossen</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Rüdinger Spedition GmbH</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Krautheim (BW)</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Ansprechpartnerseite listet Namen/Positionen/Durchwahlen, aber keine E-Mail-Adressen im Klartext (JS-verschleierte 'E-Mail schreiben'-Links); curl-Nachfassen ohne Treffer</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>barth Logistikgruppe</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Hechingen (BW)</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Ansprechpartnerseite enthält nur Telefon-/Faxnummern je Standort, keine Personen und keine E-Mail-Adressen; curl-Nachfassen ohne Treffer</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Wiedmann &amp; Winz GmbH</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Geislingen an der Steige (BW)</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Nur Funktionsadressen (mail@, offer@, anfrage@, bewerbung@), keine personenbezogenen E-Mails auf Kontaktseite</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>CL Spedition Berlin Transport- und Logistik GmbH</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Ansprechpartnerseite nennt Namen und Funktionen, aber nur Sammeladressen info@/dispo@/ber@</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Spedition Kollmannsberger – Startseite</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Großmehring (BY)</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Homepage nur mail@ – Lead stattdessen über die separate Ansprechpartnerseite qualifiziert (siehe Leads)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Schwarzer Group / Schwarzer Spedition</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Heiligenstedten (SH)</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Persönliche E-Mails vorhanden, aber Hauptsitz und Standorte außerhalb des Zielgebiets Süd-/Ostdeutschland</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Sachsen-Anhalt Logistik</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Sachsen-Anhalt (virtuell)</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Kein reales Unternehmen – virtuelle TruckersMP-Speditionsgemeinschaft (Gaming-Community); nur info@</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>ELOS Speditions GmbH</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Zwickau (SN)</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Nur zentrale Adresse info@elos-spedition.de auffindbar, keine persönlichen Ansprechpartner-Mails</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Roman Mayer Logistik GmbH</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Nürnberg / Gersthofen (BY)</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Kontaktseite nur mit info@romanmayer-logistik.de, keine personenbezogenen E-Mails</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Köhl Logistik</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Pfalz</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>HTTP 503 beim Abruf; zudem Sitz in Rheinland-Pfalz außerhalb des Zielgebiets</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Spedition Ebenroth GmbH</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Döbeln (SN)</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Keine Team-/Ansprechpartnerseite mit persönlichen E-Mails auffindbar</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Baltic Lloyd – Startseite/Kontaktseite</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Rostock (MV)</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Startseite nur dispo@, /kontakt/ liefert HTTP 404 – Lead stattdessen über /dasteam/ qualifiziert (siehe Leads)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Krage &amp; Gerloff – Ansprechpartnerseite</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Schwanebeck (ST)</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>URL /ansprechpartner liefert HTTP 404; Geschäftsführung nicht mit persönlicher E-Mail belegbar – nur Standortleitung Magdeburg qualifiziert</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Seifert Logistics Group / Noerpel-Gruppe / Karl Schmidt Spedition</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Ulm bzw. Heilbronn (BW)</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Konzerngröße (2.500–4.000+ Mitarbeitende, 45+ Standorte) – außerhalb des Mittelstandsprofils</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>LOXXESS AG</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Tegernsee (BY)</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Nicht weiterverfolgt – Konzernstruktur/AG, kein Ansprechpartnerverzeichnis mit persönlichen E-Mails</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>TML Spedition GmbH</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Leipzig (SN)</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Keine Ansprechpartnerseite mit namentlichen E-Mail-Adressen auffindbar</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Spedition Schiffers</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Nettetal (NRW)</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Region außerhalb des Zielgebiets Süd-/Ostdeutschland</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>RTC Spedition &amp; Logistik GmbH</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Nur Zentralkontakt/Geschäftsführername belegt, keine persönliche E-Mail auf gecrawlten Seiten</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Sachsenland – Startseite</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Dresden (SN)</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Homepage ohne E-Mail-Adressen – Leads stattdessen über /kontakt-dresden/ qualifiziert (siehe Leads)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Watzlawek Logistik</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Hamm/Ahlen</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Geschäftsleitung Lukas Watzlawek nur über info@watzlawek-trans.com erreichbar, keine persönliche E-Mail</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>H. Gautzsch Spedition GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Münster</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Ansprechpartnerliste nennt für alle Personen nur info@gautzsch-spedition.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>KÜHN Transport- und Lagerungsgesellschaft mbH</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Ostbevern</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>nur info@kuehn-transporte.com auffindbar</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Feldmann Spedition GmbH</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Gütersloh</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>nur dispo@feldmann-spedition.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>WLS Spedition GmbH</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Steinhagen</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>nur kontakt@wls-spedition.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Hartmann International GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Paderborn</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Team-/Kontaktseiten nennen nur info@ bzw. standortbezogene Sammeladressen</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Loeber-Lehnhof GmbH</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Siegen</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Geschäftsführer Roman Mayer ohne persönliche E-Mail; gefundene Adresse gehört zum Webseitenbetreuer</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Schröder Logistik GmbH</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Kirchlengern</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Teamseite zeigt Geschäftsführer ohne E-Mail, nur faktura@schroeder-logistik.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Loewe Logistics &amp; Care GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Herford</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>keine E-Mail-Adressen auf gecrawlten Seiten auffindbar</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Spedition Gerhard Siebel GmbH</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Kreuztal</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>nur info@siebel-spedition.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Gössling Spedition GmbH</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Arnsberg</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>nur gs@goessling-spedition.de (Funktionsadresse ohne Personenzuordnung)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Kerber Transporte GmbH</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Brilon</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>nur info@kerber-transporte.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Spedition Mikus GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Meschede</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>nur info@spedition-mikus.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Glexx GmbH</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Meschede</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>nur post@glexx-logistik.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Kleinwächter GmbH &amp; Co. Spedition</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Hallenberg</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>keine erreichbare Website/keine E-Mails über getestete Domains</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Alfons Brass Spedition und Lagerei</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Medebach</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>keine E-Mails über getestete Domains auffindbar</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Mönig Spedition Meschede GmbH</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Meschede</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>keine E-Mails über getestete Domains auffindbar</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Schulte-Lindhorst GmbH &amp; Co.</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Rietberg</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>nur info@schulte-lindhorst.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Thermotraffic GmbH</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Versmold</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>nur info@/sales@thermotraffic.de; zudem Konzernstruktur</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Tevex Logistics GmbH</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Rheda-Wiedenbrück</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>nur info@tevex.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Greiwing logistics for you GmbH</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Greven</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>nur info@greiwing.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Sievert Logistik SE</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Lengerich</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>nur info.logistik@sievert.de; Teil der Sievert-Gruppe</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>MP Logistik GmbH</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Rheine</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>nur info@/warehouse@mplogistik.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Wetralog GmbH</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Münster</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>nur schadenservice@wetralog.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Hövener Spedition GmbH</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Rheine</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>nur info@hoevener-spedition.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Spedition Karl Kerkeling GmbH</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Coesfeld</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>nur info@spedition-kerkeling.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>MAX-Logistik GmbH</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Senden</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>nur info@max-logistik.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Lipperland Logistik GmbH / Möbelspedition Lipperland</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Oelde</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>gefundene Adressen ohne Positionszuordnung (Datenschutz-/Impressumskontext), kein belegter Entscheidungsträger</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Rosner Logistik GmbH</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Oelde</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>keine E-Mails auf gecrawlten Seiten</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Dingwerth Logistik GmbH</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Beelen</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>keine E-Mails auf gecrawlten Seiten</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>TEDO Logistik GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Ibbenbüren</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>nur info@tedo-logistik.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Richter Express OHG</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Saerbeck</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>nur info@richter-express.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Schöpper Transport GmbH</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Greven</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>nur info@ bzw. eine Adresse ohne belegte Positionszuordnung</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Spedition Kockel GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Soest</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>nur info@spedition-kockel.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Mimberg Spedition - Baustoffe GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Werl</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>nur Funktions-/Beispieladressen, keine Entscheidungsträger-E-Mail</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Artur Kossack Spedition</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Hiddenhausen</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>nur info@kossack.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Westfalen-Lippe Speditions- und Lagerhausgesellschaft mbH</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Herford</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>nur info@wl-spedition.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Martin Oelrich GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Ladbergen</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>gehört zur pfenning logistics group (Konzern), keine persönliche E-Mail</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>FIEGE / Nagel-Group / Duvenbeck</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Greven / Versmold / Bocholt</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Konzerne mit &gt;5.000 Mitarbeitern, außerhalb Zielprofil</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Heinrich Kottmann Spedition GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Büren</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Website ohne verwertbare E-Mail-Adressen</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Würfel-Massong Logistik GmbH</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Paderborn</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>keine E-Mails auf gecrawlten Seiten</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Wilhelm Altendorf GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Minden</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Zahlreiche personenbezogene E-Mails auf der Website, aber keine davon einem Geschäftsführer/Prokuristen oder zulässigen Bereichsleiter zugeordnet</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Kolbus GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Rahden</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Keine persönliche Entscheider-E-Mail auf Website/Impressum/Kontakt gefunden</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>AUMUND Fördertechnik GmbH</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Rheinberg</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Nur Kontaktformulare, keine persönliche E-Mail</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>THIELE GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Iserlohn</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Nur Sammeladressen (hebetechnik@) – keine persönliche Entscheider-E-Mail</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>HASCO Hasenclever GmbH + Co KG</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Lüdenscheid</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Gebr. Eickhoff Maschinenfabrik</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Bochum</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Herbert Kannegiesser GmbH</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Vlotho</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>HAVER &amp; BOECKER OHG</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Oelde</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Personenbezogene Mails nur im Vertriebs-/Auslandsnetz, kein Entscheider mit Rolle belegt</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Reifenhäuser GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Troisdorf</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Nur Fachbereichs-/Recruiting-Mails, keine Geschäftsführung</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>battenfeld-cincinnati Germany GmbH</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Bad Oeynhausen</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Nur Vertriebs-/Länderkontakte, keine Entscheider-E-Mail</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Hanning Elektro-Werke GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Oerlinghausen</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Nur Vertriebspartner-Mails; Impressum-Mail gehört zum externen Datenschutzbeauftragten</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Dürkopp Adler GmbH</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Bielefeld</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Nur Vertriebspartner-Adressen; zudem Konzernstruktur</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Klingelnberg GmbH</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Hückeswagen</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Nur Funktionspostfächer (kegelrad@, seminar@ etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Kampf Schneid- und Wickeltechnik GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Wiehl</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Nur weltweite Vertriebs-/Agenturkontakte, keine Geschäftsführung</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Achenbach Buschhütten GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Kreuztal</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Nur Funktionspostfach fertigung@</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Gebr. Becker GmbH</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Wuppertal</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Personenbezogene Mails nur im Vertriebsinnendienst/Service ohne Entscheiderrolle</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>KettenWulf Betriebs GmbH</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Eslohe</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>ELHA-MASCHINENBAU Liemke KG</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Halle (Westf.)</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Nur ausländische Vertriebspartner-Mails</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>G. Siempelkamp GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Krefeld</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Keine persönliche Entscheider-E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Hennecke GmbH</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Sankt Augustin</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Kautex Maschinenbau GmbH</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Bonn</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Lödige Industries GmbH</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Warburg/Paderborn</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Schmidt + Clemens GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Lindlar</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>MSK Verpackungs-Systeme GmbH</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Kleve</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Nur Kontaktformulare, keine persönliche E-Mail</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>SPALECK GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Bocholt</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Keine persönliche Entscheider-E-Mail auffindbar</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Rhein-Nadel Automation GmbH</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Aachen</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>STRACK NORMA GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Lüdenscheid</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>TRACTO-TECHNIK GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Lennestadt</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Albrecht Bäumer GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Freudenberg</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Düchting Pumpen Maschinenfabrik GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Wetter (Ruhr)</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>A. Monforts Textilmaschinen GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Mönchengladbach</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Einziger belegter Entscheider (Betriebsleiter) sitzt in der österreichischen Niederlassung – außerhalb NRW</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Murtfeldt Kunststoffe GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Dortmund</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>DENIOS SE</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Bad Oeynhausen</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Keine persönliche Entscheider-E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Venjakob Maschinenbau GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Rheda-Wiedenbrück</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Remmert GmbH</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Löhne</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Rippert GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Herzebrock-Clarholz</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Ohrmann GmbH Montagetechnik</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Rheda-Wiedenbrück</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Sollich KG</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Bad Salzuflen</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>steute Technologies GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Löhne</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Torwegge GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Bielefeld</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Wemhöner Surface Technologies GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Herford</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Nur internationale Handelsvertreter-Mails, keine Geschäftsführung</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>RK Rose+Krieger GmbH</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Minden</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Nur Funktions-/Auslandspostfächer; zudem Konzernzugehörigkeit (Phoenix Mecano)</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Carl Werthenbach Konstruktionsteile GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Bielefeld</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Geschäftsführer im Impressum genannt, aber nur info@/industrietechnik@ – keine persönliche E-Mail</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Seppeler Holding und Verwaltungs GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Rietberg</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Geschäftsführer im Impressum genannt, aber nur info-holding@ – keine persönliche E-Mail</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>MIT Moderne Industrietechnik GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Vlotho</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Geschäftsführung genannt, E-Mail nur als Sammeladresse mit@systemarmaturen.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Schubert &amp; Salzer / ventiltechnik.de (Vlotho)</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Vlotho</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Persönliche Mails nur für Vertriebsleitung/Sales Director – keine Geschäftsführung, Vertrieb zählt laut Vorgabe nicht</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Heilig Maschinenbau GmbH</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Bad Salzuflen</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Impressum nennt GF Sascha Heilig, die angegebene Adresse heilig@heilig-maschinenbau.de ist jedoch nicht eindeutig persönlich (Firmenname = Nachname) – bei Unsicherheit verworfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>ATL Luhden GmbH</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Luhden</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Betriebsleiter/Prokurist mit persönlicher Mail belegt, Standort liegt jedoch in Niedersachsen (nicht NRW)</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>DUBOR Groneweg GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Bad Salzuflen</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Ansprechpartnerseite mit Entscheidern vorhanden, aber Branche Backmittel/Lebensmittel – kein Maschinenbau; GF-Adressen zudem nur info@</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>AMR-Engineering GmbH</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Essen</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Geschäftsführer im Impressum genannt, aber nur Sammeladresse amr@amr.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>SIEBTECHNIK TEMA GmbH</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Mülheim an der Ruhr</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>HAZEMAG &amp; EPR GmbH</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Dülmen</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>BOGE KOMPRESSOREN Otto Boge GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Bielefeld</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Nur Länder-Sammelpostfächer</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>PROBAT SE</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Emmerich am Rhein</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Otto Junker GmbH</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Simmerath</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>REMBE GmbH Safety+Control</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Brilon</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>OVENTROP GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Olsberg</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>BJB GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Arnsberg</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Ruhrpumpen GmbH</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Witten</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Winkelmann Group GmbH + Co. KG</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Ahlen</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>GERSTUNG Sondermaschinen GmbH</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Mönchengladbach</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>AUMAT Maschinenbau GmbH</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>NRW</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Maschinen- und Industriebau Feld GmbH</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>NRW</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Ansprechpartnerseite vorhanden, aber ohne persönliche E-Mail-Adressen</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>VGS Automatisierungstechnik GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Schloß Holte-Stukenbrock</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Ebert Maschinenbau GmbH</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Minden</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>BELU GmbH</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Bielefeld</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Pfister Fertigungstechnik / GMM mbH / MB Klich</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>NRW</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>CNC-Lohnfertiger ohne persönliche Entscheider-E-Mail auf der Website</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Selzer Formenbau GmbH / Dietrich Formenbau / KM Formenbau / Jedig &amp; Heyns / Wilfrid Humme</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Lüdenscheid</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Werkzeug-/Formenbauer ohne persönliche Entscheider-E-Mail auf der Website</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Hagener Fördertechnik – Stefan Maschmeier (Prokurist)</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Hagen</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Als zweiter Entscheider geprüft, aber nur info@hafoe.de hinterlegt – daher nicht verwendet</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads-adept/leads-adept.xlsx
+++ b/leads-adept/leads-adept.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Verworfen" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$I$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$I$91</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I77"/>
+  <dimension ref="A1:I91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -497,27 +497,27 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Christian Jordan</t>
+          <t>Florian Meierhöfer</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsleitung</t>
+          <t>Geschäftsführer</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>c.jordan@dreckshage.de</t>
+          <t>florian.meierhoefer@am-maschinenbau.de</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>0521 9259-101</t>
+          <t>+49 9682 89491-28</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>August Dreckshage GmbH &amp; Co. KG</t>
+          <t>AM Maschinenbau GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -527,44 +527,44 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Bielefeld (Ostwestfalen-Lippe)</t>
+          <t>Erbendorf (Bayern, Oberpfalz)</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Bielefelder Familienunternehmen für Antriebs- und Lineartechnik, technische Walzen, Profile und Systeme sowie Werkstoffe – Zulieferer und Fertigungspartner des Maschinenbaus.</t>
+          <t>Familiengeführter Maschinenbau- und Fertigungsbetrieb (Inhaber &amp; Geschäftsführer Alfons Meierhöfer, Geschäftsführer Florian Meierhöfer) mit Konstruktion, Zerspanung und Baugruppenfertigung.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>https://dreckshage.de/de/kontakt/ansprechpartner | https://dreckshage.de/en/contact/contact-partner (Zitat: 'Geschäftsleitung | Christian Jordan | Telefon 0521 9259-101 | E-Mail | c.jordan@dreckshage.de')</t>
+          <t>https://www.am-maschinenbau.de/infos-kontakt/ansprechpartner/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Markus Bürger</t>
+          <t>Christian Jordan</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführung</t>
+          <t>Geschäftsleitung</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>m.buerger@blechwerk.de</t>
+          <t>c.jordan@dreckshage.de</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>+49 (0) 5222 / 91793-0</t>
+          <t>0521 9259-101</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Blechwerk Bürger GmbH</t>
+          <t>August Dreckshage GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -574,24 +574,24 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Bad Salzuflen (Ostwestfalen-Lippe)</t>
+          <t>Bielefeld (Ostwestfalen-Lippe)</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Inhabergeführter Betrieb der metallverarbeitenden Fertigung (Blechbearbeitung, Laserschneiden, Kanten, Schweißbaugruppen) für Maschinenbau-Kunden in OWL.</t>
+          <t>Bielefelder Familienunternehmen für Antriebs- und Lineartechnik, technische Walzen, Profile und Systeme sowie Werkstoffe – Zulieferer und Fertigungspartner des Maschinenbaus.</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>https://blechwerk.de/unternehmen/ansprechpartner/ | https://blechwerk.de/ (Zitat u. a.: '40 Mitarbeitern mit mehr als 20 Jahren Erfahrung in der Metall- und Blechv...', Standort 32107 Bad Salzuflen)</t>
+          <t>https://dreckshage.de/de/kontakt/ansprechpartner | https://dreckshage.de/en/contact/contact-partner (Zitat: 'Geschäftsleitung | Christian Jordan | Telefon 0521 9259-101 | E-Mail | c.jordan@dreckshage.de')</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Holger Krebs</t>
+          <t>Michael Binder</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -601,17 +601,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>krebs@ctechnik.de</t>
+          <t>mbinder@binder-foerdertechnik.de</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>+49 2154 89102-0</t>
+          <t>+49 7191 327017</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>C-Technik Maschinen- und Anlagenbau GmbH</t>
+          <t>BINDER GmbH Fördertechnik</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,44 +621,44 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Willich (Niederrhein); zweiter Standort Hagen</t>
+          <t>Burgstetten (Baden-Württemberg)</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Inhabergeführter Sondermaschinen- und Anlagenbauer mit Konstruktion, Kalkulation und Projektmanagement; Sitz 47877 Willich, weiterer Standort im Raum Hagen.</t>
+          <t>Familiengeführter Hersteller von Fördertechnik und Intralogistik-Anlagen (Sondermaschinen- und Anlagenbau). Zweiter Geschäftsführer: Stephan Binder (sbinder@binder-foerdertechnik.de, gleiche Quelle).</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>https://ctechnik.de/kontakt/ | https://ctechnik.de/ (Adresse 47877 Willich) | Zweiter Geschäftsführer auf derselben Seite: 'Mirko Krebs | Geschäftsführer | T. +49 2154 89102 – 211 | mkrebs@ctechnik.de'</t>
+          <t>https://www.binder-foerdertechnik.de/unternehmen/ansprechpartner/ | https://www.intralogistik-bw.de/mitglieder/intralogistik-anbieter/binder/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Dirk Haßmann</t>
+          <t>Bernd Fischer</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Leiter Einkauf (Bereichsleiter Einkauf/Supply Chain)</t>
+          <t>Geschäftsführer Vertrieb</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Dirk.Hassmann@flaco.de</t>
+          <t>b.fischer@btd-gmbh.de</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>+49 (0) 5241 603-62</t>
+          <t>+49 7157 562-100</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>FLACO-Geräte GmbH</t>
+          <t>BTD Behälter- und Speichertechnik Dettenhausen GmbH</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -668,44 +668,44 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Gütersloh (Ostwestfalen-Lippe)</t>
+          <t>Dettenhausen (Baden-Württemberg)</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Hersteller von Fluid-, Tank- und Werkstatttechnik sowie Fluidsystemen für Fertigungsbetriebe. Geschäftsführer Thomas Voigt ist auf der Kontaktseite genannt, jedoch ohne persönliche E-Mail – daher der Einkaufsleiter als Entscheider hinterlegt.</t>
+          <t>Mittelständischer Fertigungsbetrieb für Behälter- und Speichertechnik (Druckbehälter, Pufferspeicher) mit eigener Konstruktion und Serienfertigung. Technischer Leiter: Benjamin Dörlemann (b.doerlemann@btd-gmbh.de, gleiche Quelle).</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>https://flaco.de/de/kontakt-beratung.html | https://flaco.de/de/kontakt-beratung.html (Zitat zur Geschäftsführung ohne E-Mail: 'Thomas Voigt | Geschäftsführer | Tel. +49 (0) 5241 - 603 - 0')</t>
+          <t>https://www.btd-gmbh.de/ansprechpartner</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Frederic Lanz</t>
+          <t>Markus Bürger</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>CEO / Vice Chairman of the Board</t>
+          <t>Geschäftsführung</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>lanz@kemper.eu</t>
+          <t>m.buerger@blechwerk.de</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>+49 (0) 2564 68-119</t>
+          <t>+49 (0) 5222 / 91793-0</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>KEMPER GmbH</t>
+          <t>Blechwerk Bürger GmbH</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -715,44 +715,44 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Vreden (Münsterland, NRW)</t>
+          <t>Bad Salzuflen (Ostwestfalen-Lippe)</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Familiengeführter Hersteller von Absaug- und Filteranlagen sowie Schweißrauchabsaugung für die metallverarbeitende Fertigung. Sitz 48691 Vreden.</t>
+          <t>Inhabergeführter Betrieb der metallverarbeitenden Fertigung (Blechbearbeitung, Laserschneiden, Kanten, Schweißbaugruppen) für Maschinenbau-Kunden in OWL.</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>https://kemper.eu/Unternehmen/Kontakt/ | https://kemper.eu/Unternehmen/ (Adresse 48691 Vreden)</t>
+          <t>https://blechwerk.de/unternehmen/ansprechpartner/ | https://blechwerk.de/ (Zitat u. a.: '40 Mitarbeitern mit mehr als 20 Jahren Erfahrung in der Metall- und Blechv...', Standort 32107 Bad Salzuflen)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Dr. Sascha Falkenberg</t>
+          <t>Holger Krebs</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Managing Director / Member of the Board (Geschäftsführer)</t>
+          <t>Geschäftsführer</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>s.falkenberg@minda.com</t>
+          <t>krebs@ctechnik.de</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>+49 (0) 5721 / 9789-20</t>
+          <t>+49 2154 89102-0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>MINDA Industrieanlagen GmbH</t>
+          <t>C-Technik Maschinen- und Anlagenbau GmbH</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -762,44 +762,44 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Minden (Ostwestfalen-Lippe)</t>
+          <t>Willich (Niederrhein); zweiter Standort Hagen</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Anlagenbauer für Material- und Fördertechnik in der Wellpappen-, Holzwerkstoff- und Reifenindustrie mit Hauptsitz Minden.</t>
+          <t>Inhabergeführter Sondermaschinen- und Anlagenbauer mit Konstruktion, Kalkulation und Projektmanagement; Sitz 47877 Willich, weiterer Standort im Raum Hagen.</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>https://minda.com/en/contact/general-management | https://minda.com/en/contact/management (Produktionsleitung Minden: 'Dirk Juras | Head of Production | +49 (0) 571 / 3997 - 0 | d.juras@minda.com')</t>
+          <t>https://ctechnik.de/kontakt/ | https://ctechnik.de/ (Adresse 47877 Willich) | Zweiter Geschäftsführer auf derselben Seite: 'Mirko Krebs | Geschäftsführer | T. +49 2154 89102 – 211 | mkrebs@ctechnik.de'</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Olaf Clemens</t>
+          <t>Maik Vogtt</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführender Gesellschafter</t>
+          <t>Fertigung (Ansprechpartner Produktion)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>olaf.clemens@sn-packaging.de</t>
+          <t>mavog@emsland-metallbau.de</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>+49 2267 699-0</t>
+          <t>+49 5971 8004-156</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>SN Maschinenbau GmbH</t>
+          <t>Emsland Metallbau GmbH</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -809,44 +809,44 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Wipperfürth (Bergisches Land / Rheinland)</t>
+          <t>Salzbergen (Niedersachsen)</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Familiengeführter Hersteller von Beutelverpackungsmaschinen (Form-, Füll- und Verschließmaschinen) mit Firmensitz und Entwicklung in Wipperfürth. International tätig über die Marke SN Packaging.</t>
+          <t>Mittelständischer Metall- und Stahlbau-/Fertigungsbetrieb mit Blechbearbeitung, Schweißbaugruppen und Auftragsfertigung für den Maschinen- und Anlagenbau. Einkauf/Supply Chain: André Hülsmann (anhue@emsland-metallbau.de, gleiche Quelle).</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>https://sn-maschinenbau.de/service-kontakt/kontakt-sales/beratung-vertrieb | https://sn-maschinenbau.de/unternehmen/ (Zitat: 'An unserem Firmensitz in Wipperfürth entwickeln täglich rund 300 Mitarbeiterinnen und Mitarbeiter führende Beutelverpackungslösung...', 51688 Wipperfürth)</t>
+          <t>https://www.emsland-metallbau.de/kontakt/kontakt-zu-uns/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Roland Mertens</t>
+          <t>Dirk Haßmann</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsleitung Sales (Chief Sales Officer)</t>
+          <t>Leiter Einkauf (Bereichsleiter Einkauf/Supply Chain)</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>rmertens@schoellerwerk.de</t>
+          <t>Dirk.Hassmann@flaco.de</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>+49 2482 81 129</t>
+          <t>+49 (0) 5241 603-62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Schoeller Werk GmbH &amp; Co. KG</t>
+          <t>FLACO-Geräte GmbH</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -856,44 +856,44 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Hellenthal (Eifel, NRW)</t>
+          <t>Gütersloh (Ostwestfalen-Lippe)</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Metallverarbeitende Fertigung: Hersteller längsnahtgeschweißter Edelstahlrohre für Industrie und Automotive. Teil der familiengeführten Schoeller-Gruppe.</t>
+          <t>Hersteller von Fluid-, Tank- und Werkstatttechnik sowie Fluidsystemen für Fertigungsbetriebe. Geschäftsführer Thomas Voigt ist auf der Kontaktseite genannt, jedoch ohne persönliche E-Mail – daher der Einkaufsleiter als Entscheider hinterlegt.</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>https://schoellerwerk.de/kontakt/ | https://www.schoellerwerk.de/en/contact/ (englische Fassung derselben Ansprechpartner-Tabelle: 'Roland Mertens | Chief Sales Officer')</t>
+          <t>https://flaco.de/de/kontakt-beratung.html | https://flaco.de/de/kontakt-beratung.html (Zitat zur Geschäftsführung ohne E-Mail: 'Thomas Voigt | Geschäftsführer | Tel. +49 (0) 5241 - 603 - 0')</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Andreas Sommer</t>
+          <t>Holger Fries</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer (Werkzeugmachermeister)</t>
+          <t>Geschäftsführung</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>asommer@oelfke.de</t>
+          <t>h.fries@fries-gmbh.de</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>+49 2351 676950</t>
+          <t>+49 2743 9223-13</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Ulrich Oelfke Formenbau GmbH &amp; Co. KG</t>
+          <t>Fries Maschinen- und Anlagenbau GmbH</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -903,44 +903,44 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Lüdenscheid (Sauerland / Märkischer Kreis)</t>
+          <t>Derschen (Rheinland-Pfalz, Westerwald)</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Inhabergeführter Werkzeug- und Formenbaubetrieb für Spritzgießwerkzeuge in Lüdenscheid, Kerkhagen 15.</t>
+          <t>Familiengeführter Maschinen- und Anlagenbauer seit 1980 mit Zerspanung, Schweißtechnik, Montage und eigener Konstruktion.</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>https://oelfke.de/kontakt/ | https://oelfke.de/impressum/ (Zitat: 'Ulrich Oelfke | Formenbau GmbH &amp; Co. KG | Geschäftsführer | Andreas Sommer | Kerkhagen 15 | 58513 Lüdenscheid') | Weiterer Entscheider: 'Julian Sommer | Geschäftsleitung | Feinwerkmechanikermeister | jsommer@oelfke.de' (https://oelfke.de/kontakt/)</t>
+          <t>https://www.fries-gmbh.de/kontakt</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Ulrich Rotte</t>
+          <t>Andreas Schneider</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführender Gesellschafter</t>
+          <t>Geschäftsführer (Dipl.-Wirt.-Ing.)</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>rotte@ulrich-rotte.de</t>
+          <t>a.schneider@icmgmbh-chemnitz.de</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>+49 5258 9789-0</t>
+          <t>+49 371 27836 450</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Ulrich Rotte Anlagenbau &amp; Fördertechnik GmbH</t>
+          <t>ICM GmbH – Innovation + Cooperation für den Maschinenbau</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -950,44 +950,44 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Salzkotten / Kreis Paderborn (Ostwestfalen-Lippe)</t>
+          <t>Chemnitz (Sachsen)</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1994 gegründetes Familienunternehmen für Anlagenbau und Fördertechnik, u. a. für Holztechnik, technische Laminate und Industrieautomation.</t>
+          <t>Chemnitzer Entwicklungs- und Engineering-Dienstleister für den Maschinen- und Anlagenbau (Produktentwicklung, Konstruktion, Automation).</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>https://www.ulrich-rotte.de/ueber-uns/ | https://www.ulrich-rotte.de/ueber-uns/ (Zitat: 'Gegründet 1994 von Ulrich und Brigitte Rotte haben wir inzwischen 90 Mitarbeiter und einen Jahresumsatz von 16 Millionen...', 33154 Salzkotten) | Zweiter Entscheider auf derselben Seite: 'Benedikt Rotte | Geschäftsführender Gesellschafter | +49 5258 9789-0 | benedikt.rotte@ulrich-rotte.de'</t>
+          <t>https://www.icmgmbh-chemnitz.de/kontakt | https://www.icmgmbh-chemnitz.de/impressum ('Geschäftsführer: Herr Dipl.-Wirt.-Ing. Andreas Schneider') | https://www.icmgmbh-chemnitz.de/leistungen/anlagenbau-und-automation</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Dipl.-Ing. Norbert Felder</t>
+          <t>Frederic Lanz</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer / Konstruktion &amp; Entwicklung</t>
+          <t>CEO / Vice Chairman of the Board</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>felder@weidmann-mb.de</t>
+          <t>lanz@kemper.eu</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>+49 2241 2014101</t>
+          <t>+49 (0) 2564 68-119</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>WEIDMANN Maschinenbau GmbH</t>
+          <t>KEMPER GmbH</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -997,24 +997,24 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Troisdorf (Raum Köln/Bonn, Rheinland)</t>
+          <t>Vreden (Münsterland, NRW)</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Sondermaschinenbauer für automatisierte Produktions- und Montageanlagen (u. a. Montageautomaten) mit Sitz 53842 Troisdorf.</t>
+          <t>Familiengeführter Hersteller von Absaug- und Filteranlagen sowie Schweißrauchabsaugung für die metallverarbeitende Fertigung. Sitz 48691 Vreden.</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>https://weidmann-maschinenbau.de/ansprechpartner.php | https://weidmann-maschinenbau.de/unternehmen.php (Standort 53842 Troisdorf)</t>
+          <t>https://kemper.eu/Unternehmen/Kontakt/ | https://kemper.eu/Unternehmen/ (Adresse 48691 Vreden)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Dominic Scheumann</t>
+          <t>Johann Liebl</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1024,17 +1024,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>d.scheumann@wibra-formenbau.de</t>
+          <t>johann.liebl@lieblmetall.de</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>+49 (0) 2351 / 36824-10</t>
+          <t>+49 9438 90091</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>WIBRA Formenbau GmbH</t>
+          <t>Lieblmetall GmbH</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1044,702 +1044,702 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Lüdenscheid (Sauerland / Märkischer Kreis)</t>
+          <t>Ebermannsdorf (Bayern, Oberpfalz)</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Werkzeug- und Formenbauer in Lüdenscheid (58511) mit eigener Konstruktion und Betriebsleitung; zwei geschäftsführende Gesellschafter.</t>
+          <t>Familiengeführter Fertigungsbetrieb für Blechbearbeitung und Lohnfertigung (Laserschneiden, CNC-Biegen, Schweißbaugruppen) für den Maschinenbau. Betriebsleitung &amp; Gesellschafter: Martin Liebl (martin.liebl@lieblmetall.de, gleiche Quelle).</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>https://wibraformenbau.de/kontakt/ | https://wibraformenbau.de/kontakt/ (zweiter Geschäftsführer: 'Sebastian Scholz | Geschäftsführer | Telefon: +49 (0) 23 51 / 36824 12 | E-Mail: s.scholz@wibra-formenbau.de'; Betriebsleiter: 'Jürgen Manz | Betriebsleiter | j.manz@wibra-formenbau.de')</t>
+          <t>https://www.lieblmetall.de/de/kontakt</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Christoph Dahlmann</t>
+          <t>Dr. Sascha Falkenberg</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführung</t>
+          <t>Managing Director / Member of the Board (Geschäftsführer)</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>c.dahlmann@als-arnsberg.de</t>
+          <t>s.falkenberg@minda.com</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>02932 9306-15</t>
+          <t>+49 (0) 5721 / 9789-20</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>A.L.S. Allgemeine Land- und Seespedition GmbH</t>
+          <t>MINDA Industrieanlagen GmbH</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Maschinenbau &amp; Fertigung</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Arnsberg (Sauerland)</t>
+          <t>Minden (Ostwestfalen-Lippe)</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Mittelständische Spedition mit nationalen und internationalen Verkehren, Überseeverkehr, Zollabwicklung und Logistikzentrum. Klare Leitungsstruktur mit vier Prokuristen (Vertrieb, Disposition, Marketing, kaufmännische Logistikleitung).</t>
+          <t>Anlagenbauer für Material- und Fördertechnik in der Wellpappen-, Holzwerkstoff- und Reifenindustrie mit Hauptsitz Minden.</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>https://www.als-arnsberg.de/ansprechpartner | https://www.regiomanager.de/suedwestfalen/ranking/mobilitaet-logistik/spedition-und-logistik/hochsauerlandkreis/</t>
+          <t>https://minda.com/en/contact/general-management | https://minda.com/en/contact/management (Produktionsleitung Minden: 'Dirk Juras | Head of Production | +49 (0) 571 / 3997 - 0 | d.juras@minda.com')</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>René Fröhlich</t>
+          <t>Diana Reich</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer</t>
+          <t>Geschäftsführung</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>r.froehlich@lrp24.de</t>
+          <t>diana.reich@msr-chemnitz.de</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>+49 341 222 8 66 55 (Zentrale)</t>
+          <t>+49 371 81495-21</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>ALN Logistik GmbH</t>
+          <t>MSR Elektro- und Anlagenbau GmbH</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Maschinenbau &amp; Fertigung</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Leipzig (Sachsen)</t>
+          <t>Chemnitz (Sachsen)</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Spedition für Transport-, Sonder- und Lagerlogistik mit Sitz Brahestraße 10, 04347 Leipzig und Lagerstandorten in Leipzig und Berlin.</t>
+          <t>Mittelständischer Elektro- und Anlagenbauer aus Chemnitz mit Projektierung, Schaltanlagenbau und Automatisierung für Industrieanlagen. Zweiter Geschäftsführer: Sven Mehnert (sven.mehnert@msr-chemnitz.de, gleiche Quelle).</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>https://aln-logistik.de/logistik-experten/ansprechpartner/</t>
+          <t>https://www.msr-chemnitz.de/kontakt/ | https://www.msr-chemnitz.de/ueber-uns/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Hubertus Beumer</t>
+          <t>Heiko Müller</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer</t>
+          <t>Geschäftsführer (lt. Impressum vertretungsberechtigt), Technik und Vertrieb</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>hubertus.beumer@b-logistik.de</t>
+          <t>heiko.mueller@mueller-sut.de</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>+49 2524 911-0 (Zentrale, keine Durchwahl veröffentlicht)</t>
+          <t>+49 9254 7913</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>B Logistik GmbH</t>
+          <t>Müller Maschinen und Anlagen GmbH &amp; Co. KG (MÜLLER Gefrees)</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Maschinenbau &amp; Fertigung</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Ennigerloh (Münsterland, NRW)</t>
+          <t>Gefrees (Bayern, Oberfranken)</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Mittelständischer, inhabergeführter Kontraktlogistiker mit 65.000 qm Logistikfläche an drei Standorten (u. a. Pharma-Logistik-Centrum, Retail/E-Commerce, Nahrungsmittel). Branchenmix mit hohen Compliance-Anforderungen (Pharma/GDP) und kundenindividuellen Value-Added-Services — klassisches Umfeld für manuelle Prozesse und ERP-/LVS-Integration.</t>
+          <t>Inhabergeführter Hersteller von Pressen und Sondermaschinen (C-Gestell-Pressen, Stanzautomaten, CNC-Stanzanlagen) inkl. Kundendienst und Retrofit.</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>https://www.b-logistik.de/kontakt | https://www.b-logistik.de/ | https://www.b-logistik.de/ueber-uns/unser-team</t>
+          <t>https://mueller-sut.de/kontakt/ansprechpartner/ | https://mueller-sut.de/impressum/ ('Müller Maschinen und Anlagen GmbH &amp; Co. KG ... Vertreten durch Herr Heiko Müller')</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Jan Feldberg</t>
+          <t>Johannes Rehm</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer</t>
+          <t>Geschäftsführer / CEO</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>jan.feldberg@btg-feldberg.de</t>
+          <t>j.rehm@rehm-group.com</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>+49 (0) 2871 9970 260</t>
+          <t>+49 7344 9606-0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>BTG Feldberg &amp; Sohn GmbH &amp; Co. KG</t>
+          <t>Rehm Thermal Systems GmbH</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Maschinenbau &amp; Fertigung</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Bocholt (Westmünsterland)</t>
+          <t>Blaubeuren-Seissen (Baden-Württemberg)</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Familiengeführte Spedition (Geschäftsführer Jan und Jörg Feldberg) mit Stückgut, Luft- und Seefracht, Logistikzentrum, Umzugslogistik sowie eigenem Projektmanagement und QM.</t>
+          <t>Familiengeführter Sondermaschinenbauer für thermische Systemlösungen und Fertigungsanlagen der Elektronik- und Leistungselektronikproduktion.</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>https://www.btg-feldberg.de/ansprechpartner | https://www.regiomanager.de/ranking/mobilitaet-logistik/spedition-und-logistik/muensterland/</t>
+          <t>https://www.rehm-group.com/unternehmen.html</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Mathias Ronneberger</t>
+          <t>Volker Rößner</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer (Shipping – Chartering &amp; Brokerage), Mitinhaber</t>
+          <t>Geschäftsführer, Vertrieb</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>ronneberger@balticlloyd.com</t>
+          <t>v.roessner@roessner-maschinenbau.de</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>+49 381 666 139 14</t>
+          <t>+49 6631 9622-24</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Baltic Lloyd Schiffahrt-Spedition-Logistik GmbH</t>
+          <t>Rößner Maschinenbau GmbH</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Maschinenbau &amp; Fertigung</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Rostock (Mecklenburg-Vorpommern)</t>
+          <t>Alsfeld (Hessen)</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Im Rostocker Überseehafen (Am Skandinavienkai 2-3) ansässige Spedition für Schifffahrt, Hafenumschlag, Lagerung und Landverkehre; seit einer Nachfolgeregelung inhabergeführt durch drei langjährige Mitarbeiter.</t>
+          <t>Familiengeführter Maschinenbau- und Lohnfertigungsbetrieb (Schweiß- und Stahlbaugruppen, Brikettierpressen) mit eigener Konstruktion.</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>https://balticlloyd.com/dasteam/ | https://www.mbg-mv.de/rostocker-logistikunternehmen-auf-erfolgskurs-dreifache-nachfolgeregelung-sichert-zukunft</t>
+          <t>https://www.roessner-maschinenbau.de/kontakt/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Ronny Oldag</t>
+          <t>Susanne Wolf</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer (Cargo Handling, Storage), Mitinhaber</t>
+          <t>Geschäftsführende Gesellschafterin</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>oldag@balticlloyd.com</t>
+          <t>susanne.wolf@sme-leipzig.de</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>+49 381 666 139 12</t>
+          <t>+49 341 2574 616</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Baltic Lloyd Schiffahrt-Spedition-Logistik GmbH</t>
+          <t>SME Sondermaschinenbau Engelsdorf GmbH</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Maschinenbau &amp; Fertigung</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Rostock (Mecklenburg-Vorpommern)</t>
+          <t>Leipzig (Sachsen)</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer mit Zuständigkeit für Umschlag und Lagerung im Rostocker Überseehafen; dritter Geschäftsführer Wolfgang Nuß.</t>
+          <t>Familiengeführter Sondermaschinenbauer für Förder-, Handling- und Montagetechnik sowie Roboterzellen (Automotive, Baustoffe, Konsumgüter). Zweiter Geschäftsführender Gesellschafter (Vertrieb): Jan Wolf (jan.wolf@sme-leipzig.de, gleiche Quelle).</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>https://balticlloyd.com/dasteam/</t>
+          <t>https://www.sme-leipzig.de/ | https://www.sme-leipzig.de/industriezweige/automotive/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Wolfgang Heidel</t>
+          <t>Olaf Clemens</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsleitung</t>
+          <t>Geschäftsführender Gesellschafter</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>wolfgang.heidel@bayern-express-spedition.de</t>
+          <t>olaf.clemens@sn-packaging.de</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>+49 89 329892-10</t>
+          <t>+49 2267 699-0</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Bayern Express Spedition GmbH</t>
+          <t>SN Maschinenbau GmbH</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Maschinenbau &amp; Fertigung</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Garching bei München, weiterer Standort Pilsting-Ganacker, Bayern</t>
+          <t>Wipperfürth (Bergisches Land / Rheinland)</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Familiengeführte bayerische Spedition (Familie Heidel) mit Fernverkehr, Nahverkehrsdisposition, Stückgut-/VTL-Systemverkehr und eigener Abwicklung an zwei Standorten.</t>
+          <t>Familiengeführter Hersteller von Beutelverpackungsmaschinen (Form-, Füll- und Verschließmaschinen) mit Firmensitz und Entwicklung in Wipperfürth. International tätig über die Marke SN Packaging.</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>https://www.bayern-express-spedition.de/mitarbeiter.php</t>
+          <t>https://sn-maschinenbau.de/service-kontakt/kontakt-sales/beratung-vertrieb | https://sn-maschinenbau.de/unternehmen/ (Zitat: 'An unserem Firmensitz in Wipperfürth entwickeln täglich rund 300 Mitarbeiterinnen und Mitarbeiter führende Beutelverpackungslösung...', 51688 Wipperfürth)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Christian Messing</t>
+          <t>Roland Mertens</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer</t>
+          <t>Geschäftsleitung Sales (Chief Sales Officer)</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>c.messing@spedition-messing.de</t>
+          <t>rmertens@schoellerwerk.de</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>02541 9487-10</t>
+          <t>+49 2482 81 129</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Bernhard Messing GmbH &amp; Co. KG (Spedition Messing)</t>
+          <t>Schoeller Werk GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Maschinenbau &amp; Fertigung</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Coesfeld</t>
+          <t>Hellenthal (Eifel, NRW)</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Familiengeführte Spedition mit Sammelgut, Fernverkehr, Tourendisposition, eigener Lagerlogistik und Bereich Bio &amp; Frische (Lebensmittellogistik). Mehrere Familienmitglieder (Christian, Andreas, Esther Meßing) im Unternehmen.</t>
+          <t>Metallverarbeitende Fertigung: Hersteller längsnahtgeschweißter Edelstahlrohre für Industrie und Automotive. Teil der familiengeführten Schoeller-Gruppe.</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>https://www.spedition-messing.de/ansprechpartner | https://www.regiomanager.de/ranking/mobilitaet-logistik/spedition-und-logistik/kreis-coesfeld/</t>
+          <t>https://schoellerwerk.de/kontakt/ | https://www.schoellerwerk.de/en/contact/ (englische Fassung derselben Ansprechpartner-Tabelle: 'Roland Mertens | Chief Sales Officer')</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Tim Bönders</t>
+          <t>Mario Taenzler</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführender Gesellschafter (4. Generation)</t>
+          <t>Geschäftsführer</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>tboenders@bk-group.de</t>
+          <t>m.taenzler@tma-sachsen.de</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>nicht öffentlich</t>
+          <t>+49 35795 2891-0</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Bönders GmbH (B+K Group)</t>
+          <t>Taenzler Maschinen- und Anlagenbau GmbH</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Maschinenbau &amp; Fertigung</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Krefeld</t>
+          <t>Laußnitz (Sachsen)</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Inhabergeführter Logistikdienstleister aus Krefeld (seit über 70 Jahren, 4. Generation) mit Kontraktlogistik, Ersatzteillogistik, Warehousing und Distribution für ausgewählte Schlüsselbranchen.</t>
+          <t>Inhabergeführter Maschinen- und Anlagenbauer mit eigener CNC-Fertigung; Anlagenbau u. a. für die Automobilindustrie sowie Elektrotechnik/SPS und Konstruktion im Haus.</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>https://www.boenders.de/about/management/ | https://www.regiomanager.de/niederrhein/ranking/mobilitaet-logistik/spedition-und-logistik/krefeld/</t>
+          <t>https://tma-sachsen.de/kontakt/ | https://tma-sachsen.de/impressum/ (Impressum: 'Taenzler Maschinen- und Anlagenbau GmbH, Grenzstraße 13, 01936 Laußnitz ... Geschäftsführer: Herr Mario Taenzler')</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Norman Lippe</t>
+          <t>Andreas Sommer</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer</t>
+          <t>Geschäftsführer (Werkzeugmachermeister)</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>norman.lippe@cargotrans.de</t>
+          <t>asommer@oelfke.de</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>+49 2361 3061-0 (Zentrale Recklinghausen)</t>
+          <t>+49 2351 676950</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>CARGOTRANS GmbH &amp; Co. KG</t>
+          <t>Ulrich Oelfke Formenbau GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Maschinenbau &amp; Fertigung</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Recklinghausen (Hauptsitz), Verwaltung Dortmund, NL Hamburg</t>
+          <t>Lüdenscheid (Sauerland / Märkischer Kreis)</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Mittelständische Spedition im nördlichen Ruhrgebiet mit Road-/Intermodal-Verkehren, Warehousing und Zollservice; vollständige Ansprechpartnerliste inkl. Dispositions- und Lagerleitung öffentlich.</t>
+          <t>Inhabergeführter Werkzeug- und Formenbaubetrieb für Spritzgießwerkzeuge in Lüdenscheid, Kerkhagen 15.</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>https://www.cargotrans.de/kontakt | https://www.regiomanager.de/ranking/mobilitaet-logistik/spedition-und-logistik/dortmund/</t>
+          <t>https://oelfke.de/kontakt/ | https://oelfke.de/impressum/ (Zitat: 'Ulrich Oelfke | Formenbau GmbH &amp; Co. KG | Geschäftsführer | Andreas Sommer | Kerkhagen 15 | 58513 Lüdenscheid') | Weiterer Entscheider: 'Julian Sommer | Geschäftsleitung | Feinwerkmechanikermeister | jsommer@oelfke.de' (https://oelfke.de/kontakt/)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Jens Haverland</t>
+          <t>Ulrich Rotte</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer</t>
+          <t>Geschäftsführender Gesellschafter</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>jhaverland@cargomar.de</t>
+          <t>rotte@ulrich-rotte.de</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>+49 421 5590-10 (Zentrale)</t>
+          <t>+49 5258 9789-0</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Cargomar GmbH Internationale Spedition / Cargomar Air &amp; Sea GmbH</t>
+          <t>Ulrich Rotte Anlagenbau &amp; Fördertechnik GmbH</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Maschinenbau &amp; Fertigung</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Bremen</t>
+          <t>Salzkotten / Kreis Paderborn (Ostwestfalen-Lippe)</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Inhabergeführte Bremer Spedition mit See-/Luftfracht, Import/Export sowie eigener Lagerlogistik (Teamleitung Lagerlogistik im Haus).</t>
+          <t>1994 gegründetes Familienunternehmen für Anlagenbau und Fördertechnik, u. a. für Holztechnik, technische Laminate und Industrieautomation.</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>https://www.cargomar.de/</t>
+          <t>https://www.ulrich-rotte.de/ueber-uns/ | https://www.ulrich-rotte.de/ueber-uns/ (Zitat: 'Gegründet 1994 von Ulrich und Brigitte Rotte haben wir inzwischen 90 Mitarbeiter und einen Jahresumsatz von 16 Millionen...', 33154 Salzkotten) | Zweiter Entscheider auf derselben Seite: 'Benedikt Rotte | Geschäftsführender Gesellschafter | +49 5258 9789-0 | benedikt.rotte@ulrich-rotte.de'</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Dr. Rimbert J. Kelber</t>
+          <t>Dipl.-Ing. Norbert Felder</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Niederlassungsleitung</t>
+          <t>Geschäftsführer / Konstruktion &amp; Entwicklung</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>rimbert.kelber@koester-hapke-sped.com</t>
+          <t>felder@weidmann-mb.de</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>+49 5132 822-100</t>
+          <t>+49 2241 2014101</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Carl Köster &amp; Louis Hapke GmbH &amp; Co. KG</t>
+          <t>WEIDMANN Maschinenbau GmbH</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Maschinenbau &amp; Fertigung</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Sehnde-Höver bei Hannover, Niedersachsen</t>
+          <t>Troisdorf (Raum Köln/Bonn, Rheinland)</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Mittelständische, inhabergeführte Spedition seit 1854 mit nationalen/internationalen Stückgutverkehren, Messelogistik und eigener Lagerlogistik (eigene Lagerleitung).</t>
+          <t>Sondermaschinenbauer für automatisierte Produktions- und Montageanlagen (u. a. Montageautomaten) mit Sitz 53842 Troisdorf.</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>https://koester-hapke-sped.com/ansprechpartner/ | https://koester-hapke-sped.com/wir-ueber-uns/ | https://koester-hapke-sped.com/kontakt/</t>
+          <t>https://weidmann-maschinenbau.de/ansprechpartner.php | https://weidmann-maschinenbau.de/unternehmen.php (Standort 53842 Troisdorf)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Andreas Grimmeißen</t>
+          <t>Dominic Scheumann</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>CEO – Geschäftsführer</t>
+          <t>Geschäftsführer</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>andreas.grimmeissen@ewo-logistics.com</t>
+          <t>d.scheumann@wibra-formenbau.de</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>+49 7191 969 93 10</t>
+          <t>+49 (0) 2351 / 36824-10</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>E.W.O Logistics GmbH</t>
+          <t>WIBRA Formenbau GmbH</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Maschinenbau &amp; Fertigung</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Backnang bei Stuttgart (Baden-Württemberg)</t>
+          <t>Lüdenscheid (Sauerland / Märkischer Kreis)</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Inhabergeführte Speditions- und Logistikgesellschaft im Raum Stuttgart/Backnang, Familienunternehmen (Geschäftsführung, Verkaufs- und Dispositionsleitung sämtlich Familie Grimmeißen).</t>
+          <t>Werkzeug- und Formenbauer in Lüdenscheid (58511) mit eigener Konstruktion und Betriebsleitung; zwei geschäftsführende Gesellschafter.</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>https://www.ewo-logistics.com/ewo-logistics-backnang-stuttgart-badenwuerttemberg-deutschland/</t>
+          <t>https://wibraformenbau.de/kontakt/ | https://wibraformenbau.de/kontakt/ (zweiter Geschäftsführer: 'Sebastian Scholz | Geschäftsführer | Telefon: +49 (0) 23 51 / 36824 12 | E-Mail: s.scholz@wibra-formenbau.de'; Betriebsleiter: 'Jürgen Manz | Betriebsleiter | j.manz@wibra-formenbau.de')</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Doris Grimmeißen</t>
+          <t>Rainer Grimm</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>CEO – Geschäftsführerin</t>
+          <t>Geschäftsführer (Dipl.-Ing. TU)</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>doris.grimmeissen@ewo-logistics.com</t>
+          <t>grimm@fm-control.de</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>+49 7191 969 93 20</t>
+          <t>+49 3741 1702-0</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>E.W.O Logistics GmbH</t>
+          <t>fm control GmbH</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Maschinenbau &amp; Fertigung</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Backnang bei Stuttgart (Baden-Württemberg)</t>
+          <t>Plauen (Sachsen)</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Zweite Geschäftsführerin des inhabergeführten Logistikunternehmens im Rems-Murr-Kreis.</t>
+          <t>Inhabergeführtes Unternehmen für Automatisierungs- und Materialflusssteuerung (Steuerungstechnik, Softwareentwicklung) für Produktions- und Förderanlagen.</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>https://www.ewo-logistics.com/ewo-logistics-backnang-stuttgart-badenwuerttemberg-deutschland/</t>
+          <t>https://www.fm-control.de/kontakt/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Anja Hollenhorst</t>
+          <t>Christoph Dahlmann</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführerin (lt. Impressum; auf der Website Ansprechpartnerin Kundenservice)</t>
+          <t>Geschäftsführung</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>anja@hti-spedition.de</t>
+          <t>c.dahlmann@als-arnsberg.de</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>+49 251 74787-0 (Zentrale, Durchwahlen 11-21)</t>
+          <t>02932 9306-15</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>HTI Spedition und Logistik GmbH</t>
+          <t>A.L.S. Allgemeine Land- und Seespedition GmbH</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1749,44 +1749,44 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Münster (NRW)</t>
+          <t>Arnsberg (Sauerland)</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Familiengeführte Spedition (Familie Hollenhorst) mit Fernverkehr, Luft-/Seefracht inkl. Zollabwicklung, Lager und Status Reglementierter Beauftragter. Zoll-, Fracht- und Dispositionsprozesse mit hohem Dokumentenaufkommen — gutes Feld für Prozessautomatisierung und Systemanbindung.</t>
+          <t>Mittelständische Spedition mit nationalen und internationalen Verkehren, Überseeverkehr, Zollabwicklung und Logistikzentrum. Klare Leitungsstruktur mit vier Prokuristen (Vertrieb, Disposition, Marketing, kaufmännische Logistikleitung).</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>https://hti-spedition.de/ | https://hti-spedition.de/impressum/</t>
+          <t>https://www.als-arnsberg.de/ansprechpartner | https://www.regiomanager.de/suedwestfalen/ranking/mobilitaet-logistik/spedition-und-logistik/hochsauerlandkreis/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Klaus Hüttemann</t>
+          <t>René Fröhlich</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer / geschäftsführender Gesellschafter (2. Generation)</t>
+          <t>Geschäftsführer</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>k.huettemann@huelog.de</t>
+          <t>r.froehlich@lrp24.de</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>+49 2065 909116</t>
+          <t>+49 341 222 8 66 55 (Zentrale)</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>HUETTEMANN Logistik GmbH (HUETTEMANN Group)</t>
+          <t>ALN Logistik GmbH</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -1796,24 +1796,24 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Duisburg</t>
+          <t>Leipzig (Sachsen)</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Inhabergeführte Logistikgruppe aus Duisburg mit Kontraktlogistik, Lagerlogistik, Hafenumschlag und Transport. Klaus Hüttemann führt die Gruppe in zweiter Generation als geschäftsführender Gesellschafter.</t>
+          <t>Spedition für Transport-, Sonder- und Lagerlogistik mit Sitz Brahestraße 10, 04347 Leipzig und Lagerstandorten in Leipzig und Berlin.</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>https://www.huettemann-logistik.de/unternehmensgruppe/management/ | https://www.regiomanager.de/revier/ranking/mobilitaet-logistik/spedition-und-logistik/duisburg/</t>
+          <t>https://aln-logistik.de/logistik-experten/ansprechpartner/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Hanjo Heinen</t>
+          <t>Hubertus Beumer</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1823,17 +1823,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>hanjo.heinen@heinen-ht.de</t>
+          <t>hubertus.beumer@b-logistik.de</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>nicht öffentlich</t>
+          <t>+49 2524 911-0 (Zentrale, keine Durchwahl veröffentlicht)</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Heinen Transport GmbH (Heinen Gruppe: HT, HLS, HHL, HSK, HHV, HG)</t>
+          <t>B Logistik GmbH</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -1843,44 +1843,44 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Meerbusch (Hauptsitz), Logistikzentrum Duisburg</t>
+          <t>Ennigerloh (Münsterland, NRW)</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Familiengeführte Transport- und Logistikgruppe im Rheinland mit Logistikzentrum in Duisburg, Speditions-, Lager- und Kontraktlogistikgesellschaften. Weitere Entscheider: Pascal Heinen (Prokurist / Leitung Logistik, pascal.heinen@heinen-ht.de), Sabine Heinen (Prokuristin, sabine.heinen@heinen-ht.de).</t>
+          <t>Mittelständischer, inhabergeführter Kontraktlogistiker mit 65.000 qm Logistikfläche an drei Standorten (u. a. Pharma-Logistik-Centrum, Retail/E-Commerce, Nahrungsmittel). Branchenmix mit hohen Compliance-Anforderungen (Pharma/GDP) und kundenindividuellen Value-Added-Services — klassisches Umfeld für manuelle Prozesse und ERP-/LVS-Integration.</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>https://www.heinen-transport-gmbh.de/ansprechpartner | https://www.heinen-transport-gmbh.de/impressum</t>
+          <t>https://www.b-logistik.de/kontakt | https://www.b-logistik.de/ | https://www.b-logistik.de/ueber-uns/unser-team</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Ludger Henke</t>
+          <t>Jan Feldberg</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführung</t>
+          <t>Geschäftsführer</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>l.henke@henke-spedition.de</t>
+          <t>jan.feldberg@btg-feldberg.de</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>+49 5250 9850-0</t>
+          <t>+49 (0) 2871 9970 260</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Heinrich Henke Güterfernverkehr und Spedition GmbH &amp; Co.</t>
+          <t>BTG Feldberg &amp; Sohn GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -1890,44 +1890,44 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Delbrück (Kreis Paderborn)</t>
+          <t>Bocholt (Westmünsterland)</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Familienspedition in dritter Generation mit Fernverkehr, Disposition und Lagerlogistik im Raum Paderborn. Mehrere Familienmitglieder (Ludger, Ludgerus, Regina Henke) im Unternehmen tätig.</t>
+          <t>Familiengeführte Spedition (Geschäftsführer Jan und Jörg Feldberg) mit Stückgut, Luft- und Seefracht, Logistikzentrum, Umzugslogistik sowie eigenem Projektmanagement und QM.</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>https://www.henke-spedition.de/kontakt | https://www.regiomanager.de/ostwestfalen/ranking/mobilitaet-logistik/spedition-und-logistik/kreis-paderborn/</t>
+          <t>https://www.btg-feldberg.de/ansprechpartner | https://www.regiomanager.de/ranking/mobilitaet-logistik/spedition-und-logistik/muensterland/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Bernd Specht</t>
+          <t>Mathias Ronneberger</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer</t>
+          <t>Geschäftsführer (Shipping – Chartering &amp; Brokerage), Mitinhaber</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>b.specht@wichmann-transporte.de</t>
+          <t>ronneberger@balticlloyd.com</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>+49 5481/808-51</t>
+          <t>+49 381 666 139 14</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Heinrich Wichmann Transporte GmbH</t>
+          <t>Baltic Lloyd Schiffahrt-Spedition-Logistik GmbH</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -1937,44 +1937,44 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Lengerich (Kreis Steinfurt)</t>
+          <t>Rostock (Mecklenburg-Vorpommern)</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Mittelständisches Transportunternehmen mit eigener Werkstatt, Disposition und Fuhrparkmanagement im nördlichen Münsterland.</t>
+          <t>Im Rostocker Überseehafen (Am Skandinavienkai 2-3) ansässige Spedition für Schifffahrt, Hafenumschlag, Lagerung und Landverkehre; seit einer Nachfolgeregelung inhabergeführt durch drei langjährige Mitarbeiter.</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>https://www.wichmann-transporte.de/kontakt | https://www.regiomanager.de/muensterland/ranking/mobilitaet-logistik/spedition-und-logistik/kreis-steinfurt/</t>
+          <t>https://balticlloyd.com/dasteam/ | https://www.mbg-mv.de/rostocker-logistikunternehmen-auf-erfolgskurs-dreifache-nachfolgeregelung-sichert-zukunft</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Peter Plank</t>
+          <t>Ronny Oldag</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Vorsitzender Geschäftsführer / Inhaber</t>
+          <t>Geschäftsführer (Cargo Handling, Storage), Mitinhaber</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>peterplank@hellmold-plank.de</t>
+          <t>oldag@balticlloyd.com</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>+49 641 95201-16</t>
+          <t>+49 381 666 139 12</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Hellmold &amp; Plank GmbH &amp; Co. KG Spedition</t>
+          <t>Baltic Lloyd Schiffahrt-Spedition-Logistik GmbH</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -1984,44 +1984,44 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Gießen (Europastr. 7+9, 35394), Hessen</t>
+          <t>Rostock (Mecklenburg-Vorpommern)</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1904 gegründete, inhabergeführte hessische Spedition (seit 1996 im Alleinbesitz der Familie Plank) mit Systemverkehren, Fernverkehr und Lagerlogistik; zweite Generation (Niklas Plank) in der Geschäftsführung.</t>
+          <t>Geschäftsführer mit Zuständigkeit für Umschlag und Lagerung im Rostocker Überseehafen; dritter Geschäftsführer Wolfgang Nuß.</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>https://www.hellmold-plank.de/de/kontakt | https://www.hellmold-plank.de/</t>
+          <t>https://balticlloyd.com/dasteam/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Oliver Hüer</t>
+          <t>Wolfgang Heidel</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer</t>
+          <t>Geschäftsleitung</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>oliver@hueer.com</t>
+          <t>wolfgang.heidel@bayern-express-spedition.de</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>0251 87189-130</t>
+          <t>+49 89 329892-10</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Hüer Transport und Logistik GmbH</t>
+          <t>Bayern Express Spedition GmbH</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2031,44 +2031,44 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Münster</t>
+          <t>Garching bei München, weiterer Standort Pilsting-Ganacker, Bayern</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Inhabergeführte Spedition in Münster mit Nahverkehr, Kurierdienst und Logistikdienstleistungen. Familienstruktur: Oliver Hüer (GF) und Patrycja Hüer (Prokuristin).</t>
+          <t>Familiengeführte bayerische Spedition (Familie Heidel) mit Fernverkehr, Nahverkehrsdisposition, Stückgut-/VTL-Systemverkehr und eigener Abwicklung an zwei Standorten.</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>https://www.hueer.com/kontakt | https://www.hueer.com/</t>
+          <t>https://www.bayern-express-spedition.de/mitarbeiter.php</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Ingo Kaiser</t>
+          <t>Christian Messing</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführung (Management)</t>
+          <t>Geschäftsführer</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>ingo.kaiser@ikg-spedition.de</t>
+          <t>c.messing@spedition-messing.de</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>+49 7223 281689-19</t>
+          <t>02541 9487-10</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>IKG Spedition GmbH</t>
+          <t>Bernhard Messing GmbH &amp; Co. KG (Spedition Messing)</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -2078,44 +2078,44 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Baden-Baden / Sinzheim, Baden-Württemberg</t>
+          <t>Coesfeld</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Familiengeführte Spedition (Ingo und Kristina Kaiser) mit intermodalen Transporten Richtung Italien/Frankreich/Schweiz, eigenem Lager und Fuhrpark sowie Niederlassung in Busto Arsizio.</t>
+          <t>Familiengeführte Spedition mit Sammelgut, Fernverkehr, Tourendisposition, eigener Lagerlogistik und Bereich Bio &amp; Frische (Lebensmittellogistik). Mehrere Familienmitglieder (Christian, Andreas, Esther Meßing) im Unternehmen.</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>https://www.ikg-spedition.de/team/ | https://www.ikg-spedition.de/</t>
+          <t>https://www.spedition-messing.de/ansprechpartner | https://www.regiomanager.de/ranking/mobilitaet-logistik/spedition-und-logistik/kreis-coesfeld/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Joachim Berends</t>
+          <t>Tim Bönders</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer</t>
+          <t>Geschäftsführender Gesellschafter (4. Generation)</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>j.berends@bentheimer-eisenbahn.de</t>
+          <t>tboenders@bk-group.de</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>+49 5921 8034-0</t>
+          <t>nicht öffentlich</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Kraftverkehr Emsland GmbH</t>
+          <t>Bönders GmbH (B+K Group)</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2125,44 +2125,44 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Nordhorn, Niedersachsen</t>
+          <t>Krefeld</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer der Kraftverkehr Emsland GmbH (Spedition/Logistiklager der Bentheimer Eisenbahn-Gruppe). Hinweis: die auf der Ansprechpartner-Seite genannte E-Mail läuft über die Domain der Muttergesellschaft.</t>
+          <t>Inhabergeführter Logistikdienstleister aus Krefeld (seit über 70 Jahren, 4. Generation) mit Kontraktlogistik, Ersatzteillogistik, Warehousing und Distribution für ausgewählte Schlüsselbranchen.</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>https://www.kraftverkehr-emsland.de/kontakt/</t>
+          <t>https://www.boenders.de/about/management/ | https://www.regiomanager.de/niederrhein/ranking/mobilitaet-logistik/spedition-und-logistik/krefeld/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Marco Oppermann</t>
+          <t>Norman Lippe</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Speditionsleitung &amp; Prokurist</t>
+          <t>Geschäftsführer</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>marco.oppermann@kraftverkehr-emsland.de</t>
+          <t>norman.lippe@cargotrans.de</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>+49 5921 8034-96</t>
+          <t>+49 2361 3061-0 (Zentrale Recklinghausen)</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Kraftverkehr Emsland GmbH</t>
+          <t>CARGOTRANS GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -2172,44 +2172,44 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Nordhorn, Niedersachsen</t>
+          <t>Recklinghausen (Hauptsitz), Verwaltung Dortmund, NL Hamburg</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Mittelständische Spedition mit Sammelgut, Ladungsverkehren und eigenem Warehousing-Bereich; Prokurist und Speditionsleiter mit Entscheidungsbefugnis über Prozesse/IT-Themen.</t>
+          <t>Mittelständische Spedition im nördlichen Ruhrgebiet mit Road-/Intermodal-Verkehren, Warehousing und Zollservice; vollständige Ansprechpartnerliste inkl. Dispositions- und Lagerleitung öffentlich.</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>https://www.kraftverkehr-emsland.de/kontakt/ | https://www.kraftverkehr-emsland.de/spedition-logistiklager/</t>
+          <t>https://www.cargotrans.de/kontakt | https://www.regiomanager.de/ranking/mobilitaet-logistik/spedition-und-logistik/dortmund/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Lena Milde</t>
+          <t>Jens Haverland</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Standort-/Niederlassungsleitung Magdeburg</t>
+          <t>Geschäftsführer</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>lena.milde@krage-gerloff.de</t>
+          <t>jhaverland@cargomar.de</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>+49 39424 951 0 (Zentrale Schwanebeck)</t>
+          <t>+49 421 5590-10 (Zentrale)</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Krage &amp; Gerloff Logistik GmbH</t>
+          <t>Cargomar GmbH Internationale Spedition / Cargomar Air &amp; Sea GmbH</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2219,44 +2219,44 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Magdeburg (Sachsen-Anhalt)</t>
+          <t>Bremen</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>1995 gegründeter Logistikdienstleister mit Hauptsitz Schwanebeck und Logistikstandort Tucheimer Straße 5, 39126 Magdeburg; Lager- und Transportlogistik.</t>
+          <t>Inhabergeführte Bremer Spedition mit See-/Luftfracht, Import/Export sowie eigener Lagerlogistik (Teamleitung Lagerlogistik im Haus).</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>https://www.krage-gerloff.de/magdeburg</t>
+          <t>https://www.cargomar.de/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Andreas Köhler</t>
+          <t>Dr. Rimbert J. Kelber</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer</t>
+          <t>Niederlassungsleitung</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>a.koehler@koehler-transport.de</t>
+          <t>rimbert.kelber@koester-hapke-sped.com</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>+49 221 96640-10</t>
+          <t>+49 5132 822-100</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>KÖHLER GmbH &amp; Co. KG</t>
+          <t>Carl Köster &amp; Louis Hapke GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -2266,44 +2266,44 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Sehnde-Höver bei Hannover, Niedersachsen</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Inhabergeführtes Familienunternehmen in Köln mit Transport, Lager und eigener Werkstatt. Etwas unterhalb der Zielgröße, aber klar mittelständisch und inhabergeführt.</t>
+          <t>Mittelständische, inhabergeführte Spedition seit 1854 mit nationalen/internationalen Stückgutverkehren, Messelogistik und eigener Lagerlogistik (eigene Lagerleitung).</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>https://www.koehler-transport.com/ansprechpartner | https://www.koehler-transport.com/</t>
+          <t>https://koester-hapke-sped.com/ansprechpartner/ | https://koester-hapke-sped.com/wir-ueber-uns/ | https://koester-hapke-sped.com/kontakt/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Alexander Schwarz</t>
+          <t>Andreas Grimmeißen</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Business Development Manager &amp; Lager Management</t>
+          <t>CEO – Geschäftsführer</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>a.schwarz@lkt-thiele.com</t>
+          <t>andreas.grimmeissen@ewo-logistics.com</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>+49 36373 129831-20</t>
+          <t>+49 7191 969 93 10</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>LOGISTIK KONTOR GmbH (LKT Thiele)</t>
+          <t>E.W.O Logistics GmbH</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -2313,44 +2313,44 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Buttstädt (Thüringen)</t>
+          <t>Backnang bei Stuttgart (Baden-Württemberg)</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Verantwortlich für Geschäftsentwicklung und Lagermanagement – Bereichsleiter-Ebene für Lager-/Distributionslogistik bei der Thüringer Spedition.</t>
+          <t>Inhabergeführte Speditions- und Logistikgesellschaft im Raum Stuttgart/Backnang, Familienunternehmen (Geschäftsführung, Verkaufs- und Dispositionsleitung sämtlich Familie Grimmeißen).</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>https://www.lkt-thiele.com/unternehmen/team/</t>
+          <t>https://www.ewo-logistics.com/ewo-logistics-backnang-stuttgart-badenwuerttemberg-deutschland/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Stephan Voigt</t>
+          <t>Doris Grimmeißen</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer</t>
+          <t>CEO – Geschäftsführerin</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>s.voigt@lkt-thiele.com</t>
+          <t>doris.grimmeissen@ewo-logistics.com</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>+49 36373 129831-13</t>
+          <t>+49 7191 969 93 20</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>LOGISTIK KONTOR GmbH (LKT Thiele)</t>
+          <t>E.W.O Logistics GmbH</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -2360,44 +2360,44 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Buttstädt (Thüringen)</t>
+          <t>Backnang bei Stuttgart (Baden-Württemberg)</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Seit 2004 tätige mittelständische Spedition mit Sitz Vor dem Lohe 5, 99628 Buttstädt und Niederlassung Wiebelsheim; nationale/internationale Transporte, Lagerung, Charterverkehr.</t>
+          <t>Zweite Geschäftsführerin des inhabergeführten Logistikunternehmens im Rems-Murr-Kreis.</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>https://www.lkt-thiele.com/unternehmen/team/ | https://www.lkt-thiele.com/</t>
+          <t>https://www.ewo-logistics.com/ewo-logistics-backnang-stuttgart-badenwuerttemberg-deutschland/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>David Liedhegener</t>
+          <t>Anja Hollenhorst</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführender Gesellschafter</t>
+          <t>Geschäftsführerin (lt. Impressum; auf der Website Ansprechpartnerin Kundenservice)</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>d.liedhegener@liedhegener-logistik.de</t>
+          <t>anja@hti-spedition.de</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>02933 - 9 22 22 10</t>
+          <t>+49 251 74787-0 (Zentrale, Durchwahlen 11-21)</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Liedhegener-Logistik GmbH &amp; Co. KG</t>
+          <t>HTI Spedition und Logistik GmbH</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -2407,44 +2407,44 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Sundern (Sauerland)</t>
+          <t>Münster (NRW)</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Inhabergeführter Logistikdienstleister mit Transport, Verladung und Lagerlogistik im Sauerland. Familie Liedhegener (David und Sandra Liedhegener) in Geschäftsführung und Verwaltung.</t>
+          <t>Familiengeführte Spedition (Familie Hollenhorst) mit Fernverkehr, Luft-/Seefracht inkl. Zollabwicklung, Lager und Status Reglementierter Beauftragter. Zoll-, Fracht- und Dispositionsprozesse mit hohem Dokumentenaufkommen — gutes Feld für Prozessautomatisierung und Systemanbindung.</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>https://www.liedhegener-logistik.de/kontakt | https://www.regiomanager.de/suedwestfalen/ranking/mobilitaet-logistik/spedition-und-logistik/hochsauerlandkreis/</t>
+          <t>https://hti-spedition.de/ | https://hti-spedition.de/impressum/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Jakob Riesen</t>
+          <t>Klaus Hüttemann</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer</t>
+          <t>Geschäftsführer / geschäftsführender Gesellschafter (2. Generation)</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>j.riesen@mbi-spedition.de</t>
+          <t>k.huettemann@huelog.de</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>+49 (521) 93 803 - 0</t>
+          <t>+49 2065 909116</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>MBI Internationale Spedition GmbH</t>
+          <t>HUETTEMANN Logistik GmbH (HUETTEMANN Group)</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -2454,44 +2454,44 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Bielefeld</t>
+          <t>Duisburg</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Familiengeführte internationale Spedition mit Kontraktlogistik, Lagerung, Kommissionierung und Zollabwicklung. Zwei Geschäftsführer aus der Familie Riesen (Jakob und Peter Riesen).</t>
+          <t>Inhabergeführte Logistikgruppe aus Duisburg mit Kontraktlogistik, Lagerlogistik, Hafenumschlag und Transport. Klaus Hüttemann führt die Gruppe in zweiter Generation als geschäftsführender Gesellschafter.</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>https://www.mbi-spedition.de/unser-team/ | https://www.mbi-spedition.de/</t>
+          <t>https://www.huettemann-logistik.de/unternehmensgruppe/management/ | https://www.regiomanager.de/revier/ranking/mobilitaet-logistik/spedition-und-logistik/duisburg/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Christof Mielke</t>
+          <t>Hanjo Heinen</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführung</t>
+          <t>Geschäftsführer</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>mielke@mielke-logistik.de</t>
+          <t>hanjo.heinen@heinen-ht.de</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>0271 / 37514-0</t>
+          <t>nicht öffentlich</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Mielke Logistik GmbH</t>
+          <t>Heinen Transport GmbH (Heinen Gruppe: HT, HLS, HHL, HSK, HHV, HG)</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -2501,44 +2501,44 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Freudenberg (Siegerland)</t>
+          <t>Meerbusch (Hauptsitz), Logistikzentrum Duisburg</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Familiengeführte Spedition mit Schwer-/Spezialtransport, Disposition national und international sowie Lagerstandorten (u. a. Außenlager Netphen). Zweite Generation (Tim Christopher Mielke) bereits in der Geschäftsführung.</t>
+          <t>Familiengeführte Transport- und Logistikgruppe im Rheinland mit Logistikzentrum in Duisburg, Speditions-, Lager- und Kontraktlogistikgesellschaften. Weitere Entscheider: Pascal Heinen (Prokurist / Leitung Logistik, pascal.heinen@heinen-ht.de), Sabine Heinen (Prokuristin, sabine.heinen@heinen-ht.de).</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>https://www.mielke-logistik.de/ansprechpartner | https://www.regiomanager.de/suedwestfalen/ranking/mobilitaet-logistik/spedition-und-logistik/kreis-siegen-wittgenstein/</t>
+          <t>https://www.heinen-transport-gmbh.de/ansprechpartner | https://www.heinen-transport-gmbh.de/impressum</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>René Langen</t>
+          <t>Ludger Henke</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsleitung</t>
+          <t>Geschäftsführung</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>r.langen@speditionlangen.de</t>
+          <t>l.henke@henke-spedition.de</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>+49 2166 9539-0</t>
+          <t>+49 5250 9850-0</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Paul Langen GmbH &amp; Co. KG</t>
+          <t>Heinrich Henke Güterfernverkehr und Spedition GmbH &amp; Co.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -2548,44 +2548,44 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Mönchengladbach</t>
+          <t>Delbrück (Kreis Paderborn)</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Familienunternehmen seit 1883 mit Spedition, Lagerlogistik und Möbel-/Sperrgutlogistik, europaweite Distribution ab Mönchengladbach.</t>
+          <t>Familienspedition in dritter Generation mit Fernverkehr, Disposition und Lagerlogistik im Raum Paderborn. Mehrere Familienmitglieder (Ludger, Ludgerus, Regina Henke) im Unternehmen tätig.</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>https://www.speditionlangen.de/kontakt | https://www.regiomanager.de/ranking/mobilitaet-logistik/spedition-und-logistik/moenchengladbach/</t>
+          <t>https://www.henke-spedition.de/kontakt | https://www.regiomanager.de/ostwestfalen/ranking/mobilitaet-logistik/spedition-und-logistik/kreis-paderborn/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Benjamin Peelen</t>
+          <t>Bernd Specht</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer (Peelen Logistik GmbH)</t>
+          <t>Geschäftsführer</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>benjamin.peelen@peelen.de</t>
+          <t>b.specht@wichmann-transporte.de</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>+49 2843 9597-114 (Peelen Logistik GmbH, Rheinberg)</t>
+          <t>+49 5481/808-51</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Peelen Transporte GmbH / Peelen Logistik GmbH</t>
+          <t>Heinrich Wichmann Transporte GmbH</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -2595,44 +2595,44 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Duisburg (Betriebshof) / Rheinberg (Logistikzentrum Niederrhein)</t>
+          <t>Lengerich (Kreis Steinfurt)</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Familiengeführte Transport- und Logistikgruppe am Niederrhein mit eigenem Fuhrpark, Warehouse (LZN Rheinberg) und Kontraktlogistik.</t>
+          <t>Mittelständisches Transportunternehmen mit eigener Werkstatt, Disposition und Fuhrparkmanagement im nördlichen Münsterland.</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>https://www.peelen.de/kontakt | https://www.regiomanager.de/revier/ranking/mobilitaet-logistik/spedition-und-logistik/duisburg/</t>
+          <t>https://www.wichmann-transporte.de/kontakt | https://www.regiomanager.de/muensterland/ranking/mobilitaet-logistik/spedition-und-logistik/kreis-steinfurt/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Florian Meyer</t>
+          <t>Peter Plank</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführung / Logistik- und Lagerleitung</t>
+          <t>Vorsitzender Geschäftsführer / Inhaber</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>florian.meyer@rdllogistik.de</t>
+          <t>peterplank@hellmold-plank.de</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>+49 (0)2151 36806-16</t>
+          <t>+49 641 95201-16</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>RDL Logistik Rheinische Distributions- und Lagerlogistik GmbH</t>
+          <t>Hellmold &amp; Plank GmbH &amp; Co. KG Spedition</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -2642,44 +2642,44 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Krefeld (Niederrhein, NRW), zweiter Standort Willich</t>
+          <t>Gießen (Europastr. 7+9, 35394), Hessen</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>Inhabergeführter Lager- und Distributionslogistiker am Niederrhein (seit 2000) mit Lagerlogistik, Distribution und Fuhrpark an zwei Standorten. Geschäftsführung leitet operativ Lager und Abrechnung selbst — Digitalisierung von Lagerverwaltung, Disposition und Abrechnung ist unmittelbar chef-relevant.</t>
+          <t>1904 gegründete, inhabergeführte hessische Spedition (seit 1996 im Alleinbesitz der Familie Plank) mit Systemverkehren, Fernverkehr und Lagerlogistik; zweite Generation (Niklas Plank) in der Geschäftsführung.</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>https://rdllogistik.de/ueber-uns/ | https://rdllogistik.de/ | https://rdllogistik.de/impressum/</t>
+          <t>https://www.hellmold-plank.de/de/kontakt | https://www.hellmold-plank.de/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Udo Feldmann</t>
+          <t>Oliver Hüer</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Leitung Disposition Landmaschinen &amp; Prokurist</t>
+          <t>Geschäftsführer</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>feldmann@reiling-logistik.de</t>
+          <t>oliver@hueer.com</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>05247/9837-14</t>
+          <t>0251 87189-130</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Reiling Logistik GmbH &amp; Co. KG</t>
+          <t>Hüer Transport und Logistik GmbH</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -2689,44 +2689,44 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Harsewinkel (Kreis Gütersloh)</t>
+          <t>Münster</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Inhabergeführte Logistikgruppe (Geschäftsführer Christian Reiling und Carsten Mannefeld) mit Schüttgut-, Landmaschinen- und Kommunallogistik. Persönliche E-Mail der Geschäftsführer nicht eindeutig belegt, daher Prokurist als Ansprechpartner.</t>
+          <t>Inhabergeführte Spedition in Münster mit Nahverkehr, Kurierdienst und Logistikdienstleistungen. Familienstruktur: Oliver Hüer (GF) und Patrycja Hüer (Prokuristin).</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>https://www.reiling-logistik.de | https://www.regiomanager.de/ostwestfalen/ranking/mobilitaet-logistik/spedition-und-logistik/kreis-guetersloh/</t>
+          <t>https://www.hueer.com/kontakt | https://www.hueer.com/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Michael Hoeper</t>
+          <t>Ingo Kaiser</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer</t>
+          <t>Geschäftsführung (Management)</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>hoeper@hoeper-spedition.de</t>
+          <t>ingo.kaiser@ikg-spedition.de</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>02862-418327-10</t>
+          <t>+49 7223 281689-19</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Richard Hoeper GmbH &amp; Co. KG (Hoeper Spedition)</t>
+          <t>IKG Spedition GmbH</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -2736,44 +2736,44 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Südlohn-Oeding (Westmünsterland, NRW)</t>
+          <t>Baden-Baden / Sinzheim, Baden-Württemberg</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>Familienunternehmen in zweiter Generation mit Transporten, eigenem Fuhrpark, Lagerlogistik und Palettenmanagement im Westmünsterland. Kleinerer, aber voll ausgebauter Betrieb mit Dispo-, QM- und Projektmanagement-Funktionen; Hinweis: liegt vermutlich unterhalb der 50-Mitarbeiter-Schwelle.</t>
+          <t>Familiengeführte Spedition (Ingo und Kristina Kaiser) mit intermodalen Transporten Richtung Italien/Frankreich/Schweiz, eigenem Lager und Fuhrpark sowie Niederlassung in Busto Arsizio.</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>https://hoeper-spedition.de/team/ | https://hoeper-spedition.de/ | https://hoeper-spedition.de/impressum/</t>
+          <t>https://www.ikg-spedition.de/team/ | https://www.ikg-spedition.de/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Tanja Meininghaus</t>
+          <t>Joachim Berends</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführerin</t>
+          <t>Geschäftsführer</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>tanja.meininghaus@sitra-spedition.de</t>
+          <t>j.berends@bentheimer-eisenbahn.de</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>+49 40 751006-0 (Zentrale)</t>
+          <t>+49 5921 8034-0</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>SITRA Spedition GmbH</t>
+          <t>Kraftverkehr Emsland GmbH</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -2783,44 +2783,44 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Hamburg</t>
+          <t>Nordhorn, Niedersachsen</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Inhabergeführte Hamburger Spedition mit nationalen Stückgut-/Ladungsverkehren, internationalem Geschäft und eigener Disposition; bewusst als persönlich erreichbare Alternative zu Konzernen positioniert.</t>
+          <t>Geschäftsführer der Kraftverkehr Emsland GmbH (Spedition/Logistiklager der Bentheimer Eisenbahn-Gruppe). Hinweis: die auf der Ansprechpartner-Seite genannte E-Mail läuft über die Domain der Muttergesellschaft.</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>https://sitra-spedition.de/team/ | https://sitra-spedition.de/</t>
+          <t>https://www.kraftverkehr-emsland.de/kontakt/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Mike Forker</t>
+          <t>Marco Oppermann</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführender Gesellschafter</t>
+          <t>Speditionsleitung &amp; Prokurist</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>forker@sachsenland-gmbh.de</t>
+          <t>marco.oppermann@kraftverkehr-emsland.de</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>+49 351 799010</t>
+          <t>+49 5921 8034-96</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Sachsenland Transport &amp; Logistik GmbH</t>
+          <t>Kraftverkehr Emsland GmbH</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -2830,44 +2830,44 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Dresden (Sachsen)</t>
+          <t>Nordhorn, Niedersachsen</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>Selbstbeschreibung: 'Wir sind ein mittelständisches, inhabergeführtes Transport- und Logistikunternehmen'. Sitz Magdeburger Straße 58, 01067 Dresden, weitere Standorte Duisburg, Vilnius, Kiew; Transport, Lager, Zoll, Air &amp; Sea.</t>
+          <t>Mittelständische Spedition mit Sammelgut, Ladungsverkehren und eigenem Warehousing-Bereich; Prokurist und Speditionsleiter mit Entscheidungsbefugnis über Prozesse/IT-Themen.</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>https://www.sachsenland-gmbh.de/kontakt-dresden/ | https://www.sachsenland-gmbh.de/</t>
+          <t>https://www.kraftverkehr-emsland.de/kontakt/ | https://www.kraftverkehr-emsland.de/spedition-logistiklager/</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Sandra Aleksanderek</t>
+          <t>Lena Milde</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführung</t>
+          <t>Standort-/Niederlassungsleitung Magdeburg</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>sandra.aleksanderek@sander-logistics.de</t>
+          <t>lena.milde@krage-gerloff.de</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>+49 40 73354-128</t>
+          <t>+49 39424 951 0 (Zentrale Schwanebeck)</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Sander Logistics GmbH</t>
+          <t>Krage &amp; Gerloff Logistik GmbH</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -2877,44 +2877,44 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Hamburg (Altenwerder), weitere Standorte Itzehoe und Rostock</t>
+          <t>Magdeburg (Sachsen-Anhalt)</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Mittelständisches, familiengeführtes Logistikunternehmen mit Sammelgut, Komplettladungen, Seefracht sowie Lager-, Beschaffungs- und Kontraktlogistik an fünf Standorten.</t>
+          <t>1995 gegründeter Logistikdienstleister mit Hauptsitz Schwanebeck und Logistikstandort Tucheimer Straße 5, 39126 Magdeburg; Lager- und Transportlogistik.</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>https://sander-logistics.de/ihre-ansprechpartner/ | https://sander-logistics.de/kontakt/</t>
+          <t>https://www.krage-gerloff.de/magdeburg</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Markus Baur</t>
+          <t>Andreas Köhler</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer / Leiter Finanz- und Lohnbuchhaltung</t>
+          <t>Geschäftsführer</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>m.baur@spedition-baur.de</t>
+          <t>a.koehler@koehler-transport.de</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>+49 7371 9515 20</t>
+          <t>+49 221 96640-10</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Spedition Anton Baur GmbH</t>
+          <t>KÖHLER GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -2924,44 +2924,44 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Ertingen (Baden-Württemberg)</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>Familiengeführte Spedition in 88521 Ertingen mit Niederlassung Stuttgart (A. Baur Mineralöl-Abfertigungsspedition). Schwerpunkte Fernverkehr, Schüttgut-/Kipper-/Schubbodentransporte, Kran- und Baustofflogistik sowie Mineralöltransporte.</t>
+          <t>Inhabergeführtes Familienunternehmen in Köln mit Transport, Lager und eigener Werkstatt. Etwas unterhalb der Zielgröße, aber klar mittelständisch und inhabergeführt.</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>https://www.spedition-baur.de/team</t>
+          <t>https://www.koehler-transport.com/ansprechpartner | https://www.koehler-transport.com/</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Thomas Baur</t>
+          <t>Alexander Schwarz</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer / Abrechnung Baustoff- und Holztransporte</t>
+          <t>Business Development Manager &amp; Lager Management</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>t.baur@spedition-baur.de</t>
+          <t>a.schwarz@lkt-thiele.com</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>+49 7371 9515 10</t>
+          <t>+49 36373 129831-20</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Spedition Anton Baur GmbH</t>
+          <t>LOGISTIK KONTOR GmbH (LKT Thiele)</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -2971,24 +2971,24 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Ertingen (Baden-Württemberg)</t>
+          <t>Buttstädt (Thüringen)</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Zweiter Geschäftsführer des inhabergeführten Familienbetriebs (Zentrale Industriestraße 8, 88521 Ertingen). Zusätzlich Prokuristen Adrian und Tobias Baur im Unternehmen.</t>
+          <t>Verantwortlich für Geschäftsentwicklung und Lagermanagement – Bereichsleiter-Ebene für Lager-/Distributionslogistik bei der Thüringer Spedition.</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>https://www.spedition-baur.de/team</t>
+          <t>https://www.lkt-thiele.com/unternehmen/team/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Frank Blodt</t>
+          <t>Stephan Voigt</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -2998,17 +2998,17 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>frankblodt@spedition-blodt.de</t>
+          <t>s.voigt@lkt-thiele.com</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>+49 6131 25007-0</t>
+          <t>+49 36373 129831-13</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Spedition Blodt GmbH</t>
+          <t>LOGISTIK KONTOR GmbH (LKT Thiele)</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -3018,44 +3018,44 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Mainz, Rheinland-Pfalz</t>
+          <t>Buttstädt (Thüringen)</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>Familiengeführte Spedition in Mainz mit Transport, Lagerlogistik und Projektmanagement; Geschäftsführung und Lagerlogistik liegen in der Familie Blodt.</t>
+          <t>Seit 2004 tätige mittelständische Spedition mit Sitz Vor dem Lohe 5, 99628 Buttstädt und Niederlassung Wiebelsheim; nationale/internationale Transporte, Lagerung, Charterverkehr.</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>https://spedition-blodt.de/unser-team/</t>
+          <t>https://www.lkt-thiele.com/unternehmen/team/ | https://www.lkt-thiele.com/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Miriam Blodt</t>
+          <t>David Liedhegener</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführerin</t>
+          <t>Geschäftsführender Gesellschafter</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>miriamblodt@spedition-blodt.de</t>
+          <t>d.liedhegener@liedhegener-logistik.de</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>+49 6131 25007-0</t>
+          <t>02933 - 9 22 22 10</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Spedition Blodt GmbH</t>
+          <t>Liedhegener-Logistik GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -3065,24 +3065,24 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Mainz, Rheinland-Pfalz</t>
+          <t>Sundern (Sauerland)</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Zweite Geschäftsführerin des inhabergeführten Mainzer Speditions- und Lagerlogistikbetriebs.</t>
+          <t>Inhabergeführter Logistikdienstleister mit Transport, Verladung und Lagerlogistik im Sauerland. Familie Liedhegener (David und Sandra Liedhegener) in Geschäftsführung und Verwaltung.</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>https://spedition-blodt.de/unser-team/</t>
+          <t>https://www.liedhegener-logistik.de/kontakt | https://www.regiomanager.de/suedwestfalen/ranking/mobilitaet-logistik/spedition-und-logistik/hochsauerlandkreis/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Bernd Häger</t>
+          <t>Jakob Riesen</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3092,17 +3092,17 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>bhaeger@spedition-haeger.de</t>
+          <t>j.riesen@mbi-spedition.de</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>02904 9740-0</t>
+          <t>+49 (521) 93 803 - 0</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Spedition Häger GmbH &amp; Co. KG / Häger Transporte u. Logistik GmbH &amp; Co. KG</t>
+          <t>MBI Internationale Spedition GmbH</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -3112,44 +3112,44 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Bestwig (Sauerland, NRW)</t>
+          <t>Bielefeld</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>Familiengeführte Sauerland-Spedition mit Transport-, Lager- und Kontraktlogistik über zwei Schwestergesellschaften. Zwei-Firmen-Struktur und gewachsene Dispositions-/Lagerprozesse sprechen für manuelle Abläufe mit Digitalisierungs- und Systemintegrationsbedarf.</t>
+          <t>Familiengeführte internationale Spedition mit Kontraktlogistik, Lagerung, Kommissionierung und Zollabwicklung. Zwei Geschäftsführer aus der Familie Riesen (Jakob und Peter Riesen).</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>https://www.spedition-haeger.de/kontakt/</t>
+          <t>https://www.mbi-spedition.de/unser-team/ | https://www.mbi-spedition.de/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Gregor Roes</t>
+          <t>Christof Mielke</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer</t>
+          <t>Geschäftsführung</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>g.roes@spedition-hoevelmann.de</t>
+          <t>mielke@mielke-logistik.de</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>+49 2851 962-121</t>
+          <t>0271 / 37514-0</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Spedition Hövelmann GmbH &amp; Co. KG</t>
+          <t>Mielke Logistik GmbH</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -3159,24 +3159,24 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Rees (Niederrhein)</t>
+          <t>Freudenberg (Siegerland)</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Familiengeführte Niederrhein-Spedition mit Transport-, Lager- und Kontraktlogistik. Weitere Entscheider: Markus Hövelmann (Gesellschafter, m.hoevelmann@spedition-hoevelmann.de), Ricarda Hövelmann (Gesellschafterin, r.hoevelmann@spedition-hoevelmann.de), Jörg Möllenbeck (Prokurist, j.moellenbeck@spedition-hoevelmann.de).</t>
+          <t>Familiengeführte Spedition mit Schwer-/Spezialtransport, Disposition national und international sowie Lagerstandorten (u. a. Außenlager Netphen). Zweite Generation (Tim Christopher Mielke) bereits in der Geschäftsführung.</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>https://www.spedition-hoevelmann.de/kontakt</t>
+          <t>https://www.mielke-logistik.de/ansprechpartner | https://www.regiomanager.de/suedwestfalen/ranking/mobilitaet-logistik/spedition-und-logistik/kreis-siegen-wittgenstein/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Verena Wiechers</t>
+          <t>René Langen</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3186,17 +3186,17 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>v.wiechers@wiechers-spedition.de</t>
+          <t>r.langen@speditionlangen.de</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>+49 234 94338-27</t>
+          <t>+49 2166 9539-0</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Spedition Josef Wiechers GmbH (WIECHERS Spedition + Logistik)</t>
+          <t>Paul Langen GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -3206,44 +3206,44 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Bochum (Hauptsitz), Standort Duisburg</t>
+          <t>Mönchengladbach</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>Familiengeführte Spedition aus Bochum mit Standort Duisburg, Schwerpunkt Transport-, Lager- und Distributionslogistik im Ruhrgebiet. Zusätzlicher Ansprechpartner: Markus Koch (Speditionsleitung, Prokurist), m.koch@wiechers-spedition.de.</t>
+          <t>Familienunternehmen seit 1883 mit Spedition, Lagerlogistik und Möbel-/Sperrgutlogistik, europaweite Distribution ab Mönchengladbach.</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>https://www.wiechers-spedition.de/kontakt | https://www.regiomanager.de/ranking/mobilitaet-logistik/spedition-und-logistik/bochum/</t>
+          <t>https://www.speditionlangen.de/kontakt | https://www.regiomanager.de/ranking/mobilitaet-logistik/spedition-und-logistik/moenchengladbach/</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Dr. Christine Kollmannsberger</t>
+          <t>Benjamin Peelen</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsleitung / Geschäftsführerin</t>
+          <t>Geschäftsführer (Peelen Logistik GmbH)</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>C.Kollmannsberger@spedition-kollmannsberger.de</t>
+          <t>benjamin.peelen@peelen.de</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>+49 8456 966-212</t>
+          <t>+49 2843 9597-114 (Peelen Logistik GmbH, Rheinberg)</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Spedition Kollmannsberger KG</t>
+          <t>Peelen Transporte GmbH / Peelen Logistik GmbH</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -3253,44 +3253,44 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Großmehring bei Ingolstadt (Bayern)</t>
+          <t>Duisburg (Betriebshof) / Rheinberg (Logistikzentrum Niederrhein)</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Zweite Person der Geschäftsleitung des Familienunternehmens; Dispositionsleitung Helmut Atzmüller ebenfalls mit persönlicher Adresse gelistet.</t>
+          <t>Familiengeführte Transport- und Logistikgruppe am Niederrhein mit eigenem Fuhrpark, Warehouse (LZN Rheinberg) und Kontraktlogistik.</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>https://www.spedition-kollmannsberger.de/spedition-ansprechpartner</t>
+          <t>https://www.peelen.de/kontakt | https://www.regiomanager.de/revier/ranking/mobilitaet-logistik/spedition-und-logistik/duisburg/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Ludwig Kollmannsberger</t>
+          <t>Florian Meyer</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsleitung / Geschäftsführer</t>
+          <t>Geschäftsführung / Logistik- und Lagerleitung</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>L.Kollmannsberger@spedition-kollmannsberger.de</t>
+          <t>florian.meyer@rdllogistik.de</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>+49 8456 966-211</t>
+          <t>+49 (0)2151 36806-16</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Spedition Kollmannsberger KG</t>
+          <t>RDL Logistik Rheinische Distributions- und Lagerlogistik GmbH</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -3300,44 +3300,44 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Großmehring bei Ingolstadt (Bayern)</t>
+          <t>Krefeld (Niederrhein, NRW), zweiter Standort Willich</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>Familiengeführte Spedition im InTerPark Ingolstadt (Dieselstraße 6, 85098 Großmehring) mit Transport-, Lager- und Distributionslogistik für den Raum Ingolstadt/Oberbayern.</t>
+          <t>Inhabergeführter Lager- und Distributionslogistiker am Niederrhein (seit 2000) mit Lagerlogistik, Distribution und Fuhrpark an zwei Standorten. Geschäftsführung leitet operativ Lager und Abrechnung selbst — Digitalisierung von Lagerverwaltung, Disposition und Abrechnung ist unmittelbar chef-relevant.</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>https://www.spedition-kollmannsberger.de/spedition-ansprechpartner | https://www.spedition-kollmannsberger.de/</t>
+          <t>https://rdllogistik.de/ueber-uns/ | https://rdllogistik.de/ | https://rdllogistik.de/impressum/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Jürgen Frömberg</t>
+          <t>Udo Feldmann</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer</t>
+          <t>Leitung Disposition Landmaschinen &amp; Prokurist</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>jFroemberg@spedition-maier.de</t>
+          <t>feldmann@reiling-logistik.de</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>+49 7731 828-201</t>
+          <t>05247/9837-14</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Spedition Maier GmbH</t>
+          <t>Reiling Logistik GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -3347,44 +3347,44 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Singen (Hohentwiel), Baden-Württemberg</t>
+          <t>Harsewinkel (Kreis Gütersloh)</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>Mittelständische Spedition mit Standorten Singen, Pfullendorf und Ramsen (CH). Sammelgut, Charterverkehr, Zollabwicklung sowie eigene Lagerlogistik mit mehreren Betriebs- und Standortleitern.</t>
+          <t>Inhabergeführte Logistikgruppe (Geschäftsführer Christian Reiling und Carsten Mannefeld) mit Schüttgut-, Landmaschinen- und Kommunallogistik. Persönliche E-Mail der Geschäftsführer nicht eindeutig belegt, daher Prokurist als Ansprechpartner.</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>https://www.spedition-maier.de/team/</t>
+          <t>https://www.reiling-logistik.de | https://www.regiomanager.de/ostwestfalen/ranking/mobilitaet-logistik/spedition-und-logistik/kreis-guetersloh/</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Thomas Marizzi</t>
+          <t>Michael Hoeper</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsleitung – Speditionsleitung</t>
+          <t>Geschäftsführer</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>tMarizzi@spedition-maier.de</t>
+          <t>hoeper@hoeper-spedition.de</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>+49 7731 828-188</t>
+          <t>02862-418327-10</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Spedition Maier GmbH</t>
+          <t>Richard Hoeper GmbH &amp; Co. KG (Hoeper Spedition)</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -3394,44 +3394,44 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Singen (Hohentwiel), Baden-Württemberg</t>
+          <t>Südlohn-Oeding (Westmünsterland, NRW)</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>Mitglied der Geschäftsleitung mit Verantwortung für den Speditionsbereich; kaufmännische Leitung Jochen Sigg (jsigg@spedition-maier.de) ebenfalls auf derselben Seite belegt.</t>
+          <t>Familienunternehmen in zweiter Generation mit Transporten, eigenem Fuhrpark, Lagerlogistik und Palettenmanagement im Westmünsterland. Kleinerer, aber voll ausgebauter Betrieb mit Dispo-, QM- und Projektmanagement-Funktionen; Hinweis: liegt vermutlich unterhalb der 50-Mitarbeiter-Schwelle.</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>https://www.spedition-maier.de/team/</t>
+          <t>https://hoeper-spedition.de/team/ | https://hoeper-spedition.de/ | https://hoeper-spedition.de/impressum/</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Nicole Körtge</t>
+          <t>Tanja Meininghaus</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Leitung Auftragsmanagement/Logistik</t>
+          <t>Geschäftsführerin</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>nicolekoertge@spedition-wagner.net</t>
+          <t>tanja.meininghaus@sitra-spedition.de</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>+49 2642 9022922</t>
+          <t>+49 40 751006-0 (Zentrale)</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Spedition Wagner GmbH</t>
+          <t>SITRA Spedition GmbH</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -3441,44 +3441,44 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Remagen (Am Römerhof 60, 53424), Rheinland-Pfalz</t>
+          <t>Hamburg</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>Familiengeführter Logistikdienstleister mit Kontraktlogistik für die Getränkeindustrie (u. a. Krombacher), Lagerlogistik, Displaybau und eigenem Fuhrpark. Geschäftsführung (Arlt/Gaßner/Kröhl) ohne öffentliche E-Mail – Bereichsleitung Logistik als Entscheidungsträger.</t>
+          <t>Inhabergeführte Hamburger Spedition mit nationalen Stückgut-/Ladungsverkehren, internationalem Geschäft und eigener Disposition; bewusst als persönlich erreichbare Alternative zu Konzernen positioniert.</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>https://spedition-wagner.net/unternehmen/team/</t>
+          <t>https://sitra-spedition.de/team/ | https://sitra-spedition.de/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Matthias Schork</t>
+          <t>Mike Forker</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer</t>
+          <t>Geschäftsführender Gesellschafter</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>m.schork@wuest.com</t>
+          <t>forker@sachsenland-gmbh.de</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>+49 9141 8684-140</t>
+          <t>+49 351 799010</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Spedition Wüst (Wüst GmbH &amp; Co. KG)</t>
+          <t>Sachsenland Transport &amp; Logistik GmbH</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -3488,44 +3488,44 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Weißenburg i. Bay., weiteres Logistikzentrum Ansbach, Bayern</t>
+          <t>Dresden (Sachsen)</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>Mittelständische bayerische Spedition mit Stückgut- und Ladungsverkehren sowie zwei eigenen Logistikzentren (Lagerung, Kommissionierung, Value Added Services).</t>
+          <t>Selbstbeschreibung: 'Wir sind ein mittelständisches, inhabergeführtes Transport- und Logistikunternehmen'. Sitz Magdeburger Straße 58, 01067 Dresden, weitere Standorte Duisburg, Vilnius, Kiew; Transport, Lager, Zoll, Air &amp; Sea.</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>https://www.wuest.com/kontakt/ | https://www.wuest.com/</t>
+          <t>https://www.sachsenland-gmbh.de/kontakt-dresden/ | https://www.sachsenland-gmbh.de/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Michael Müller</t>
+          <t>Sandra Aleksanderek</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Logistikleiter</t>
+          <t>Geschäftsführung</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>m.mueller@wuest.com</t>
+          <t>sandra.aleksanderek@sander-logistics.de</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>+49 9141 8684-106</t>
+          <t>+49 40 73354-128</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Spedition Wüst (Wüst GmbH &amp; Co. KG)</t>
+          <t>Sander Logistics GmbH</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -3535,44 +3535,44 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Weißenburg i. Bay., Bayern</t>
+          <t>Hamburg (Altenwerder), weitere Standorte Itzehoe und Rostock</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>Verantwortlicher für die Logistikzentren Weißenburg und Ansbach – direkter Entscheider für Lager-/Kontraktlogistikprozesse.</t>
+          <t>Mittelständisches, familiengeführtes Logistikunternehmen mit Sammelgut, Komplettladungen, Seefracht sowie Lager-, Beschaffungs- und Kontraktlogistik an fünf Standorten.</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>https://www.wuest.com/kontakt/</t>
+          <t>https://sander-logistics.de/ihre-ansprechpartner/ | https://sander-logistics.de/kontakt/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Bernd Stratkötter</t>
+          <t>Markus Baur</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer, Auftragsmanagement &amp; Disposition</t>
+          <t>Geschäftsführer / Leiter Finanz- und Lohnbuchhaltung</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>bs@stratkoetter.de</t>
+          <t>m.baur@spedition-baur.de</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>02523 / 9200-12</t>
+          <t>+49 7371 9515 20</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Stratkötter Logistik + Transport GmbH &amp; Co. KG</t>
+          <t>Spedition Anton Baur GmbH</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -3582,44 +3582,44 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Wadersloh (Kreis Warendorf)</t>
+          <t>Ertingen (Baden-Württemberg)</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>Familienbetrieb mit drei Geschäftsführern aus der Familie Stratkötter (Werner, Bernd, Thomas), Schwerpunkt Auftragsmanagement, Disposition und Lagerlogistik im Münsterland.</t>
+          <t>Familiengeführte Spedition in 88521 Ertingen mit Niederlassung Stuttgart (A. Baur Mineralöl-Abfertigungsspedition). Schwerpunkte Fernverkehr, Schüttgut-/Kipper-/Schubbodentransporte, Kran- und Baustofflogistik sowie Mineralöltransporte.</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>https://www.stratkoetter.de/ansprechpartner | https://www.regiomanager.de/muensterland/ranking/mobilitaet-logistik/spedition-und-logistik/kreis-warendorf/</t>
+          <t>https://www.spedition-baur.de/team</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Ralf Greinert</t>
+          <t>Thomas Baur</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer</t>
+          <t>Geschäftsführer / Abrechnung Baustoff- und Holztransporte</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>ralf.greinert@teamlogistic.de</t>
+          <t>t.baur@spedition-baur.de</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>+49 2602 1309-0 (Zentrale)</t>
+          <t>+49 7371 9515 10</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>TEAM Logistic GmbH &amp; Co. KG</t>
+          <t>Spedition Anton Baur GmbH</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -3629,24 +3629,24 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Montabaur (Westerwaldstr. 2a, 56410), Rheinland-Pfalz</t>
+          <t>Ertingen (Baden-Württemberg)</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>Familiengeführte Spedition im Westerwald (Familie Greinert) mit eigener Disposition, Werkstatt und Verwaltung; Transporte national/international.</t>
+          <t>Zweiter Geschäftsführer des inhabergeführten Familienbetriebs (Zentrale Industriestraße 8, 88521 Ertingen). Zusätzlich Prokuristen Adrian und Tobias Baur im Unternehmen.</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>https://teamlogistic.de/ansprechpartner/ | https://teamlogistic.de/impressum/</t>
+          <t>https://www.spedition-baur.de/team</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Uwe Diel</t>
+          <t>Frank Blodt</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -3656,17 +3656,17 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>uwe.diel@teamlogistic.de</t>
+          <t>frankblodt@spedition-blodt.de</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>+49 2602 1309-0 (Zentrale)</t>
+          <t>+49 6131 25007-0</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>TEAM Logistic GmbH &amp; Co. KG</t>
+          <t>Spedition Blodt GmbH</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -3676,44 +3676,44 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Montabaur, Rheinland-Pfalz</t>
+          <t>Mainz, Rheinland-Pfalz</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>Zweiter Geschäftsführer der Team Logistic GmbH &amp; Co. KG, mittelständische Spedition mit eigenem Fuhrpark.</t>
+          <t>Familiengeführte Spedition in Mainz mit Transport, Lagerlogistik und Projektmanagement; Geschäftsführung und Lagerlogistik liegen in der Familie Blodt.</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>https://teamlogistic.de/ansprechpartner/</t>
+          <t>https://spedition-blodt.de/unser-team/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Manuel Keller</t>
+          <t>Miriam Blodt</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Bereichsleiter / Mitglied der Geschäftsleitung</t>
+          <t>Geschäftsführerin</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Manuel.Keller@teamlog.de</t>
+          <t>miriamblodt@spedition-blodt.de</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>+49 6021 1507-121</t>
+          <t>+49 6131 25007-0</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>TEAMLOG (Team Log GmbH &amp; Co. KG)</t>
+          <t>Spedition Blodt GmbH</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -3723,44 +3723,44 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Aschaffenburg (Bayern)</t>
+          <t>Mainz, Rheinland-Pfalz</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>Inhabergeführter Kontrakt- und Lagerlogistiker mit Zentrale Germanenstraße 30, 63741 Aschaffenburg und 15 Standorten im Rhein-Main-Gebiet.</t>
+          <t>Zweite Geschäftsführerin des inhabergeführten Mainzer Speditions- und Lagerlogistikbetriebs.</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>https://teamlog.de/kontakt/ | https://teamlog.de/</t>
+          <t>https://spedition-blodt.de/unser-team/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Theodor Schulz</t>
+          <t>Bernd Häger</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer (Disposition &amp; Kundenbetreuung)</t>
+          <t>Geschäftsführer</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>ts@schulz-spedition.de</t>
+          <t>bhaeger@spedition-haeger.de</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>+49 251 26333-211</t>
+          <t>02904 9740-0</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Theodor Schulz GmbH &amp; Co. KG (Schulz Spedition)</t>
+          <t>Spedition Häger GmbH &amp; Co. KG / Häger Transporte u. Logistik GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -3770,44 +3770,44 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Münster (NRW)</t>
+          <t>Bestwig (Sauerland, NRW)</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>Inhabergeführte Münsteraner Spedition mit Transport, Lagerung/Lagerverwaltung, Palettenmanagement und Abrechnung als eigene Abteilungen. Geschäftsführung sitzt selbst in der Disposition — kurze Entscheidungswege, viele manuell getriebene Dispo- und Abrechnungsprozesse als Digitalisierungsansatz.</t>
+          <t>Familiengeführte Sauerland-Spedition mit Transport-, Lager- und Kontraktlogistik über zwei Schwestergesellschaften. Zwei-Firmen-Struktur und gewachsene Dispositions-/Lagerprozesse sprechen für manuelle Abläufe mit Digitalisierungs- und Systemintegrationsbedarf.</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>https://www.schulz-spedition.de/ | https://www.schulz-spedition.de/#unternehmen</t>
+          <t>https://www.spedition-haeger.de/kontakt/</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Christian Vetten</t>
+          <t>Gregor Roes</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer (Ansprechpartner Transporte/Lagerlogistik)</t>
+          <t>Geschäftsführer</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>christian.vetten@vetten-gruppe.de</t>
+          <t>g.roes@spedition-hoevelmann.de</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>02162 5302-379</t>
+          <t>+49 2851 962-121</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Vetten Gruppe (Gebr. Vetten GmbH &amp; Co. KG)</t>
+          <t>Spedition Hövelmann GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -3817,44 +3817,44 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Mönchengladbach (Niederrhein, NRW)</t>
+          <t>Rees (Niederrhein)</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>Familienbetrieb seit 1931 mit Transport, Lagerlogistik, Textil- und Kontraktlogistik auf &gt;100.000 qm Lagerfläche. Gewachsene Gruppenstruktur mit mehreren Standorten, Variantenvielfalt (Textilaufbereitung, Kontraktlogistik) und vorhandener Logistik-IT (ecovium/SPEDION im Einsatz) — viel Potenzial für Prozessdigitalisierung und Schnittstellen-/ERP-Themen.</t>
+          <t>Familiengeführte Niederrhein-Spedition mit Transport-, Lager- und Kontraktlogistik. Weitere Entscheider: Markus Hövelmann (Gesellschafter, m.hoevelmann@spedition-hoevelmann.de), Ricarda Hövelmann (Gesellschafterin, r.hoevelmann@spedition-hoevelmann.de), Jörg Möllenbeck (Prokurist, j.moellenbeck@spedition-hoevelmann.de).</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>https://vetten-gruppe.de/kontakt/ | https://vetten-gruppe.de/ | https://vetten-gruppe.de/impressum/ | https://vetten-gruppe.de/die-vetten-gruppe/</t>
+          <t>https://www.spedition-hoevelmann.de/kontakt</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Dirk Schröder</t>
+          <t>Verena Wiechers</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer</t>
+          <t>Geschäftsleitung</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>dirk.schroeder@westfalia-intralog.com</t>
+          <t>v.wiechers@wiechers-spedition.de</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>+49 (0) 5221 - 1809 - 690</t>
+          <t>+49 234 94338-27</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>WESTFALIA intralog GmbH</t>
+          <t>Spedition Josef Wiechers GmbH (WIECHERS Spedition + Logistik)</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -3864,44 +3864,44 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Herford (OWL)</t>
+          <t>Bochum (Hauptsitz), Standort Duisburg</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>Kontraktlogistiker mit Standorten in Herford und Bremerhaven, Schwerpunkt Lager- und Value-Added-Services für Industriekunden.</t>
+          <t>Familiengeführte Spedition aus Bochum mit Standort Duisburg, Schwerpunkt Transport-, Lager- und Distributionslogistik im Ruhrgebiet. Zusätzlicher Ansprechpartner: Markus Koch (Speditionsleitung, Prokurist), m.koch@wiechers-spedition.de.</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>https://www.westfalia-intralog.de/kontakt | https://www.regiomanager.de/ostwestfalen-lippe/ranking/mobilitaet-logistik/spedition-und-logistik/kreis-herford/</t>
+          <t>https://www.wiechers-spedition.de/kontakt | https://www.regiomanager.de/ranking/mobilitaet-logistik/spedition-und-logistik/bochum/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Andreas Koch</t>
+          <t>Dr. Christine Kollmannsberger</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer</t>
+          <t>Geschäftsleitung / Geschäftsführerin</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>a.koch@eckhardt-logistik.de</t>
+          <t>C.Kollmannsberger@spedition-kollmannsberger.de</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>+49 711 80000-0 (Zentrale)</t>
+          <t>+49 8456 966-212</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Walter Eckhardt GmbH Spedition + Logistik</t>
+          <t>Spedition Kollmannsberger KG</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -3911,44 +3911,44 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Korntal-Münchingen (Raum Stuttgart), Baden-Württemberg</t>
+          <t>Großmehring bei Ingolstadt (Bayern)</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>Inhabergeführte Spedition seit 1987 mit Stückgut, Gefahrgut- und Pflanzentransporten sowie eigenem Lager-/Kommissionierzentrum (seit 2019). Eigene Bereiche für Umschlag, Lagerlogistik und Disposition.</t>
+          <t>Zweite Person der Geschäftsleitung des Familienunternehmens; Dispositionsleitung Helmut Atzmüller ebenfalls mit persönlicher Adresse gelistet.</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>https://eckhardt-logistik.de/kontakt/ansprechpartner | https://eckhardt-logistik.de/</t>
+          <t>https://www.spedition-kollmannsberger.de/spedition-ansprechpartner</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Marc Eckhardt</t>
+          <t>Ludwig Kollmannsberger</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Gesellschafter (Inhaberfamilie)</t>
+          <t>Geschäftsleitung / Geschäftsführer</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>m.eckhardt@eckhardt-logistik.de</t>
+          <t>L.Kollmannsberger@spedition-kollmannsberger.de</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>+49 711 80000-0 (Zentrale)</t>
+          <t>+49 8456 966-211</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Walter Eckhardt GmbH Spedition + Logistik</t>
+          <t>Spedition Kollmannsberger KG</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -3958,44 +3958,44 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Korntal-Münchingen (Raum Stuttgart), Baden-Württemberg</t>
+          <t>Großmehring bei Ingolstadt (Bayern)</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>Gesellschafter und Namensträger des familiengeführten Speditions- und Logistikunternehmens; zweiter Entscheidungsträger neben der Geschäftsführung.</t>
+          <t>Familiengeführte Spedition im InTerPark Ingolstadt (Dieselstraße 6, 85098 Großmehring) mit Transport-, Lager- und Distributionslogistik für den Raum Ingolstadt/Oberbayern.</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>https://eckhardt-logistik.de/kontakt/ansprechpartner | https://eckhardt-logistik.de/</t>
+          <t>https://www.spedition-kollmannsberger.de/spedition-ansprechpartner | https://www.spedition-kollmannsberger.de/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Dirk Valerius</t>
+          <t>Jürgen Frömberg</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführender Gesellschafter</t>
+          <t>Geschäftsführer</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>d.valerius@werneke.de</t>
+          <t>jFroemberg@spedition-maier.de</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>02922 / 8060 - 260</t>
+          <t>+49 7731 828-201</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Werneke Logistic GmbH &amp; Co. KG</t>
+          <t>Spedition Maier GmbH</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -4005,69 +4005,727 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Werl (Kreis Soest / Südwestfalen)</t>
+          <t>Singen (Hohentwiel), Baden-Württemberg</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>Inhabergeführter Logistikdienstleister mit Stückgut, Sammelgut, Charterverkehr und vier Lagerstandorten (Kontraktlogistik). Familie Werneke weiterhin im Unternehmen aktiv.</t>
+          <t>Mittelständische Spedition mit Standorten Singen, Pfullendorf und Ramsen (CH). Sammelgut, Charterverkehr, Zollabwicklung sowie eigene Lagerlogistik mit mehreren Betriebs- und Standortleitern.</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>https://www.werneke.de/ansprechpartner | https://www.regiomanager.de/suedwestfalen/ranking/mobilitaet-logistik/spedition-und-logistik/kreis-soest/</t>
+          <t>https://www.spedition-maier.de/team/</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>Thomas Marizzi</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsleitung – Speditionsleitung</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>tMarizzi@spedition-maier.de</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>+49 7731 828-188</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>Spedition Maier GmbH</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>Singen (Hohentwiel), Baden-Württemberg</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>Mitglied der Geschäftsleitung mit Verantwortung für den Speditionsbereich; kaufmännische Leitung Jochen Sigg (jsigg@spedition-maier.de) ebenfalls auf derselben Seite belegt.</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>https://www.spedition-maier.de/team/</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Nicole Körtge</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Leitung Auftragsmanagement/Logistik</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>nicolekoertge@spedition-wagner.net</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>+49 2642 9022922</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Spedition Wagner GmbH</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>Remagen (Am Römerhof 60, 53424), Rheinland-Pfalz</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>Familiengeführter Logistikdienstleister mit Kontraktlogistik für die Getränkeindustrie (u. a. Krombacher), Lagerlogistik, Displaybau und eigenem Fuhrpark. Geschäftsführung (Arlt/Gaßner/Kröhl) ohne öffentliche E-Mail – Bereichsleitung Logistik als Entscheidungsträger.</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>https://spedition-wagner.net/unternehmen/team/</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Matthias Schork</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführer</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>m.schork@wuest.com</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>+49 9141 8684-140</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>Spedition Wüst (Wüst GmbH &amp; Co. KG)</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>Weißenburg i. Bay., weiteres Logistikzentrum Ansbach, Bayern</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>Mittelständische bayerische Spedition mit Stückgut- und Ladungsverkehren sowie zwei eigenen Logistikzentren (Lagerung, Kommissionierung, Value Added Services).</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wuest.com/kontakt/ | https://www.wuest.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Michael Müller</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Logistikleiter</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>m.mueller@wuest.com</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>+49 9141 8684-106</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>Spedition Wüst (Wüst GmbH &amp; Co. KG)</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>Weißenburg i. Bay., Bayern</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>Verantwortlicher für die Logistikzentren Weißenburg und Ansbach – direkter Entscheider für Lager-/Kontraktlogistikprozesse.</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wuest.com/kontakt/</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>Bernd Stratkötter</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführer, Auftragsmanagement &amp; Disposition</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>bs@stratkoetter.de</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>02523 / 9200-12</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>Stratkötter Logistik + Transport GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>Wadersloh (Kreis Warendorf)</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>Familienbetrieb mit drei Geschäftsführern aus der Familie Stratkötter (Werner, Bernd, Thomas), Schwerpunkt Auftragsmanagement, Disposition und Lagerlogistik im Münsterland.</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>https://www.stratkoetter.de/ansprechpartner | https://www.regiomanager.de/muensterland/ranking/mobilitaet-logistik/spedition-und-logistik/kreis-warendorf/</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Ralf Greinert</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführer</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>ralf.greinert@teamlogistic.de</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>+49 2602 1309-0 (Zentrale)</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>TEAM Logistic GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>Montabaur (Westerwaldstr. 2a, 56410), Rheinland-Pfalz</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>Familiengeführte Spedition im Westerwald (Familie Greinert) mit eigener Disposition, Werkstatt und Verwaltung; Transporte national/international.</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>https://teamlogistic.de/ansprechpartner/ | https://teamlogistic.de/impressum/</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>Uwe Diel</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführer</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>uwe.diel@teamlogistic.de</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>+49 2602 1309-0 (Zentrale)</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>TEAM Logistic GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>Montabaur, Rheinland-Pfalz</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>Zweiter Geschäftsführer der Team Logistic GmbH &amp; Co. KG, mittelständische Spedition mit eigenem Fuhrpark.</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>https://teamlogistic.de/ansprechpartner/</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Manuel Keller</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Bereichsleiter / Mitglied der Geschäftsleitung</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Manuel.Keller@teamlog.de</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>+49 6021 1507-121</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>TEAMLOG (Team Log GmbH &amp; Co. KG)</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>Aschaffenburg (Bayern)</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>Inhabergeführter Kontrakt- und Lagerlogistiker mit Zentrale Germanenstraße 30, 63741 Aschaffenburg und 15 Standorten im Rhein-Main-Gebiet.</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>https://teamlog.de/kontakt/ | https://teamlog.de/</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>Theodor Schulz</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführer (Disposition &amp; Kundenbetreuung)</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>ts@schulz-spedition.de</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>+49 251 26333-211</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>Theodor Schulz GmbH &amp; Co. KG (Schulz Spedition)</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>Münster (NRW)</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>Inhabergeführte Münsteraner Spedition mit Transport, Lagerung/Lagerverwaltung, Palettenmanagement und Abrechnung als eigene Abteilungen. Geschäftsführung sitzt selbst in der Disposition — kurze Entscheidungswege, viele manuell getriebene Dispo- und Abrechnungsprozesse als Digitalisierungsansatz.</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>https://www.schulz-spedition.de/ | https://www.schulz-spedition.de/#unternehmen</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Christian Vetten</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführer (Ansprechpartner Transporte/Lagerlogistik)</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>christian.vetten@vetten-gruppe.de</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>02162 5302-379</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>Vetten Gruppe (Gebr. Vetten GmbH &amp; Co. KG)</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>Mönchengladbach (Niederrhein, NRW)</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>Familienbetrieb seit 1931 mit Transport, Lagerlogistik, Textil- und Kontraktlogistik auf &gt;100.000 qm Lagerfläche. Gewachsene Gruppenstruktur mit mehreren Standorten, Variantenvielfalt (Textilaufbereitung, Kontraktlogistik) und vorhandener Logistik-IT (ecovium/SPEDION im Einsatz) — viel Potenzial für Prozessdigitalisierung und Schnittstellen-/ERP-Themen.</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>https://vetten-gruppe.de/kontakt/ | https://vetten-gruppe.de/ | https://vetten-gruppe.de/impressum/ | https://vetten-gruppe.de/die-vetten-gruppe/</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Dirk Schröder</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführer</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>dirk.schroeder@westfalia-intralog.com</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>+49 (0) 5221 - 1809 - 690</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>WESTFALIA intralog GmbH</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>Herford (OWL)</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>Kontraktlogistiker mit Standorten in Herford und Bremerhaven, Schwerpunkt Lager- und Value-Added-Services für Industriekunden.</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>https://www.westfalia-intralog.de/kontakt | https://www.regiomanager.de/ostwestfalen-lippe/ranking/mobilitaet-logistik/spedition-und-logistik/kreis-herford/</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Andreas Koch</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführer</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>a.koch@eckhardt-logistik.de</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>+49 711 80000-0 (Zentrale)</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>Walter Eckhardt GmbH Spedition + Logistik</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>Korntal-Münchingen (Raum Stuttgart), Baden-Württemberg</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>Inhabergeführte Spedition seit 1987 mit Stückgut, Gefahrgut- und Pflanzentransporten sowie eigenem Lager-/Kommissionierzentrum (seit 2019). Eigene Bereiche für Umschlag, Lagerlogistik und Disposition.</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>https://eckhardt-logistik.de/kontakt/ansprechpartner | https://eckhardt-logistik.de/</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>Marc Eckhardt</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>Gesellschafter (Inhaberfamilie)</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>m.eckhardt@eckhardt-logistik.de</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>+49 711 80000-0 (Zentrale)</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>Walter Eckhardt GmbH Spedition + Logistik</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>Korntal-Münchingen (Raum Stuttgart), Baden-Württemberg</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>Gesellschafter und Namensträger des familiengeführten Speditions- und Logistikunternehmens; zweiter Entscheidungsträger neben der Geschäftsführung.</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>https://eckhardt-logistik.de/kontakt/ansprechpartner | https://eckhardt-logistik.de/</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Dirk Valerius</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführender Gesellschafter</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>d.valerius@werneke.de</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>02922 / 8060 - 260</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>Werneke Logistic GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>Werl (Kreis Soest / Südwestfalen)</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>Inhabergeführter Logistikdienstleister mit Stückgut, Sammelgut, Charterverkehr und vier Lagerstandorten (Kontraktlogistik). Familie Werneke weiterhin im Unternehmen aktiv.</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>https://www.werneke.de/ansprechpartner | https://www.regiomanager.de/suedwestfalen/ranking/mobilitaet-logistik/spedition-und-logistik/kreis-soest/</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
           <t>Jörg Küpper</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>Geschäftsführer</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
+      <c r="C91" s="2" t="inlineStr">
         <is>
           <t>j.kuepper@d-log.de</t>
         </is>
       </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>+49 201 2897960</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>d-log GmbH</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>Logistik &amp; Supply Chain</t>
-        </is>
-      </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>Logistik &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
         <is>
           <t>Essen</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>Inhabergeführter Logistikdienstleister aus Essen (Schacht Neu-Cöln) mit Transport-, Lager- und Distributionslogistik im Ruhrgebiet.</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr">
+      <c r="I91" s="2" t="inlineStr">
         <is>
           <t>https://www.d-log.de/impressum | https://www.regiomanager.de/ranking/mobilitaet-logistik/spedition-und-logistik/essen/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I77"/>
+  <autoFilter ref="A1:I91"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4123,10 +4781,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C3" t="n">
-        <v>69</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4">
@@ -4162,10 +4820,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="C6" t="n">
-        <v>191</v>
+        <v>227</v>
       </c>
     </row>
   </sheetData>
@@ -4179,7 +4837,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D192"/>
+  <dimension ref="A1:D228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -6897,12 +7555,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Wilhelm Altendorf GmbH &amp; Co. KG</t>
+          <t>Enns Maschinenbau GmbH</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Minden</t>
+          <t>Bad Oeynhausen</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -6912,19 +7570,19 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Zahlreiche personenbezogene E-Mails auf der Website, aber keine davon einem Geschäftsführer/Prokuristen oder zulässigen Bereichsleiter zugeordnet</t>
+          <t>Liegt in NRW – außerhalb des Fokusgebiets (persönliche E-Mail andreas@enns-mb.de wäre vorhanden)</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Kolbus GmbH &amp; Co. KG</t>
+          <t>KASTO Maschinenbau GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Rahden</t>
+          <t>Achern (BW)</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -6934,19 +7592,19 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Keine persönliche Entscheider-E-Mail auf Website/Impressum/Kontakt gefunden</t>
+          <t>Auf allen gecrawlten Seiten nur Sammeladressen (kasto@kasto.com) – keine persönliche E-Mail</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>AUMUND Fördertechnik GmbH</t>
+          <t>Heldele GmbH</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Rheinberg</t>
+          <t>Salach (BW)</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -6956,19 +7614,19 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Nur Kontaktformulare, keine persönliche E-Mail</t>
+          <t>Nur Standort-Sammeladresse salach@heldele.de – keine persönliche E-Mail</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>THIELE GmbH &amp; Co. KG</t>
+          <t>ASP Automation GmbH</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Iserlohn</t>
+          <t>Treuchtlingen (BY)</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -6978,19 +7636,19 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Nur Sammeladressen (hebetechnik@) – keine persönliche Entscheider-E-Mail</t>
+          <t>Nur info@asp-automation.de; Inhaber Werner Schramm ohne persönliche E-Mail</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>HASCO Hasenclever GmbH + Co KG</t>
+          <t>Neumüller GmbH</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Lüdenscheid</t>
+          <t>Thyrnau (BY)</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -7000,19 +7658,19 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Persönliche E-Mails nur für Kran-Service und Einkauf/Buchhaltung – kein Entscheidungsträger belegbar</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Gebr. Eickhoff Maschinenfabrik</t>
+          <t>XENON Automatisierungstechnik GmbH</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Dresden (SN)</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -7022,19 +7680,19 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Nur Standort-Sammeladressen, keine persönliche E-Mail auf gecrawlten Seiten</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Herbert Kannegiesser GmbH</t>
+          <t>SITEC Industrietechnologie GmbH</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Vlotho</t>
+          <t>Chemnitz (SN)</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -7044,19 +7702,19 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Keine persönliche E-Mail auffindbar</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>HAVER &amp; BOECKER OHG</t>
+          <t>NILES-SIMMONS Industrieanlagen GmbH</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Oelde</t>
+          <t>Chemnitz (SN)</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -7066,19 +7724,19 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Personenbezogene Mails nur im Vertriebs-/Auslandsnetz, kein Entscheider mit Rolle belegt</t>
+          <t>Nur sales-Sammeladresse; zudem Konzernverbund NSH Group</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Reifenhäuser GmbH &amp; Co. KG</t>
+          <t>Schnaithmann Maschinenbau GmbH</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Troisdorf</t>
+          <t>Remshalden (BW)</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -7088,19 +7746,19 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Nur Fachbereichs-/Recruiting-Mails, keine Geschäftsführung</t>
+          <t>Keine E-Mail-Adressen im Quelltext (nur Formular)</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>battenfeld-cincinnati Germany GmbH</t>
+          <t>ZELTWANGER Gruppe</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Bad Oeynhausen</t>
+          <t>Tübingen (BW)</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -7110,19 +7768,19 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Nur Vertriebs-/Länderkontakte, keine Entscheider-E-Mail</t>
+          <t>Nur funktionale Adressen (holding@, vertrieb.mb@, service@)</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Hanning Elektro-Werke GmbH &amp; Co. KG</t>
+          <t>Eckerle Technologies GmbH</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Oerlinghausen</t>
+          <t>Malsch (BW)</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -7132,19 +7790,19 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Nur Vertriebspartner-Mails; Impressum-Mail gehört zum externen Datenschutzbeauftragten</t>
+          <t>Persönliche E-Mails nur für Vertrieb/Auftragsabwicklung; kein Geschäftsführer/Prokurist mit E-Mail</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Dürkopp Adler GmbH</t>
+          <t>Höfelmeyer Waagen GmbH</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Bielefeld</t>
+          <t>Georgsmarienhütte (NI)</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -7154,19 +7812,19 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Nur Vertriebspartner-Adressen; zudem Konzernstruktur</t>
+          <t>Einzige persönliche E-Mail gehört Marketing – kein Entscheidungsträger</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Klingelnberg GmbH</t>
+          <t>Haupt Hydraulik &amp; Pneumatik (Inh. Thomas Zander e.K.)</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Hückeswagen</t>
+          <t>Riesa (SN)</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -7176,19 +7834,19 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Nur Funktionspostfächer (kegelrad@, seminar@ etc.)</t>
+          <t>Inhaber Thomas Zander ohne persönliche E-Mail; nur Vertriebs-/Technikmitarbeiter</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Kampf Schneid- und Wickeltechnik GmbH &amp; Co. KG</t>
+          <t>indusa GmbH</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Wiehl</t>
+          <t>Waldems (HE)</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -7198,19 +7856,19 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Nur weltweite Vertriebs-/Agenturkontakte, keine Geschäftsführung</t>
+          <t>Geschäftsleitung Dirk Schnieders ohne E-Mail; gelistete Adressen sind Gebiets-/Handelsvertretungen</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Achenbach Buschhütten GmbH &amp; Co. KG</t>
+          <t>Papierverarbeitung Golzern GmbH</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Kreuztal</t>
+          <t>Grimma (SN)</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -7220,19 +7878,19 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Nur Funktionspostfach fertigung@</t>
+          <t>Falsche Branche (Papierverarbeitung), kein Maschinen-/Anlagenbau</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Gebr. Becker GmbH</t>
+          <t>Kampfer (Formen- und Sondermaschinenbau)</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Wuppertal</t>
+          <t>Betzenstein (BY)</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -7242,19 +7900,19 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Personenbezogene Mails nur im Vertriebsinnendienst/Service ohne Entscheiderrolle</t>
+          <t>Deutlich unter 50 Mitarbeiter – außerhalb des ICP (E-Mail des Inhabers wäre vorhanden)</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>KettenWulf Betriebs GmbH</t>
+          <t>ESMO AG / esmo automation</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Eslohe</t>
+          <t>Rosenheim (BY)</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -7264,19 +7922,19 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Nur Funktionsadressen (sales.automation@, service.automation@); l.ingenhag ohne Positionsbeleg</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ELHA-MASCHINENBAU Liemke KG</t>
+          <t>Grenzebach Maschinenbau GmbH</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Halle (Westf.)</t>
+          <t>Asbach-Bäumenheim (BY)</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -7286,19 +7944,19 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Nur ausländische Vertriebspartner-Mails</t>
+          <t>Nur Standort-Sammeladressen; zudem Konzerngröße</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>G. Siempelkamp GmbH &amp; Co. KG</t>
+          <t>teamtechnik / BBS Automation</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Krefeld</t>
+          <t>Freiberg a.N. (BW)</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -7308,19 +7966,19 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Keine persönliche Entscheider-E-Mail öffentlich</t>
+          <t>Konzernstruktur, nur info-Adressen je Standort</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Hennecke GmbH</t>
+          <t>SCHMID Group</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Sankt Augustin</t>
+          <t>Freudenstadt (BW)</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -7330,19 +7988,19 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Keine persönlichen E-Mails, nur Sammeladressen</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Kautex Maschinenbau GmbH</t>
+          <t>HEDELIUS Maschinenfabrik GmbH</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Bonn</t>
+          <t>Meppen (NI)</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -7352,19 +8010,19 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Nur Funktions-/Händleradressen, keine persönliche E-Mail</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Lödige Industries GmbH</t>
+          <t>WENZEL Group GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Warburg/Paderborn</t>
+          <t>Wiesthal (BY)</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -7374,19 +8032,19 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Nur sales-Sammeladressen je Land</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Schmidt + Clemens GmbH &amp; Co. KG</t>
+          <t>Maschinenfabrik EIRICH GmbH &amp; Co KG</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Lindlar</t>
+          <t>Hardheim (BW)</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -7396,19 +8054,19 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Nur eirich@eirich.de bzw. Auslandsgesellschaften</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>MSK Verpackungs-Systeme GmbH</t>
+          <t>PSB intralogistics GmbH</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Kleve</t>
+          <t>Pirmasens (RP)</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -7418,19 +8076,19 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Nur Kontaktformulare, keine persönliche E-Mail</t>
+          <t>Keine persönlichen E-Mails auf gecrawlten Seiten</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>SPALECK GmbH &amp; Co. KG</t>
+          <t>Langhammer GmbH</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Bocholt</t>
+          <t>Eisenberg (RP)</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -7440,19 +8098,19 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Keine persönliche Entscheider-E-Mail auffindbar</t>
+          <t>Keine E-Mail-Adressen im Quelltext</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Rhein-Nadel Automation GmbH</t>
+          <t>ROEMHELD Gruppe</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Aachen</t>
+          <t>Laubach (HE)</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -7462,19 +8120,19 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Keine persönlichen E-Mails auffindbar</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>STRACK NORMA GmbH &amp; Co. KG</t>
+          <t>HEMA Maschinen- und Apparateschutz GmbH</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Lüdenscheid</t>
+          <t>Seligenstadt (HE)</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -7484,19 +8142,19 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Keine E-Mail-Adressen im Quelltext</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>TRACTO-TECHNIK GmbH &amp; Co. KG</t>
+          <t>Sielaff GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Lennestadt</t>
+          <t>Herrieden (BY)</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -7506,19 +8164,19 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Nur Standort-Sammeladressen</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Albrecht Bäumer GmbH &amp; Co. KG</t>
+          <t>MAFAC – E. Schwarz GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Freudenberg</t>
+          <t>Alpirsbach (BW)</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -7528,19 +8186,19 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Nur Adressen von Auslandsvertretungen, keine eigene Führungskraft</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Düchting Pumpen Maschinenfabrik GmbH &amp; Co. KG</t>
+          <t>IMSTec GmbH</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Wetter (Ruhr)</t>
+          <t>Heidelberg (BW)</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -7550,19 +8208,19 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Nur Team-Sammeladresse und US-Tochter</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A. Monforts Textilmaschinen GmbH &amp; Co. KG</t>
+          <t>Pahnke Engineering GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Mönchengladbach</t>
+          <t>Hamburg</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -7572,19 +8230,19 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Einziger belegter Entscheider (Betriebsleiter) sitzt in der österreichischen Niederlassung – außerhalb NRW</t>
+          <t>Standort außerhalb der Zielbundesländer</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Murtfeldt Kunststoffe GmbH &amp; Co. KG</t>
+          <t>SMB Sondermaschinenbau GmbH</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>Uplengen (NI)</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -7594,19 +8252,19 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Nur info@smb-sondermaschinen.de; GF Wolfgang Blank ohne persönliche E-Mail</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>DENIOS SE</t>
+          <t>DMV Sondermaschinenbau GmbH</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Bad Oeynhausen</t>
+          <t>Bad Wünnenberg</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -7616,19 +8274,19 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Keine persönliche Entscheider-E-Mail öffentlich</t>
+          <t>Nur dmv@dmv-sondermaschinenbau.de; zudem NRW</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Venjakob Maschinenbau GmbH &amp; Co. KG</t>
+          <t>Knecht Maschinenbau GmbH</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Rheda-Wiedenbrück</t>
+          <t>Bergatreute (BW)</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -7638,19 +8296,19 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Keine persönliche E-Mail auf Website auffindbar</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Remmert GmbH</t>
+          <t>Rühle &amp; Co. Maschinenbau GmbH</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Löhne</t>
+          <t>Walzbachtal (BW)</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -7660,19 +8318,19 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Keine E-Mail-Adressen der Geschäftsführung veröffentlicht</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Rippert GmbH &amp; Co. KG</t>
+          <t>Emsland Metallbau GmbH – Arnd Brinkmann (Vertrieb)</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Herzebrock-Clarholz</t>
+          <t>Salzbergen (NI)</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -7682,19 +8340,19 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Für Vertriebskontakt keine E-Mail wörtlich gelistet (nur Sammeladresse Anfragen_Vertrieb@)</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Ohrmann GmbH Montagetechnik</t>
+          <t>Wilhelm Altendorf GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Rheda-Wiedenbrück</t>
+          <t>Minden</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -7704,19 +8362,19 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Zahlreiche personenbezogene E-Mails auf der Website, aber keine davon einem Geschäftsführer/Prokuristen oder zulässigen Bereichsleiter zugeordnet</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Sollich KG</t>
+          <t>Kolbus GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Bad Salzuflen</t>
+          <t>Rahden</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -7726,19 +8384,19 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Keine persönliche Entscheider-E-Mail auf Website/Impressum/Kontakt gefunden</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>steute Technologies GmbH &amp; Co. KG</t>
+          <t>AUMUND Fördertechnik GmbH</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Löhne</t>
+          <t>Rheinberg</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -7748,19 +8406,19 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Nur Kontaktformulare, keine persönliche E-Mail</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Torwegge GmbH &amp; Co. KG</t>
+          <t>THIELE GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Bielefeld</t>
+          <t>Iserlohn</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -7770,19 +8428,19 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Nur Sammeladressen (hebetechnik@) – keine persönliche Entscheider-E-Mail</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Wemhöner Surface Technologies GmbH &amp; Co. KG</t>
+          <t>HASCO Hasenclever GmbH + Co KG</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Herford</t>
+          <t>Lüdenscheid</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -7792,19 +8450,19 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Nur internationale Handelsvertreter-Mails, keine Geschäftsführung</t>
+          <t>Keine persönliche E-Mail öffentlich</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>RK Rose+Krieger GmbH</t>
+          <t>Gebr. Eickhoff Maschinenfabrik</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Minden</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -7814,19 +8472,19 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Nur Funktions-/Auslandspostfächer; zudem Konzernzugehörigkeit (Phoenix Mecano)</t>
+          <t>Keine persönliche E-Mail öffentlich</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Carl Werthenbach Konstruktionsteile GmbH &amp; Co. KG</t>
+          <t>Herbert Kannegiesser GmbH</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Bielefeld</t>
+          <t>Vlotho</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -7836,19 +8494,19 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Geschäftsführer im Impressum genannt, aber nur info@/industrietechnik@ – keine persönliche E-Mail</t>
+          <t>Keine persönliche E-Mail öffentlich</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Seppeler Holding und Verwaltungs GmbH &amp; Co. KG</t>
+          <t>HAVER &amp; BOECKER OHG</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Rietberg</t>
+          <t>Oelde</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -7858,19 +8516,19 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Geschäftsführer im Impressum genannt, aber nur info-holding@ – keine persönliche E-Mail</t>
+          <t>Personenbezogene Mails nur im Vertriebs-/Auslandsnetz, kein Entscheider mit Rolle belegt</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>MIT Moderne Industrietechnik GmbH &amp; Co. KG</t>
+          <t>Reifenhäuser GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Vlotho</t>
+          <t>Troisdorf</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -7880,19 +8538,19 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Geschäftsführung genannt, E-Mail nur als Sammeladresse mit@systemarmaturen.de</t>
+          <t>Nur Fachbereichs-/Recruiting-Mails, keine Geschäftsführung</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Schubert &amp; Salzer / ventiltechnik.de (Vlotho)</t>
+          <t>battenfeld-cincinnati Germany GmbH</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Vlotho</t>
+          <t>Bad Oeynhausen</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -7902,19 +8560,19 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Persönliche Mails nur für Vertriebsleitung/Sales Director – keine Geschäftsführung, Vertrieb zählt laut Vorgabe nicht</t>
+          <t>Nur Vertriebs-/Länderkontakte, keine Entscheider-E-Mail</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Heilig Maschinenbau GmbH</t>
+          <t>Hanning Elektro-Werke GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Bad Salzuflen</t>
+          <t>Oerlinghausen</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -7924,19 +8582,19 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Impressum nennt GF Sascha Heilig, die angegebene Adresse heilig@heilig-maschinenbau.de ist jedoch nicht eindeutig persönlich (Firmenname = Nachname) – bei Unsicherheit verworfen</t>
+          <t>Nur Vertriebspartner-Mails; Impressum-Mail gehört zum externen Datenschutzbeauftragten</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>ATL Luhden GmbH</t>
+          <t>Dürkopp Adler GmbH</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Luhden</t>
+          <t>Bielefeld</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -7946,19 +8604,19 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Betriebsleiter/Prokurist mit persönlicher Mail belegt, Standort liegt jedoch in Niedersachsen (nicht NRW)</t>
+          <t>Nur Vertriebspartner-Adressen; zudem Konzernstruktur</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>DUBOR Groneweg GmbH &amp; Co. KG</t>
+          <t>Klingelnberg GmbH</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Bad Salzuflen</t>
+          <t>Hückeswagen</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -7968,19 +8626,19 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Ansprechpartnerseite mit Entscheidern vorhanden, aber Branche Backmittel/Lebensmittel – kein Maschinenbau; GF-Adressen zudem nur info@</t>
+          <t>Nur Funktionspostfächer (kegelrad@, seminar@ etc.)</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>AMR-Engineering GmbH</t>
+          <t>Kampf Schneid- und Wickeltechnik GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Essen</t>
+          <t>Wiehl</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -7990,19 +8648,19 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Geschäftsführer im Impressum genannt, aber nur Sammeladresse amr@amr.de</t>
+          <t>Nur weltweite Vertriebs-/Agenturkontakte, keine Geschäftsführung</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>SIEBTECHNIK TEMA GmbH</t>
+          <t>Achenbach Buschhütten GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Mülheim an der Ruhr</t>
+          <t>Kreuztal</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -8012,19 +8670,19 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Nur Funktionspostfach fertigung@</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>HAZEMAG &amp; EPR GmbH</t>
+          <t>Gebr. Becker GmbH</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Dülmen</t>
+          <t>Wuppertal</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -8034,19 +8692,19 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Personenbezogene Mails nur im Vertriebsinnendienst/Service ohne Entscheiderrolle</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>BOGE KOMPRESSOREN Otto Boge GmbH &amp; Co. KG</t>
+          <t>KettenWulf Betriebs GmbH</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Bielefeld</t>
+          <t>Eslohe</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -8056,19 +8714,19 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Nur Länder-Sammelpostfächer</t>
+          <t>Keine persönliche E-Mail öffentlich</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>PROBAT SE</t>
+          <t>ELHA-MASCHINENBAU Liemke KG</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Emmerich am Rhein</t>
+          <t>Halle (Westf.)</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -8078,19 +8736,19 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Nur ausländische Vertriebspartner-Mails</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Otto Junker GmbH</t>
+          <t>G. Siempelkamp GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Simmerath</t>
+          <t>Krefeld</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -8100,19 +8758,19 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Keine persönliche Entscheider-E-Mail öffentlich</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>REMBE GmbH Safety+Control</t>
+          <t>Hennecke GmbH</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Brilon</t>
+          <t>Sankt Augustin</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -8129,12 +8787,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>OVENTROP GmbH &amp; Co. KG</t>
+          <t>Kautex Maschinenbau GmbH</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Olsberg</t>
+          <t>Bonn</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -8151,12 +8809,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>BJB GmbH &amp; Co. KG</t>
+          <t>Lödige Industries GmbH</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Arnsberg</t>
+          <t>Warburg/Paderborn</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -8173,12 +8831,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Ruhrpumpen GmbH</t>
+          <t>Schmidt + Clemens GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Witten</t>
+          <t>Lindlar</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -8195,12 +8853,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Winkelmann Group GmbH + Co. KG</t>
+          <t>MSK Verpackungs-Systeme GmbH</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Ahlen</t>
+          <t>Kleve</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -8210,19 +8868,19 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Nur Kontaktformulare, keine persönliche E-Mail</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>GERSTUNG Sondermaschinen GmbH</t>
+          <t>SPALECK GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Mönchengladbach</t>
+          <t>Bocholt</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -8232,19 +8890,19 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Keine persönliche Entscheider-E-Mail auffindbar</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>AUMAT Maschinenbau GmbH</t>
+          <t>Rhein-Nadel Automation GmbH</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>NRW</t>
+          <t>Aachen</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -8261,12 +8919,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Maschinen- und Industriebau Feld GmbH</t>
+          <t>STRACK NORMA GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>NRW</t>
+          <t>Lüdenscheid</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -8276,19 +8934,19 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Ansprechpartnerseite vorhanden, aber ohne persönliche E-Mail-Adressen</t>
+          <t>Keine persönliche E-Mail öffentlich</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>VGS Automatisierungstechnik GmbH &amp; Co. KG</t>
+          <t>TRACTO-TECHNIK GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Schloß Holte-Stukenbrock</t>
+          <t>Lennestadt</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -8305,12 +8963,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Ebert Maschinenbau GmbH</t>
+          <t>Albrecht Bäumer GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Minden</t>
+          <t>Freudenberg</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -8327,12 +8985,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>BELU GmbH</t>
+          <t>Düchting Pumpen Maschinenfabrik GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Bielefeld</t>
+          <t>Wetter (Ruhr)</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -8349,12 +9007,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Pfister Fertigungstechnik / GMM mbH / MB Klich</t>
+          <t>A. Monforts Textilmaschinen GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>NRW</t>
+          <t>Mönchengladbach</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -8364,19 +9022,19 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>CNC-Lohnfertiger ohne persönliche Entscheider-E-Mail auf der Website</t>
+          <t>Einziger belegter Entscheider (Betriebsleiter) sitzt in der österreichischen Niederlassung – außerhalb NRW</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Selzer Formenbau GmbH / Dietrich Formenbau / KM Formenbau / Jedig &amp; Heyns / Wilfrid Humme</t>
+          <t>Murtfeldt Kunststoffe GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Lüdenscheid</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -8386,27 +9044,819 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Werkzeug-/Formenbauer ohne persönliche Entscheider-E-Mail auf der Website</t>
+          <t>Keine persönliche E-Mail öffentlich</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
+          <t>DENIOS SE</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Bad Oeynhausen</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Keine persönliche Entscheider-E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Venjakob Maschinenbau GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Rheda-Wiedenbrück</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Remmert GmbH</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Löhne</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Rippert GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Herzebrock-Clarholz</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Ohrmann GmbH Montagetechnik</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Rheda-Wiedenbrück</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Sollich KG</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Bad Salzuflen</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>steute Technologies GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Löhne</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Torwegge GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Bielefeld</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Wemhöner Surface Technologies GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Herford</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Nur internationale Handelsvertreter-Mails, keine Geschäftsführung</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>RK Rose+Krieger GmbH</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Minden</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Nur Funktions-/Auslandspostfächer; zudem Konzernzugehörigkeit (Phoenix Mecano)</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Carl Werthenbach Konstruktionsteile GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Bielefeld</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Geschäftsführer im Impressum genannt, aber nur info@/industrietechnik@ – keine persönliche E-Mail</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Seppeler Holding und Verwaltungs GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Rietberg</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Geschäftsführer im Impressum genannt, aber nur info-holding@ – keine persönliche E-Mail</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>MIT Moderne Industrietechnik GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Vlotho</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Geschäftsführung genannt, E-Mail nur als Sammeladresse mit@systemarmaturen.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Schubert &amp; Salzer / ventiltechnik.de (Vlotho)</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Vlotho</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Persönliche Mails nur für Vertriebsleitung/Sales Director – keine Geschäftsführung, Vertrieb zählt laut Vorgabe nicht</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Heilig Maschinenbau GmbH</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Bad Salzuflen</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Impressum nennt GF Sascha Heilig, die angegebene Adresse heilig@heilig-maschinenbau.de ist jedoch nicht eindeutig persönlich (Firmenname = Nachname) – bei Unsicherheit verworfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>ATL Luhden GmbH</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Luhden</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Betriebsleiter/Prokurist mit persönlicher Mail belegt, Standort liegt jedoch in Niedersachsen (nicht NRW)</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>DUBOR Groneweg GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Bad Salzuflen</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Ansprechpartnerseite mit Entscheidern vorhanden, aber Branche Backmittel/Lebensmittel – kein Maschinenbau; GF-Adressen zudem nur info@</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>AMR-Engineering GmbH</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Essen</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Geschäftsführer im Impressum genannt, aber nur Sammeladresse amr@amr.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>SIEBTECHNIK TEMA GmbH</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Mülheim an der Ruhr</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>HAZEMAG &amp; EPR GmbH</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Dülmen</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>BOGE KOMPRESSOREN Otto Boge GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Bielefeld</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Nur Länder-Sammelpostfächer</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>PROBAT SE</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Emmerich am Rhein</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Otto Junker GmbH</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Simmerath</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>REMBE GmbH Safety+Control</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Brilon</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>OVENTROP GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Olsberg</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>BJB GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Arnsberg</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Ruhrpumpen GmbH</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Witten</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Winkelmann Group GmbH + Co. KG</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Ahlen</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>GERSTUNG Sondermaschinen GmbH</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Mönchengladbach</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>AUMAT Maschinenbau GmbH</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>NRW</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Maschinen- und Industriebau Feld GmbH</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>NRW</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Ansprechpartnerseite vorhanden, aber ohne persönliche E-Mail-Adressen</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>VGS Automatisierungstechnik GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Schloß Holte-Stukenbrock</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Ebert Maschinenbau GmbH</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Minden</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>BELU GmbH</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Bielefeld</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Pfister Fertigungstechnik / GMM mbH / MB Klich</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>NRW</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>CNC-Lohnfertiger ohne persönliche Entscheider-E-Mail auf der Website</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Selzer Formenbau GmbH / Dietrich Formenbau / KM Formenbau / Jedig &amp; Heyns / Wilfrid Humme</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Lüdenscheid</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Werkzeug-/Formenbauer ohne persönliche Entscheider-E-Mail auf der Website</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
           <t>Hagener Fördertechnik – Stefan Maschmeier (Prokurist)</t>
         </is>
       </c>
-      <c r="B192" t="inlineStr">
+      <c r="B228" t="inlineStr">
         <is>
           <t>Hagen</t>
         </is>
       </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>Maschinenbau &amp; Fertigung</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
         <is>
           <t>Als zweiter Entscheider geprüft, aber nur info@hafoe.de hinterlegt – daher nicht verwendet</t>
         </is>

--- a/leads-adept/leads-adept.xlsx
+++ b/leads-adept/leads-adept.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Verworfen" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$I$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$I$105</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I91"/>
+  <dimension ref="A1:I105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4724,8 +4724,666 @@
         </is>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>Johan Bogaerts</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführer</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>johan.bogaerts@arichemie.com</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>+49 6198 5912-0 (Zentrale; keine persönliche Durchwahl veröffentlicht)</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>ARICHEMIE GmbH</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>Chemie &amp; Prozessindustrie</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>Eppstein-Bremthal (Hessen)</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>Inhabergeführte Füllstoff- und Farbenfabrik, entwickelt und produziert Pigment-Präparationen ausschließlich für B2B-Kunden. Mitglied bei HessenChemie.</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>https://arichemie.com/de/arichemie/kontakt/ | https://www.arichemie.com | https://www.hessenchemie.de/mitgliedsunternehmen</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>Adem Baygin</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>Prokurist, Leitung Vertrieb</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>a.baygin@astorplast.de</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>+49 7172 303-47</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>ASTORPLAST Klebetechnik GmbH</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>Chemie &amp; Prozessindustrie</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>Alfdorf (Baden-Württemberg)</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>Hersteller von Klebebändern und Klebelösungen, u. a. für Luft- und Winddichtung sowie Profiltechnik; Mitglied im Industrieverband Klebstoffe.</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>https://www.astorplast.de/kontakt | https://www.klebstoffe.com/mitglieder/</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Roland Albrecht</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Prokurist, Produktionsleitung</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>r.albrecht@aurora-kunststoffe.de</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>+49 7942 9142-49</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>AURORA Kunststoffe GmbH</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>Chemie &amp; Prozessindustrie</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>Neuenstein (Baden-Württemberg)</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>Mittelständischer Compoundeur für technische Kunststoff-Compounds und hochwertige Rezyklate mit eigener Extrusion.</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aurora-kunststoffe.de/ansprechpartner</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>Thomas Rätzsch</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsleitung</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>t.raetzsch@aurora-kunststoffe.de</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>+49 7942 9142-0</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>AURORA Kunststoffe GmbH</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>Chemie &amp; Prozessindustrie</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>Neuenstein (Baden-Württemberg)</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>Mittelständischer Compoundeur für technische Kunststoff-Compounds und hochwertige Rezyklate mit eigener Extrusion.</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aurora-kunststoffe.de/ansprechpartner | https://www.aurora-kunststoffe.de/kontakt/</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>Franco Menchetti</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>Vertriebsleiter &amp; Prokurist</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Franco.Menchetti@cta-gmbh.de</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>+49 7141 299916-148</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>CTA GmbH</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>Chemie &amp; Prozessindustrie</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>Ludwigsburg (Baden-Württemberg)</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>Lohnabfüller und Lohnfertiger für chemisch-technische Produkte (Flüssigkeiten, Aerosole, Sets) inkl. Standort in den USA.</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cta-gmbh.de/kontakt/ | https://www.cta-gmbh.de/lohnabfuellung-in-den-usa-ihre-ansprechpartner/</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>Hans-Dieter Worch</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführer</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>hans-dieter.worch@cta-gmbh.de</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>+49 7141 299916-0 (Zentrale; keine persönliche Durchwahl veröffentlicht)</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>CTA GmbH</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>Chemie &amp; Prozessindustrie</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>Ludwigsburg (Baden-Württemberg)</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>Lohnabfüller und Lohnfertiger für chemisch-technische Produkte (Flüssigkeiten, Aerosole, Sets) inkl. Standort in den USA.</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cta-gmbh.de/lohnabfuellung-in-den-usa-ihre-ansprechpartner/ | https://www.cta-gmbh.de/kontakt/ (dort: 'Hans-Dieter Worch Geschäftsführer')</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Dimitri Peters</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Werksleiter (Produktion)</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>d.peters@dr-demuth.com</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>+49 5551 9794-36</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Demuth Derisol Lackfarben GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>Chemie &amp; Prozessindustrie</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>Raum Northeim (Niedersachsen)</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>Seit über 60 Jahren Hersteller von Lackfarben und Beschichtungen 'Made in Germany'; eigene Produktion mit Werksleitung und Labor.</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dr-demuth.com/das-team</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>Ludwig Haring</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführung</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>l.haring@dr-demuth.com</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>+49 5551 9794-10</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Demuth Derisol Lackfarben GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>Chemie &amp; Prozessindustrie</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>Raum Northeim (Niedersachsen)</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>Seit über 60 Jahren Hersteller von Lackfarben und Beschichtungen 'Made in Germany'; eigene Produktion mit Werksleitung und Labor.</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dr-demuth.com/das-team | https://www.dr-demuth.com/das-team (Zitat: 'Unser Team von rund 60 Mitarbeitern')</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>Rainer Hähnle</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Einkaufsleiter</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>rainer.haehnle@haering.de</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>+49 7130 4702-70</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>HAERING GmbH</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>Chemie &amp; Prozessindustrie</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>Untergruppenbach-Unterheinriet (Baden-Württemberg)</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>Seit rund 140 Jahren mittelständischer Hersteller von Farben, Lacken und Bautenschutzprodukten mit eigenem Farbstudio und Auslieferungslager.</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.haering.de/kontakt | https://www.haering.de/unternehmen (Zitat: '100 Mitarbeiter') | https://www.haering-lacke.de/kontakt</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>Sergey Krasnikov</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>EDV-Leiter (IT)</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>sergey.krasnikov@haering.de</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>+49 7130 4702-32</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>HAERING GmbH</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>Chemie &amp; Prozessindustrie</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>Untergruppenbach-Unterheinriet (Baden-Württemberg)</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>Seit rund 140 Jahren mittelständischer Hersteller von Farben, Lacken und Bautenschutzprodukten mit eigenem Farbstudio und Auslieferungslager.</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>https://www.haering.de/kontakt</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Dirk Ruppmann</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Betriebsleitung / Prokurist</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>dirkruppmann@kapp-chemie.com</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>+49 6772 9311-250</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>KAPP-CHEMIE GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>Chemie &amp; Prozessindustrie</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>Miehlen (Rheinland-Pfalz)</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>Mittelständischer Spezialchemie-Hersteller (u. a. Farbstoffe, technische Chemikalien, Lohnfertigung). Gehört zur familiengeführten STOCKMEIER-Gruppe.</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.stockmeier.com/de/kapp-chemie/kontakt/ | https://www.kapp-chemie.de/de/kapp-chemie/kontakt/</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>Hendrik Breiden</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Leitung Einkauf/Logistik</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>hendrikbreiden@kapp-chemie.com</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>+49 6772 9311-150</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>KAPP-CHEMIE GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>Chemie &amp; Prozessindustrie</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>Miehlen (Rheinland-Pfalz)</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>Mittelständischer Spezialchemie-Hersteller (u. a. Farbstoffe, technische Chemikalien, Lohnfertigung). Gehört zur familiengeführten STOCKMEIER-Gruppe.</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>https://www.stockmeier.com/de/kapp-chemie/kontakt/ | https://www.kapp-chemie.de/de/kapp-chemie/kontakt/</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>Marco Hermann</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführer</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>marcohermann@kapp-chemie.com</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>+49 6772 9311-360</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>KAPP-CHEMIE GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>Chemie &amp; Prozessindustrie</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>Miehlen (Rheinland-Pfalz)</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>Mittelständischer Spezialchemie-Hersteller (u. a. Farbstoffe, technische Chemikalien, Lohnfertigung). Gehört zur familiengeführten STOCKMEIER-Gruppe.</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>https://www.stockmeier.com/de/kapp-chemie/kontakt/ | https://www.kapp-chemie.de/de/kapp-chemie/kontakt/</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>Michael Stache</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführender Gesellschafter</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>michael.stache@wigol.de</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>+49 6241 4141-0 (Zentrale; keine persönliche Durchwahl veröffentlicht)</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>WIGOL W. Stache GmbH</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>Chemie &amp; Prozessindustrie</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>Worms (Rheinland-Pfalz)</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>Familiengeführter Hersteller von Reinigungs- und Prozesschemie für Lebensmittel-/Getränke-, Pharma-, Kosmetikindustrie sowie Oberflächentechnik und Industriereinigung.</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wigol.de/de/kontakt</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I91"/>
+  <autoFilter ref="A1:I105"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4807,10 +5465,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6">
@@ -4820,10 +5478,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="C6" t="n">
-        <v>227</v>
+        <v>267</v>
       </c>
     </row>
   </sheetData>
@@ -4837,7 +5495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D228"/>
+  <dimension ref="A1:D268"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -4871,892 +5529,892 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Hermann Ritter GmbH &amp; Co. KG (Ritter Spedition)</t>
+          <t>Kurt Obermeier GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Feilitzsch-Zedtwitz, Bayern</t>
+          <t>Bad Berleburg</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>nur 40 Mitarbeiter (unter Zielgröße) und nur info@-Adresse</t>
+          <t>Persönliche GF-Adresse vorhanden (jochen.obermeier@obermeier.de), aber Standort NRW – außerhalb des Fokusgebiets</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Metzger Spedition GmbH</t>
+          <t>Otto Bollmann GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Neu-Kupfer, Baden-Württemberg</t>
+          <t>Mönchengladbach</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>nur info@metzger-spedition.de, keine Personen auf der Website</t>
+          <t>Standort NRW – außerhalb des Fokusgebiets</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Rüdinger Spedition GmbH</t>
+          <t>KNEHO-LACKE GmbH</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Krautheim, Baden-Württemberg</t>
+          <t>Horn-Bad Meinberg</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Ansprechpartner mit Namen/Positionen, aber E-Mail-Adressen verschleiert; auch per curl keine Adresse im Quelltext</t>
+          <t>Standort NRW – außerhalb des Fokusgebiets</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ZUFALL logistics group (Friedrich Zufall GmbH &amp; Co. KG)</t>
+          <t>GLUKON GmbH</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Göttingen, Niedersachsen</t>
+          <t>Dätgen</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>nur standortbezogene Sammeladressen (goettingen@, kassel@ …), keine persönliche E-Mail der Geschäftsführung</t>
+          <t>Schleswig-Holstein – außerhalb der Zielbundesländer</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Heinrich Koch Internationale Spedition GmbH &amp; Co. KG</t>
+          <t>Karl Wörwag Lack- und Farbenfabrik</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Osnabrück, Niedersachsen</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>auf der Kontaktseite nur info@koch-international.de, keine Ansprechpartner-Seite mit Personen-E-Mails</t>
+          <t>Website leitet auf PPG – Konzernzugehörigkeit, kein Mittelstand</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Döderlein Spedition GmbH</t>
+          <t>SurTec International GmbH</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Nördlingen, Bayern</t>
+          <t>Bad Camberg</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>nur info@doederlein.de, keine Ansprechpartner-/Teamseite</t>
+          <t>Freudenberg-Gruppe – laut Vorgabe ausgeschlossen</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Elflein Spedition &amp; Transport GmbH</t>
+          <t>ECKART GmbH</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bamberg, Bayern</t>
+          <t>Hartenstein</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Geschäftsführer mit Durchwahl gelistet, aber E-Mail-Links leer ('#') – keine wörtliche Adresse auf der Seite</t>
+          <t>Altana-Konzern – laut Vorgabe ausgeschlossen</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Spedicam GmbH</t>
+          <t>Deutsche Derustit GmbH</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Neufahrn (Raum München), Bayern</t>
+          <t>Dietzenbach</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>nur Funktionsadressen (Gf@, Sl@, Vl@ …), keine personenbezogenen E-Mails</t>
+          <t>Persönliche Adressen nur in einem JS-PLZ-Routing-Skript, keine Positionszuordnung, nicht im sichtbaren Seitentext</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Wiedmann &amp; Winz GmbH</t>
+          <t>AKRO-PLASTIC GmbH</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Geislingen an der Steige, Baden-Württemberg</t>
+          <t>Niederzissen</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>nur Funktionsadressen (mail@, offer@, anfrage@), keine Ansprechpartner-Seite</t>
+          <t>Persönliche Adressen nur als Formular-Routing im Quelltext, keine Zuordnung zu Position/Entscheidungsträger</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BKV Logistik GmbH &amp; Co. KG</t>
+          <t>G.E. Habich's Söhne GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Rheinstetten, Baden-Württemberg</t>
+          <t>Reinhardshagen</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>nur Funktionsadressen (kontakt@, transportlogistik@, kontraktlogistik@)</t>
+          <t>Nur Vertriebs-/Innendienstkontakte, kein Geschäftsführer/Prokurist/Bereichsleiter</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BECK Spedition + Logistik GmbH</t>
+          <t>Chemische Fabrik Dr. Stöcker GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Filderstadt, Baden-Württemberg</t>
+          <t>Pfaffen-Schwabenheim</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>nur info@becksped.de, keine Personen auf der Kontaktseite</t>
+          <t>Nur Vertrieb/Kundenbetreuung, keine Entscheidungsträger-Adresse</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Abt Spedition &amp; Service</t>
+          <t>Duroplast Chemie GmbH</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Schwäbisch Gmünd, Baden-Württemberg</t>
+          <t>Neustadt (Wied)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Ansprechpartner Jochen Abt genannt, aber nur info@abt-spedition.de</t>
+          <t>Nur Sammeladresse customers@; zudem nur ca. 20 Mitarbeiter</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Honold Contract Logistics GmbH</t>
+          <t>Pröll GmbH</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Neu-Ulm, Bayern</t>
+          <t>Weißenburg i. Bay.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Geschäftsführer namentlich genannt, aber nur Sammeladresse kontraktlogistik@honold.net</t>
+          <t>Nur F&amp;E- und QM-Leitung mit persönlicher Adresse, keine GF/Prokurist/Produktions-/IT-/Logistikleitung</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LTG Logistik und Transport GmbH</t>
+          <t>Textilchemie Dr. Petry GmbH</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Hamburg</t>
+          <t>Reutlingen</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>keine E-Mail-Adressen auf der Kontaktseite</t>
+          <t>Nur Entwicklungsleiter auffindbar, Kontaktseite nur office@/contact@</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>RM Logistik GmbH</t>
+          <t>Emil Frei GmbH &amp; Co. KG (FreiLacke)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Grasberg / Bremen</t>
+          <t>Bräunlingen</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Geschäftsführung (Familie Meyer) mit Telefon, aber keine E-Mail-Adressen auf der Seite</t>
+          <t>Nur Export-/Vertriebsmitarbeiter mit persönlicher Adresse</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Spedition Bode GmbH &amp; Co. KG</t>
+          <t>Buzil-Werk Wagner GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bad Oldesloe/Bargteheide, Schleswig-Holstein</t>
+          <t>Memmingen</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>persönliche GF-Adresse vorhanden, aber Standort außerhalb der definierten Zielregionen</t>
+          <t>Nur Funktionsadressen (service@, orders@, auftragsbearbeitung@)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Finsterwalder Transport &amp; Logistik GmbH</t>
+          <t>Hermann Otto GmbH (OTTO-CHEMIE)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Türkheim, Bayern</t>
+          <t>Fridolfing</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>nur standortbezogene Sammeladressen (sales.tu@ …)</t>
+          <t>Nur Funktionsadressen (info@, technik@, vertrieb@, industry@)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Noerpel-Gruppe</t>
+          <t>Zeller+Gmelin GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ulm / Hamburg / Hannover</t>
+          <t>Eislingen</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>über 1.000 Mitarbeiter, außerhalb der Zielgröße; nur info@noerpel.de</t>
+          <t>Nur info@ auf der Kontaktseite</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Rudolph Logistik Gruppe</t>
+          <t>Ruderer Klebetechnik GmbH</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Gudensberg, Hessen</t>
+          <t>Zorneding</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ca. 4.500 Mitarbeiter an 42 Standorten – Konzerngröße, außerhalb Zielprofil</t>
+          <t>Nur info(at)ruderer.de</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LOXXESS AG</t>
+          <t>Klebchemie M. G. Becker (KLEIBERIT)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tegernsee, Bayern</t>
+          <t>Weingarten</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Kontraktlogistiker deutlich über 1.000 Mitarbeitern – außerhalb Zielgröße</t>
+          <t>Nur Auslands-/Vertriebskontakte, keine deutsche Entscheidungsträger-Adresse</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Spedition König</t>
+          <t>Chemische Werke Kluthe GmbH</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Esslingen, Baden-Württemberg</t>
+          <t>Heidelberg</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>nur info@koenig-sped.de</t>
+          <t>Keine persönliche Adresse auffindbar (nur Funktionsadressen)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Spedition Kübler GmbH</t>
+          <t>Nabaltec AG</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Michelfeld/Schwäbisch Hall, Baden-Württemberg</t>
+          <t>Schwandorf</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>nur info@kuebler-spedition.de, keine personenbezogenen E-Mails</t>
+          <t>Nur tec-service@nabaltec.de</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>E3 Spedition (E3 Gruppe)</t>
+          <t>Remmers GmbH</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Homberg (Hessen) u. a.</t>
+          <t>Löningen</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Ansprechpartner nur über JavaScript-Filter, keine E-Mails im Seitenquelltext</t>
+          <t>Nur Presse-/Marketingkontakte</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Carl Köster &amp; Louis Hapke – Kontaktseite</t>
+          <t>Werner &amp; Mertz GmbH</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Sehnde-Höver, Niedersachsen</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Hinweis: /kontakt/ enthält nur info@; verwertbare Daten ausschließlich auf /ansprechpartner/ (siehe Lead)</t>
+          <t>Nur Funktions- und Recruiting-Adressen</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Kraftverkehr Münsterland C. Weilke GmbH &amp; Co. KG</t>
+          <t>KRAIBURG TPE GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Greven</t>
+          <t>Waldkraiburg</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>nur info@weilke.de auf Website, keine Ansprechpartner-/Teamseite mit Personen-E-Mails gefunden</t>
+          <t>Keine Entscheidungsträger-Adresse auf den Kontaktseiten</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Richter Spedition GmbH</t>
+          <t>Hermann Bantleon GmbH</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Schwerte</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>nur info@richter-spedition.de, keine Personenseite; Geschäftsführung nicht mit E-Mail veröffentlicht</t>
+          <t>Nur Adressen ausländischer Vertriebspartner</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Gustav Mäuler GmbH &amp; Co. KG</t>
+          <t>Woellner GmbH</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Remscheid</t>
+          <t>Ludwigshafen</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>nur info@ und verkauf@ (Funktionsadressen), keine namentlichen Ansprechpartner auf Homepage und Kontaktseite</t>
+          <t>Keine persönliche Adresse auffindbar</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Spedition Zobel</t>
+          <t>Wakol GmbH</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Wetter (Ruhr)</t>
+          <t>Pirmasens</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Ansprechpartner-Seite nennt nur Personalmanagement; keine E-Mail der Geschäftsführer Philip/Christian Zobel veröffentlicht</t>
+          <t>Keine persönliche Adresse auffindbar</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>LLS-Service GmbH</t>
+          <t>Votteler Lackfabrik GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Gladbeck</t>
+          <t>Korntal-Münchingen</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>nur info@lls.services, keine namentlichen Entscheidungsträger auf der Website</t>
+          <t>Nur Länder-Sammeladressen (d.info@, at.info@)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Emmerich &amp; Rosenberger GmbH &amp; Co. KG (EMRO)</t>
+          <t>Laverana GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Duisburg</t>
+          <t>Wennigsen</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>nur info@emro.de, keine Ansprechpartner-Seite mit persönlichen E-Mails gefunden</t>
+          <t>Nur Ombudsmann-Kanzlei, keine Firmen-Entscheidungsträger-Adresse</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>NW Logistik</t>
+          <t>Annemarie Börlind / Börlind GmbH</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ahlen</t>
+          <t>Calw</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Website nicht erreichbar (DNS-Fehler), keine Daten verifizierbar</t>
+          <t>Nur Pressekontakt</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Emons Spedition GmbH</t>
+          <t>L. Brüggemann GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Heilbronn</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Konzernähnliche Größe (&gt;3.000 Mitarbeiter, 100 Standorte) — außerhalb Mittelstands-Zielprofil</t>
+          <t>Nur HR-Kontakt aus Stellenanzeigen</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>TEAM Logistic (Greinert/Diel)</t>
+          <t>RHENOCOLL-Werk e.K.</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Raum Montabaur (RLP)</t>
+          <t>Konken</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>persönliche GF-E-Mails vorhanden, aber außerhalb Zielregion und Größe nicht verifiziert — nachqualifizierbar</t>
+          <t>Nur Personal-/Karrierekontakt</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>TEAM Logistic GmbH</t>
+          <t>Carl Schlenk AG</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Raum Montabaur (Vorwahl 02602)</t>
+          <t>Roth</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Persönliche E-Mails vorhanden, aber Standort außerhalb Ruhrgebiet/Rheinland/Niederrhein</t>
+          <t>Nur Karriere-/Recruiting-Kontakte</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Spedition Schiffers GmbH</t>
+          <t>Se Tylose GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Mönchengladbach</t>
+          <t>Wiesbaden</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Website nicht erreichbar (DNS-Fehler, auch per curl); E-Mails nicht auf einer gecrawlten Seite verifizierbar</t>
+          <t>Nur eine Vertriebsadresse ohne Entscheidungsträger-Zuordnung</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>meta4log GmbH</t>
+          <t>Chemische Fabrik Dr. Weigert GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Essen</t>
+          <t>Hamburg</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Nur info@meta4log.de auf der Website; keine persönliche E-Mail des Geschäftsführers (Bernd Jungclaus)</t>
+          <t>Außerhalb der Zielbundesländer; zudem nur Vertriebsaußendienst</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Rheinkraft International GmbH (RKI)</t>
+          <t>Kurt Bühnen GmbH &amp; Co. KG (BÜHNEN)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Duisburg</t>
+          <t>Bremen</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Nur info@rki-logistics.com, keine Personen auf Kontaktseite</t>
+          <t>Außerhalb der Zielbundesländer</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Windgätter u. Sohn GmbH</t>
+          <t>Gebrüder Dorfner GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>Hirschau</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Ansprechpartner mit Durchwahl, aber nur Sammeladresse dispo@windgaetter-transporte.de</t>
+          <t>Nur Funktionsadressen (acs.sales@, CS-ACS@)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Hoff Transport und Logistik GmbH &amp; Co. KG</t>
+          <t>Aurora Kunststoffe – Kontaktseite /kontakt</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Krefeld</t>
+          <t>Neuenstein</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Nur info@/order@/karriere@; keine Personen genannt</t>
+          <t>Hinweis: /kontakt enthält nur info@; verwertbare Daten ausschließlich unter /ansprechpartner (siehe Leads)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AXTRA GmbH &amp; Co. KG</t>
+          <t>Pfinder KG</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Essen</t>
+          <t>Böblingen</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Nur info@axtra.de, keine Ansprechpartnerseite</t>
+          <t>Nur pfinder@pfinder.de (Sammeladresse)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Meinolf Jacobi Spedition GmbH</t>
+          <t>Hermann Ritter GmbH &amp; Co. KG (Ritter Spedition)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Feilitzsch-Zedtwitz, Bayern</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -5766,19 +6424,19 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Keine E-Mail-Adresse auf der Website auffindbar</t>
+          <t>nur 40 Mitarbeiter (unter Zielgröße) und nur info@-Adresse</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Johs. Stelten GmbH &amp; Co. KG</t>
+          <t>Metzger Spedition GmbH</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Krefeld</t>
+          <t>Neu-Kupfer, Baden-Württemberg</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -5788,19 +6446,19 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Nur info@steltenkg.de; keine persönliche E-Mail der Geschäftsführung</t>
+          <t>nur info@metzger-spedition.de, keine Personen auf der Website</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Spedition Minor GmbH</t>
+          <t>Rüdinger Spedition GmbH</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Gelsenkirchen</t>
+          <t>Krautheim, Baden-Württemberg</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -5810,19 +6468,19 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Nur info@spedition-minor.de</t>
+          <t>Ansprechpartner mit Namen/Positionen, aber E-Mail-Adressen verschleiert; auch per curl keine Adresse im Quelltext</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Hubert Kläsener GmbH &amp; Co. KG</t>
+          <t>ZUFALL logistics group (Friedrich Zufall GmbH &amp; Co. KG)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Gelsenkirchen</t>
+          <t>Göttingen, Niedersachsen</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -5832,19 +6490,19 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail auf Website/Kontaktseite</t>
+          <t>nur standortbezogene Sammeladressen (goettingen@, kassel@ …), keine persönliche E-Mail der Geschäftsführung</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Scheren Logistik GmbH</t>
+          <t>Heinrich Koch Internationale Spedition GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Düsseldorf</t>
+          <t>Osnabrück, Niedersachsen</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -5854,19 +6512,19 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Team-Seite nennt Personen nur mit Vornamen/Initial, nur info@scheren.de</t>
+          <t>auf der Kontaktseite nur info@koch-international.de, keine Ansprechpartner-Seite mit Personen-E-Mails</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MSG Speditionsgesellschaft mbH</t>
+          <t>Döderlein Spedition GmbH</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Mönchengladbach</t>
+          <t>Nördlingen, Bayern</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -5876,19 +6534,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Nur Funktionsadressen (Management@, National@, Sea@ etc.), keine Personenzuordnung</t>
+          <t>nur info@doederlein.de, keine Ansprechpartner-/Teamseite</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Graf-Transporte Internationale Spedition GmbH</t>
+          <t>Elflein Spedition &amp; Transport GmbH</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Bamberg, Bayern</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -5898,19 +6556,19 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Keine E-Mail-Adressen auf der Website auffindbar</t>
+          <t>Geschäftsführer mit Durchwahl gelistet, aber E-Mail-Links leer ('#') – keine wörtliche Adresse auf der Seite</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Curt Richter SE</t>
+          <t>Spedicam GmbH</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Neufahrn (Raum München), Bayern</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -5920,19 +6578,19 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Keine persönlichen E-Mails auf gecrawlten Seiten</t>
+          <t>nur Funktionsadressen (Gf@, Sl@, Vl@ …), keine personenbezogenen E-Mails</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Deußen Logistik GmbH</t>
+          <t>Wiedmann &amp; Winz GmbH</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Geislingen an der Steige, Baden-Württemberg</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -5942,19 +6600,19 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Keine erreichbare Firmenwebsite mit persönlichen E-Mails gefunden</t>
+          <t>nur Funktionsadressen (mail@, offer@, anfrage@), keine Ansprechpartner-Seite</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>HEUEL LOGISTICS</t>
+          <t>BKV Logistik GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Dortmund/Arnsberg</t>
+          <t>Rheinstetten, Baden-Württemberg</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -5964,19 +6622,19 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Nur Funktionsadressen (angebot@, info@)</t>
+          <t>nur Funktionsadressen (kontakt@, transportlogistik@, kontraktlogistik@)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>LOXX Logistics</t>
+          <t>BECK Spedition + Logistik GmbH</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Duisburg</t>
+          <t>Filderstadt, Baden-Württemberg</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -5986,19 +6644,19 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Persönliche E-Mails vorhanden, aber inzwischen Teil der Rhenus-Gruppe (Konzern) – ausgeschlossen</t>
+          <t>nur info@becksped.de, keine Personen auf der Kontaktseite</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Hendricks Unternehmensgruppe</t>
+          <t>Abt Spedition &amp; Service</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Neuss</t>
+          <t>Schwäbisch Gmünd, Baden-Württemberg</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -6008,19 +6666,19 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Nur Funktionsadressen (automotive@hendricks.group)</t>
+          <t>Ansprechpartner Jochen Abt genannt, aber nur info@abt-spedition.de</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>TechnoCargo Logistik GmbH u. Co. KG</t>
+          <t>Honold Contract Logistics GmbH</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Neuss</t>
+          <t>Neu-Ulm, Bayern</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -6030,19 +6688,19 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Nur bewerbung@technocargo.de; Konzernstruktur (Bertschi-nahe Geschäftsführung)</t>
+          <t>Geschäftsführer namentlich genannt, aber nur Sammeladresse kontraktlogistik@honold.net</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>NEUFRA Speditions-Gesellschaft mbH</t>
+          <t>LTG Logistik und Transport GmbH</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Neuss</t>
+          <t>Hamburg</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -6052,19 +6710,19 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Keine persönlichen E-Mails auffindbar</t>
+          <t>keine E-Mail-Adressen auf der Kontaktseite</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Bodenheim Spedition GmbH</t>
+          <t>RM Logistik GmbH</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Krefeld</t>
+          <t>Grasberg / Bremen</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -6074,19 +6732,19 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Kontaktseite enthält nur Platzhalter (email@example.org)</t>
+          <t>Geschäftsführung (Familie Meyer) mit Telefon, aber keine E-Mail-Adressen auf der Seite</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Spedition Kronenberg GmbH</t>
+          <t>Spedition Bode GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Bad Oldesloe/Bargteheide, Schleswig-Holstein</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -6096,19 +6754,19 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Nur Sammeladresse DispoKronenberg@aol.com; zudem unter 50 MA</t>
+          <t>persönliche GF-Adresse vorhanden, aber Standort außerhalb der definierten Zielregionen</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>GATE 41 Logistics GmbH &amp; Co. KG</t>
+          <t>Finsterwalder Transport &amp; Logistik GmbH</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Mönchengladbach</t>
+          <t>Türkheim, Bayern</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -6118,19 +6776,19 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Website enthält nur Platzhalter-Adresse, keine echten E-Mails</t>
+          <t>nur standortbezogene Sammeladressen (sales.tu@ …)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Die Richrath's GmbH</t>
+          <t>Noerpel-Gruppe</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Düsseldorf</t>
+          <t>Ulm / Hamburg / Hannover</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -6140,19 +6798,19 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Nur support@die-richraths.de</t>
+          <t>über 1.000 Mitarbeiter, außerhalb der Zielgröße; nur info@noerpel.de</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sägewerk Transporte GmbH</t>
+          <t>Rudolph Logistik Gruppe</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Düsseldorf</t>
+          <t>Gudensberg, Hessen</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -6162,19 +6820,19 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Keine persönlichen E-Mails auf der Website</t>
+          <t>ca. 4.500 Mitarbeiter an 42 Standorten – Konzerngröße, außerhalb Zielprofil</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Wilhelm Rotthege</t>
+          <t>LOXXESS AG</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Essen/Düsseldorf</t>
+          <t>Tegernsee, Bayern</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -6184,19 +6842,19 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Nur Standort-Sammeladressen (essen@, duesseldorf@)</t>
+          <t>Kontraktlogistiker deutlich über 1.000 Mitarbeitern – außerhalb Zielgröße</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Spedition Buerhaus / GDS Logistik / OFL Olympia Food Logistics / BM Spedition / A. Siepmann / Joachim Schultz / LOGIFLEX / P+M Logistik / Rosenbaum / Guckuk / ABC-Logistik / VCK Logistics</t>
+          <t>Spedition König</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>diverse (Dortmund, Bochum, Duisburg, MG, Köln, Düsseldorf)</t>
+          <t>Esslingen, Baden-Württemberg</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -6206,19 +6864,19 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Sammelposten: keine erreichbare Website mit persönlichen E-Mails der Entscheidungsträger gefunden</t>
+          <t>nur info@koenig-sped.de</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Emons, DSV, DB Schenker, Rhenus, Kühne+Nagel, Dachser, DHL, BLG, Yusen, Kintetsu</t>
+          <t>Spedition Kübler GmbH</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>diverse</t>
+          <t>Michelfeld/Schwäbisch Hall, Baden-Württemberg</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -6228,19 +6886,19 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Konzerne bzw. laut Vorgabe ausgeschlossen</t>
+          <t>nur info@kuebler-spedition.de, keine personenbezogenen E-Mails</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Rüdinger Spedition GmbH</t>
+          <t>E3 Spedition (E3 Gruppe)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Krautheim (BW)</t>
+          <t>Homberg (Hessen) u. a.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -6250,19 +6908,19 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Ansprechpartnerseite listet Namen/Positionen/Durchwahlen, aber keine E-Mail-Adressen im Klartext (JS-verschleierte 'E-Mail schreiben'-Links); curl-Nachfassen ohne Treffer</t>
+          <t>Ansprechpartner nur über JavaScript-Filter, keine E-Mails im Seitenquelltext</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>barth Logistikgruppe</t>
+          <t>Carl Köster &amp; Louis Hapke – Kontaktseite</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Hechingen (BW)</t>
+          <t>Sehnde-Höver, Niedersachsen</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -6272,19 +6930,19 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Ansprechpartnerseite enthält nur Telefon-/Faxnummern je Standort, keine Personen und keine E-Mail-Adressen; curl-Nachfassen ohne Treffer</t>
+          <t>Hinweis: /kontakt/ enthält nur info@; verwertbare Daten ausschließlich auf /ansprechpartner/ (siehe Lead)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Wiedmann &amp; Winz GmbH</t>
+          <t>Kraftverkehr Münsterland C. Weilke GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Geislingen an der Steige (BW)</t>
+          <t>Greven</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -6294,19 +6952,19 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Nur Funktionsadressen (mail@, offer@, anfrage@, bewerbung@), keine personenbezogenen E-Mails auf Kontaktseite</t>
+          <t>nur info@weilke.de auf Website, keine Ansprechpartner-/Teamseite mit Personen-E-Mails gefunden</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CL Spedition Berlin Transport- und Logistik GmbH</t>
+          <t>Richter Spedition GmbH</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Schwerte</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -6316,19 +6974,19 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Ansprechpartnerseite nennt Namen und Funktionen, aber nur Sammeladressen info@/dispo@/ber@</t>
+          <t>nur info@richter-spedition.de, keine Personenseite; Geschäftsführung nicht mit E-Mail veröffentlicht</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Spedition Kollmannsberger – Startseite</t>
+          <t>Gustav Mäuler GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Großmehring (BY)</t>
+          <t>Remscheid</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -6338,19 +6996,19 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Homepage nur mail@ – Lead stattdessen über die separate Ansprechpartnerseite qualifiziert (siehe Leads)</t>
+          <t>nur info@ und verkauf@ (Funktionsadressen), keine namentlichen Ansprechpartner auf Homepage und Kontaktseite</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Schwarzer Group / Schwarzer Spedition</t>
+          <t>Spedition Zobel</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Heiligenstedten (SH)</t>
+          <t>Wetter (Ruhr)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -6360,19 +7018,19 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Persönliche E-Mails vorhanden, aber Hauptsitz und Standorte außerhalb des Zielgebiets Süd-/Ostdeutschland</t>
+          <t>Ansprechpartner-Seite nennt nur Personalmanagement; keine E-Mail der Geschäftsführer Philip/Christian Zobel veröffentlicht</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sachsen-Anhalt Logistik</t>
+          <t>LLS-Service GmbH</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Sachsen-Anhalt (virtuell)</t>
+          <t>Gladbeck</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -6382,19 +7040,19 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Kein reales Unternehmen – virtuelle TruckersMP-Speditionsgemeinschaft (Gaming-Community); nur info@</t>
+          <t>nur info@lls.services, keine namentlichen Entscheidungsträger auf der Website</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ELOS Speditions GmbH</t>
+          <t>Emmerich &amp; Rosenberger GmbH &amp; Co. KG (EMRO)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Zwickau (SN)</t>
+          <t>Duisburg</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -6404,19 +7062,19 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Nur zentrale Adresse info@elos-spedition.de auffindbar, keine persönlichen Ansprechpartner-Mails</t>
+          <t>nur info@emro.de, keine Ansprechpartner-Seite mit persönlichen E-Mails gefunden</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Roman Mayer Logistik GmbH</t>
+          <t>NW Logistik</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Nürnberg / Gersthofen (BY)</t>
+          <t>Ahlen</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -6426,19 +7084,19 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Kontaktseite nur mit info@romanmayer-logistik.de, keine personenbezogenen E-Mails</t>
+          <t>Website nicht erreichbar (DNS-Fehler), keine Daten verifizierbar</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Köhl Logistik</t>
+          <t>Emons Spedition GmbH</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Pfalz</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -6448,19 +7106,19 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>HTTP 503 beim Abruf; zudem Sitz in Rheinland-Pfalz außerhalb des Zielgebiets</t>
+          <t>Konzernähnliche Größe (&gt;3.000 Mitarbeiter, 100 Standorte) — außerhalb Mittelstands-Zielprofil</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Spedition Ebenroth GmbH</t>
+          <t>TEAM Logistic (Greinert/Diel)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Döbeln (SN)</t>
+          <t>Raum Montabaur (RLP)</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -6470,19 +7128,19 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Keine Team-/Ansprechpartnerseite mit persönlichen E-Mails auffindbar</t>
+          <t>persönliche GF-E-Mails vorhanden, aber außerhalb Zielregion und Größe nicht verifiziert — nachqualifizierbar</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Baltic Lloyd – Startseite/Kontaktseite</t>
+          <t>TEAM Logistic GmbH</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Rostock (MV)</t>
+          <t>Raum Montabaur (Vorwahl 02602)</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -6492,19 +7150,19 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Startseite nur dispo@, /kontakt/ liefert HTTP 404 – Lead stattdessen über /dasteam/ qualifiziert (siehe Leads)</t>
+          <t>Persönliche E-Mails vorhanden, aber Standort außerhalb Ruhrgebiet/Rheinland/Niederrhein</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Krage &amp; Gerloff – Ansprechpartnerseite</t>
+          <t>Spedition Schiffers GmbH</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Schwanebeck (ST)</t>
+          <t>Mönchengladbach</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -6514,19 +7172,19 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>URL /ansprechpartner liefert HTTP 404; Geschäftsführung nicht mit persönlicher E-Mail belegbar – nur Standortleitung Magdeburg qualifiziert</t>
+          <t>Website nicht erreichbar (DNS-Fehler, auch per curl); E-Mails nicht auf einer gecrawlten Seite verifizierbar</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Seifert Logistics Group / Noerpel-Gruppe / Karl Schmidt Spedition</t>
+          <t>meta4log GmbH</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Ulm bzw. Heilbronn (BW)</t>
+          <t>Essen</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -6536,19 +7194,19 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Konzerngröße (2.500–4.000+ Mitarbeitende, 45+ Standorte) – außerhalb des Mittelstandsprofils</t>
+          <t>Nur info@meta4log.de auf der Website; keine persönliche E-Mail des Geschäftsführers (Bernd Jungclaus)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>LOXXESS AG</t>
+          <t>Rheinkraft International GmbH (RKI)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Tegernsee (BY)</t>
+          <t>Duisburg</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -6558,19 +7216,19 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Nicht weiterverfolgt – Konzernstruktur/AG, kein Ansprechpartnerverzeichnis mit persönlichen E-Mails</t>
+          <t>Nur info@rki-logistics.com, keine Personen auf Kontaktseite</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>TML Spedition GmbH</t>
+          <t>Windgätter u. Sohn GmbH</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Leipzig (SN)</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -6580,19 +7238,19 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Keine Ansprechpartnerseite mit namentlichen E-Mail-Adressen auffindbar</t>
+          <t>Ansprechpartner mit Durchwahl, aber nur Sammeladresse dispo@windgaetter-transporte.de</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Spedition Schiffers</t>
+          <t>Hoff Transport und Logistik GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Nettetal (NRW)</t>
+          <t>Krefeld</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -6602,19 +7260,19 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Region außerhalb des Zielgebiets Süd-/Ostdeutschland</t>
+          <t>Nur info@/order@/karriere@; keine Personen genannt</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>RTC Spedition &amp; Logistik GmbH</t>
+          <t>AXTRA GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Essen</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -6624,19 +7282,19 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Nur Zentralkontakt/Geschäftsführername belegt, keine persönliche E-Mail auf gecrawlten Seiten</t>
+          <t>Nur info@axtra.de, keine Ansprechpartnerseite</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sachsenland – Startseite</t>
+          <t>Meinolf Jacobi Spedition GmbH</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Dresden (SN)</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -6646,19 +7304,19 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Homepage ohne E-Mail-Adressen – Leads stattdessen über /kontakt-dresden/ qualifiziert (siehe Leads)</t>
+          <t>Keine E-Mail-Adresse auf der Website auffindbar</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Watzlawek Logistik</t>
+          <t>Johs. Stelten GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Hamm/Ahlen</t>
+          <t>Krefeld</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -6668,19 +7326,19 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Geschäftsleitung Lukas Watzlawek nur über info@watzlawek-trans.com erreichbar, keine persönliche E-Mail</t>
+          <t>Nur info@steltenkg.de; keine persönliche E-Mail der Geschäftsführung</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>H. Gautzsch Spedition GmbH &amp; Co. KG</t>
+          <t>Spedition Minor GmbH</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Münster</t>
+          <t>Gelsenkirchen</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -6690,19 +7348,19 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Ansprechpartnerliste nennt für alle Personen nur info@gautzsch-spedition.de</t>
+          <t>Nur info@spedition-minor.de</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>KÜHN Transport- und Lagerungsgesellschaft mbH</t>
+          <t>Hubert Kläsener GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Ostbevern</t>
+          <t>Gelsenkirchen</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -6712,19 +7370,19 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>nur info@kuehn-transporte.com auffindbar</t>
+          <t>Keine persönliche E-Mail auf Website/Kontaktseite</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Feldmann Spedition GmbH</t>
+          <t>Scheren Logistik GmbH</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Gütersloh</t>
+          <t>Düsseldorf</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -6734,19 +7392,19 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>nur dispo@feldmann-spedition.de</t>
+          <t>Team-Seite nennt Personen nur mit Vornamen/Initial, nur info@scheren.de</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>WLS Spedition GmbH</t>
+          <t>MSG Speditionsgesellschaft mbH</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Steinhagen</t>
+          <t>Mönchengladbach</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -6756,19 +7414,19 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>nur kontakt@wls-spedition.de</t>
+          <t>Nur Funktionsadressen (Management@, National@, Sea@ etc.), keine Personenzuordnung</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Hartmann International GmbH &amp; Co. KG</t>
+          <t>Graf-Transporte Internationale Spedition GmbH</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -6778,19 +7436,19 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Team-/Kontaktseiten nennen nur info@ bzw. standortbezogene Sammeladressen</t>
+          <t>Keine E-Mail-Adressen auf der Website auffindbar</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Loeber-Lehnhof GmbH</t>
+          <t>Curt Richter SE</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Siegen</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -6800,19 +7458,19 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Geschäftsführer Roman Mayer ohne persönliche E-Mail; gefundene Adresse gehört zum Webseitenbetreuer</t>
+          <t>Keine persönlichen E-Mails auf gecrawlten Seiten</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Schröder Logistik GmbH</t>
+          <t>Deußen Logistik GmbH</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Kirchlengern</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -6822,19 +7480,19 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Teamseite zeigt Geschäftsführer ohne E-Mail, nur faktura@schroeder-logistik.de</t>
+          <t>Keine erreichbare Firmenwebsite mit persönlichen E-Mails gefunden</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Loewe Logistics &amp; Care GmbH &amp; Co. KG</t>
+          <t>HEUEL LOGISTICS</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Herford</t>
+          <t>Dortmund/Arnsberg</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6844,19 +7502,19 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>keine E-Mail-Adressen auf gecrawlten Seiten auffindbar</t>
+          <t>Nur Funktionsadressen (angebot@, info@)</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Spedition Gerhard Siebel GmbH</t>
+          <t>LOXX Logistics</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Kreuztal</t>
+          <t>Duisburg</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6866,19 +7524,19 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>nur info@siebel-spedition.de</t>
+          <t>Persönliche E-Mails vorhanden, aber inzwischen Teil der Rhenus-Gruppe (Konzern) – ausgeschlossen</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Gössling Spedition GmbH</t>
+          <t>Hendricks Unternehmensgruppe</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Arnsberg</t>
+          <t>Neuss</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6888,19 +7546,19 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>nur gs@goessling-spedition.de (Funktionsadresse ohne Personenzuordnung)</t>
+          <t>Nur Funktionsadressen (automotive@hendricks.group)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Kerber Transporte GmbH</t>
+          <t>TechnoCargo Logistik GmbH u. Co. KG</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Brilon</t>
+          <t>Neuss</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6910,19 +7568,19 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>nur info@kerber-transporte.de</t>
+          <t>Nur bewerbung@technocargo.de; Konzernstruktur (Bertschi-nahe Geschäftsführung)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Spedition Mikus GmbH &amp; Co. KG</t>
+          <t>NEUFRA Speditions-Gesellschaft mbH</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Meschede</t>
+          <t>Neuss</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6932,19 +7590,19 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>nur info@spedition-mikus.de</t>
+          <t>Keine persönlichen E-Mails auffindbar</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Glexx GmbH</t>
+          <t>Bodenheim Spedition GmbH</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Meschede</t>
+          <t>Krefeld</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6954,19 +7612,19 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>nur post@glexx-logistik.de</t>
+          <t>Kontaktseite enthält nur Platzhalter (email@example.org)</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Kleinwächter GmbH &amp; Co. Spedition</t>
+          <t>Spedition Kronenberg GmbH</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Hallenberg</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6976,19 +7634,19 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>keine erreichbare Website/keine E-Mails über getestete Domains</t>
+          <t>Nur Sammeladresse DispoKronenberg@aol.com; zudem unter 50 MA</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Alfons Brass Spedition und Lagerei</t>
+          <t>GATE 41 Logistics GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Medebach</t>
+          <t>Mönchengladbach</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6998,19 +7656,19 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>keine E-Mails über getestete Domains auffindbar</t>
+          <t>Website enthält nur Platzhalter-Adresse, keine echten E-Mails</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Mönig Spedition Meschede GmbH</t>
+          <t>Die Richrath's GmbH</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Meschede</t>
+          <t>Düsseldorf</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -7020,19 +7678,19 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>keine E-Mails über getestete Domains auffindbar</t>
+          <t>Nur support@die-richraths.de</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Schulte-Lindhorst GmbH &amp; Co.</t>
+          <t>Sägewerk Transporte GmbH</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Rietberg</t>
+          <t>Düsseldorf</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -7042,19 +7700,19 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>nur info@schulte-lindhorst.de</t>
+          <t>Keine persönlichen E-Mails auf der Website</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Thermotraffic GmbH</t>
+          <t>Wilhelm Rotthege</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Versmold</t>
+          <t>Essen/Düsseldorf</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -7064,19 +7722,19 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>nur info@/sales@thermotraffic.de; zudem Konzernstruktur</t>
+          <t>Nur Standort-Sammeladressen (essen@, duesseldorf@)</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Tevex Logistics GmbH</t>
+          <t>Spedition Buerhaus / GDS Logistik / OFL Olympia Food Logistics / BM Spedition / A. Siepmann / Joachim Schultz / LOGIFLEX / P+M Logistik / Rosenbaum / Guckuk / ABC-Logistik / VCK Logistics</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Rheda-Wiedenbrück</t>
+          <t>diverse (Dortmund, Bochum, Duisburg, MG, Köln, Düsseldorf)</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -7086,19 +7744,19 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>nur info@tevex.de</t>
+          <t>Sammelposten: keine erreichbare Website mit persönlichen E-Mails der Entscheidungsträger gefunden</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Greiwing logistics for you GmbH</t>
+          <t>Emons, DSV, DB Schenker, Rhenus, Kühne+Nagel, Dachser, DHL, BLG, Yusen, Kintetsu</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Greven</t>
+          <t>diverse</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -7108,19 +7766,19 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>nur info@greiwing.de</t>
+          <t>Konzerne bzw. laut Vorgabe ausgeschlossen</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Sievert Logistik SE</t>
+          <t>Rüdinger Spedition GmbH</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Lengerich</t>
+          <t>Krautheim (BW)</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -7130,19 +7788,19 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>nur info.logistik@sievert.de; Teil der Sievert-Gruppe</t>
+          <t>Ansprechpartnerseite listet Namen/Positionen/Durchwahlen, aber keine E-Mail-Adressen im Klartext (JS-verschleierte 'E-Mail schreiben'-Links); curl-Nachfassen ohne Treffer</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>MP Logistik GmbH</t>
+          <t>barth Logistikgruppe</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Rheine</t>
+          <t>Hechingen (BW)</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -7152,19 +7810,19 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>nur info@/warehouse@mplogistik.com</t>
+          <t>Ansprechpartnerseite enthält nur Telefon-/Faxnummern je Standort, keine Personen und keine E-Mail-Adressen; curl-Nachfassen ohne Treffer</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Wetralog GmbH</t>
+          <t>Wiedmann &amp; Winz GmbH</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Münster</t>
+          <t>Geislingen an der Steige (BW)</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -7174,19 +7832,19 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>nur schadenservice@wetralog.de</t>
+          <t>Nur Funktionsadressen (mail@, offer@, anfrage@, bewerbung@), keine personenbezogenen E-Mails auf Kontaktseite</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Hövener Spedition GmbH</t>
+          <t>CL Spedition Berlin Transport- und Logistik GmbH</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Rheine</t>
+          <t>Berlin</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -7196,19 +7854,19 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>nur info@hoevener-spedition.de</t>
+          <t>Ansprechpartnerseite nennt Namen und Funktionen, aber nur Sammeladressen info@/dispo@/ber@</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Spedition Karl Kerkeling GmbH</t>
+          <t>Spedition Kollmannsberger – Startseite</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Coesfeld</t>
+          <t>Großmehring (BY)</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -7218,19 +7876,19 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>nur info@spedition-kerkeling.de</t>
+          <t>Homepage nur mail@ – Lead stattdessen über die separate Ansprechpartnerseite qualifiziert (siehe Leads)</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>MAX-Logistik GmbH</t>
+          <t>Schwarzer Group / Schwarzer Spedition</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Senden</t>
+          <t>Heiligenstedten (SH)</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -7240,19 +7898,19 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>nur info@max-logistik.de</t>
+          <t>Persönliche E-Mails vorhanden, aber Hauptsitz und Standorte außerhalb des Zielgebiets Süd-/Ostdeutschland</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Lipperland Logistik GmbH / Möbelspedition Lipperland</t>
+          <t>Sachsen-Anhalt Logistik</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Oelde</t>
+          <t>Sachsen-Anhalt (virtuell)</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -7262,19 +7920,19 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>gefundene Adressen ohne Positionszuordnung (Datenschutz-/Impressumskontext), kein belegter Entscheidungsträger</t>
+          <t>Kein reales Unternehmen – virtuelle TruckersMP-Speditionsgemeinschaft (Gaming-Community); nur info@</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Rosner Logistik GmbH</t>
+          <t>ELOS Speditions GmbH</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Oelde</t>
+          <t>Zwickau (SN)</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -7284,19 +7942,19 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>keine E-Mails auf gecrawlten Seiten</t>
+          <t>Nur zentrale Adresse info@elos-spedition.de auffindbar, keine persönlichen Ansprechpartner-Mails</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Dingwerth Logistik GmbH</t>
+          <t>Roman Mayer Logistik GmbH</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Beelen</t>
+          <t>Nürnberg / Gersthofen (BY)</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -7306,19 +7964,19 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>keine E-Mails auf gecrawlten Seiten</t>
+          <t>Kontaktseite nur mit info@romanmayer-logistik.de, keine personenbezogenen E-Mails</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>TEDO Logistik GmbH &amp; Co. KG</t>
+          <t>Köhl Logistik</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Ibbenbüren</t>
+          <t>Pfalz</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -7328,19 +7986,19 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>nur info@tedo-logistik.de</t>
+          <t>HTTP 503 beim Abruf; zudem Sitz in Rheinland-Pfalz außerhalb des Zielgebiets</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Richter Express OHG</t>
+          <t>Spedition Ebenroth GmbH</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Saerbeck</t>
+          <t>Döbeln (SN)</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -7350,19 +8008,19 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>nur info@richter-express.de</t>
+          <t>Keine Team-/Ansprechpartnerseite mit persönlichen E-Mails auffindbar</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Schöpper Transport GmbH</t>
+          <t>Baltic Lloyd – Startseite/Kontaktseite</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Greven</t>
+          <t>Rostock (MV)</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7372,19 +8030,19 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>nur info@ bzw. eine Adresse ohne belegte Positionszuordnung</t>
+          <t>Startseite nur dispo@, /kontakt/ liefert HTTP 404 – Lead stattdessen über /dasteam/ qualifiziert (siehe Leads)</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Spedition Kockel GmbH &amp; Co. KG</t>
+          <t>Krage &amp; Gerloff – Ansprechpartnerseite</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Soest</t>
+          <t>Schwanebeck (ST)</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7394,19 +8052,19 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>nur info@spedition-kockel.de</t>
+          <t>URL /ansprechpartner liefert HTTP 404; Geschäftsführung nicht mit persönlicher E-Mail belegbar – nur Standortleitung Magdeburg qualifiziert</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Mimberg Spedition - Baustoffe GmbH &amp; Co. KG</t>
+          <t>Seifert Logistics Group / Noerpel-Gruppe / Karl Schmidt Spedition</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Werl</t>
+          <t>Ulm bzw. Heilbronn (BW)</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7416,19 +8074,19 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>nur Funktions-/Beispieladressen, keine Entscheidungsträger-E-Mail</t>
+          <t>Konzerngröße (2.500–4.000+ Mitarbeitende, 45+ Standorte) – außerhalb des Mittelstandsprofils</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Artur Kossack Spedition</t>
+          <t>LOXXESS AG</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Hiddenhausen</t>
+          <t>Tegernsee (BY)</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7438,19 +8096,19 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>nur info@kossack.de</t>
+          <t>Nicht weiterverfolgt – Konzernstruktur/AG, kein Ansprechpartnerverzeichnis mit persönlichen E-Mails</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Westfalen-Lippe Speditions- und Lagerhausgesellschaft mbH</t>
+          <t>TML Spedition GmbH</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Herford</t>
+          <t>Leipzig (SN)</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7460,19 +8118,19 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>nur info@wl-spedition.de</t>
+          <t>Keine Ansprechpartnerseite mit namentlichen E-Mail-Adressen auffindbar</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Martin Oelrich GmbH &amp; Co. KG</t>
+          <t>Spedition Schiffers</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Ladbergen</t>
+          <t>Nettetal (NRW)</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7482,19 +8140,19 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>gehört zur pfenning logistics group (Konzern), keine persönliche E-Mail</t>
+          <t>Region außerhalb des Zielgebiets Süd-/Ostdeutschland</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>FIEGE / Nagel-Group / Duvenbeck</t>
+          <t>RTC Spedition &amp; Logistik GmbH</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Greven / Versmold / Bocholt</t>
+          <t>Berlin</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -7504,19 +8162,19 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Konzerne mit &gt;5.000 Mitarbeitern, außerhalb Zielprofil</t>
+          <t>Nur Zentralkontakt/Geschäftsführername belegt, keine persönliche E-Mail auf gecrawlten Seiten</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Heinrich Kottmann Spedition GmbH &amp; Co. KG</t>
+          <t>Sachsenland – Startseite</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Büren</t>
+          <t>Dresden (SN)</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -7526,19 +8184,19 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Website ohne verwertbare E-Mail-Adressen</t>
+          <t>Homepage ohne E-Mail-Adressen – Leads stattdessen über /kontakt-dresden/ qualifiziert (siehe Leads)</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Würfel-Massong Logistik GmbH</t>
+          <t>Watzlawek Logistik</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Hamm/Ahlen</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -7548,899 +8206,899 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>keine E-Mails auf gecrawlten Seiten</t>
+          <t>Geschäftsleitung Lukas Watzlawek nur über info@watzlawek-trans.com erreichbar, keine persönliche E-Mail</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Enns Maschinenbau GmbH</t>
+          <t>H. Gautzsch Spedition GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Bad Oeynhausen</t>
+          <t>Münster</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Liegt in NRW – außerhalb des Fokusgebiets (persönliche E-Mail andreas@enns-mb.de wäre vorhanden)</t>
+          <t>Ansprechpartnerliste nennt für alle Personen nur info@gautzsch-spedition.de</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>KASTO Maschinenbau GmbH &amp; Co. KG</t>
+          <t>KÜHN Transport- und Lagerungsgesellschaft mbH</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Achern (BW)</t>
+          <t>Ostbevern</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Auf allen gecrawlten Seiten nur Sammeladressen (kasto@kasto.com) – keine persönliche E-Mail</t>
+          <t>nur info@kuehn-transporte.com auffindbar</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Heldele GmbH</t>
+          <t>Feldmann Spedition GmbH</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Salach (BW)</t>
+          <t>Gütersloh</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Nur Standort-Sammeladresse salach@heldele.de – keine persönliche E-Mail</t>
+          <t>nur dispo@feldmann-spedition.de</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ASP Automation GmbH</t>
+          <t>WLS Spedition GmbH</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Treuchtlingen (BY)</t>
+          <t>Steinhagen</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Nur info@asp-automation.de; Inhaber Werner Schramm ohne persönliche E-Mail</t>
+          <t>nur kontakt@wls-spedition.de</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Neumüller GmbH</t>
+          <t>Hartmann International GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Thyrnau (BY)</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Persönliche E-Mails nur für Kran-Service und Einkauf/Buchhaltung – kein Entscheidungsträger belegbar</t>
+          <t>Team-/Kontaktseiten nennen nur info@ bzw. standortbezogene Sammeladressen</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>XENON Automatisierungstechnik GmbH</t>
+          <t>Loeber-Lehnhof GmbH</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Dresden (SN)</t>
+          <t>Siegen</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Nur Standort-Sammeladressen, keine persönliche E-Mail auf gecrawlten Seiten</t>
+          <t>Geschäftsführer Roman Mayer ohne persönliche E-Mail; gefundene Adresse gehört zum Webseitenbetreuer</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>SITEC Industrietechnologie GmbH</t>
+          <t>Schröder Logistik GmbH</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Chemnitz (SN)</t>
+          <t>Kirchlengern</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail auffindbar</t>
+          <t>Teamseite zeigt Geschäftsführer ohne E-Mail, nur faktura@schroeder-logistik.de</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>NILES-SIMMONS Industrieanlagen GmbH</t>
+          <t>Loewe Logistics &amp; Care GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Chemnitz (SN)</t>
+          <t>Herford</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Nur sales-Sammeladresse; zudem Konzernverbund NSH Group</t>
+          <t>keine E-Mail-Adressen auf gecrawlten Seiten auffindbar</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Schnaithmann Maschinenbau GmbH</t>
+          <t>Spedition Gerhard Siebel GmbH</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Remshalden (BW)</t>
+          <t>Kreuztal</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Keine E-Mail-Adressen im Quelltext (nur Formular)</t>
+          <t>nur info@siebel-spedition.de</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ZELTWANGER Gruppe</t>
+          <t>Gössling Spedition GmbH</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Tübingen (BW)</t>
+          <t>Arnsberg</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Nur funktionale Adressen (holding@, vertrieb.mb@, service@)</t>
+          <t>nur gs@goessling-spedition.de (Funktionsadresse ohne Personenzuordnung)</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Eckerle Technologies GmbH</t>
+          <t>Kerber Transporte GmbH</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Malsch (BW)</t>
+          <t>Brilon</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Persönliche E-Mails nur für Vertrieb/Auftragsabwicklung; kein Geschäftsführer/Prokurist mit E-Mail</t>
+          <t>nur info@kerber-transporte.de</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Höfelmeyer Waagen GmbH</t>
+          <t>Spedition Mikus GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Georgsmarienhütte (NI)</t>
+          <t>Meschede</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Einzige persönliche E-Mail gehört Marketing – kein Entscheidungsträger</t>
+          <t>nur info@spedition-mikus.de</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Haupt Hydraulik &amp; Pneumatik (Inh. Thomas Zander e.K.)</t>
+          <t>Glexx GmbH</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Riesa (SN)</t>
+          <t>Meschede</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Inhaber Thomas Zander ohne persönliche E-Mail; nur Vertriebs-/Technikmitarbeiter</t>
+          <t>nur post@glexx-logistik.de</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>indusa GmbH</t>
+          <t>Kleinwächter GmbH &amp; Co. Spedition</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Waldems (HE)</t>
+          <t>Hallenberg</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Geschäftsleitung Dirk Schnieders ohne E-Mail; gelistete Adressen sind Gebiets-/Handelsvertretungen</t>
+          <t>keine erreichbare Website/keine E-Mails über getestete Domains</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Papierverarbeitung Golzern GmbH</t>
+          <t>Alfons Brass Spedition und Lagerei</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Grimma (SN)</t>
+          <t>Medebach</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Falsche Branche (Papierverarbeitung), kein Maschinen-/Anlagenbau</t>
+          <t>keine E-Mails über getestete Domains auffindbar</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Kampfer (Formen- und Sondermaschinenbau)</t>
+          <t>Mönig Spedition Meschede GmbH</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Betzenstein (BY)</t>
+          <t>Meschede</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Deutlich unter 50 Mitarbeiter – außerhalb des ICP (E-Mail des Inhabers wäre vorhanden)</t>
+          <t>keine E-Mails über getestete Domains auffindbar</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ESMO AG / esmo automation</t>
+          <t>Schulte-Lindhorst GmbH &amp; Co.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Rosenheim (BY)</t>
+          <t>Rietberg</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Nur Funktionsadressen (sales.automation@, service.automation@); l.ingenhag ohne Positionsbeleg</t>
+          <t>nur info@schulte-lindhorst.de</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Grenzebach Maschinenbau GmbH</t>
+          <t>Thermotraffic GmbH</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Asbach-Bäumenheim (BY)</t>
+          <t>Versmold</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Nur Standort-Sammeladressen; zudem Konzerngröße</t>
+          <t>nur info@/sales@thermotraffic.de; zudem Konzernstruktur</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>teamtechnik / BBS Automation</t>
+          <t>Tevex Logistics GmbH</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Freiberg a.N. (BW)</t>
+          <t>Rheda-Wiedenbrück</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Konzernstruktur, nur info-Adressen je Standort</t>
+          <t>nur info@tevex.de</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>SCHMID Group</t>
+          <t>Greiwing logistics for you GmbH</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Freudenstadt (BW)</t>
+          <t>Greven</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Keine persönlichen E-Mails, nur Sammeladressen</t>
+          <t>nur info@greiwing.de</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>HEDELIUS Maschinenfabrik GmbH</t>
+          <t>Sievert Logistik SE</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Meppen (NI)</t>
+          <t>Lengerich</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Nur Funktions-/Händleradressen, keine persönliche E-Mail</t>
+          <t>nur info.logistik@sievert.de; Teil der Sievert-Gruppe</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>WENZEL Group GmbH &amp; Co. KG</t>
+          <t>MP Logistik GmbH</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Wiesthal (BY)</t>
+          <t>Rheine</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Nur sales-Sammeladressen je Land</t>
+          <t>nur info@/warehouse@mplogistik.com</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Maschinenfabrik EIRICH GmbH &amp; Co KG</t>
+          <t>Wetralog GmbH</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Hardheim (BW)</t>
+          <t>Münster</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Nur eirich@eirich.de bzw. Auslandsgesellschaften</t>
+          <t>nur schadenservice@wetralog.de</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>PSB intralogistics GmbH</t>
+          <t>Hövener Spedition GmbH</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Pirmasens (RP)</t>
+          <t>Rheine</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Keine persönlichen E-Mails auf gecrawlten Seiten</t>
+          <t>nur info@hoevener-spedition.de</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Langhammer GmbH</t>
+          <t>Spedition Karl Kerkeling GmbH</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Eisenberg (RP)</t>
+          <t>Coesfeld</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Keine E-Mail-Adressen im Quelltext</t>
+          <t>nur info@spedition-kerkeling.de</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ROEMHELD Gruppe</t>
+          <t>MAX-Logistik GmbH</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Laubach (HE)</t>
+          <t>Senden</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Keine persönlichen E-Mails auffindbar</t>
+          <t>nur info@max-logistik.de</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>HEMA Maschinen- und Apparateschutz GmbH</t>
+          <t>Lipperland Logistik GmbH / Möbelspedition Lipperland</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Seligenstadt (HE)</t>
+          <t>Oelde</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Keine E-Mail-Adressen im Quelltext</t>
+          <t>gefundene Adressen ohne Positionszuordnung (Datenschutz-/Impressumskontext), kein belegter Entscheidungsträger</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Sielaff GmbH &amp; Co. KG</t>
+          <t>Rosner Logistik GmbH</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Herrieden (BY)</t>
+          <t>Oelde</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Nur Standort-Sammeladressen</t>
+          <t>keine E-Mails auf gecrawlten Seiten</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>MAFAC – E. Schwarz GmbH &amp; Co. KG</t>
+          <t>Dingwerth Logistik GmbH</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Alpirsbach (BW)</t>
+          <t>Beelen</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Nur Adressen von Auslandsvertretungen, keine eigene Führungskraft</t>
+          <t>keine E-Mails auf gecrawlten Seiten</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>IMSTec GmbH</t>
+          <t>TEDO Logistik GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Heidelberg (BW)</t>
+          <t>Ibbenbüren</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Nur Team-Sammeladresse und US-Tochter</t>
+          <t>nur info@tedo-logistik.de</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Pahnke Engineering GmbH &amp; Co. KG</t>
+          <t>Richter Express OHG</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Hamburg</t>
+          <t>Saerbeck</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Standort außerhalb der Zielbundesländer</t>
+          <t>nur info@richter-express.de</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>SMB Sondermaschinenbau GmbH</t>
+          <t>Schöpper Transport GmbH</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Uplengen (NI)</t>
+          <t>Greven</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Nur info@smb-sondermaschinen.de; GF Wolfgang Blank ohne persönliche E-Mail</t>
+          <t>nur info@ bzw. eine Adresse ohne belegte Positionszuordnung</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>DMV Sondermaschinenbau GmbH</t>
+          <t>Spedition Kockel GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Bad Wünnenberg</t>
+          <t>Soest</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Nur dmv@dmv-sondermaschinenbau.de; zudem NRW</t>
+          <t>nur info@spedition-kockel.de</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Knecht Maschinenbau GmbH</t>
+          <t>Mimberg Spedition - Baustoffe GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Bergatreute (BW)</t>
+          <t>Werl</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail auf Website auffindbar</t>
+          <t>nur Funktions-/Beispieladressen, keine Entscheidungsträger-E-Mail</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Rühle &amp; Co. Maschinenbau GmbH</t>
+          <t>Artur Kossack Spedition</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Walzbachtal (BW)</t>
+          <t>Hiddenhausen</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Keine E-Mail-Adressen der Geschäftsführung veröffentlicht</t>
+          <t>nur info@kossack.de</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Emsland Metallbau GmbH – Arnd Brinkmann (Vertrieb)</t>
+          <t>Westfalen-Lippe Speditions- und Lagerhausgesellschaft mbH</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Salzbergen (NI)</t>
+          <t>Herford</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Für Vertriebskontakt keine E-Mail wörtlich gelistet (nur Sammeladresse Anfragen_Vertrieb@)</t>
+          <t>nur info@wl-spedition.de</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Wilhelm Altendorf GmbH &amp; Co. KG</t>
+          <t>Martin Oelrich GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Minden</t>
+          <t>Ladbergen</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Zahlreiche personenbezogene E-Mails auf der Website, aber keine davon einem Geschäftsführer/Prokuristen oder zulässigen Bereichsleiter zugeordnet</t>
+          <t>gehört zur pfenning logistics group (Konzern), keine persönliche E-Mail</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Kolbus GmbH &amp; Co. KG</t>
+          <t>FIEGE / Nagel-Group / Duvenbeck</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Rahden</t>
+          <t>Greven / Versmold / Bocholt</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Keine persönliche Entscheider-E-Mail auf Website/Impressum/Kontakt gefunden</t>
+          <t>Konzerne mit &gt;5.000 Mitarbeitern, außerhalb Zielprofil</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>AUMUND Fördertechnik GmbH</t>
+          <t>Heinrich Kottmann Spedition GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Rheinberg</t>
+          <t>Büren</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Nur Kontaktformulare, keine persönliche E-Mail</t>
+          <t>Website ohne verwertbare E-Mail-Adressen</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>THIELE GmbH &amp; Co. KG</t>
+          <t>Würfel-Massong Logistik GmbH</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Iserlohn</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Nur Sammeladressen (hebetechnik@) – keine persönliche Entscheider-E-Mail</t>
+          <t>keine E-Mails auf gecrawlten Seiten</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>HASCO Hasenclever GmbH + Co KG</t>
+          <t>Enns Maschinenbau GmbH</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Lüdenscheid</t>
+          <t>Bad Oeynhausen</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -8450,19 +9108,19 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Liegt in NRW – außerhalb des Fokusgebiets (persönliche E-Mail andreas@enns-mb.de wäre vorhanden)</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Gebr. Eickhoff Maschinenfabrik</t>
+          <t>KASTO Maschinenbau GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Achern (BW)</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -8472,19 +9130,19 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Auf allen gecrawlten Seiten nur Sammeladressen (kasto@kasto.com) – keine persönliche E-Mail</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Herbert Kannegiesser GmbH</t>
+          <t>Heldele GmbH</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Vlotho</t>
+          <t>Salach (BW)</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -8494,19 +9152,19 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Nur Standort-Sammeladresse salach@heldele.de – keine persönliche E-Mail</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>HAVER &amp; BOECKER OHG</t>
+          <t>ASP Automation GmbH</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Oelde</t>
+          <t>Treuchtlingen (BY)</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -8516,19 +9174,19 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Personenbezogene Mails nur im Vertriebs-/Auslandsnetz, kein Entscheider mit Rolle belegt</t>
+          <t>Nur info@asp-automation.de; Inhaber Werner Schramm ohne persönliche E-Mail</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Reifenhäuser GmbH &amp; Co. KG</t>
+          <t>Neumüller GmbH</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Troisdorf</t>
+          <t>Thyrnau (BY)</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -8538,19 +9196,19 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Nur Fachbereichs-/Recruiting-Mails, keine Geschäftsführung</t>
+          <t>Persönliche E-Mails nur für Kran-Service und Einkauf/Buchhaltung – kein Entscheidungsträger belegbar</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>battenfeld-cincinnati Germany GmbH</t>
+          <t>XENON Automatisierungstechnik GmbH</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Bad Oeynhausen</t>
+          <t>Dresden (SN)</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -8560,19 +9218,19 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Nur Vertriebs-/Länderkontakte, keine Entscheider-E-Mail</t>
+          <t>Nur Standort-Sammeladressen, keine persönliche E-Mail auf gecrawlten Seiten</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Hanning Elektro-Werke GmbH &amp; Co. KG</t>
+          <t>SITEC Industrietechnologie GmbH</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Oerlinghausen</t>
+          <t>Chemnitz (SN)</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -8582,19 +9240,19 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Nur Vertriebspartner-Mails; Impressum-Mail gehört zum externen Datenschutzbeauftragten</t>
+          <t>Keine persönliche E-Mail auffindbar</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Dürkopp Adler GmbH</t>
+          <t>NILES-SIMMONS Industrieanlagen GmbH</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Bielefeld</t>
+          <t>Chemnitz (SN)</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -8604,19 +9262,19 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Nur Vertriebspartner-Adressen; zudem Konzernstruktur</t>
+          <t>Nur sales-Sammeladresse; zudem Konzernverbund NSH Group</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Klingelnberg GmbH</t>
+          <t>Schnaithmann Maschinenbau GmbH</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Hückeswagen</t>
+          <t>Remshalden (BW)</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -8626,19 +9284,19 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Nur Funktionspostfächer (kegelrad@, seminar@ etc.)</t>
+          <t>Keine E-Mail-Adressen im Quelltext (nur Formular)</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Kampf Schneid- und Wickeltechnik GmbH &amp; Co. KG</t>
+          <t>ZELTWANGER Gruppe</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Wiehl</t>
+          <t>Tübingen (BW)</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -8648,19 +9306,19 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Nur weltweite Vertriebs-/Agenturkontakte, keine Geschäftsführung</t>
+          <t>Nur funktionale Adressen (holding@, vertrieb.mb@, service@)</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Achenbach Buschhütten GmbH &amp; Co. KG</t>
+          <t>Eckerle Technologies GmbH</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Kreuztal</t>
+          <t>Malsch (BW)</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -8670,19 +9328,19 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Nur Funktionspostfach fertigung@</t>
+          <t>Persönliche E-Mails nur für Vertrieb/Auftragsabwicklung; kein Geschäftsführer/Prokurist mit E-Mail</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Gebr. Becker GmbH</t>
+          <t>Höfelmeyer Waagen GmbH</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Wuppertal</t>
+          <t>Georgsmarienhütte (NI)</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -8692,19 +9350,19 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Personenbezogene Mails nur im Vertriebsinnendienst/Service ohne Entscheiderrolle</t>
+          <t>Einzige persönliche E-Mail gehört Marketing – kein Entscheidungsträger</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>KettenWulf Betriebs GmbH</t>
+          <t>Haupt Hydraulik &amp; Pneumatik (Inh. Thomas Zander e.K.)</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Eslohe</t>
+          <t>Riesa (SN)</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -8714,19 +9372,19 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Inhaber Thomas Zander ohne persönliche E-Mail; nur Vertriebs-/Technikmitarbeiter</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>ELHA-MASCHINENBAU Liemke KG</t>
+          <t>indusa GmbH</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Halle (Westf.)</t>
+          <t>Waldems (HE)</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -8736,19 +9394,19 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Nur ausländische Vertriebspartner-Mails</t>
+          <t>Geschäftsleitung Dirk Schnieders ohne E-Mail; gelistete Adressen sind Gebiets-/Handelsvertretungen</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>G. Siempelkamp GmbH &amp; Co. KG</t>
+          <t>Papierverarbeitung Golzern GmbH</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Krefeld</t>
+          <t>Grimma (SN)</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -8758,19 +9416,19 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Keine persönliche Entscheider-E-Mail öffentlich</t>
+          <t>Falsche Branche (Papierverarbeitung), kein Maschinen-/Anlagenbau</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Hennecke GmbH</t>
+          <t>Kampfer (Formen- und Sondermaschinenbau)</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Sankt Augustin</t>
+          <t>Betzenstein (BY)</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -8780,19 +9438,19 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Deutlich unter 50 Mitarbeiter – außerhalb des ICP (E-Mail des Inhabers wäre vorhanden)</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Kautex Maschinenbau GmbH</t>
+          <t>ESMO AG / esmo automation</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Bonn</t>
+          <t>Rosenheim (BY)</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -8802,19 +9460,19 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Nur Funktionsadressen (sales.automation@, service.automation@); l.ingenhag ohne Positionsbeleg</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Lödige Industries GmbH</t>
+          <t>Grenzebach Maschinenbau GmbH</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Warburg/Paderborn</t>
+          <t>Asbach-Bäumenheim (BY)</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -8824,19 +9482,19 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Nur Standort-Sammeladressen; zudem Konzerngröße</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Schmidt + Clemens GmbH &amp; Co. KG</t>
+          <t>teamtechnik / BBS Automation</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Lindlar</t>
+          <t>Freiberg a.N. (BW)</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -8846,19 +9504,19 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Konzernstruktur, nur info-Adressen je Standort</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>MSK Verpackungs-Systeme GmbH</t>
+          <t>SCHMID Group</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Kleve</t>
+          <t>Freudenstadt (BW)</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -8868,19 +9526,19 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Nur Kontaktformulare, keine persönliche E-Mail</t>
+          <t>Keine persönlichen E-Mails, nur Sammeladressen</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>SPALECK GmbH &amp; Co. KG</t>
+          <t>HEDELIUS Maschinenfabrik GmbH</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Bocholt</t>
+          <t>Meppen (NI)</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -8890,19 +9548,19 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Keine persönliche Entscheider-E-Mail auffindbar</t>
+          <t>Nur Funktions-/Händleradressen, keine persönliche E-Mail</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Rhein-Nadel Automation GmbH</t>
+          <t>WENZEL Group GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Aachen</t>
+          <t>Wiesthal (BY)</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -8912,19 +9570,19 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Nur sales-Sammeladressen je Land</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>STRACK NORMA GmbH &amp; Co. KG</t>
+          <t>Maschinenfabrik EIRICH GmbH &amp; Co KG</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Lüdenscheid</t>
+          <t>Hardheim (BW)</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -8934,19 +9592,19 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Nur eirich@eirich.de bzw. Auslandsgesellschaften</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>TRACTO-TECHNIK GmbH &amp; Co. KG</t>
+          <t>PSB intralogistics GmbH</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Lennestadt</t>
+          <t>Pirmasens (RP)</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -8956,19 +9614,19 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Keine persönlichen E-Mails auf gecrawlten Seiten</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Albrecht Bäumer GmbH &amp; Co. KG</t>
+          <t>Langhammer GmbH</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Freudenberg</t>
+          <t>Eisenberg (RP)</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -8978,19 +9636,19 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Keine E-Mail-Adressen im Quelltext</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Düchting Pumpen Maschinenfabrik GmbH &amp; Co. KG</t>
+          <t>ROEMHELD Gruppe</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Wetter (Ruhr)</t>
+          <t>Laubach (HE)</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -9000,19 +9658,19 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Keine persönlichen E-Mails auffindbar</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A. Monforts Textilmaschinen GmbH &amp; Co. KG</t>
+          <t>HEMA Maschinen- und Apparateschutz GmbH</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Mönchengladbach</t>
+          <t>Seligenstadt (HE)</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -9022,19 +9680,19 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Einziger belegter Entscheider (Betriebsleiter) sitzt in der österreichischen Niederlassung – außerhalb NRW</t>
+          <t>Keine E-Mail-Adressen im Quelltext</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Murtfeldt Kunststoffe GmbH &amp; Co. KG</t>
+          <t>Sielaff GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>Herrieden (BY)</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -9044,19 +9702,19 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Nur Standort-Sammeladressen</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>DENIOS SE</t>
+          <t>MAFAC – E. Schwarz GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Bad Oeynhausen</t>
+          <t>Alpirsbach (BW)</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -9066,19 +9724,19 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Keine persönliche Entscheider-E-Mail öffentlich</t>
+          <t>Nur Adressen von Auslandsvertretungen, keine eigene Führungskraft</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Venjakob Maschinenbau GmbH &amp; Co. KG</t>
+          <t>IMSTec GmbH</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Rheda-Wiedenbrück</t>
+          <t>Heidelberg (BW)</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -9088,19 +9746,19 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Nur Team-Sammeladresse und US-Tochter</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Remmert GmbH</t>
+          <t>Pahnke Engineering GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Löhne</t>
+          <t>Hamburg</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -9110,19 +9768,19 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Standort außerhalb der Zielbundesländer</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Rippert GmbH &amp; Co. KG</t>
+          <t>SMB Sondermaschinenbau GmbH</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Herzebrock-Clarholz</t>
+          <t>Uplengen (NI)</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -9132,19 +9790,19 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Nur info@smb-sondermaschinen.de; GF Wolfgang Blank ohne persönliche E-Mail</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Ohrmann GmbH Montagetechnik</t>
+          <t>DMV Sondermaschinenbau GmbH</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Rheda-Wiedenbrück</t>
+          <t>Bad Wünnenberg</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -9154,19 +9812,19 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Nur dmv@dmv-sondermaschinenbau.de; zudem NRW</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Sollich KG</t>
+          <t>Knecht Maschinenbau GmbH</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Bad Salzuflen</t>
+          <t>Bergatreute (BW)</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -9176,19 +9834,19 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Keine persönliche E-Mail auf Website auffindbar</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>steute Technologies GmbH &amp; Co. KG</t>
+          <t>Rühle &amp; Co. Maschinenbau GmbH</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Löhne</t>
+          <t>Walzbachtal (BW)</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -9198,19 +9856,19 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Keine E-Mail-Adressen der Geschäftsführung veröffentlicht</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Torwegge GmbH &amp; Co. KG</t>
+          <t>Emsland Metallbau GmbH – Arnd Brinkmann (Vertrieb)</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Bielefeld</t>
+          <t>Salzbergen (NI)</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -9220,19 +9878,19 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Für Vertriebskontakt keine E-Mail wörtlich gelistet (nur Sammeladresse Anfragen_Vertrieb@)</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Wemhöner Surface Technologies GmbH &amp; Co. KG</t>
+          <t>Wilhelm Altendorf GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Herford</t>
+          <t>Minden</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -9242,19 +9900,19 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Nur internationale Handelsvertreter-Mails, keine Geschäftsführung</t>
+          <t>Zahlreiche personenbezogene E-Mails auf der Website, aber keine davon einem Geschäftsführer/Prokuristen oder zulässigen Bereichsleiter zugeordnet</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>RK Rose+Krieger GmbH</t>
+          <t>Kolbus GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Minden</t>
+          <t>Rahden</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -9264,19 +9922,19 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Nur Funktions-/Auslandspostfächer; zudem Konzernzugehörigkeit (Phoenix Mecano)</t>
+          <t>Keine persönliche Entscheider-E-Mail auf Website/Impressum/Kontakt gefunden</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Carl Werthenbach Konstruktionsteile GmbH &amp; Co. KG</t>
+          <t>AUMUND Fördertechnik GmbH</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Bielefeld</t>
+          <t>Rheinberg</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -9286,19 +9944,19 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Geschäftsführer im Impressum genannt, aber nur info@/industrietechnik@ – keine persönliche E-Mail</t>
+          <t>Nur Kontaktformulare, keine persönliche E-Mail</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Seppeler Holding und Verwaltungs GmbH &amp; Co. KG</t>
+          <t>THIELE GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Rietberg</t>
+          <t>Iserlohn</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -9308,19 +9966,19 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Geschäftsführer im Impressum genannt, aber nur info-holding@ – keine persönliche E-Mail</t>
+          <t>Nur Sammeladressen (hebetechnik@) – keine persönliche Entscheider-E-Mail</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>MIT Moderne Industrietechnik GmbH &amp; Co. KG</t>
+          <t>HASCO Hasenclever GmbH + Co KG</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Vlotho</t>
+          <t>Lüdenscheid</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -9330,19 +9988,19 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Geschäftsführung genannt, E-Mail nur als Sammeladresse mit@systemarmaturen.de</t>
+          <t>Keine persönliche E-Mail öffentlich</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Schubert &amp; Salzer / ventiltechnik.de (Vlotho)</t>
+          <t>Gebr. Eickhoff Maschinenfabrik</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Vlotho</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -9352,19 +10010,19 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Persönliche Mails nur für Vertriebsleitung/Sales Director – keine Geschäftsführung, Vertrieb zählt laut Vorgabe nicht</t>
+          <t>Keine persönliche E-Mail öffentlich</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Heilig Maschinenbau GmbH</t>
+          <t>Herbert Kannegiesser GmbH</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Bad Salzuflen</t>
+          <t>Vlotho</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -9374,19 +10032,19 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Impressum nennt GF Sascha Heilig, die angegebene Adresse heilig@heilig-maschinenbau.de ist jedoch nicht eindeutig persönlich (Firmenname = Nachname) – bei Unsicherheit verworfen</t>
+          <t>Keine persönliche E-Mail öffentlich</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>ATL Luhden GmbH</t>
+          <t>HAVER &amp; BOECKER OHG</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Luhden</t>
+          <t>Oelde</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -9396,19 +10054,19 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Betriebsleiter/Prokurist mit persönlicher Mail belegt, Standort liegt jedoch in Niedersachsen (nicht NRW)</t>
+          <t>Personenbezogene Mails nur im Vertriebs-/Auslandsnetz, kein Entscheider mit Rolle belegt</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>DUBOR Groneweg GmbH &amp; Co. KG</t>
+          <t>Reifenhäuser GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Bad Salzuflen</t>
+          <t>Troisdorf</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -9418,19 +10076,19 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Ansprechpartnerseite mit Entscheidern vorhanden, aber Branche Backmittel/Lebensmittel – kein Maschinenbau; GF-Adressen zudem nur info@</t>
+          <t>Nur Fachbereichs-/Recruiting-Mails, keine Geschäftsführung</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>AMR-Engineering GmbH</t>
+          <t>battenfeld-cincinnati Germany GmbH</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Essen</t>
+          <t>Bad Oeynhausen</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -9440,19 +10098,19 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Geschäftsführer im Impressum genannt, aber nur Sammeladresse amr@amr.de</t>
+          <t>Nur Vertriebs-/Länderkontakte, keine Entscheider-E-Mail</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>SIEBTECHNIK TEMA GmbH</t>
+          <t>Hanning Elektro-Werke GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Mülheim an der Ruhr</t>
+          <t>Oerlinghausen</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -9462,19 +10120,19 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Nur Vertriebspartner-Mails; Impressum-Mail gehört zum externen Datenschutzbeauftragten</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>HAZEMAG &amp; EPR GmbH</t>
+          <t>Dürkopp Adler GmbH</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Dülmen</t>
+          <t>Bielefeld</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -9484,19 +10142,19 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Nur Vertriebspartner-Adressen; zudem Konzernstruktur</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>BOGE KOMPRESSOREN Otto Boge GmbH &amp; Co. KG</t>
+          <t>Klingelnberg GmbH</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Bielefeld</t>
+          <t>Hückeswagen</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -9506,19 +10164,19 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Nur Länder-Sammelpostfächer</t>
+          <t>Nur Funktionspostfächer (kegelrad@, seminar@ etc.)</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>PROBAT SE</t>
+          <t>Kampf Schneid- und Wickeltechnik GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Emmerich am Rhein</t>
+          <t>Wiehl</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -9528,19 +10186,19 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Nur weltweite Vertriebs-/Agenturkontakte, keine Geschäftsführung</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Otto Junker GmbH</t>
+          <t>Achenbach Buschhütten GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Simmerath</t>
+          <t>Kreuztal</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -9550,19 +10208,19 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Nur Funktionspostfach fertigung@</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>REMBE GmbH Safety+Control</t>
+          <t>Gebr. Becker GmbH</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Brilon</t>
+          <t>Wuppertal</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -9572,19 +10230,19 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Personenbezogene Mails nur im Vertriebsinnendienst/Service ohne Entscheiderrolle</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>OVENTROP GmbH &amp; Co. KG</t>
+          <t>KettenWulf Betriebs GmbH</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Olsberg</t>
+          <t>Eslohe</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -9601,12 +10259,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>BJB GmbH &amp; Co. KG</t>
+          <t>ELHA-MASCHINENBAU Liemke KG</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Arnsberg</t>
+          <t>Halle (Westf.)</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -9616,19 +10274,19 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Nur ausländische Vertriebspartner-Mails</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Ruhrpumpen GmbH</t>
+          <t>G. Siempelkamp GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Witten</t>
+          <t>Krefeld</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -9638,19 +10296,19 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Keine persönliche Entscheider-E-Mail öffentlich</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Winkelmann Group GmbH + Co. KG</t>
+          <t>Hennecke GmbH</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Ahlen</t>
+          <t>Sankt Augustin</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -9667,12 +10325,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>GERSTUNG Sondermaschinen GmbH</t>
+          <t>Kautex Maschinenbau GmbH</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Mönchengladbach</t>
+          <t>Bonn</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -9689,12 +10347,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>AUMAT Maschinenbau GmbH</t>
+          <t>Lödige Industries GmbH</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>NRW</t>
+          <t>Warburg/Paderborn</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -9711,12 +10369,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Maschinen- und Industriebau Feld GmbH</t>
+          <t>Schmidt + Clemens GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>NRW</t>
+          <t>Lindlar</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -9726,19 +10384,19 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Ansprechpartnerseite vorhanden, aber ohne persönliche E-Mail-Adressen</t>
+          <t>Keine persönliche E-Mail öffentlich</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>VGS Automatisierungstechnik GmbH &amp; Co. KG</t>
+          <t>MSK Verpackungs-Systeme GmbH</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Schloß Holte-Stukenbrock</t>
+          <t>Kleve</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -9748,19 +10406,19 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Nur Kontaktformulare, keine persönliche E-Mail</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Ebert Maschinenbau GmbH</t>
+          <t>SPALECK GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Minden</t>
+          <t>Bocholt</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -9770,19 +10428,19 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Keine persönliche Entscheider-E-Mail auffindbar</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>BELU GmbH</t>
+          <t>Rhein-Nadel Automation GmbH</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Bielefeld</t>
+          <t>Aachen</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -9799,12 +10457,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Pfister Fertigungstechnik / GMM mbH / MB Klich</t>
+          <t>STRACK NORMA GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>NRW</t>
+          <t>Lüdenscheid</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -9814,19 +10472,19 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>CNC-Lohnfertiger ohne persönliche Entscheider-E-Mail auf der Website</t>
+          <t>Keine persönliche E-Mail öffentlich</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Selzer Formenbau GmbH / Dietrich Formenbau / KM Formenbau / Jedig &amp; Heyns / Wilfrid Humme</t>
+          <t>TRACTO-TECHNIK GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Lüdenscheid</t>
+          <t>Lennestadt</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -9836,27 +10494,907 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Werkzeug-/Formenbauer ohne persönliche Entscheider-E-Mail auf der Website</t>
+          <t>Keine persönliche E-Mail öffentlich</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
+          <t>Albrecht Bäumer GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Freudenberg</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Düchting Pumpen Maschinenfabrik GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Wetter (Ruhr)</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>A. Monforts Textilmaschinen GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Mönchengladbach</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Einziger belegter Entscheider (Betriebsleiter) sitzt in der österreichischen Niederlassung – außerhalb NRW</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Murtfeldt Kunststoffe GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Dortmund</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>DENIOS SE</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Bad Oeynhausen</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Keine persönliche Entscheider-E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Venjakob Maschinenbau GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Rheda-Wiedenbrück</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Remmert GmbH</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Löhne</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Rippert GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Herzebrock-Clarholz</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Ohrmann GmbH Montagetechnik</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Rheda-Wiedenbrück</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Sollich KG</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Bad Salzuflen</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>steute Technologies GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Löhne</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Torwegge GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Bielefeld</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Wemhöner Surface Technologies GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Herford</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Nur internationale Handelsvertreter-Mails, keine Geschäftsführung</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>RK Rose+Krieger GmbH</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Minden</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Nur Funktions-/Auslandspostfächer; zudem Konzernzugehörigkeit (Phoenix Mecano)</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Carl Werthenbach Konstruktionsteile GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Bielefeld</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Geschäftsführer im Impressum genannt, aber nur info@/industrietechnik@ – keine persönliche E-Mail</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Seppeler Holding und Verwaltungs GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Rietberg</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Geschäftsführer im Impressum genannt, aber nur info-holding@ – keine persönliche E-Mail</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>MIT Moderne Industrietechnik GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Vlotho</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Geschäftsführung genannt, E-Mail nur als Sammeladresse mit@systemarmaturen.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Schubert &amp; Salzer / ventiltechnik.de (Vlotho)</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Vlotho</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Persönliche Mails nur für Vertriebsleitung/Sales Director – keine Geschäftsführung, Vertrieb zählt laut Vorgabe nicht</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Heilig Maschinenbau GmbH</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Bad Salzuflen</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Impressum nennt GF Sascha Heilig, die angegebene Adresse heilig@heilig-maschinenbau.de ist jedoch nicht eindeutig persönlich (Firmenname = Nachname) – bei Unsicherheit verworfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>ATL Luhden GmbH</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Luhden</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Betriebsleiter/Prokurist mit persönlicher Mail belegt, Standort liegt jedoch in Niedersachsen (nicht NRW)</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>DUBOR Groneweg GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Bad Salzuflen</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Ansprechpartnerseite mit Entscheidern vorhanden, aber Branche Backmittel/Lebensmittel – kein Maschinenbau; GF-Adressen zudem nur info@</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>AMR-Engineering GmbH</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Essen</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Geschäftsführer im Impressum genannt, aber nur Sammeladresse amr@amr.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>SIEBTECHNIK TEMA GmbH</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Mülheim an der Ruhr</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>HAZEMAG &amp; EPR GmbH</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Dülmen</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>BOGE KOMPRESSOREN Otto Boge GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Bielefeld</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Nur Länder-Sammelpostfächer</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>PROBAT SE</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Emmerich am Rhein</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Otto Junker GmbH</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Simmerath</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>REMBE GmbH Safety+Control</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Brilon</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>OVENTROP GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Olsberg</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>BJB GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Arnsberg</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Ruhrpumpen GmbH</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Witten</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Winkelmann Group GmbH + Co. KG</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Ahlen</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>GERSTUNG Sondermaschinen GmbH</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Mönchengladbach</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>AUMAT Maschinenbau GmbH</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>NRW</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Maschinen- und Industriebau Feld GmbH</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>NRW</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Ansprechpartnerseite vorhanden, aber ohne persönliche E-Mail-Adressen</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>VGS Automatisierungstechnik GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Schloß Holte-Stukenbrock</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Ebert Maschinenbau GmbH</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Minden</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>BELU GmbH</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Bielefeld</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Pfister Fertigungstechnik / GMM mbH / MB Klich</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>NRW</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>CNC-Lohnfertiger ohne persönliche Entscheider-E-Mail auf der Website</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Selzer Formenbau GmbH / Dietrich Formenbau / KM Formenbau / Jedig &amp; Heyns / Wilfrid Humme</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Lüdenscheid</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Werkzeug-/Formenbauer ohne persönliche Entscheider-E-Mail auf der Website</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
           <t>Hagener Fördertechnik – Stefan Maschmeier (Prokurist)</t>
         </is>
       </c>
-      <c r="B228" t="inlineStr">
+      <c r="B268" t="inlineStr">
         <is>
           <t>Hagen</t>
         </is>
       </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>Maschinenbau &amp; Fertigung</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr">
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
         <is>
           <t>Als zweiter Entscheider geprüft, aber nur info@hafoe.de hinterlegt – daher nicht verwendet</t>
         </is>

--- a/leads-adept/leads-adept.xlsx
+++ b/leads-adept/leads-adept.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Verworfen" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$I$121</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$I$134</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I121"/>
+  <dimension ref="A1:I134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -5667,27 +5667,27 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Franco Menchetti</t>
+          <t>Senol Topcu</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Vertriebsleiter &amp; Prokurist</t>
+          <t>Geschäftsführer</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Franco.Menchetti@cta-gmbh.de</t>
+          <t>s.topcu@chemopur.info</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>+49 7141 299916-148</t>
+          <t>+49 2323 98797-0</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>CTA GmbH</t>
+          <t>CHEMOPUR H. Brand GmbH</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
@@ -5697,44 +5697,44 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>Ludwigsburg (Baden-Württemberg)</t>
+          <t>Herne (Baukauer Str. 125, 44653 Herne)</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>Lohnabfüller und Lohnfertiger für chemisch-technische Produkte (Flüssigkeiten, Aerosole, Sets) inkl. Standort in den USA.</t>
+          <t>Mittelständischer Hersteller von Polyurethan- und Reaktionsharzsystemen sowie Beschichtungs-/Bauchemieprodukten mit eigener Anwendungstechnik und F&amp;E.</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>https://www.cta-gmbh.de/kontakt/ | https://www.cta-gmbh.de/lohnabfuellung-in-den-usa-ihre-ansprechpartner/</t>
+          <t>https://chemopur.de/kontakt/ | https://chemopur.de/impressum/</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>Hans-Dieter Worch</t>
+          <t>Martin Polczyk</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer</t>
+          <t>Managing Director / CEO</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>hans-dieter.worch@cta-gmbh.de</t>
+          <t>polczyk@cofermin.de</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>+49 7141 299916-0 (Zentrale; keine persönliche Durchwahl veröffentlicht)</t>
+          <t>+49 201 43878-35</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>CTA GmbH</t>
+          <t>COFERMIN Group / Cofermin Chemicals GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
@@ -5744,44 +5744,44 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Ludwigsburg (Baden-Württemberg)</t>
+          <t>Essen</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>Lohnabfüller und Lohnfertiger für chemisch-technische Produkte (Flüssigkeiten, Aerosole, Sets) inkl. Standort in den USA.</t>
+          <t>Inhabergeführte Essener Gruppe für Chemikalien- und Mineralstoffhandel, Feuerfest und chemische Spezialitäten mit mehreren Produktions- und Handelsgesellschaften.</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>https://www.cta-gmbh.de/lohnabfuellung-in-den-usa-ihre-ansprechpartner/ | https://www.cta-gmbh.de/kontakt/ (dort: 'Hans-Dieter Worch Geschäftsführer')</t>
+          <t>https://cofermin.de/ansprechpartner/</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Dimitri Peters</t>
+          <t>Franco Menchetti</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Werksleiter (Produktion)</t>
+          <t>Vertriebsleiter &amp; Prokurist</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>d.peters@dr-demuth.com</t>
+          <t>Franco.Menchetti@cta-gmbh.de</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>+49 5551 9794-36</t>
+          <t>+49 7141 299916-148</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>Dr. Demuth Derisol Lackfarben GmbH &amp; Co. KG</t>
+          <t>CTA GmbH</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
@@ -5791,44 +5791,44 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>Raum Northeim (Niedersachsen)</t>
+          <t>Ludwigsburg (Baden-Württemberg)</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>Seit über 60 Jahren Hersteller von Lackfarben und Beschichtungen 'Made in Germany'; eigene Produktion mit Werksleitung und Labor.</t>
+          <t>Lohnabfüller und Lohnfertiger für chemisch-technische Produkte (Flüssigkeiten, Aerosole, Sets) inkl. Standort in den USA.</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>https://www.dr-demuth.com/das-team</t>
+          <t>https://www.cta-gmbh.de/kontakt/ | https://www.cta-gmbh.de/lohnabfuellung-in-den-usa-ihre-ansprechpartner/</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>Ludwig Haring</t>
+          <t>Hans-Dieter Worch</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführung</t>
+          <t>Geschäftsführer</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>l.haring@dr-demuth.com</t>
+          <t>hans-dieter.worch@cta-gmbh.de</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>+49 5551 9794-10</t>
+          <t>+49 7141 299916-0 (Zentrale; keine persönliche Durchwahl veröffentlicht)</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>Dr. Demuth Derisol Lackfarben GmbH &amp; Co. KG</t>
+          <t>CTA GmbH</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
@@ -5838,44 +5838,44 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>Raum Northeim (Niedersachsen)</t>
+          <t>Ludwigsburg (Baden-Württemberg)</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>Seit über 60 Jahren Hersteller von Lackfarben und Beschichtungen 'Made in Germany'; eigene Produktion mit Werksleitung und Labor.</t>
+          <t>Lohnabfüller und Lohnfertiger für chemisch-technische Produkte (Flüssigkeiten, Aerosole, Sets) inkl. Standort in den USA.</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>https://www.dr-demuth.com/das-team | https://www.dr-demuth.com/das-team (Zitat: 'Unser Team von rund 60 Mitarbeitern')</t>
+          <t>https://www.cta-gmbh.de/lohnabfuellung-in-den-usa-ihre-ansprechpartner/ | https://www.cta-gmbh.de/kontakt/ (dort: 'Hans-Dieter Worch Geschäftsführer')</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Rainer Hähnle</t>
+          <t>Benjamin Wrobel</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Einkaufsleiter</t>
+          <t>COO (Chief Operating Officer)</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>rainer.haehnle@haering.de</t>
+          <t>b.wrobel@wocklum.de</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>+49 7130 4702-70</t>
+          <t>+49 2375 925 291</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>HAERING GmbH</t>
+          <t>Chemische Fabrik Wocklum (Wocklum Chemie)</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
@@ -5885,44 +5885,44 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>Untergruppenbach-Unterheinriet (Baden-Württemberg)</t>
+          <t>Balve (Sauerland/Westfalen)</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>Seit rund 140 Jahren mittelständischer Hersteller von Farben, Lacken und Bautenschutzprodukten mit eigenem Farbstudio und Auslieferungslager.</t>
+          <t>Familiengeführte Chemiegruppe mit Lohnfertigung/Contract Manufacturing, Bulk-Handel sowie Recycling und Entsorgung chemischer Produkte. Geschäftsführer laut Seite: Gero Hertin (nur Sammeladresse geschaeftsfuehrung@wocklum-gruppe.de).</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>https://www.haering.de/kontakt | https://www.haering.de/unternehmen (Zitat: '100 Mitarbeiter') | https://www.haering-lacke.de/kontakt</t>
+          <t>https://wocklum-chemie.de/kontakt/</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>Sergey Krasnikov</t>
+          <t>Julian Cirkel</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>EDV-Leiter (IT)</t>
+          <t>Geschäftsführer (Managing Director), Inhaberfamilie</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>sergey.krasnikov@haering.de</t>
+          <t>julian.cirkel@cirkel.de</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>+49 7130 4702-32</t>
+          <t>+49 2364 938124</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>HAERING GmbH</t>
+          <t>Cirkel GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
@@ -5932,44 +5932,44 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>Untergruppenbach-Unterheinriet (Baden-Württemberg)</t>
+          <t>Haltern am See (Werk Wickede, Standort Emsdetten)</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>Seit rund 140 Jahren mittelständischer Hersteller von Farben, Lacken und Bautenschutzprodukten mit eigenem Farbstudio und Auslieferungslager.</t>
+          <t>Familiengeführter Hersteller mineralischer Bau- und Prozessstoffe (Baustoffe, multifunktionale Mineralien) mit mehreren Produktionsstandorten in NRW.</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>https://www.haering.de/kontakt</t>
+          <t>https://www.cirkel.de/kontakt</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>Dirk Ruppmann</t>
+          <t>Dr. Sabrina Mondrzyk</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Betriebsleitung / Prokurist</t>
+          <t>Kaufmännische Leitung</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>dirkruppmann@kapp-chemie.com</t>
+          <t>sabrina.mondrzyk@dhc-solvent.de</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>+49 6772 9311-250</t>
+          <t>+49 208 9940-161</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>KAPP-CHEMIE GmbH &amp; Co. KG</t>
+          <t>DHC Solvent Chemie GmbH</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
@@ -5979,44 +5979,44 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>Miehlen (Rheinland-Pfalz)</t>
+          <t>Mülheim an der Ruhr</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>Mittelständischer Spezialchemie-Hersteller (u. a. Farbstoffe, technische Chemikalien, Lohnfertigung). Gehört zur familiengeführten STOCKMEIER-Gruppe.</t>
+          <t>Hersteller und Aufbereiter von Lösemitteln und Lösemittelrecycling für Lack-, Klebstoff- und Prozessindustrie. Geschäftsführer laut Impressum: Thomas Schreiber, Michaela Hodyas (nur info@-Adresse veröffentlicht).</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>https://www.stockmeier.com/de/kapp-chemie/kontakt/ | https://www.kapp-chemie.de/de/kapp-chemie/kontakt/</t>
+          <t>https://dhc-solvent.de/vertrieb/ | https://dhc-solvent.de/impressum/</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>Hendrik Breiden</t>
+          <t>Dimitri Peters</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Leitung Einkauf/Logistik</t>
+          <t>Werksleiter (Produktion)</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>hendrikbreiden@kapp-chemie.com</t>
+          <t>d.peters@dr-demuth.com</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>+49 6772 9311-150</t>
+          <t>+49 5551 9794-36</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>KAPP-CHEMIE GmbH &amp; Co. KG</t>
+          <t>Dr. Demuth Derisol Lackfarben GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
@@ -6026,44 +6026,44 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>Miehlen (Rheinland-Pfalz)</t>
+          <t>Raum Northeim (Niedersachsen)</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>Mittelständischer Spezialchemie-Hersteller (u. a. Farbstoffe, technische Chemikalien, Lohnfertigung). Gehört zur familiengeführten STOCKMEIER-Gruppe.</t>
+          <t>Seit über 60 Jahren Hersteller von Lackfarben und Beschichtungen 'Made in Germany'; eigene Produktion mit Werksleitung und Labor.</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>https://www.stockmeier.com/de/kapp-chemie/kontakt/ | https://www.kapp-chemie.de/de/kapp-chemie/kontakt/</t>
+          <t>https://www.dr-demuth.com/das-team</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>Marco Hermann</t>
+          <t>Ludwig Haring</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer</t>
+          <t>Geschäftsführung</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>marcohermann@kapp-chemie.com</t>
+          <t>l.haring@dr-demuth.com</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>+49 6772 9311-360</t>
+          <t>+49 5551 9794-10</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>KAPP-CHEMIE GmbH &amp; Co. KG</t>
+          <t>Dr. Demuth Derisol Lackfarben GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
@@ -6073,69 +6073,680 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Miehlen (Rheinland-Pfalz)</t>
+          <t>Raum Northeim (Niedersachsen)</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>Mittelständischer Spezialchemie-Hersteller (u. a. Farbstoffe, technische Chemikalien, Lohnfertigung). Gehört zur familiengeführten STOCKMEIER-Gruppe.</t>
+          <t>Seit über 60 Jahren Hersteller von Lackfarben und Beschichtungen 'Made in Germany'; eigene Produktion mit Werksleitung und Labor.</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>https://www.stockmeier.com/de/kapp-chemie/kontakt/ | https://www.kapp-chemie.de/de/kapp-chemie/kontakt/</t>
+          <t>https://www.dr-demuth.com/das-team | https://www.dr-demuth.com/das-team (Zitat: 'Unser Team von rund 60 Mitarbeitern')</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>Olaf Fresdorf</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>Leitung Produktion sowie Leitung Beratung und Verkauf</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>fresdorf@eurotech-kunststofftechnik.de</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>+49 208 6209220</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>Eurotech Kunststofftechnik GmbH</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>Chemie &amp; Prozessindustrie</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>Oberhausen (Otto-Roelen-Straße 1, 46147)</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>Kunststoffverarbeitender Betrieb im Ruhrgebiet (Halbzeuge, Zuschnitt, Fertigteile) mit eigener Produktion und technischer Beratung.</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>https://www.eurotech.nrw/unternehmen</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>Gerd Kleemeyer</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführer</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>gerd.kleemeyer@gera-chemie.de</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>+49 208 802080</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>GERA Chemie GmbH</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>Chemie &amp; Prozessindustrie</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>Mülheim an der Ruhr</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>Inhabergeführter Hersteller/Konfektionierer chemischer Spezialitäten mit eigener Produktion und Labor im Ruhrgebiet.</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gera-chemie.de/team/</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>Rainer Hähnle</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>Einkaufsleiter</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>rainer.haehnle@haering.de</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>+49 7130 4702-70</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>HAERING GmbH</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>Chemie &amp; Prozessindustrie</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>Untergruppenbach-Unterheinriet (Baden-Württemberg)</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>Seit rund 140 Jahren mittelständischer Hersteller von Farben, Lacken und Bautenschutzprodukten mit eigenem Farbstudio und Auslieferungslager.</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>https://www.haering.de/kontakt | https://www.haering.de/unternehmen (Zitat: '100 Mitarbeiter') | https://www.haering-lacke.de/kontakt</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>Sergey Krasnikov</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>EDV-Leiter (IT)</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>sergey.krasnikov@haering.de</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>+49 7130 4702-32</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>HAERING GmbH</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>Chemie &amp; Prozessindustrie</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>Untergruppenbach-Unterheinriet (Baden-Württemberg)</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>Seit rund 140 Jahren mittelständischer Hersteller von Farben, Lacken und Bautenschutzprodukten mit eigenem Farbstudio und Auslieferungslager.</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>https://www.haering.de/kontakt</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>Daniel Neubner</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director (Geschäftsführer)</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>dn@harke.com</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>+49 208 3069-1050</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>HARKE GROUP / HARKE Chemicals GmbH</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>Chemie &amp; Prozessindustrie</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>Mülheim an der Ruhr</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>Inhabergeführte Unternehmensgruppe für Spezialchemikalien, Distribution, Lohnabfüllung/CoPacking und Eigenprodukte (u.a. SOLUBLON). Sitz Xantener Straße 1, Mülheim an der Ruhr.</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>https://www.harke.com/contact/ | https://www.harke.com/harke-group/about-us/</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>Benjamin Hille</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>Leiter Logistik</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>benjamin.hille@harold-scholz.de</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>+49 2361 98880</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>Harold Scholz &amp; Co. GmbH (Scholz Farbpigmente)</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>Chemie &amp; Prozessindustrie</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>Recklinghausen (Suderwich)</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>Familiengeführter Hersteller von Farbpigmenten und Pigmentpräparationen für Bau, Farbe &amp; Lack sowie Kunststoff, mit Tochtergesellschaften in AT, CH und BeNeLux.</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>https://www.harold-scholz.de/uber-uns/unser-team | https://www.harold-scholz.de/impressum</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>Dirk Ruppmann</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>Betriebsleitung / Prokurist</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>dirkruppmann@kapp-chemie.com</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>+49 6772 9311-250</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>KAPP-CHEMIE GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>Chemie &amp; Prozessindustrie</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>Miehlen (Rheinland-Pfalz)</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>Mittelständischer Spezialchemie-Hersteller (u. a. Farbstoffe, technische Chemikalien, Lohnfertigung). Gehört zur familiengeführten STOCKMEIER-Gruppe.</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>https://www.stockmeier.com/de/kapp-chemie/kontakt/ | https://www.kapp-chemie.de/de/kapp-chemie/kontakt/</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>Hendrik Breiden</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>Leitung Einkauf/Logistik</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>hendrikbreiden@kapp-chemie.com</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>+49 6772 9311-150</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>KAPP-CHEMIE GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>Chemie &amp; Prozessindustrie</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>Miehlen (Rheinland-Pfalz)</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>Mittelständischer Spezialchemie-Hersteller (u. a. Farbstoffe, technische Chemikalien, Lohnfertigung). Gehört zur familiengeführten STOCKMEIER-Gruppe.</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>https://www.stockmeier.com/de/kapp-chemie/kontakt/ | https://www.kapp-chemie.de/de/kapp-chemie/kontakt/</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>Marco Hermann</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführer</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>marcohermann@kapp-chemie.com</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>+49 6772 9311-360</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>KAPP-CHEMIE GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>Chemie &amp; Prozessindustrie</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>Miehlen (Rheinland-Pfalz)</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>Mittelständischer Spezialchemie-Hersteller (u. a. Farbstoffe, technische Chemikalien, Lohnfertigung). Gehört zur familiengeführten STOCKMEIER-Gruppe.</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>https://www.stockmeier.com/de/kapp-chemie/kontakt/ | https://www.kapp-chemie.de/de/kapp-chemie/kontakt/</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>Jochen Obermeier</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>CEO / Geschäftsleitung (Inhaberfamilie)</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>jochen.obermeier@obermeier.de</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>+49 2751 524-0</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>Kurt Obermeier GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>Chemie &amp; Prozessindustrie</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>Bad Berleburg (Wittgenstein/Westfalen)</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>Familienunternehmen der Spezialchemie: Silikone, Trennmittel, Metallbearbeitungs- und Spezialchemikalien mit eigenem Vertrieb und Anwendungstechnik/F&amp;E.</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>https://www.obermeier.de/kontakt/ansprechpartner/</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>Tobias Adamczyk</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Manager</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>tobias.adamczyk@orontec.com</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>+49 202 52746318</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>ORONTEC GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>Chemie &amp; Prozessindustrie</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>Dortmund (Hauptsitz), Niederlassung Wuppertal</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>Mittelständischer Anbieter chemisch-technischer Spezialprodukte und Prozesschemikalien für Industrieanwendungen mit internationalen Partnerstandorten.</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>https://orontec.com/kontakt/ | https://orontec.com/unternehmen/standorte/</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>Marko Sonnemann</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführer</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>ms@pentacarbon.de</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>+49 2364 89979-70</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>PentaCarbon GmbH</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>Chemie &amp; Prozessindustrie</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>Haltern am See</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>Inhabergeführter Spezialist für Kohlenstoff-/Graphitprodukte und technische Rohstoffe für die Prozessindustrie mit eigener Materialwirtschaft und Standorten in Polen und der Ukraine.</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>https://www.pentacarbon.de/unternehmen/</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>Oliver Sentek</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführer</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>sentek@technifol.de</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>+49 2368 87962-22</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>Technifol Verpackungsfolien GmbH</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>Chemie &amp; Prozessindustrie</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>Oer-Erkenschwick (Karlstr. 1, 45739)</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>Anbieter von Kunststoff-Verpackungsfolien und Verpackungsmaschinen inkl. eigenem Service; zweiter Geschäftsführer Manuel Zielke (zielke@technifol.de).</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>https://technifol.de/ansprechpartner/</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
           <t>Michael Stache</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
         <is>
           <t>Geschäftsführender Gesellschafter</t>
         </is>
       </c>
-      <c r="C121" s="2" t="inlineStr">
+      <c r="C134" s="2" t="inlineStr">
         <is>
           <t>michael.stache@wigol.de</t>
         </is>
       </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>+49 6241 4141-0 (Zentrale; keine persönliche Durchwahl veröffentlicht)</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>WIGOL W. Stache GmbH</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr">
         <is>
           <t>Worms (Rheinland-Pfalz)</t>
         </is>
       </c>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>Familiengeführter Hersteller von Reinigungs- und Prozesschemie für Lebensmittel-/Getränke-, Pharma-, Kosmetikindustrie sowie Oberflächentechnik und Industriereinigung.</t>
         </is>
       </c>
-      <c r="I121" s="2" t="inlineStr">
+      <c r="I134" s="2" t="inlineStr">
         <is>
           <t>https://www.wigol.de/de/kontakt</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I121"/>
+  <autoFilter ref="A1:I134"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6217,10 +6828,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="C5" t="n">
-        <v>40</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6">
@@ -6230,10 +6841,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="C6" t="n">
-        <v>298</v>
+        <v>341</v>
       </c>
     </row>
   </sheetData>
@@ -6247,7 +6858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D299"/>
+  <dimension ref="A1:D342"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -7843,958 +8454,958 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Hermann Ritter GmbH &amp; Co. KG (Ritter Spedition)</t>
+          <t>HUELSEMANN Coatings GmbH (Hülsemann Lacke)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Feilitzsch-Zedtwitz, Bayern</t>
+          <t>Wuppertal</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>nur 40 Mitarbeiter (unter Zielgröße) und nur info@-Adresse</t>
+          <t>Nur info@huelsemann.com auf Unternehmens-/Kontaktseite; keine persönliche E-Mail der Geschäftsführer Philipp/Thomas Hülsemann auffindbar</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Metzger Spedition GmbH</t>
+          <t>Schwerter Lackfabrik (SL-Lacke)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Neu-Kupfer, Baden-Württemberg</t>
+          <t>Wuppertal/Schwerte</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>nur info@metzger-spedition.de, keine Personen auf der Website</t>
+          <t>Nur info@sl-lacke.de; keine Personen mit E-Mail genannt</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Rüdinger Spedition GmbH</t>
+          <t>Rach GmbH (Rachlacke)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Krautheim, Baden-Württemberg</t>
+          <t>Oberhausen</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Ansprechpartner mit Namen/Positionen, aber E-Mail-Adressen verschleiert; auch per curl keine Adresse im Quelltext</t>
+          <t>Ansprechpartner-Seite ohne wörtliche E-Mail-Adressen</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ZUFALL logistics group (Friedrich Zufall GmbH &amp; Co. KG)</t>
+          <t>Swd Lubricants GmbH &amp; Co. KG (Schmierstoffwerk Duisburg)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Göttingen, Niedersachsen</t>
+          <t>Duisburg</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>nur standortbezogene Sammeladressen (goettingen@, kassel@ …), keine persönliche E-Mail der Geschäftsführung</t>
+          <t>Seite liefert keinen crawlbaren Inhalt/keine E-Mail-Adressen</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Heinrich Koch Internationale Spedition GmbH &amp; Co. KG</t>
+          <t>Assindia Chemie GmbH</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Osnabrück, Niedersachsen</t>
+          <t>Bottrop</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>auf der Kontaktseite nur info@koch-international.de, keine Ansprechpartner-Seite mit Personen-E-Mails</t>
+          <t>Nur info[at]assindia.de, keine Personen mit E-Mail</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Döderlein Spedition GmbH</t>
+          <t>ERKOL FILL GmbH</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Nördlingen, Bayern</t>
+          <t>Solingen</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>nur info@doederlein.de, keine Ansprechpartner-/Teamseite</t>
+          <t>Geschäftsführende Gesellschafter (Gökhan/Ahmet/Yusuf Erkol) genannt, aber nur info@erkolfill.de</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Elflein Spedition &amp; Transport GmbH</t>
+          <t>FRAGOL GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Bamberg, Bayern</t>
+          <t>Mülheim an der Ruhr</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Geschäftsführer mit Durchwahl gelistet, aber E-Mail-Links leer ('#') – keine wörtliche Adresse auf der Seite</t>
+          <t>Nur Funktionspostfächer (htf@, lubes@, rewe@), keine persönlichen Adressen</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Spedicam GmbH</t>
+          <t>MOLYDUVAL GmbH</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Neufahrn (Raum München), Bayern</t>
+          <t>Ratingen</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>nur Funktionsadressen (Gf@, Sl@, Vl@ …), keine personenbezogenen E-Mails</t>
+          <t>Impressum nennt GF Carsten und Tobias Wunsch sowie twunsch@molyduval.com, aber ohne wörtliche Zuordnung zu einer Person – Zuordnung wäre Vermutung</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Wiedmann &amp; Winz GmbH</t>
+          <t>certoplast Technische Klebebänder GmbH</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Geislingen an der Steige, Baden-Württemberg</t>
+          <t>Wuppertal</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>nur Funktionsadressen (mail@, offer@, anfrage@), keine Ansprechpartner-Seite</t>
+          <t>GF Dr. Andreas Hohmann und Dr. René Rambusch genannt, aber nur Abteilungspostfächer (automotive@, verkauf@, einkauf@, ps@)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>BKV Logistik GmbH &amp; Co. KG</t>
+          <t>MR Chemie GmbH</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Rheinstetten, Baden-Württemberg</t>
+          <t>Unna</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>nur Funktionsadressen (kontakt@, transportlogistik@, kontraktlogistik@)</t>
+          <t>Geschäftsführer Carsten Renzing-Krahe und Sandra Jüngling nur mit post@mr-chemie.de; personalisierte Adressen nur für Vertrieb/Customer Service</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>BECK Spedition + Logistik GmbH</t>
+          <t>BIW Isolierstoffe GmbH</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Filderstadt, Baden-Württemberg</t>
+          <t>Ennepetal</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>nur info@becksped.de, keine Personen auf der Kontaktseite</t>
+          <t>Nur Sales Manager/Key Account mit persönlicher E-Mail, keine Geschäftsführung oder Bereichsleitung Produktion/IT/Logistik</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Abt Spedition &amp; Service</t>
+          <t>Murtfeldt Kunststoffe GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Schwäbisch Gmünd, Baden-Württemberg</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Ansprechpartner Jochen Abt genannt, aber nur info@abt-spedition.de</t>
+          <t>Kontaktseite listet nur Außendienst und Channel Management, keine Geschäftsführung/Bereichsleitung mit E-Mail</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Honold Contract Logistics GmbH</t>
+          <t>Peter Greven GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Neu-Ulm, Bayern</t>
+          <t>Bad Münstereifel</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Geschäftsführer namentlich genannt, aber nur Sammeladresse kontraktlogistik@honold.net</t>
+          <t>Viele persönliche E-Mails, aber ausschließlich Account-/Product-Manager – keine Geschäftsführung/Prokura oder Leitung IT/Produktion/Logistik</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>LTG Logistik und Transport GmbH</t>
+          <t>Grillo-Werke AG</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Hamburg</t>
+          <t>Duisburg</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>keine E-Mail-Adressen auf der Kontaktseite</t>
+          <t>Persönliche E-Mails nur für Produkt-/Vertriebsansprechpartner, kein Vorstand/GF/Prokurist mit E-Mail</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>RM Logistik GmbH</t>
+          <t>Enke-Werk Johannes Enke GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Grasberg / Bremen</t>
+          <t>Düsseldorf</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Geschäftsführung (Familie Meyer) mit Telefon, aber keine E-Mail-Adressen auf der Seite</t>
+          <t>Persönliche E-Mails nur für Innen-/Außendienst und Anwendungstechnik; Geschäftsleitung ohne E-Mail</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Spedition Bode GmbH &amp; Co. KG</t>
+          <t>WEICON GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Bad Oldesloe/Bargteheide, Schleswig-Holstein</t>
+          <t>Münster</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>persönliche GF-Adresse vorhanden, aber Standort außerhalb der definierten Zielregionen</t>
+          <t>Persönliche E-Mails nur für E-Commerce und Presse; Geschäftsführung (Familie Weidling) ohne veröffentlichte Adresse</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Finsterwalder Transport &amp; Logistik GmbH</t>
+          <t>Carl Bechem GmbH</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Türkheim, Bayern</t>
+          <t>Hagen</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>nur standortbezogene Sammeladressen (sales.tu@ …)</t>
+          <t>Nur bechem@bechem.de und marketing@bechem.de</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Noerpel-Gruppe</t>
+          <t>Rhenus Lub GmbH &amp; Co KG</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Ulm / Hamburg / Hannover</t>
+          <t>Mönchengladbach</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>über 1.000 Mitarbeiter, außerhalb der Zielgröße; nur info@noerpel.de</t>
+          <t>Website liefert nur Händler-/Distributoren-Adressen im Ausland, keine eigenen Entscheider-Adressen</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Rudolph Logistik Gruppe</t>
+          <t>Ewald Dörken AG / DÖRKEN Coatings</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Gudensberg, Hessen</t>
+          <t>Herdecke</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>ca. 4.500 Mitarbeiter an 42 Standorten – Konzerngröße, außerhalb Zielprofil</t>
+          <t>Nur Bereichspostfächer (coatings@, membranes@)</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>LOXXESS AG</t>
+          <t>Jowat SE</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Tegernsee, Bayern</t>
+          <t>Detmold</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Kontraktlogistiker deutlich über 1.000 Mitarbeitern – außerhalb Zielgröße</t>
+          <t>Keine persönlichen E-Mail-Adressen auf Kontakt-/Impressumsseiten</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Spedition König</t>
+          <t>Follmann Chemie GmbH</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Esslingen, Baden-Württemberg</t>
+          <t>Minden</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>nur info@koenig-sped.de</t>
+          <t>Nur zwei ausländische Vertriebsadressen, keine Entscheider im NRW-Stammhaus</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Spedition Kübler GmbH</t>
+          <t>STOCKMEIER Gruppe</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Michelfeld/Schwäbisch Hall, Baden-Württemberg</t>
+          <t>Bielefeld</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>nur info@kuebler-spedition.de, keine personenbezogenen E-Mails</t>
+          <t>Nur Standort-Sammeladressen; persönliche Adressen nur als Messekontakte ohne Positionsangabe</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>E3 Spedition (E3 Gruppe)</t>
+          <t>Schomburg GmbH</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Homberg (Hessen) u. a.</t>
+          <t>Detmold</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Ansprechpartner nur über JavaScript-Filter, keine E-Mails im Seitenquelltext</t>
+          <t>Nur zwei Objektmanager-Adressen, keine Entscheider</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Carl Köster &amp; Louis Hapke – Kontaktseite</t>
+          <t>Heinrich Hahne GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Sehnde-Höver, Niedersachsen</t>
+          <t>Heiligenhaus</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Hinweis: /kontakt/ enthält nur info@; verwertbare Daten ausschließlich auf /ansprechpartner/ (siehe Lead)</t>
+          <t>Vertriebskontakte laufen über Konzernadressen @sievert.de (Sievert-Gruppe, Osnabrück) – kein NRW-Mittelständler mehr</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Kraftverkehr Münsterland C. Weilke GmbH &amp; Co. KG</t>
+          <t>Klöber GmbH</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Greven</t>
+          <t>Ennepetal</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>nur info@weilke.de auf Website, keine Ansprechpartner-/Teamseite mit Personen-E-Mails gefunden</t>
+          <t>Adressen laufen über BMI Group (@bmigroup.com), Konzernzugehörigkeit</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Richter Spedition GmbH</t>
+          <t>Dr. Kurt Wolff GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Schwerte</t>
+          <t>Bielefeld</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>nur info@richter-spedition.de, keine Personenseite; Geschäftsführung nicht mit E-Mail veröffentlicht</t>
+          <t>ewolff@drwolffgroup.com steht nur als Impressums-Kontakt ohne Personenzuordnung</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Gustav Mäuler GmbH &amp; Co. KG</t>
+          <t>Gerhardi Kunststofftechnik GmbH</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Remscheid</t>
+          <t>Lüdenscheid</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>nur info@ und verkauf@ (Funktionsadressen), keine namentlichen Ansprechpartner auf Homepage und Kontaktseite</t>
+          <t>Nur Funktionspostfächer (beschwerden@, managementorganisation@)</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Spedition Zobel</t>
+          <t>BIA Kunststoff- und Galvanotechnik GmbH</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Wetter (Ruhr)</t>
+          <t>Solingen</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Ansprechpartner-Seite nennt nur Personalmanagement; keine E-Mail der Geschäftsführer Philip/Christian Zobel veröffentlicht</t>
+          <t>Nur Funktions- und Auslandsadressen</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>LLS-Service GmbH</t>
+          <t>Bollig &amp; Kemper GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Gladbeck</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>nur info@lls.services, keine namentlichen Entscheidungsträger auf der Website</t>
+          <t>Keine E-Mail-Adressen auf den erreichbaren Seiten</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Emmerich &amp; Rosenberger GmbH &amp; Co. KG (EMRO)</t>
+          <t>Hesse GmbH &amp; Co. KG (Hesse Lignal)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Duisburg</t>
+          <t>Hamm</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>nur info@emro.de, keine Ansprechpartner-Seite mit persönlichen E-Mails gefunden</t>
+          <t>Nur bestellingen@hesse-lignal.com (Funktionsadresse)</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>NW Logistik</t>
+          <t>HERCUTEC Chemie GmbH</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Ahlen</t>
+          <t>Bottrop</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Website nicht erreichbar (DNS-Fehler), keine Daten verifizierbar</t>
+          <t>Keine E-Mail-Adressen crawlbar</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Emons Spedition GmbH</t>
+          <t>Gremmler Bauchemie GmbH</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Gelsenkirchen</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Konzernähnliche Größe (&gt;3.000 Mitarbeiter, 100 Standorte) — außerhalb Mittelstands-Zielprofil</t>
+          <t>Nur externe Kanzleiadresse für Hinweisgeberverfahren</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>TEAM Logistic (Greinert/Diel)</t>
+          <t>RAVENOL / Ravensberger Schmierstoffvertrieb GmbH</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Raum Montabaur (RLP)</t>
+          <t>Werther (Westf.)</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>persönliche GF-E-Mails vorhanden, aber außerhalb Zielregion und Größe nicht verifiziert — nachqualifizierbar</t>
+          <t>Persönliche Adresse nur im Karrierebereich (Recruiting), kein Entscheidungsträger</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>TEAM Logistic GmbH</t>
+          <t>Triflex GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Raum Montabaur (Vorwahl 02602)</t>
+          <t>Minden</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Persönliche E-Mails vorhanden, aber Standort außerhalb Ruhrgebiet/Rheinland/Niederrhein</t>
+          <t>Nur datenschutzbeauftragter@triflex.de</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Spedition Schiffers GmbH</t>
+          <t>Masterflex SE</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Mönchengladbach</t>
+          <t>Gelsenkirchen</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Website nicht erreichbar (DNS-Fehler, auch per curl); E-Mails nicht auf einer gecrawlten Seite verifizierbar</t>
+          <t>Nur info.masterflex@masterflexgroup.com</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>meta4log GmbH</t>
+          <t>Bio-Circle Surface Technology GmbH</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Essen</t>
+          <t>Gütersloh</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Nur info@meta4log.de auf der Website; keine persönliche E-Mail des Geschäftsführers (Bernd Jungclaus)</t>
+          <t>Keine persönlichen E-Mail-Adressen auffindbar</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Rheinkraft International GmbH (RKI)</t>
+          <t>Osmo Holz und Color GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Duisburg</t>
+          <t>Warendorf</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Nur info@rki-logistics.com, keine Personen auf Kontaktseite</t>
+          <t>Keine persönlichen E-Mail-Adressen auffindbar</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Windgätter u. Sohn GmbH</t>
+          <t>SysKem Chemie GmbH</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>Wuppertal</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Ansprechpartner mit Durchwahl, aber nur Sammeladresse dispo@windgaetter-transporte.de</t>
+          <t>Keine E-Mail-Adressen crawlbar</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Hoff Transport und Logistik GmbH &amp; Co. KG</t>
+          <t>Linker Chemie-Group</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Krefeld</t>
+          <t>Wuppertal</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Nur info@/order@/karriere@; keine Personen genannt</t>
+          <t>Keine persönlichen E-Mail-Adressen auffindbar</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>AXTRA GmbH &amp; Co. KG</t>
+          <t>Traxit International GmbH</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Essen</t>
+          <t>Schwelm</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Nur info@axtra.de, keine Ansprechpartnerseite</t>
+          <t>Persönliche Adressen nur für Auslandsvertretungen, keine Entscheider am Stammsitz</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Meinolf Jacobi Spedition GmbH</t>
+          <t>AB-Pulverlacke</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>NRW</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Keine E-Mail-Adresse auf der Website auffindbar</t>
+          <t>Nur GMX-Sammeladresse, keine Personenzuordnung</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Johs. Stelten GmbH &amp; Co. KG</t>
+          <t>IDEALCHEMIE GmbH</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Krefeld</t>
+          <t>Gelsenkirchen</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Nur info@steltenkg.de; keine persönliche E-Mail der Geschäftsführung</t>
+          <t>Nur Platzhalter-/Fremdadressen im Quelltext</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Spedition Minor GmbH</t>
+          <t>Assortierte Kleinkandidaten (Bonalin, Reckli, Säkaphen, PAGEL, Deitermann, Königswarter &amp; Ebell, Deutsche NovoChem, Robotchemie, Speform, wefa Westdeutsche Farben, ultrament, Reinex, Oel-Chemie Tüllmann, Reininghaus-Chemie, Peter Lacke, Metaflux, Renia, brocolor, Zowo-Lacke, Graichen, Eggen, Wefapress, Barlog, Coroplast, Botament, MC-Bauchemie, Jaeger Lacke, Wibarco, Overlack, Stüwe, Bostik, Lubcon)</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Gelsenkirchen</t>
+          <t>NRW</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Nur info@spedition-minor.de</t>
+          <t>Keine wörtlich veröffentlichten persönlichen E-Mail-Adressen von Entscheidungsträgern auf Homepage/Impressum/Kontakt/Team gefunden</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Hubert Kläsener GmbH &amp; Co. KG</t>
+          <t>Hermann Ritter GmbH &amp; Co. KG (Ritter Spedition)</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Gelsenkirchen</t>
+          <t>Feilitzsch-Zedtwitz, Bayern</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -8804,19 +9415,19 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail auf Website/Kontaktseite</t>
+          <t>nur 40 Mitarbeiter (unter Zielgröße) und nur info@-Adresse</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Scheren Logistik GmbH</t>
+          <t>Metzger Spedition GmbH</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Düsseldorf</t>
+          <t>Neu-Kupfer, Baden-Württemberg</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -8826,19 +9437,19 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Team-Seite nennt Personen nur mit Vornamen/Initial, nur info@scheren.de</t>
+          <t>nur info@metzger-spedition.de, keine Personen auf der Website</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>MSG Speditionsgesellschaft mbH</t>
+          <t>Rüdinger Spedition GmbH</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Mönchengladbach</t>
+          <t>Krautheim, Baden-Württemberg</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -8848,19 +9459,19 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Nur Funktionsadressen (Management@, National@, Sea@ etc.), keine Personenzuordnung</t>
+          <t>Ansprechpartner mit Namen/Positionen, aber E-Mail-Adressen verschleiert; auch per curl keine Adresse im Quelltext</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Graf-Transporte Internationale Spedition GmbH</t>
+          <t>ZUFALL logistics group (Friedrich Zufall GmbH &amp; Co. KG)</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Göttingen, Niedersachsen</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -8870,19 +9481,19 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Keine E-Mail-Adressen auf der Website auffindbar</t>
+          <t>nur standortbezogene Sammeladressen (goettingen@, kassel@ …), keine persönliche E-Mail der Geschäftsführung</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Curt Richter SE</t>
+          <t>Heinrich Koch Internationale Spedition GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Osnabrück, Niedersachsen</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -8892,19 +9503,19 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Keine persönlichen E-Mails auf gecrawlten Seiten</t>
+          <t>auf der Kontaktseite nur info@koch-international.de, keine Ansprechpartner-Seite mit Personen-E-Mails</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Deußen Logistik GmbH</t>
+          <t>Döderlein Spedition GmbH</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Nördlingen, Bayern</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -8914,19 +9525,19 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Keine erreichbare Firmenwebsite mit persönlichen E-Mails gefunden</t>
+          <t>nur info@doederlein.de, keine Ansprechpartner-/Teamseite</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>HEUEL LOGISTICS</t>
+          <t>Elflein Spedition &amp; Transport GmbH</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Dortmund/Arnsberg</t>
+          <t>Bamberg, Bayern</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -8936,19 +9547,19 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Nur Funktionsadressen (angebot@, info@)</t>
+          <t>Geschäftsführer mit Durchwahl gelistet, aber E-Mail-Links leer ('#') – keine wörtliche Adresse auf der Seite</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>LOXX Logistics</t>
+          <t>Spedicam GmbH</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Duisburg</t>
+          <t>Neufahrn (Raum München), Bayern</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -8958,19 +9569,19 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Persönliche E-Mails vorhanden, aber inzwischen Teil der Rhenus-Gruppe (Konzern) – ausgeschlossen</t>
+          <t>nur Funktionsadressen (Gf@, Sl@, Vl@ …), keine personenbezogenen E-Mails</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Hendricks Unternehmensgruppe</t>
+          <t>Wiedmann &amp; Winz GmbH</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Neuss</t>
+          <t>Geislingen an der Steige, Baden-Württemberg</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -8980,19 +9591,19 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Nur Funktionsadressen (automotive@hendricks.group)</t>
+          <t>nur Funktionsadressen (mail@, offer@, anfrage@), keine Ansprechpartner-Seite</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>TechnoCargo Logistik GmbH u. Co. KG</t>
+          <t>BKV Logistik GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Neuss</t>
+          <t>Rheinstetten, Baden-Württemberg</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -9002,19 +9613,19 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Nur bewerbung@technocargo.de; Konzernstruktur (Bertschi-nahe Geschäftsführung)</t>
+          <t>nur Funktionsadressen (kontakt@, transportlogistik@, kontraktlogistik@)</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>NEUFRA Speditions-Gesellschaft mbH</t>
+          <t>BECK Spedition + Logistik GmbH</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Neuss</t>
+          <t>Filderstadt, Baden-Württemberg</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -9024,19 +9635,19 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Keine persönlichen E-Mails auffindbar</t>
+          <t>nur info@becksped.de, keine Personen auf der Kontaktseite</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Bodenheim Spedition GmbH</t>
+          <t>Abt Spedition &amp; Service</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Krefeld</t>
+          <t>Schwäbisch Gmünd, Baden-Württemberg</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -9046,19 +9657,19 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Kontaktseite enthält nur Platzhalter (email@example.org)</t>
+          <t>Ansprechpartner Jochen Abt genannt, aber nur info@abt-spedition.de</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Spedition Kronenberg GmbH</t>
+          <t>Honold Contract Logistics GmbH</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Neu-Ulm, Bayern</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -9068,19 +9679,19 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Nur Sammeladresse DispoKronenberg@aol.com; zudem unter 50 MA</t>
+          <t>Geschäftsführer namentlich genannt, aber nur Sammeladresse kontraktlogistik@honold.net</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>GATE 41 Logistics GmbH &amp; Co. KG</t>
+          <t>LTG Logistik und Transport GmbH</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Mönchengladbach</t>
+          <t>Hamburg</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -9090,19 +9701,19 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Website enthält nur Platzhalter-Adresse, keine echten E-Mails</t>
+          <t>keine E-Mail-Adressen auf der Kontaktseite</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Die Richrath's GmbH</t>
+          <t>RM Logistik GmbH</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Düsseldorf</t>
+          <t>Grasberg / Bremen</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -9112,19 +9723,19 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Nur support@die-richraths.de</t>
+          <t>Geschäftsführung (Familie Meyer) mit Telefon, aber keine E-Mail-Adressen auf der Seite</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Sägewerk Transporte GmbH</t>
+          <t>Spedition Bode GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Düsseldorf</t>
+          <t>Bad Oldesloe/Bargteheide, Schleswig-Holstein</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -9134,19 +9745,19 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Keine persönlichen E-Mails auf der Website</t>
+          <t>persönliche GF-Adresse vorhanden, aber Standort außerhalb der definierten Zielregionen</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Wilhelm Rotthege</t>
+          <t>Finsterwalder Transport &amp; Logistik GmbH</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Essen/Düsseldorf</t>
+          <t>Türkheim, Bayern</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -9156,19 +9767,19 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Nur Standort-Sammeladressen (essen@, duesseldorf@)</t>
+          <t>nur standortbezogene Sammeladressen (sales.tu@ …)</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Spedition Buerhaus / GDS Logistik / OFL Olympia Food Logistics / BM Spedition / A. Siepmann / Joachim Schultz / LOGIFLEX / P+M Logistik / Rosenbaum / Guckuk / ABC-Logistik / VCK Logistics</t>
+          <t>Noerpel-Gruppe</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>diverse (Dortmund, Bochum, Duisburg, MG, Köln, Düsseldorf)</t>
+          <t>Ulm / Hamburg / Hannover</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -9178,19 +9789,19 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Sammelposten: keine erreichbare Website mit persönlichen E-Mails der Entscheidungsträger gefunden</t>
+          <t>über 1.000 Mitarbeiter, außerhalb der Zielgröße; nur info@noerpel.de</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Emons, DSV, DB Schenker, Rhenus, Kühne+Nagel, Dachser, DHL, BLG, Yusen, Kintetsu</t>
+          <t>Rudolph Logistik Gruppe</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>diverse</t>
+          <t>Gudensberg, Hessen</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -9200,19 +9811,19 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Konzerne bzw. laut Vorgabe ausgeschlossen</t>
+          <t>ca. 4.500 Mitarbeiter an 42 Standorten – Konzerngröße, außerhalb Zielprofil</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Rüdinger Spedition GmbH</t>
+          <t>LOXXESS AG</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Krautheim (BW)</t>
+          <t>Tegernsee, Bayern</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -9222,19 +9833,19 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Ansprechpartnerseite listet Namen/Positionen/Durchwahlen, aber keine E-Mail-Adressen im Klartext (JS-verschleierte 'E-Mail schreiben'-Links); curl-Nachfassen ohne Treffer</t>
+          <t>Kontraktlogistiker deutlich über 1.000 Mitarbeitern – außerhalb Zielgröße</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>barth Logistikgruppe</t>
+          <t>Spedition König</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Hechingen (BW)</t>
+          <t>Esslingen, Baden-Württemberg</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -9244,19 +9855,19 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Ansprechpartnerseite enthält nur Telefon-/Faxnummern je Standort, keine Personen und keine E-Mail-Adressen; curl-Nachfassen ohne Treffer</t>
+          <t>nur info@koenig-sped.de</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Wiedmann &amp; Winz GmbH</t>
+          <t>Spedition Kübler GmbH</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Geislingen an der Steige (BW)</t>
+          <t>Michelfeld/Schwäbisch Hall, Baden-Württemberg</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -9266,19 +9877,19 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Nur Funktionsadressen (mail@, offer@, anfrage@, bewerbung@), keine personenbezogenen E-Mails auf Kontaktseite</t>
+          <t>nur info@kuebler-spedition.de, keine personenbezogenen E-Mails</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>CL Spedition Berlin Transport- und Logistik GmbH</t>
+          <t>E3 Spedition (E3 Gruppe)</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Homberg (Hessen) u. a.</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -9288,19 +9899,19 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Ansprechpartnerseite nennt Namen und Funktionen, aber nur Sammeladressen info@/dispo@/ber@</t>
+          <t>Ansprechpartner nur über JavaScript-Filter, keine E-Mails im Seitenquelltext</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Spedition Kollmannsberger – Startseite</t>
+          <t>Carl Köster &amp; Louis Hapke – Kontaktseite</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Großmehring (BY)</t>
+          <t>Sehnde-Höver, Niedersachsen</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -9310,19 +9921,19 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Homepage nur mail@ – Lead stattdessen über die separate Ansprechpartnerseite qualifiziert (siehe Leads)</t>
+          <t>Hinweis: /kontakt/ enthält nur info@; verwertbare Daten ausschließlich auf /ansprechpartner/ (siehe Lead)</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Schwarzer Group / Schwarzer Spedition</t>
+          <t>Kraftverkehr Münsterland C. Weilke GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Heiligenstedten (SH)</t>
+          <t>Greven</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -9332,19 +9943,19 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Persönliche E-Mails vorhanden, aber Hauptsitz und Standorte außerhalb des Zielgebiets Süd-/Ostdeutschland</t>
+          <t>nur info@weilke.de auf Website, keine Ansprechpartner-/Teamseite mit Personen-E-Mails gefunden</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Sachsen-Anhalt Logistik</t>
+          <t>Richter Spedition GmbH</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Sachsen-Anhalt (virtuell)</t>
+          <t>Schwerte</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -9354,19 +9965,19 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Kein reales Unternehmen – virtuelle TruckersMP-Speditionsgemeinschaft (Gaming-Community); nur info@</t>
+          <t>nur info@richter-spedition.de, keine Personenseite; Geschäftsführung nicht mit E-Mail veröffentlicht</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ELOS Speditions GmbH</t>
+          <t>Gustav Mäuler GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Zwickau (SN)</t>
+          <t>Remscheid</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -9376,19 +9987,19 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Nur zentrale Adresse info@elos-spedition.de auffindbar, keine persönlichen Ansprechpartner-Mails</t>
+          <t>nur info@ und verkauf@ (Funktionsadressen), keine namentlichen Ansprechpartner auf Homepage und Kontaktseite</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Roman Mayer Logistik GmbH</t>
+          <t>Spedition Zobel</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Nürnberg / Gersthofen (BY)</t>
+          <t>Wetter (Ruhr)</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -9398,19 +10009,19 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Kontaktseite nur mit info@romanmayer-logistik.de, keine personenbezogenen E-Mails</t>
+          <t>Ansprechpartner-Seite nennt nur Personalmanagement; keine E-Mail der Geschäftsführer Philip/Christian Zobel veröffentlicht</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Köhl Logistik</t>
+          <t>LLS-Service GmbH</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Pfalz</t>
+          <t>Gladbeck</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -9420,19 +10031,19 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>HTTP 503 beim Abruf; zudem Sitz in Rheinland-Pfalz außerhalb des Zielgebiets</t>
+          <t>nur info@lls.services, keine namentlichen Entscheidungsträger auf der Website</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Spedition Ebenroth GmbH</t>
+          <t>Emmerich &amp; Rosenberger GmbH &amp; Co. KG (EMRO)</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Döbeln (SN)</t>
+          <t>Duisburg</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -9442,19 +10053,19 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Keine Team-/Ansprechpartnerseite mit persönlichen E-Mails auffindbar</t>
+          <t>nur info@emro.de, keine Ansprechpartner-Seite mit persönlichen E-Mails gefunden</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Baltic Lloyd – Startseite/Kontaktseite</t>
+          <t>NW Logistik</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Rostock (MV)</t>
+          <t>Ahlen</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -9464,19 +10075,19 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Startseite nur dispo@, /kontakt/ liefert HTTP 404 – Lead stattdessen über /dasteam/ qualifiziert (siehe Leads)</t>
+          <t>Website nicht erreichbar (DNS-Fehler), keine Daten verifizierbar</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Krage &amp; Gerloff – Ansprechpartnerseite</t>
+          <t>Emons Spedition GmbH</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Schwanebeck (ST)</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -9486,19 +10097,19 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>URL /ansprechpartner liefert HTTP 404; Geschäftsführung nicht mit persönlicher E-Mail belegbar – nur Standortleitung Magdeburg qualifiziert</t>
+          <t>Konzernähnliche Größe (&gt;3.000 Mitarbeiter, 100 Standorte) — außerhalb Mittelstands-Zielprofil</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Seifert Logistics Group / Noerpel-Gruppe / Karl Schmidt Spedition</t>
+          <t>TEAM Logistic (Greinert/Diel)</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Ulm bzw. Heilbronn (BW)</t>
+          <t>Raum Montabaur (RLP)</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -9508,19 +10119,19 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Konzerngröße (2.500–4.000+ Mitarbeitende, 45+ Standorte) – außerhalb des Mittelstandsprofils</t>
+          <t>persönliche GF-E-Mails vorhanden, aber außerhalb Zielregion und Größe nicht verifiziert — nachqualifizierbar</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>LOXXESS AG</t>
+          <t>TEAM Logistic GmbH</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Tegernsee (BY)</t>
+          <t>Raum Montabaur (Vorwahl 02602)</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -9530,19 +10141,19 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Nicht weiterverfolgt – Konzernstruktur/AG, kein Ansprechpartnerverzeichnis mit persönlichen E-Mails</t>
+          <t>Persönliche E-Mails vorhanden, aber Standort außerhalb Ruhrgebiet/Rheinland/Niederrhein</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>TML Spedition GmbH</t>
+          <t>Spedition Schiffers GmbH</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Leipzig (SN)</t>
+          <t>Mönchengladbach</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -9552,19 +10163,19 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Keine Ansprechpartnerseite mit namentlichen E-Mail-Adressen auffindbar</t>
+          <t>Website nicht erreichbar (DNS-Fehler, auch per curl); E-Mails nicht auf einer gecrawlten Seite verifizierbar</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Spedition Schiffers</t>
+          <t>meta4log GmbH</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Nettetal (NRW)</t>
+          <t>Essen</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -9574,19 +10185,19 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Region außerhalb des Zielgebiets Süd-/Ostdeutschland</t>
+          <t>Nur info@meta4log.de auf der Website; keine persönliche E-Mail des Geschäftsführers (Bernd Jungclaus)</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>RTC Spedition &amp; Logistik GmbH</t>
+          <t>Rheinkraft International GmbH (RKI)</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Duisburg</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -9596,19 +10207,19 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Nur Zentralkontakt/Geschäftsführername belegt, keine persönliche E-Mail auf gecrawlten Seiten</t>
+          <t>Nur info@rki-logistics.com, keine Personen auf Kontaktseite</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Sachsenland – Startseite</t>
+          <t>Windgätter u. Sohn GmbH</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Dresden (SN)</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -9618,19 +10229,19 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Homepage ohne E-Mail-Adressen – Leads stattdessen über /kontakt-dresden/ qualifiziert (siehe Leads)</t>
+          <t>Ansprechpartner mit Durchwahl, aber nur Sammeladresse dispo@windgaetter-transporte.de</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Watzlawek Logistik</t>
+          <t>Hoff Transport und Logistik GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Hamm/Ahlen</t>
+          <t>Krefeld</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -9640,19 +10251,19 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Geschäftsleitung Lukas Watzlawek nur über info@watzlawek-trans.com erreichbar, keine persönliche E-Mail</t>
+          <t>Nur info@/order@/karriere@; keine Personen genannt</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>H. Gautzsch Spedition GmbH &amp; Co. KG</t>
+          <t>AXTRA GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Münster</t>
+          <t>Essen</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -9662,19 +10273,19 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Ansprechpartnerliste nennt für alle Personen nur info@gautzsch-spedition.de</t>
+          <t>Nur info@axtra.de, keine Ansprechpartnerseite</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>KÜHN Transport- und Lagerungsgesellschaft mbH</t>
+          <t>Meinolf Jacobi Spedition GmbH</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Ostbevern</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -9684,19 +10295,19 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>nur info@kuehn-transporte.com auffindbar</t>
+          <t>Keine E-Mail-Adresse auf der Website auffindbar</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Feldmann Spedition GmbH</t>
+          <t>Johs. Stelten GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Gütersloh</t>
+          <t>Krefeld</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -9706,19 +10317,19 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>nur dispo@feldmann-spedition.de</t>
+          <t>Nur info@steltenkg.de; keine persönliche E-Mail der Geschäftsführung</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>WLS Spedition GmbH</t>
+          <t>Spedition Minor GmbH</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Steinhagen</t>
+          <t>Gelsenkirchen</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -9728,19 +10339,19 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>nur kontakt@wls-spedition.de</t>
+          <t>Nur info@spedition-minor.de</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Hartmann International GmbH &amp; Co. KG</t>
+          <t>Hubert Kläsener GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Gelsenkirchen</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -9750,19 +10361,19 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Team-/Kontaktseiten nennen nur info@ bzw. standortbezogene Sammeladressen</t>
+          <t>Keine persönliche E-Mail auf Website/Kontaktseite</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Loeber-Lehnhof GmbH</t>
+          <t>Scheren Logistik GmbH</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Siegen</t>
+          <t>Düsseldorf</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -9772,19 +10383,19 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Geschäftsführer Roman Mayer ohne persönliche E-Mail; gefundene Adresse gehört zum Webseitenbetreuer</t>
+          <t>Team-Seite nennt Personen nur mit Vornamen/Initial, nur info@scheren.de</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Schröder Logistik GmbH</t>
+          <t>MSG Speditionsgesellschaft mbH</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Kirchlengern</t>
+          <t>Mönchengladbach</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -9794,19 +10405,19 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Teamseite zeigt Geschäftsführer ohne E-Mail, nur faktura@schroeder-logistik.de</t>
+          <t>Nur Funktionsadressen (Management@, National@, Sea@ etc.), keine Personenzuordnung</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Loewe Logistics &amp; Care GmbH &amp; Co. KG</t>
+          <t>Graf-Transporte Internationale Spedition GmbH</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Herford</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -9816,19 +10427,19 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>keine E-Mail-Adressen auf gecrawlten Seiten auffindbar</t>
+          <t>Keine E-Mail-Adressen auf der Website auffindbar</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Spedition Gerhard Siebel GmbH</t>
+          <t>Curt Richter SE</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Kreuztal</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -9838,19 +10449,19 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>nur info@siebel-spedition.de</t>
+          <t>Keine persönlichen E-Mails auf gecrawlten Seiten</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Gössling Spedition GmbH</t>
+          <t>Deußen Logistik GmbH</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Arnsberg</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -9860,19 +10471,19 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>nur gs@goessling-spedition.de (Funktionsadresse ohne Personenzuordnung)</t>
+          <t>Keine erreichbare Firmenwebsite mit persönlichen E-Mails gefunden</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Kerber Transporte GmbH</t>
+          <t>HEUEL LOGISTICS</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Brilon</t>
+          <t>Dortmund/Arnsberg</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -9882,19 +10493,19 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>nur info@kerber-transporte.de</t>
+          <t>Nur Funktionsadressen (angebot@, info@)</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Spedition Mikus GmbH &amp; Co. KG</t>
+          <t>LOXX Logistics</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Meschede</t>
+          <t>Duisburg</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -9904,19 +10515,19 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>nur info@spedition-mikus.de</t>
+          <t>Persönliche E-Mails vorhanden, aber inzwischen Teil der Rhenus-Gruppe (Konzern) – ausgeschlossen</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Glexx GmbH</t>
+          <t>Hendricks Unternehmensgruppe</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Meschede</t>
+          <t>Neuss</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -9926,19 +10537,19 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>nur post@glexx-logistik.de</t>
+          <t>Nur Funktionsadressen (automotive@hendricks.group)</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Kleinwächter GmbH &amp; Co. Spedition</t>
+          <t>TechnoCargo Logistik GmbH u. Co. KG</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Hallenberg</t>
+          <t>Neuss</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -9948,19 +10559,19 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>keine erreichbare Website/keine E-Mails über getestete Domains</t>
+          <t>Nur bewerbung@technocargo.de; Konzernstruktur (Bertschi-nahe Geschäftsführung)</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Alfons Brass Spedition und Lagerei</t>
+          <t>NEUFRA Speditions-Gesellschaft mbH</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Medebach</t>
+          <t>Neuss</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -9970,19 +10581,19 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>keine E-Mails über getestete Domains auffindbar</t>
+          <t>Keine persönlichen E-Mails auffindbar</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Mönig Spedition Meschede GmbH</t>
+          <t>Bodenheim Spedition GmbH</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Meschede</t>
+          <t>Krefeld</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -9992,19 +10603,19 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>keine E-Mails über getestete Domains auffindbar</t>
+          <t>Kontaktseite enthält nur Platzhalter (email@example.org)</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Schulte-Lindhorst GmbH &amp; Co.</t>
+          <t>Spedition Kronenberg GmbH</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Rietberg</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -10014,19 +10625,19 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>nur info@schulte-lindhorst.de</t>
+          <t>Nur Sammeladresse DispoKronenberg@aol.com; zudem unter 50 MA</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Thermotraffic GmbH</t>
+          <t>GATE 41 Logistics GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Versmold</t>
+          <t>Mönchengladbach</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -10036,19 +10647,19 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>nur info@/sales@thermotraffic.de; zudem Konzernstruktur</t>
+          <t>Website enthält nur Platzhalter-Adresse, keine echten E-Mails</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Tevex Logistics GmbH</t>
+          <t>Die Richrath's GmbH</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Rheda-Wiedenbrück</t>
+          <t>Düsseldorf</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -10058,19 +10669,19 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>nur info@tevex.de</t>
+          <t>Nur support@die-richraths.de</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Greiwing logistics for you GmbH</t>
+          <t>Sägewerk Transporte GmbH</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Greven</t>
+          <t>Düsseldorf</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -10080,19 +10691,19 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>nur info@greiwing.de</t>
+          <t>Keine persönlichen E-Mails auf der Website</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Sievert Logistik SE</t>
+          <t>Wilhelm Rotthege</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Lengerich</t>
+          <t>Essen/Düsseldorf</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -10102,19 +10713,19 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>nur info.logistik@sievert.de; Teil der Sievert-Gruppe</t>
+          <t>Nur Standort-Sammeladressen (essen@, duesseldorf@)</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>MP Logistik GmbH</t>
+          <t>Spedition Buerhaus / GDS Logistik / OFL Olympia Food Logistics / BM Spedition / A. Siepmann / Joachim Schultz / LOGIFLEX / P+M Logistik / Rosenbaum / Guckuk / ABC-Logistik / VCK Logistics</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Rheine</t>
+          <t>diverse (Dortmund, Bochum, Duisburg, MG, Köln, Düsseldorf)</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -10124,19 +10735,19 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>nur info@/warehouse@mplogistik.com</t>
+          <t>Sammelposten: keine erreichbare Website mit persönlichen E-Mails der Entscheidungsträger gefunden</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Wetralog GmbH</t>
+          <t>Emons, DSV, DB Schenker, Rhenus, Kühne+Nagel, Dachser, DHL, BLG, Yusen, Kintetsu</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Münster</t>
+          <t>diverse</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -10146,19 +10757,19 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>nur schadenservice@wetralog.de</t>
+          <t>Konzerne bzw. laut Vorgabe ausgeschlossen</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Hövener Spedition GmbH</t>
+          <t>Rüdinger Spedition GmbH</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Rheine</t>
+          <t>Krautheim (BW)</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -10168,19 +10779,19 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>nur info@hoevener-spedition.de</t>
+          <t>Ansprechpartnerseite listet Namen/Positionen/Durchwahlen, aber keine E-Mail-Adressen im Klartext (JS-verschleierte 'E-Mail schreiben'-Links); curl-Nachfassen ohne Treffer</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Spedition Karl Kerkeling GmbH</t>
+          <t>barth Logistikgruppe</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Coesfeld</t>
+          <t>Hechingen (BW)</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -10190,19 +10801,19 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>nur info@spedition-kerkeling.de</t>
+          <t>Ansprechpartnerseite enthält nur Telefon-/Faxnummern je Standort, keine Personen und keine E-Mail-Adressen; curl-Nachfassen ohne Treffer</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>MAX-Logistik GmbH</t>
+          <t>Wiedmann &amp; Winz GmbH</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Senden</t>
+          <t>Geislingen an der Steige (BW)</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -10212,19 +10823,19 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>nur info@max-logistik.de</t>
+          <t>Nur Funktionsadressen (mail@, offer@, anfrage@, bewerbung@), keine personenbezogenen E-Mails auf Kontaktseite</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Lipperland Logistik GmbH / Möbelspedition Lipperland</t>
+          <t>CL Spedition Berlin Transport- und Logistik GmbH</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Oelde</t>
+          <t>Berlin</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -10234,19 +10845,19 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>gefundene Adressen ohne Positionszuordnung (Datenschutz-/Impressumskontext), kein belegter Entscheidungsträger</t>
+          <t>Ansprechpartnerseite nennt Namen und Funktionen, aber nur Sammeladressen info@/dispo@/ber@</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Rosner Logistik GmbH</t>
+          <t>Spedition Kollmannsberger – Startseite</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Oelde</t>
+          <t>Großmehring (BY)</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -10256,19 +10867,19 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>keine E-Mails auf gecrawlten Seiten</t>
+          <t>Homepage nur mail@ – Lead stattdessen über die separate Ansprechpartnerseite qualifiziert (siehe Leads)</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Dingwerth Logistik GmbH</t>
+          <t>Schwarzer Group / Schwarzer Spedition</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Beelen</t>
+          <t>Heiligenstedten (SH)</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -10278,19 +10889,19 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>keine E-Mails auf gecrawlten Seiten</t>
+          <t>Persönliche E-Mails vorhanden, aber Hauptsitz und Standorte außerhalb des Zielgebiets Süd-/Ostdeutschland</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>TEDO Logistik GmbH &amp; Co. KG</t>
+          <t>Sachsen-Anhalt Logistik</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Ibbenbüren</t>
+          <t>Sachsen-Anhalt (virtuell)</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -10300,19 +10911,19 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>nur info@tedo-logistik.de</t>
+          <t>Kein reales Unternehmen – virtuelle TruckersMP-Speditionsgemeinschaft (Gaming-Community); nur info@</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Richter Express OHG</t>
+          <t>ELOS Speditions GmbH</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Saerbeck</t>
+          <t>Zwickau (SN)</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -10322,19 +10933,19 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>nur info@richter-express.de</t>
+          <t>Nur zentrale Adresse info@elos-spedition.de auffindbar, keine persönlichen Ansprechpartner-Mails</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Schöpper Transport GmbH</t>
+          <t>Roman Mayer Logistik GmbH</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Greven</t>
+          <t>Nürnberg / Gersthofen (BY)</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -10344,19 +10955,19 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>nur info@ bzw. eine Adresse ohne belegte Positionszuordnung</t>
+          <t>Kontaktseite nur mit info@romanmayer-logistik.de, keine personenbezogenen E-Mails</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Spedition Kockel GmbH &amp; Co. KG</t>
+          <t>Köhl Logistik</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Soest</t>
+          <t>Pfalz</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -10366,19 +10977,19 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>nur info@spedition-kockel.de</t>
+          <t>HTTP 503 beim Abruf; zudem Sitz in Rheinland-Pfalz außerhalb des Zielgebiets</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Mimberg Spedition - Baustoffe GmbH &amp; Co. KG</t>
+          <t>Spedition Ebenroth GmbH</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Werl</t>
+          <t>Döbeln (SN)</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -10388,19 +10999,19 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>nur Funktions-/Beispieladressen, keine Entscheidungsträger-E-Mail</t>
+          <t>Keine Team-/Ansprechpartnerseite mit persönlichen E-Mails auffindbar</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Artur Kossack Spedition</t>
+          <t>Baltic Lloyd – Startseite/Kontaktseite</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Hiddenhausen</t>
+          <t>Rostock (MV)</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -10410,19 +11021,19 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>nur info@kossack.de</t>
+          <t>Startseite nur dispo@, /kontakt/ liefert HTTP 404 – Lead stattdessen über /dasteam/ qualifiziert (siehe Leads)</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Westfalen-Lippe Speditions- und Lagerhausgesellschaft mbH</t>
+          <t>Krage &amp; Gerloff – Ansprechpartnerseite</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Herford</t>
+          <t>Schwanebeck (ST)</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -10432,19 +11043,19 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>nur info@wl-spedition.de</t>
+          <t>URL /ansprechpartner liefert HTTP 404; Geschäftsführung nicht mit persönlicher E-Mail belegbar – nur Standortleitung Magdeburg qualifiziert</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Martin Oelrich GmbH &amp; Co. KG</t>
+          <t>Seifert Logistics Group / Noerpel-Gruppe / Karl Schmidt Spedition</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Ladbergen</t>
+          <t>Ulm bzw. Heilbronn (BW)</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -10454,19 +11065,19 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>gehört zur pfenning logistics group (Konzern), keine persönliche E-Mail</t>
+          <t>Konzerngröße (2.500–4.000+ Mitarbeitende, 45+ Standorte) – außerhalb des Mittelstandsprofils</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>FIEGE / Nagel-Group / Duvenbeck</t>
+          <t>LOXXESS AG</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Greven / Versmold / Bocholt</t>
+          <t>Tegernsee (BY)</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -10476,19 +11087,19 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Konzerne mit &gt;5.000 Mitarbeitern, außerhalb Zielprofil</t>
+          <t>Nicht weiterverfolgt – Konzernstruktur/AG, kein Ansprechpartnerverzeichnis mit persönlichen E-Mails</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Heinrich Kottmann Spedition GmbH &amp; Co. KG</t>
+          <t>TML Spedition GmbH</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Büren</t>
+          <t>Leipzig (SN)</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -10498,19 +11109,19 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Website ohne verwertbare E-Mail-Adressen</t>
+          <t>Keine Ansprechpartnerseite mit namentlichen E-Mail-Adressen auffindbar</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Würfel-Massong Logistik GmbH</t>
+          <t>Spedition Schiffers</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Nettetal (NRW)</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -10520,965 +11131,965 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>keine E-Mails auf gecrawlten Seiten</t>
+          <t>Region außerhalb des Zielgebiets Süd-/Ostdeutschland</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Enns Maschinenbau GmbH</t>
+          <t>RTC Spedition &amp; Logistik GmbH</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Bad Oeynhausen</t>
+          <t>Berlin</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Liegt in NRW – außerhalb des Fokusgebiets (persönliche E-Mail andreas@enns-mb.de wäre vorhanden)</t>
+          <t>Nur Zentralkontakt/Geschäftsführername belegt, keine persönliche E-Mail auf gecrawlten Seiten</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>KASTO Maschinenbau GmbH &amp; Co. KG</t>
+          <t>Sachsenland – Startseite</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Achern (BW)</t>
+          <t>Dresden (SN)</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Auf allen gecrawlten Seiten nur Sammeladressen (kasto@kasto.com) – keine persönliche E-Mail</t>
+          <t>Homepage ohne E-Mail-Adressen – Leads stattdessen über /kontakt-dresden/ qualifiziert (siehe Leads)</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Heldele GmbH</t>
+          <t>Watzlawek Logistik</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Salach (BW)</t>
+          <t>Hamm/Ahlen</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Nur Standort-Sammeladresse salach@heldele.de – keine persönliche E-Mail</t>
+          <t>Geschäftsleitung Lukas Watzlawek nur über info@watzlawek-trans.com erreichbar, keine persönliche E-Mail</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>ASP Automation GmbH</t>
+          <t>H. Gautzsch Spedition GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Treuchtlingen (BY)</t>
+          <t>Münster</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Nur info@asp-automation.de; Inhaber Werner Schramm ohne persönliche E-Mail</t>
+          <t>Ansprechpartnerliste nennt für alle Personen nur info@gautzsch-spedition.de</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Neumüller GmbH</t>
+          <t>KÜHN Transport- und Lagerungsgesellschaft mbH</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Thyrnau (BY)</t>
+          <t>Ostbevern</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Persönliche E-Mails nur für Kran-Service und Einkauf/Buchhaltung – kein Entscheidungsträger belegbar</t>
+          <t>nur info@kuehn-transporte.com auffindbar</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>XENON Automatisierungstechnik GmbH</t>
+          <t>Feldmann Spedition GmbH</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Dresden (SN)</t>
+          <t>Gütersloh</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Nur Standort-Sammeladressen, keine persönliche E-Mail auf gecrawlten Seiten</t>
+          <t>nur dispo@feldmann-spedition.de</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>SITEC Industrietechnologie GmbH</t>
+          <t>WLS Spedition GmbH</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Chemnitz (SN)</t>
+          <t>Steinhagen</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail auffindbar</t>
+          <t>nur kontakt@wls-spedition.de</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>NILES-SIMMONS Industrieanlagen GmbH</t>
+          <t>Hartmann International GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Chemnitz (SN)</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Nur sales-Sammeladresse; zudem Konzernverbund NSH Group</t>
+          <t>Team-/Kontaktseiten nennen nur info@ bzw. standortbezogene Sammeladressen</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Schnaithmann Maschinenbau GmbH</t>
+          <t>Loeber-Lehnhof GmbH</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Remshalden (BW)</t>
+          <t>Siegen</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Keine E-Mail-Adressen im Quelltext (nur Formular)</t>
+          <t>Geschäftsführer Roman Mayer ohne persönliche E-Mail; gefundene Adresse gehört zum Webseitenbetreuer</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>ZELTWANGER Gruppe</t>
+          <t>Schröder Logistik GmbH</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Tübingen (BW)</t>
+          <t>Kirchlengern</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Nur funktionale Adressen (holding@, vertrieb.mb@, service@)</t>
+          <t>Teamseite zeigt Geschäftsführer ohne E-Mail, nur faktura@schroeder-logistik.de</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Eckerle Technologies GmbH</t>
+          <t>Loewe Logistics &amp; Care GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Malsch (BW)</t>
+          <t>Herford</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Persönliche E-Mails nur für Vertrieb/Auftragsabwicklung; kein Geschäftsführer/Prokurist mit E-Mail</t>
+          <t>keine E-Mail-Adressen auf gecrawlten Seiten auffindbar</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Höfelmeyer Waagen GmbH</t>
+          <t>Spedition Gerhard Siebel GmbH</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Georgsmarienhütte (NI)</t>
+          <t>Kreuztal</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Einzige persönliche E-Mail gehört Marketing – kein Entscheidungsträger</t>
+          <t>nur info@siebel-spedition.de</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Haupt Hydraulik &amp; Pneumatik (Inh. Thomas Zander e.K.)</t>
+          <t>Gössling Spedition GmbH</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Riesa (SN)</t>
+          <t>Arnsberg</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Inhaber Thomas Zander ohne persönliche E-Mail; nur Vertriebs-/Technikmitarbeiter</t>
+          <t>nur gs@goessling-spedition.de (Funktionsadresse ohne Personenzuordnung)</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>indusa GmbH</t>
+          <t>Kerber Transporte GmbH</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Waldems (HE)</t>
+          <t>Brilon</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Geschäftsleitung Dirk Schnieders ohne E-Mail; gelistete Adressen sind Gebiets-/Handelsvertretungen</t>
+          <t>nur info@kerber-transporte.de</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Papierverarbeitung Golzern GmbH</t>
+          <t>Spedition Mikus GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Grimma (SN)</t>
+          <t>Meschede</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Falsche Branche (Papierverarbeitung), kein Maschinen-/Anlagenbau</t>
+          <t>nur info@spedition-mikus.de</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Kampfer (Formen- und Sondermaschinenbau)</t>
+          <t>Glexx GmbH</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Betzenstein (BY)</t>
+          <t>Meschede</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Deutlich unter 50 Mitarbeiter – außerhalb des ICP (E-Mail des Inhabers wäre vorhanden)</t>
+          <t>nur post@glexx-logistik.de</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>ESMO AG / esmo automation</t>
+          <t>Kleinwächter GmbH &amp; Co. Spedition</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Rosenheim (BY)</t>
+          <t>Hallenberg</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Nur Funktionsadressen (sales.automation@, service.automation@); l.ingenhag ohne Positionsbeleg</t>
+          <t>keine erreichbare Website/keine E-Mails über getestete Domains</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Grenzebach Maschinenbau GmbH</t>
+          <t>Alfons Brass Spedition und Lagerei</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Asbach-Bäumenheim (BY)</t>
+          <t>Medebach</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Nur Standort-Sammeladressen; zudem Konzerngröße</t>
+          <t>keine E-Mails über getestete Domains auffindbar</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>teamtechnik / BBS Automation</t>
+          <t>Mönig Spedition Meschede GmbH</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Freiberg a.N. (BW)</t>
+          <t>Meschede</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Konzernstruktur, nur info-Adressen je Standort</t>
+          <t>keine E-Mails über getestete Domains auffindbar</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>SCHMID Group</t>
+          <t>Schulte-Lindhorst GmbH &amp; Co.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Freudenstadt (BW)</t>
+          <t>Rietberg</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Keine persönlichen E-Mails, nur Sammeladressen</t>
+          <t>nur info@schulte-lindhorst.de</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>HEDELIUS Maschinenfabrik GmbH</t>
+          <t>Thermotraffic GmbH</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Meppen (NI)</t>
+          <t>Versmold</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Nur Funktions-/Händleradressen, keine persönliche E-Mail</t>
+          <t>nur info@/sales@thermotraffic.de; zudem Konzernstruktur</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>WENZEL Group GmbH &amp; Co. KG</t>
+          <t>Tevex Logistics GmbH</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Wiesthal (BY)</t>
+          <t>Rheda-Wiedenbrück</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Nur sales-Sammeladressen je Land</t>
+          <t>nur info@tevex.de</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Maschinenfabrik EIRICH GmbH &amp; Co KG</t>
+          <t>Greiwing logistics for you GmbH</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Hardheim (BW)</t>
+          <t>Greven</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Nur eirich@eirich.de bzw. Auslandsgesellschaften</t>
+          <t>nur info@greiwing.de</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>PSB intralogistics GmbH</t>
+          <t>Sievert Logistik SE</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Pirmasens (RP)</t>
+          <t>Lengerich</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Keine persönlichen E-Mails auf gecrawlten Seiten</t>
+          <t>nur info.logistik@sievert.de; Teil der Sievert-Gruppe</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Langhammer GmbH</t>
+          <t>MP Logistik GmbH</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Eisenberg (RP)</t>
+          <t>Rheine</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Keine E-Mail-Adressen im Quelltext</t>
+          <t>nur info@/warehouse@mplogistik.com</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>ROEMHELD Gruppe</t>
+          <t>Wetralog GmbH</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Laubach (HE)</t>
+          <t>Münster</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Keine persönlichen E-Mails auffindbar</t>
+          <t>nur schadenservice@wetralog.de</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>HEMA Maschinen- und Apparateschutz GmbH</t>
+          <t>Hövener Spedition GmbH</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Seligenstadt (HE)</t>
+          <t>Rheine</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Keine E-Mail-Adressen im Quelltext</t>
+          <t>nur info@hoevener-spedition.de</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Sielaff GmbH &amp; Co. KG</t>
+          <t>Spedition Karl Kerkeling GmbH</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Herrieden (BY)</t>
+          <t>Coesfeld</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Nur Standort-Sammeladressen</t>
+          <t>nur info@spedition-kerkeling.de</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>MAFAC – E. Schwarz GmbH &amp; Co. KG</t>
+          <t>MAX-Logistik GmbH</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Alpirsbach (BW)</t>
+          <t>Senden</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Nur Adressen von Auslandsvertretungen, keine eigene Führungskraft</t>
+          <t>nur info@max-logistik.de</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>IMSTec GmbH</t>
+          <t>Lipperland Logistik GmbH / Möbelspedition Lipperland</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Heidelberg (BW)</t>
+          <t>Oelde</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Nur Team-Sammeladresse und US-Tochter</t>
+          <t>gefundene Adressen ohne Positionszuordnung (Datenschutz-/Impressumskontext), kein belegter Entscheidungsträger</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Pahnke Engineering GmbH &amp; Co. KG</t>
+          <t>Rosner Logistik GmbH</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Hamburg</t>
+          <t>Oelde</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Standort außerhalb der Zielbundesländer</t>
+          <t>keine E-Mails auf gecrawlten Seiten</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>SMB Sondermaschinenbau GmbH</t>
+          <t>Dingwerth Logistik GmbH</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Uplengen (NI)</t>
+          <t>Beelen</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Nur info@smb-sondermaschinen.de; GF Wolfgang Blank ohne persönliche E-Mail</t>
+          <t>keine E-Mails auf gecrawlten Seiten</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>DMV Sondermaschinenbau GmbH</t>
+          <t>TEDO Logistik GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Bad Wünnenberg</t>
+          <t>Ibbenbüren</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Nur dmv@dmv-sondermaschinenbau.de; zudem NRW</t>
+          <t>nur info@tedo-logistik.de</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Knecht Maschinenbau GmbH</t>
+          <t>Richter Express OHG</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Bergatreute (BW)</t>
+          <t>Saerbeck</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail auf Website auffindbar</t>
+          <t>nur info@richter-express.de</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Rühle &amp; Co. Maschinenbau GmbH</t>
+          <t>Schöpper Transport GmbH</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Walzbachtal (BW)</t>
+          <t>Greven</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Keine E-Mail-Adressen der Geschäftsführung veröffentlicht</t>
+          <t>nur info@ bzw. eine Adresse ohne belegte Positionszuordnung</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Emsland Metallbau GmbH – Arnd Brinkmann (Vertrieb)</t>
+          <t>Spedition Kockel GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Salzbergen (NI)</t>
+          <t>Soest</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Für Vertriebskontakt keine E-Mail wörtlich gelistet (nur Sammeladresse Anfragen_Vertrieb@)</t>
+          <t>nur info@spedition-kockel.de</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Wilhelm Altendorf GmbH &amp; Co. KG</t>
+          <t>Mimberg Spedition - Baustoffe GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Minden</t>
+          <t>Werl</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Zahlreiche personenbezogene E-Mails auf der Website, aber keine davon einem Geschäftsführer/Prokuristen oder zulässigen Bereichsleiter zugeordnet</t>
+          <t>nur Funktions-/Beispieladressen, keine Entscheidungsträger-E-Mail</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Kolbus GmbH &amp; Co. KG</t>
+          <t>Artur Kossack Spedition</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Rahden</t>
+          <t>Hiddenhausen</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Keine persönliche Entscheider-E-Mail auf Website/Impressum/Kontakt gefunden</t>
+          <t>nur info@kossack.de</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>AUMUND Fördertechnik GmbH</t>
+          <t>Westfalen-Lippe Speditions- und Lagerhausgesellschaft mbH</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Rheinberg</t>
+          <t>Herford</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Nur Kontaktformulare, keine persönliche E-Mail</t>
+          <t>nur info@wl-spedition.de</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>THIELE GmbH &amp; Co. KG</t>
+          <t>Martin Oelrich GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Iserlohn</t>
+          <t>Ladbergen</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Nur Sammeladressen (hebetechnik@) – keine persönliche Entscheider-E-Mail</t>
+          <t>gehört zur pfenning logistics group (Konzern), keine persönliche E-Mail</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>HASCO Hasenclever GmbH + Co KG</t>
+          <t>FIEGE / Nagel-Group / Duvenbeck</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Lüdenscheid</t>
+          <t>Greven / Versmold / Bocholt</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Konzerne mit &gt;5.000 Mitarbeitern, außerhalb Zielprofil</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Gebr. Eickhoff Maschinenfabrik</t>
+          <t>Heinrich Kottmann Spedition GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Büren</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Website ohne verwertbare E-Mail-Adressen</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Herbert Kannegiesser GmbH</t>
+          <t>Würfel-Massong Logistik GmbH</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Vlotho</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Maschinenbau &amp; Fertigung</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>keine E-Mails auf gecrawlten Seiten</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>HAVER &amp; BOECKER OHG</t>
+          <t>Enns Maschinenbau GmbH</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Oelde</t>
+          <t>Bad Oeynhausen</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -11488,19 +12099,19 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Personenbezogene Mails nur im Vertriebs-/Auslandsnetz, kein Entscheider mit Rolle belegt</t>
+          <t>Liegt in NRW – außerhalb des Fokusgebiets (persönliche E-Mail andreas@enns-mb.de wäre vorhanden)</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Reifenhäuser GmbH &amp; Co. KG</t>
+          <t>KASTO Maschinenbau GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Troisdorf</t>
+          <t>Achern (BW)</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -11510,19 +12121,19 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Nur Fachbereichs-/Recruiting-Mails, keine Geschäftsführung</t>
+          <t>Auf allen gecrawlten Seiten nur Sammeladressen (kasto@kasto.com) – keine persönliche E-Mail</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>battenfeld-cincinnati Germany GmbH</t>
+          <t>Heldele GmbH</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Bad Oeynhausen</t>
+          <t>Salach (BW)</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -11532,19 +12143,19 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Nur Vertriebs-/Länderkontakte, keine Entscheider-E-Mail</t>
+          <t>Nur Standort-Sammeladresse salach@heldele.de – keine persönliche E-Mail</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Hanning Elektro-Werke GmbH &amp; Co. KG</t>
+          <t>ASP Automation GmbH</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Oerlinghausen</t>
+          <t>Treuchtlingen (BY)</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -11554,19 +12165,19 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Nur Vertriebspartner-Mails; Impressum-Mail gehört zum externen Datenschutzbeauftragten</t>
+          <t>Nur info@asp-automation.de; Inhaber Werner Schramm ohne persönliche E-Mail</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Dürkopp Adler GmbH</t>
+          <t>Neumüller GmbH</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Bielefeld</t>
+          <t>Thyrnau (BY)</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -11576,19 +12187,19 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Nur Vertriebspartner-Adressen; zudem Konzernstruktur</t>
+          <t>Persönliche E-Mails nur für Kran-Service und Einkauf/Buchhaltung – kein Entscheidungsträger belegbar</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Klingelnberg GmbH</t>
+          <t>XENON Automatisierungstechnik GmbH</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Hückeswagen</t>
+          <t>Dresden (SN)</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -11598,19 +12209,19 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Nur Funktionspostfächer (kegelrad@, seminar@ etc.)</t>
+          <t>Nur Standort-Sammeladressen, keine persönliche E-Mail auf gecrawlten Seiten</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Kampf Schneid- und Wickeltechnik GmbH &amp; Co. KG</t>
+          <t>SITEC Industrietechnologie GmbH</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Wiehl</t>
+          <t>Chemnitz (SN)</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -11620,19 +12231,19 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Nur weltweite Vertriebs-/Agenturkontakte, keine Geschäftsführung</t>
+          <t>Keine persönliche E-Mail auffindbar</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Achenbach Buschhütten GmbH &amp; Co. KG</t>
+          <t>NILES-SIMMONS Industrieanlagen GmbH</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Kreuztal</t>
+          <t>Chemnitz (SN)</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -11642,19 +12253,19 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Nur Funktionspostfach fertigung@</t>
+          <t>Nur sales-Sammeladresse; zudem Konzernverbund NSH Group</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Gebr. Becker GmbH</t>
+          <t>Schnaithmann Maschinenbau GmbH</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Wuppertal</t>
+          <t>Remshalden (BW)</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -11664,19 +12275,19 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Personenbezogene Mails nur im Vertriebsinnendienst/Service ohne Entscheiderrolle</t>
+          <t>Keine E-Mail-Adressen im Quelltext (nur Formular)</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>KettenWulf Betriebs GmbH</t>
+          <t>ZELTWANGER Gruppe</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Eslohe</t>
+          <t>Tübingen (BW)</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -11686,19 +12297,19 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Nur funktionale Adressen (holding@, vertrieb.mb@, service@)</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>ELHA-MASCHINENBAU Liemke KG</t>
+          <t>Eckerle Technologies GmbH</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Halle (Westf.)</t>
+          <t>Malsch (BW)</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -11708,19 +12319,19 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Nur ausländische Vertriebspartner-Mails</t>
+          <t>Persönliche E-Mails nur für Vertrieb/Auftragsabwicklung; kein Geschäftsführer/Prokurist mit E-Mail</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>G. Siempelkamp GmbH &amp; Co. KG</t>
+          <t>Höfelmeyer Waagen GmbH</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Krefeld</t>
+          <t>Georgsmarienhütte (NI)</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -11730,19 +12341,19 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Keine persönliche Entscheider-E-Mail öffentlich</t>
+          <t>Einzige persönliche E-Mail gehört Marketing – kein Entscheidungsträger</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Hennecke GmbH</t>
+          <t>Haupt Hydraulik &amp; Pneumatik (Inh. Thomas Zander e.K.)</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Sankt Augustin</t>
+          <t>Riesa (SN)</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -11752,19 +12363,19 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Inhaber Thomas Zander ohne persönliche E-Mail; nur Vertriebs-/Technikmitarbeiter</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Kautex Maschinenbau GmbH</t>
+          <t>indusa GmbH</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Bonn</t>
+          <t>Waldems (HE)</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -11774,19 +12385,19 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Geschäftsleitung Dirk Schnieders ohne E-Mail; gelistete Adressen sind Gebiets-/Handelsvertretungen</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Lödige Industries GmbH</t>
+          <t>Papierverarbeitung Golzern GmbH</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Warburg/Paderborn</t>
+          <t>Grimma (SN)</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -11796,19 +12407,19 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Falsche Branche (Papierverarbeitung), kein Maschinen-/Anlagenbau</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Schmidt + Clemens GmbH &amp; Co. KG</t>
+          <t>Kampfer (Formen- und Sondermaschinenbau)</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Lindlar</t>
+          <t>Betzenstein (BY)</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -11818,19 +12429,19 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Deutlich unter 50 Mitarbeiter – außerhalb des ICP (E-Mail des Inhabers wäre vorhanden)</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>MSK Verpackungs-Systeme GmbH</t>
+          <t>ESMO AG / esmo automation</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Kleve</t>
+          <t>Rosenheim (BY)</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -11840,19 +12451,19 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Nur Kontaktformulare, keine persönliche E-Mail</t>
+          <t>Nur Funktionsadressen (sales.automation@, service.automation@); l.ingenhag ohne Positionsbeleg</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>SPALECK GmbH &amp; Co. KG</t>
+          <t>Grenzebach Maschinenbau GmbH</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Bocholt</t>
+          <t>Asbach-Bäumenheim (BY)</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -11862,19 +12473,19 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Keine persönliche Entscheider-E-Mail auffindbar</t>
+          <t>Nur Standort-Sammeladressen; zudem Konzerngröße</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Rhein-Nadel Automation GmbH</t>
+          <t>teamtechnik / BBS Automation</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Aachen</t>
+          <t>Freiberg a.N. (BW)</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -11884,19 +12495,19 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Konzernstruktur, nur info-Adressen je Standort</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>STRACK NORMA GmbH &amp; Co. KG</t>
+          <t>SCHMID Group</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Lüdenscheid</t>
+          <t>Freudenstadt (BW)</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -11906,19 +12517,19 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Keine persönlichen E-Mails, nur Sammeladressen</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>TRACTO-TECHNIK GmbH &amp; Co. KG</t>
+          <t>HEDELIUS Maschinenfabrik GmbH</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Lennestadt</t>
+          <t>Meppen (NI)</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -11928,19 +12539,19 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Nur Funktions-/Händleradressen, keine persönliche E-Mail</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Albrecht Bäumer GmbH &amp; Co. KG</t>
+          <t>WENZEL Group GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Freudenberg</t>
+          <t>Wiesthal (BY)</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -11950,19 +12561,19 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Nur sales-Sammeladressen je Land</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Düchting Pumpen Maschinenfabrik GmbH &amp; Co. KG</t>
+          <t>Maschinenfabrik EIRICH GmbH &amp; Co KG</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Wetter (Ruhr)</t>
+          <t>Hardheim (BW)</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -11972,19 +12583,19 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Nur eirich@eirich.de bzw. Auslandsgesellschaften</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>A. Monforts Textilmaschinen GmbH &amp; Co. KG</t>
+          <t>PSB intralogistics GmbH</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Mönchengladbach</t>
+          <t>Pirmasens (RP)</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -11994,19 +12605,19 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Einziger belegter Entscheider (Betriebsleiter) sitzt in der österreichischen Niederlassung – außerhalb NRW</t>
+          <t>Keine persönlichen E-Mails auf gecrawlten Seiten</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Murtfeldt Kunststoffe GmbH &amp; Co. KG</t>
+          <t>Langhammer GmbH</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>Eisenberg (RP)</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -12016,19 +12627,19 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Keine E-Mail-Adressen im Quelltext</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>DENIOS SE</t>
+          <t>ROEMHELD Gruppe</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Bad Oeynhausen</t>
+          <t>Laubach (HE)</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -12038,19 +12649,19 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Keine persönliche Entscheider-E-Mail öffentlich</t>
+          <t>Keine persönlichen E-Mails auffindbar</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Venjakob Maschinenbau GmbH &amp; Co. KG</t>
+          <t>HEMA Maschinen- und Apparateschutz GmbH</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Rheda-Wiedenbrück</t>
+          <t>Seligenstadt (HE)</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -12060,19 +12671,19 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Keine E-Mail-Adressen im Quelltext</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Remmert GmbH</t>
+          <t>Sielaff GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Löhne</t>
+          <t>Herrieden (BY)</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -12082,19 +12693,19 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Nur Standort-Sammeladressen</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Rippert GmbH &amp; Co. KG</t>
+          <t>MAFAC – E. Schwarz GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Herzebrock-Clarholz</t>
+          <t>Alpirsbach (BW)</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -12104,19 +12715,19 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Nur Adressen von Auslandsvertretungen, keine eigene Führungskraft</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Ohrmann GmbH Montagetechnik</t>
+          <t>IMSTec GmbH</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Rheda-Wiedenbrück</t>
+          <t>Heidelberg (BW)</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -12126,19 +12737,19 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Nur Team-Sammeladresse und US-Tochter</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Sollich KG</t>
+          <t>Pahnke Engineering GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Bad Salzuflen</t>
+          <t>Hamburg</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -12148,19 +12759,19 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Standort außerhalb der Zielbundesländer</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>steute Technologies GmbH &amp; Co. KG</t>
+          <t>SMB Sondermaschinenbau GmbH</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Löhne</t>
+          <t>Uplengen (NI)</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -12170,19 +12781,19 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Nur info@smb-sondermaschinen.de; GF Wolfgang Blank ohne persönliche E-Mail</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Torwegge GmbH &amp; Co. KG</t>
+          <t>DMV Sondermaschinenbau GmbH</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Bielefeld</t>
+          <t>Bad Wünnenberg</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -12192,19 +12803,19 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Nur dmv@dmv-sondermaschinenbau.de; zudem NRW</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Wemhöner Surface Technologies GmbH &amp; Co. KG</t>
+          <t>Knecht Maschinenbau GmbH</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Herford</t>
+          <t>Bergatreute (BW)</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -12214,19 +12825,19 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Nur internationale Handelsvertreter-Mails, keine Geschäftsführung</t>
+          <t>Keine persönliche E-Mail auf Website auffindbar</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>RK Rose+Krieger GmbH</t>
+          <t>Rühle &amp; Co. Maschinenbau GmbH</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Minden</t>
+          <t>Walzbachtal (BW)</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -12236,19 +12847,19 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Nur Funktions-/Auslandspostfächer; zudem Konzernzugehörigkeit (Phoenix Mecano)</t>
+          <t>Keine E-Mail-Adressen der Geschäftsführung veröffentlicht</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Carl Werthenbach Konstruktionsteile GmbH &amp; Co. KG</t>
+          <t>Emsland Metallbau GmbH – Arnd Brinkmann (Vertrieb)</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Bielefeld</t>
+          <t>Salzbergen (NI)</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -12258,19 +12869,19 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Geschäftsführer im Impressum genannt, aber nur info@/industrietechnik@ – keine persönliche E-Mail</t>
+          <t>Für Vertriebskontakt keine E-Mail wörtlich gelistet (nur Sammeladresse Anfragen_Vertrieb@)</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Seppeler Holding und Verwaltungs GmbH &amp; Co. KG</t>
+          <t>Wilhelm Altendorf GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Rietberg</t>
+          <t>Minden</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -12280,19 +12891,19 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Geschäftsführer im Impressum genannt, aber nur info-holding@ – keine persönliche E-Mail</t>
+          <t>Zahlreiche personenbezogene E-Mails auf der Website, aber keine davon einem Geschäftsführer/Prokuristen oder zulässigen Bereichsleiter zugeordnet</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>MIT Moderne Industrietechnik GmbH &amp; Co. KG</t>
+          <t>Kolbus GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Vlotho</t>
+          <t>Rahden</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -12302,19 +12913,19 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>Geschäftsführung genannt, E-Mail nur als Sammeladresse mit@systemarmaturen.de</t>
+          <t>Keine persönliche Entscheider-E-Mail auf Website/Impressum/Kontakt gefunden</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Schubert &amp; Salzer / ventiltechnik.de (Vlotho)</t>
+          <t>AUMUND Fördertechnik GmbH</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Vlotho</t>
+          <t>Rheinberg</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -12324,19 +12935,19 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Persönliche Mails nur für Vertriebsleitung/Sales Director – keine Geschäftsführung, Vertrieb zählt laut Vorgabe nicht</t>
+          <t>Nur Kontaktformulare, keine persönliche E-Mail</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Heilig Maschinenbau GmbH</t>
+          <t>THIELE GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Bad Salzuflen</t>
+          <t>Iserlohn</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -12346,19 +12957,19 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Impressum nennt GF Sascha Heilig, die angegebene Adresse heilig@heilig-maschinenbau.de ist jedoch nicht eindeutig persönlich (Firmenname = Nachname) – bei Unsicherheit verworfen</t>
+          <t>Nur Sammeladressen (hebetechnik@) – keine persönliche Entscheider-E-Mail</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>ATL Luhden GmbH</t>
+          <t>HASCO Hasenclever GmbH + Co KG</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Luhden</t>
+          <t>Lüdenscheid</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -12368,19 +12979,19 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Betriebsleiter/Prokurist mit persönlicher Mail belegt, Standort liegt jedoch in Niedersachsen (nicht NRW)</t>
+          <t>Keine persönliche E-Mail öffentlich</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>DUBOR Groneweg GmbH &amp; Co. KG</t>
+          <t>Gebr. Eickhoff Maschinenfabrik</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Bad Salzuflen</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -12390,19 +13001,19 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Ansprechpartnerseite mit Entscheidern vorhanden, aber Branche Backmittel/Lebensmittel – kein Maschinenbau; GF-Adressen zudem nur info@</t>
+          <t>Keine persönliche E-Mail öffentlich</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>AMR-Engineering GmbH</t>
+          <t>Herbert Kannegiesser GmbH</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Essen</t>
+          <t>Vlotho</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -12412,19 +13023,19 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Geschäftsführer im Impressum genannt, aber nur Sammeladresse amr@amr.de</t>
+          <t>Keine persönliche E-Mail öffentlich</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>SIEBTECHNIK TEMA GmbH</t>
+          <t>HAVER &amp; BOECKER OHG</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Mülheim an der Ruhr</t>
+          <t>Oelde</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -12434,19 +13045,19 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Personenbezogene Mails nur im Vertriebs-/Auslandsnetz, kein Entscheider mit Rolle belegt</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>HAZEMAG &amp; EPR GmbH</t>
+          <t>Reifenhäuser GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Dülmen</t>
+          <t>Troisdorf</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -12456,19 +13067,19 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Nur Fachbereichs-/Recruiting-Mails, keine Geschäftsführung</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>BOGE KOMPRESSOREN Otto Boge GmbH &amp; Co. KG</t>
+          <t>battenfeld-cincinnati Germany GmbH</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Bielefeld</t>
+          <t>Bad Oeynhausen</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -12478,19 +13089,19 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Nur Länder-Sammelpostfächer</t>
+          <t>Nur Vertriebs-/Länderkontakte, keine Entscheider-E-Mail</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>PROBAT SE</t>
+          <t>Hanning Elektro-Werke GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Emmerich am Rhein</t>
+          <t>Oerlinghausen</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -12500,19 +13111,19 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Nur Vertriebspartner-Mails; Impressum-Mail gehört zum externen Datenschutzbeauftragten</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Otto Junker GmbH</t>
+          <t>Dürkopp Adler GmbH</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Simmerath</t>
+          <t>Bielefeld</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -12522,19 +13133,19 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Nur Vertriebspartner-Adressen; zudem Konzernstruktur</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>REMBE GmbH Safety+Control</t>
+          <t>Klingelnberg GmbH</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Brilon</t>
+          <t>Hückeswagen</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -12544,19 +13155,19 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Nur Funktionspostfächer (kegelrad@, seminar@ etc.)</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>OVENTROP GmbH &amp; Co. KG</t>
+          <t>Kampf Schneid- und Wickeltechnik GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Olsberg</t>
+          <t>Wiehl</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -12566,19 +13177,19 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Nur weltweite Vertriebs-/Agenturkontakte, keine Geschäftsführung</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>BJB GmbH &amp; Co. KG</t>
+          <t>Achenbach Buschhütten GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Arnsberg</t>
+          <t>Kreuztal</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -12588,19 +13199,19 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Nur Funktionspostfach fertigung@</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Ruhrpumpen GmbH</t>
+          <t>Gebr. Becker GmbH</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Witten</t>
+          <t>Wuppertal</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -12610,19 +13221,19 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Personenbezogene Mails nur im Vertriebsinnendienst/Service ohne Entscheiderrolle</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Winkelmann Group GmbH + Co. KG</t>
+          <t>KettenWulf Betriebs GmbH</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Ahlen</t>
+          <t>Eslohe</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -12639,12 +13250,12 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>GERSTUNG Sondermaschinen GmbH</t>
+          <t>ELHA-MASCHINENBAU Liemke KG</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Mönchengladbach</t>
+          <t>Halle (Westf.)</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -12654,19 +13265,19 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Nur ausländische Vertriebspartner-Mails</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>AUMAT Maschinenbau GmbH</t>
+          <t>G. Siempelkamp GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>NRW</t>
+          <t>Krefeld</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -12676,19 +13287,19 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Keine persönliche E-Mail öffentlich</t>
+          <t>Keine persönliche Entscheider-E-Mail öffentlich</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Maschinen- und Industriebau Feld GmbH</t>
+          <t>Hennecke GmbH</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>NRW</t>
+          <t>Sankt Augustin</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -12698,19 +13309,19 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Ansprechpartnerseite vorhanden, aber ohne persönliche E-Mail-Adressen</t>
+          <t>Keine persönliche E-Mail öffentlich</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>VGS Automatisierungstechnik GmbH &amp; Co. KG</t>
+          <t>Kautex Maschinenbau GmbH</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Schloß Holte-Stukenbrock</t>
+          <t>Bonn</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -12727,12 +13338,12 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Ebert Maschinenbau GmbH</t>
+          <t>Lödige Industries GmbH</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Minden</t>
+          <t>Warburg/Paderborn</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -12749,12 +13360,12 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>BELU GmbH</t>
+          <t>Schmidt + Clemens GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Bielefeld</t>
+          <t>Lindlar</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -12771,12 +13382,12 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Pfister Fertigungstechnik / GMM mbH / MB Klich</t>
+          <t>MSK Verpackungs-Systeme GmbH</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>NRW</t>
+          <t>Kleve</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -12786,19 +13397,19 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>CNC-Lohnfertiger ohne persönliche Entscheider-E-Mail auf der Website</t>
+          <t>Nur Kontaktformulare, keine persönliche E-Mail</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Selzer Formenbau GmbH / Dietrich Formenbau / KM Formenbau / Jedig &amp; Heyns / Wilfrid Humme</t>
+          <t>SPALECK GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Lüdenscheid</t>
+          <t>Bocholt</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -12808,27 +13419,973 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Werkzeug-/Formenbauer ohne persönliche Entscheider-E-Mail auf der Website</t>
+          <t>Keine persönliche Entscheider-E-Mail auffindbar</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
+          <t>Rhein-Nadel Automation GmbH</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Aachen</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>STRACK NORMA GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Lüdenscheid</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>TRACTO-TECHNIK GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Lennestadt</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Albrecht Bäumer GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Freudenberg</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Düchting Pumpen Maschinenfabrik GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Wetter (Ruhr)</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>A. Monforts Textilmaschinen GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Mönchengladbach</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>Einziger belegter Entscheider (Betriebsleiter) sitzt in der österreichischen Niederlassung – außerhalb NRW</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Murtfeldt Kunststoffe GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Dortmund</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>DENIOS SE</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Bad Oeynhausen</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>Keine persönliche Entscheider-E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Venjakob Maschinenbau GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Rheda-Wiedenbrück</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Remmert GmbH</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Löhne</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Rippert GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Herzebrock-Clarholz</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Ohrmann GmbH Montagetechnik</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Rheda-Wiedenbrück</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Sollich KG</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Bad Salzuflen</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>steute Technologies GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Löhne</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Torwegge GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Bielefeld</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Wemhöner Surface Technologies GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Herford</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>Nur internationale Handelsvertreter-Mails, keine Geschäftsführung</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>RK Rose+Krieger GmbH</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Minden</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>Nur Funktions-/Auslandspostfächer; zudem Konzernzugehörigkeit (Phoenix Mecano)</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Carl Werthenbach Konstruktionsteile GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Bielefeld</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>Geschäftsführer im Impressum genannt, aber nur info@/industrietechnik@ – keine persönliche E-Mail</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Seppeler Holding und Verwaltungs GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Rietberg</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>Geschäftsführer im Impressum genannt, aber nur info-holding@ – keine persönliche E-Mail</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>MIT Moderne Industrietechnik GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Vlotho</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>Geschäftsführung genannt, E-Mail nur als Sammeladresse mit@systemarmaturen.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Schubert &amp; Salzer / ventiltechnik.de (Vlotho)</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Vlotho</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>Persönliche Mails nur für Vertriebsleitung/Sales Director – keine Geschäftsführung, Vertrieb zählt laut Vorgabe nicht</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Heilig Maschinenbau GmbH</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Bad Salzuflen</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>Impressum nennt GF Sascha Heilig, die angegebene Adresse heilig@heilig-maschinenbau.de ist jedoch nicht eindeutig persönlich (Firmenname = Nachname) – bei Unsicherheit verworfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>ATL Luhden GmbH</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Luhden</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>Betriebsleiter/Prokurist mit persönlicher Mail belegt, Standort liegt jedoch in Niedersachsen (nicht NRW)</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>DUBOR Groneweg GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Bad Salzuflen</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>Ansprechpartnerseite mit Entscheidern vorhanden, aber Branche Backmittel/Lebensmittel – kein Maschinenbau; GF-Adressen zudem nur info@</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>AMR-Engineering GmbH</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Essen</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>Geschäftsführer im Impressum genannt, aber nur Sammeladresse amr@amr.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>SIEBTECHNIK TEMA GmbH</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Mülheim an der Ruhr</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>HAZEMAG &amp; EPR GmbH</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Dülmen</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>BOGE KOMPRESSOREN Otto Boge GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Bielefeld</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>Nur Länder-Sammelpostfächer</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>PROBAT SE</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Emmerich am Rhein</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Otto Junker GmbH</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Simmerath</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>REMBE GmbH Safety+Control</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Brilon</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>OVENTROP GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Olsberg</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>BJB GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Arnsberg</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Ruhrpumpen GmbH</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Witten</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Winkelmann Group GmbH + Co. KG</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Ahlen</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>GERSTUNG Sondermaschinen GmbH</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Mönchengladbach</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>AUMAT Maschinenbau GmbH</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>NRW</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Maschinen- und Industriebau Feld GmbH</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>NRW</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>Ansprechpartnerseite vorhanden, aber ohne persönliche E-Mail-Adressen</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>VGS Automatisierungstechnik GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Schloß Holte-Stukenbrock</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Ebert Maschinenbau GmbH</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Minden</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>BELU GmbH</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Bielefeld</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>Keine persönliche E-Mail öffentlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Pfister Fertigungstechnik / GMM mbH / MB Klich</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>NRW</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>CNC-Lohnfertiger ohne persönliche Entscheider-E-Mail auf der Website</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Selzer Formenbau GmbH / Dietrich Formenbau / KM Formenbau / Jedig &amp; Heyns / Wilfrid Humme</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Lüdenscheid</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>Werkzeug-/Formenbauer ohne persönliche Entscheider-E-Mail auf der Website</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
           <t>Hagener Fördertechnik – Stefan Maschmeier (Prokurist)</t>
         </is>
       </c>
-      <c r="B299" t="inlineStr">
+      <c r="B342" t="inlineStr">
         <is>
           <t>Hagen</t>
         </is>
       </c>
-      <c r="C299" t="inlineStr">
+      <c r="C342" t="inlineStr">
         <is>
           <t>Maschinenbau &amp; Fertigung</t>
         </is>
       </c>
-      <c r="D299" t="inlineStr">
+      <c r="D342" t="inlineStr">
         <is>
           <t>Als zweiter Entscheider geprüft, aber nur info@hafoe.de hinterlegt – daher nicht verwendet</t>
         </is>

--- a/leads-adept/leads-adept.xlsx
+++ b/leads-adept/leads-adept.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Verworfen" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$I$151</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$I$166</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I151"/>
+  <dimension ref="A1:I166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2283,27 +2283,27 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Holger Krebs</t>
+          <t>Andreas Bültmann</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer</t>
+          <t>Geschäftsleitung (Inhaberfamilie)</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>krebs@ctechnik.de</t>
+          <t>ab@bueltmann.com</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>+49 2154 89102-0</t>
+          <t>+49 2394 18-0</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>C-Technik Maschinen- und Anlagenbau GmbH</t>
+          <t>Bültmann GmbH</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -2313,44 +2313,44 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Willich (Niederrhein); zweiter Standort Hagen</t>
+          <t>Neuenrade (Sauerland/Märkischer Kreis)</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Inhabergeführter Sondermaschinen- und Anlagenbauer mit Konstruktion, Kalkulation und Projektmanagement; Sitz 47877 Willich, weiterer Standort im Raum Hagen.</t>
+          <t>Mitglied der Geschäftsleitung des inhabergeführten Maschinen- und Anlagenbauers für Metall-Ziehtechnik.</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>https://ctechnik.de/kontakt/ | https://ctechnik.de/ (Adresse 47877 Willich) | Zweiter Geschäftsführer auf derselben Seite: 'Mirko Krebs | Geschäftsführer | T. +49 2154 89102 – 211 | mkrebs@ctechnik.de'</t>
+          <t>https://www.bueltmann.com/kontakt-direkter-draht</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Maik Vogtt</t>
+          <t>Andreas Zimball</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Fertigung (Ansprechpartner Produktion)</t>
+          <t>Vertriebsleiter / Prokurist</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>mavog@emsland-metallbau.de</t>
+          <t>az@bueltmann.com</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>+49 5971 8004-156</t>
+          <t>+49 2394 18-253</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Emsland Metallbau GmbH</t>
+          <t>Bültmann GmbH</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -2360,44 +2360,44 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Salzbergen (Niedersachsen)</t>
+          <t>Neuenrade (Sauerland/Märkischer Kreis)</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Mittelständischer Metall- und Stahlbau-/Fertigungsbetrieb mit Blechbearbeitung, Schweißbaugruppen und Auftragsfertigung für den Maschinen- und Anlagenbau. Einkauf/Supply Chain: André Hülsmann (anhue@emsland-metallbau.de, gleiche Quelle).</t>
+          <t>Prokurist und Vertriebsleiter, damit zeichnungsberechtigter Entscheidungsträger im Familienunternehmen.</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>https://www.emsland-metallbau.de/kontakt/kontakt-zu-uns/</t>
+          <t>https://www.bueltmann.com/kontakt-direkter-draht</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Dirk Haßmann</t>
+          <t>Petra Bültmann-Steffin</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Leiter Einkauf (Bereichsleiter Einkauf/Supply Chain)</t>
+          <t>Geschäftsleitung (Inhaberfamilie)</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Dirk.Hassmann@flaco.de</t>
+          <t>pb@bueltmann.com</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>+49 (0) 5241 603-62</t>
+          <t>+49 2394 18-0</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>FLACO-Geräte GmbH</t>
+          <t>Bültmann GmbH</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -2407,44 +2407,44 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Gütersloh (Ostwestfalen-Lippe)</t>
+          <t>Neuenrade (Sauerland/Märkischer Kreis)</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Hersteller von Fluid-, Tank- und Werkstatttechnik sowie Fluidsystemen für Fertigungsbetriebe. Geschäftsführer Thomas Voigt ist auf der Kontaktseite genannt, jedoch ohne persönliche E-Mail – daher der Einkaufsleiter als Entscheider hinterlegt.</t>
+          <t>Familienunternehmen für Ziehanlagen, Rohr- und Stangenbearbeitungsanlagen sowie Sondermaschinen für die Metallindustrie.</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>https://flaco.de/de/kontakt-beratung.html | https://flaco.de/de/kontakt-beratung.html (Zitat zur Geschäftsführung ohne E-Mail: 'Thomas Voigt | Geschäftsführer | Tel. +49 (0) 5241 - 603 - 0')</t>
+          <t>https://www.bueltmann.com/kontakt-direkter-draht | https://www.regiomanager.de/suedwestfalen/ranking/produktion/maschinenbau/suedwestfalen/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Holger Fries</t>
+          <t>Holger Krebs</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführung</t>
+          <t>Geschäftsführer</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>h.fries@fries-gmbh.de</t>
+          <t>krebs@ctechnik.de</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>+49 2743 9223-13</t>
+          <t>+49 2154 89102-0</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Fries Maschinen- und Anlagenbau GmbH</t>
+          <t>C-Technik Maschinen- und Anlagenbau GmbH</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -2454,44 +2454,44 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Derschen (Rheinland-Pfalz, Westerwald)</t>
+          <t>Willich (Niederrhein); zweiter Standort Hagen</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Familiengeführter Maschinen- und Anlagenbauer seit 1980 mit Zerspanung, Schweißtechnik, Montage und eigener Konstruktion.</t>
+          <t>Inhabergeführter Sondermaschinen- und Anlagenbauer mit Konstruktion, Kalkulation und Projektmanagement; Sitz 47877 Willich, weiterer Standort im Raum Hagen.</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>https://www.fries-gmbh.de/kontakt</t>
+          <t>https://ctechnik.de/kontakt/ | https://ctechnik.de/ (Adresse 47877 Willich) | Zweiter Geschäftsführer auf derselben Seite: 'Mirko Krebs | Geschäftsführer | T. +49 2154 89102 – 211 | mkrebs@ctechnik.de'</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Andreas Schneider</t>
+          <t>Maik Vogtt</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer (Dipl.-Wirt.-Ing.)</t>
+          <t>Fertigung (Ansprechpartner Produktion)</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>a.schneider@icmgmbh-chemnitz.de</t>
+          <t>mavog@emsland-metallbau.de</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>+49 371 27836 450</t>
+          <t>+49 5971 8004-156</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>ICM GmbH – Innovation + Cooperation für den Maschinenbau</t>
+          <t>Emsland Metallbau GmbH</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -2501,44 +2501,44 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Chemnitz (Sachsen)</t>
+          <t>Salzbergen (Niedersachsen)</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Chemnitzer Entwicklungs- und Engineering-Dienstleister für den Maschinen- und Anlagenbau (Produktentwicklung, Konstruktion, Automation).</t>
+          <t>Mittelständischer Metall- und Stahlbau-/Fertigungsbetrieb mit Blechbearbeitung, Schweißbaugruppen und Auftragsfertigung für den Maschinen- und Anlagenbau. Einkauf/Supply Chain: André Hülsmann (anhue@emsland-metallbau.de, gleiche Quelle).</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>https://www.icmgmbh-chemnitz.de/kontakt | https://www.icmgmbh-chemnitz.de/impressum ('Geschäftsführer: Herr Dipl.-Wirt.-Ing. Andreas Schneider') | https://www.icmgmbh-chemnitz.de/leistungen/anlagenbau-und-automation</t>
+          <t>https://www.emsland-metallbau.de/kontakt/kontakt-zu-uns/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Frederic Lanz</t>
+          <t>Dirk Haßmann</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>CEO / Vice Chairman of the Board</t>
+          <t>Leiter Einkauf (Bereichsleiter Einkauf/Supply Chain)</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>lanz@kemper.eu</t>
+          <t>Dirk.Hassmann@flaco.de</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>+49 (0) 2564 68-119</t>
+          <t>+49 (0) 5241 603-62</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>KEMPER GmbH</t>
+          <t>FLACO-Geräte GmbH</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -2548,44 +2548,44 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Vreden (Münsterland, NRW)</t>
+          <t>Gütersloh (Ostwestfalen-Lippe)</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Familiengeführter Hersteller von Absaug- und Filteranlagen sowie Schweißrauchabsaugung für die metallverarbeitende Fertigung. Sitz 48691 Vreden.</t>
+          <t>Hersteller von Fluid-, Tank- und Werkstatttechnik sowie Fluidsystemen für Fertigungsbetriebe. Geschäftsführer Thomas Voigt ist auf der Kontaktseite genannt, jedoch ohne persönliche E-Mail – daher der Einkaufsleiter als Entscheider hinterlegt.</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>https://kemper.eu/Unternehmen/Kontakt/ | https://kemper.eu/Unternehmen/ (Adresse 48691 Vreden)</t>
+          <t>https://flaco.de/de/kontakt-beratung.html | https://flaco.de/de/kontakt-beratung.html (Zitat zur Geschäftsführung ohne E-Mail: 'Thomas Voigt | Geschäftsführer | Tel. +49 (0) 5241 - 603 - 0')</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Johann Liebl</t>
+          <t>Holger Fries</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer</t>
+          <t>Geschäftsführung</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>johann.liebl@lieblmetall.de</t>
+          <t>h.fries@fries-gmbh.de</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>+49 9438 90091</t>
+          <t>+49 2743 9223-13</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Lieblmetall GmbH</t>
+          <t>Fries Maschinen- und Anlagenbau GmbH</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -2595,44 +2595,44 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Ebermannsdorf (Bayern, Oberpfalz)</t>
+          <t>Derschen (Rheinland-Pfalz, Westerwald)</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Familiengeführter Fertigungsbetrieb für Blechbearbeitung und Lohnfertigung (Laserschneiden, CNC-Biegen, Schweißbaugruppen) für den Maschinenbau. Betriebsleitung &amp; Gesellschafter: Martin Liebl (martin.liebl@lieblmetall.de, gleiche Quelle).</t>
+          <t>Familiengeführter Maschinen- und Anlagenbauer seit 1980 mit Zerspanung, Schweißtechnik, Montage und eigener Konstruktion.</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>https://www.lieblmetall.de/de/kontakt</t>
+          <t>https://www.fries-gmbh.de/kontakt</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Dr. Sascha Falkenberg</t>
+          <t>Henning Griese</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Managing Director / Member of the Board (Geschäftsführer)</t>
+          <t>Geschäftsführer (2. Generation)</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>s.falkenberg@minda.com</t>
+          <t>h.griese@griesotec.de</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>+49 (0) 5721 / 9789-20</t>
+          <t>+49 2572 96734-14</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>MINDA Industrieanlagen GmbH</t>
+          <t>GriesoTec Maschinenbau GmbH</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -2642,44 +2642,44 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Minden (Ostwestfalen-Lippe)</t>
+          <t>Emsdetten (Münsterland)</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>Anlagenbauer für Material- und Fördertechnik in der Wellpappen-, Holzwerkstoff- und Reifenindustrie mit Hauptsitz Minden.</t>
+          <t>Geschäftsführer der zweiten Generation im Familienbetrieb für komplexe Sondermaschinen und Baugruppenfertigung.</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>https://minda.com/en/contact/general-management | https://minda.com/en/contact/management (Produktionsleitung Minden: 'Dirk Juras | Head of Production | +49 (0) 571 / 3997 - 0 | d.juras@minda.com')</t>
+          <t>https://www.griesotec.de/ansprechpartner.html</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Diana Reich</t>
+          <t>Kurt Griese</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführung</t>
+          <t>Geschäftsführer (Gründer/Inhaber)</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>diana.reich@msr-chemnitz.de</t>
+          <t>griese@griesotec.de</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>+49 371 81495-21</t>
+          <t>+49 2572 96734-10</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>MSR Elektro- und Anlagenbau GmbH</t>
+          <t>GriesoTec Maschinenbau GmbH</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -2689,44 +2689,44 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Chemnitz (Sachsen)</t>
+          <t>Emsdetten (Münsterland)</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Mittelständischer Elektro- und Anlagenbauer aus Chemnitz mit Projektierung, Schaltanlagenbau und Automatisierung für Industrieanlagen. Zweiter Geschäftsführer: Sven Mehnert (sven.mehnert@msr-chemnitz.de, gleiche Quelle).</t>
+          <t>Familienbetrieb für Sondermaschinenbau, Lohnfertigung und Industriemontage; 1991 gegründet, seit 2018 als GriesoTec firmierend.</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>https://www.msr-chemnitz.de/kontakt/ | https://www.msr-chemnitz.de/ueber-uns/</t>
+          <t>https://www.griesotec.de/ansprechpartner.html</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Heiko Müller</t>
+          <t>Thomas Scholz</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer (lt. Impressum vertretungsberechtigt), Technik und Vertrieb</t>
+          <t>Ansprechpartner/Leitung Sondermaschinenlösungen</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>heiko.mueller@mueller-sut.de</t>
+          <t>t.scholz@grunewald.de</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>+49 9254 7913</t>
+          <t>+49 2871 2507241</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Müller Maschinen und Anlagen GmbH &amp; Co. KG (MÜLLER Gefrees)</t>
+          <t>Grunewald GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -2736,44 +2736,44 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Gefrees (Bayern, Oberfranken)</t>
+          <t>Bocholt (Westmünsterland)</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>Inhabergeführter Hersteller von Pressen und Sondermaschinen (C-Gestell-Pressen, Stanzautomaten, CNC-Stanzanlagen) inkl. Kundendienst und Retrofit.</t>
+          <t>Familienunternehmen (GF Ulrich und Philipp Grunewald) für Werkzeugbau, Modellbau, Aluminiumguss und Sondermaschinenbau.</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>https://mueller-sut.de/kontakt/ansprechpartner/ | https://mueller-sut.de/impressum/ ('Müller Maschinen und Anlagen GmbH &amp; Co. KG ... Vertreten durch Herr Heiko Müller')</t>
+          <t>https://www.grunewald.de/kontakt/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Johannes Rehm</t>
+          <t>Andreas Schneider</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer / CEO</t>
+          <t>Geschäftsführer (Dipl.-Wirt.-Ing.)</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>j.rehm@rehm-group.com</t>
+          <t>a.schneider@icmgmbh-chemnitz.de</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>+49 7344 9606-0</t>
+          <t>+49 371 27836 450</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Rehm Thermal Systems GmbH</t>
+          <t>ICM GmbH – Innovation + Cooperation für den Maschinenbau</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -2783,44 +2783,44 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Blaubeuren-Seissen (Baden-Württemberg)</t>
+          <t>Chemnitz (Sachsen)</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Familiengeführter Sondermaschinenbauer für thermische Systemlösungen und Fertigungsanlagen der Elektronik- und Leistungselektronikproduktion.</t>
+          <t>Chemnitzer Entwicklungs- und Engineering-Dienstleister für den Maschinen- und Anlagenbau (Produktentwicklung, Konstruktion, Automation).</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>https://www.rehm-group.com/unternehmen.html</t>
+          <t>https://www.icmgmbh-chemnitz.de/kontakt | https://www.icmgmbh-chemnitz.de/impressum ('Geschäftsführer: Herr Dipl.-Wirt.-Ing. Andreas Schneider') | https://www.icmgmbh-chemnitz.de/leistungen/anlagenbau-und-automation</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Volker Rößner</t>
+          <t>Paul Horstmann</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer, Vertrieb</t>
+          <t>CEO / Geschäftsführer</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>v.roessner@roessner-maschinenbau.de</t>
+          <t>paul.horstmann@iq-sps.de</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>+49 6631 9622-24</t>
+          <t>+49 2557 928 53 25</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Rößner Maschinenbau GmbH</t>
+          <t>IQ-SPS GmbH</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -2830,44 +2830,44 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Alsfeld (Hessen)</t>
+          <t>Wettringen (Kreis Steinfurt, Münsterland)</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>Familiengeführter Maschinenbau- und Lohnfertigungsbetrieb (Schweiß- und Stahlbaugruppen, Brikettierpressen) mit eigener Konstruktion.</t>
+          <t>Inhabergeführter Hersteller von Webmaschinen (Draht-/Robustwebmaschinen) mit Vorrichtungsbau, Sondermaschinenbau und Maschinenüberholung.</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>https://www.roessner-maschinenbau.de/kontakt/</t>
+          <t>https://www.iq-sps.de/unternehmen/kontakt-anfahrt/</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Susanne Wolf</t>
+          <t>Frederic Lanz</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführende Gesellschafterin</t>
+          <t>CEO / Vice Chairman of the Board</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>susanne.wolf@sme-leipzig.de</t>
+          <t>lanz@kemper.eu</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>+49 341 2574 616</t>
+          <t>+49 (0) 2564 68-119</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>SME Sondermaschinenbau Engelsdorf GmbH</t>
+          <t>KEMPER GmbH</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -2877,44 +2877,44 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Leipzig (Sachsen)</t>
+          <t>Vreden (Münsterland, NRW)</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Familiengeführter Sondermaschinenbauer für Förder-, Handling- und Montagetechnik sowie Roboterzellen (Automotive, Baustoffe, Konsumgüter). Zweiter Geschäftsführender Gesellschafter (Vertrieb): Jan Wolf (jan.wolf@sme-leipzig.de, gleiche Quelle).</t>
+          <t>Familiengeführter Hersteller von Absaug- und Filteranlagen sowie Schweißrauchabsaugung für die metallverarbeitende Fertigung. Sitz 48691 Vreden.</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>https://www.sme-leipzig.de/ | https://www.sme-leipzig.de/industriezweige/automotive/</t>
+          <t>https://kemper.eu/Unternehmen/Kontakt/ | https://kemper.eu/Unternehmen/ (Adresse 48691 Vreden)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Olaf Clemens</t>
+          <t>Jochen Kemper</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführender Gesellschafter</t>
+          <t>Vice President Sales (Inhaberfamilie)</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>olaf.clemens@sn-packaging.de</t>
+          <t>jkemper@kemper.eu</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>+49 2267 699-0</t>
+          <t>+49 2564 68-138</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>SN Maschinenbau GmbH</t>
+          <t>KEMPER GmbH</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -2924,44 +2924,44 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Wipperfürth (Bergisches Land / Rheinland)</t>
+          <t>Vreden (Westmünsterland)</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>Familiengeführter Hersteller von Beutelverpackungsmaschinen (Form-, Füll- und Verschließmaschinen) mit Firmensitz und Entwicklung in Wipperfürth. International tätig über die Marke SN Packaging.</t>
+          <t>Mitglied der Gründer-/Inhaberfamilie Kemper, verantwortet den weltweiten Vertrieb des Absaugtechnik-Herstellers.</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>https://sn-maschinenbau.de/service-kontakt/kontakt-sales/beratung-vertrieb | https://sn-maschinenbau.de/unternehmen/ (Zitat: 'An unserem Firmensitz in Wipperfürth entwickeln täglich rund 300 Mitarbeiterinnen und Mitarbeiter führende Beutelverpackungslösung...', 51688 Wipperfürth)</t>
+          <t>https://www.kemper.eu/Unternehmen/Kontakt/</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Roland Mertens</t>
+          <t>André Rüssmann</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsleitung Sales (Chief Sales Officer)</t>
+          <t>Geschäftsführer (CTO)</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>rmertens@schoellerwerk.de</t>
+          <t>a.ruessmann@lr-kaelte.de</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>+49 2482 81 129</t>
+          <t>+49 2935 965-20</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Schoeller Werk GmbH &amp; Co. KG</t>
+          <t>L&amp;R Kältetechnik GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -2971,44 +2971,44 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Hellenthal (Eifel, NRW)</t>
+          <t>Sundern (Sauerland)</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Metallverarbeitende Fertigung: Hersteller längsnahtgeschweißter Edelstahlrohre für Industrie und Automotive. Teil der familiengeführten Schoeller-Gruppe.</t>
+          <t>Technischer Geschäftsführer des familiengeführten Sonderanlagenbauers für Industriekälte; verantwortet Technik/Entwicklung.</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>https://schoellerwerk.de/kontakt/ | https://www.schoellerwerk.de/en/contact/ (englische Fassung derselben Ansprechpartner-Tabelle: 'Roland Mertens | Chief Sales Officer')</t>
+          <t>https://www.lr-kaelte.de/team-2/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Mario Taenzler</t>
+          <t>Burkhard Rüssmann</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer</t>
+          <t>Geschäftsführer (CEO)</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>m.taenzler@tma-sachsen.de</t>
+          <t>b.ruessmann@lr-kaelte.de</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>+49 35795 2891-0</t>
+          <t>+49 2935 965-20</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Taenzler Maschinen- und Anlagenbau GmbH</t>
+          <t>L&amp;R Kältetechnik GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -3018,44 +3018,44 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Laußnitz (Sachsen)</t>
+          <t>Sundern (Sauerland)</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>Inhabergeführter Maschinen- und Anlagenbauer mit eigener CNC-Fertigung; Anlagenbau u. a. für die Automobilindustrie sowie Elektrotechnik/SPS und Konstruktion im Haus.</t>
+          <t>Inhabergeführter Hersteller von Industriekälteanlagen und kältetechnischem Sonderanlagenbau; in zweiter/dritter Generation von der Familie Rüssmann geführt.</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>https://tma-sachsen.de/kontakt/ | https://tma-sachsen.de/impressum/ (Impressum: 'Taenzler Maschinen- und Anlagenbau GmbH, Grenzstraße 13, 01936 Laußnitz ... Geschäftsführer: Herr Mario Taenzler')</t>
+          <t>https://www.lr-kaelte.de/team-2/ | https://www.regiomanager.de/suedwestfalen/ranking/produktion/maschinenbau/suedwestfalen/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Andreas Sommer</t>
+          <t>Markus Baumeister</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer (Werkzeugmachermeister)</t>
+          <t>Leitung IT &amp; Organisation</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>asommer@oelfke.de</t>
+          <t>m.baumeister@lr-kaelte.de</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>+49 2351 676950</t>
+          <t>+49 2935 9652-580</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Ulrich Oelfke Formenbau GmbH &amp; Co. KG</t>
+          <t>L&amp;R Kältetechnik GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -3065,44 +3065,44 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Lüdenscheid (Sauerland / Märkischer Kreis)</t>
+          <t>Sundern (Sauerland)</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Inhabergeführter Werkzeug- und Formenbaubetrieb für Spritzgießwerkzeuge in Lüdenscheid, Kerkhagen 15.</t>
+          <t>Bereichsleiter IT und Organisation; Entscheider für IT-/Digitalisierungsthemen im familiengeführten Anlagenbau.</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>https://oelfke.de/kontakt/ | https://oelfke.de/impressum/ (Zitat: 'Ulrich Oelfke | Formenbau GmbH &amp; Co. KG | Geschäftsführer | Andreas Sommer | Kerkhagen 15 | 58513 Lüdenscheid') | Weiterer Entscheider: 'Julian Sommer | Geschäftsleitung | Feinwerkmechanikermeister | jsommer@oelfke.de' (https://oelfke.de/kontakt/)</t>
+          <t>https://www.lr-kaelte.de/team-2/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Ulrich Rotte</t>
+          <t>Johann Liebl</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführender Gesellschafter</t>
+          <t>Geschäftsführer</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>rotte@ulrich-rotte.de</t>
+          <t>johann.liebl@lieblmetall.de</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>+49 5258 9789-0</t>
+          <t>+49 9438 90091</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Ulrich Rotte Anlagenbau &amp; Fördertechnik GmbH</t>
+          <t>Lieblmetall GmbH</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -3112,44 +3112,44 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Salzkotten / Kreis Paderborn (Ostwestfalen-Lippe)</t>
+          <t>Ebermannsdorf (Bayern, Oberpfalz)</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>1994 gegründetes Familienunternehmen für Anlagenbau und Fördertechnik, u. a. für Holztechnik, technische Laminate und Industrieautomation.</t>
+          <t>Familiengeführter Fertigungsbetrieb für Blechbearbeitung und Lohnfertigung (Laserschneiden, CNC-Biegen, Schweißbaugruppen) für den Maschinenbau. Betriebsleitung &amp; Gesellschafter: Martin Liebl (martin.liebl@lieblmetall.de, gleiche Quelle).</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>https://www.ulrich-rotte.de/ueber-uns/ | https://www.ulrich-rotte.de/ueber-uns/ (Zitat: 'Gegründet 1994 von Ulrich und Brigitte Rotte haben wir inzwischen 90 Mitarbeiter und einen Jahresumsatz von 16 Millionen...', 33154 Salzkotten) | Zweiter Entscheider auf derselben Seite: 'Benedikt Rotte | Geschäftsführender Gesellschafter | +49 5258 9789-0 | benedikt.rotte@ulrich-rotte.de'</t>
+          <t>https://www.lieblmetall.de/de/kontakt</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Dipl.-Ing. Norbert Felder</t>
+          <t>Dirk Juras</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer / Konstruktion &amp; Entwicklung</t>
+          <t>Produktionsleitung</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>felder@weidmann-mb.de</t>
+          <t>d.juras@minda.com</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>+49 2241 2014101</t>
+          <t>+49 571 3997-0</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>WEIDMANN Maschinenbau GmbH</t>
+          <t>MINDA Industrieanlagen GmbH</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -3159,44 +3159,44 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Troisdorf (Raum Köln/Bonn, Rheinland)</t>
+          <t>Minden (OWL)</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Sondermaschinenbauer für automatisierte Produktions- und Montageanlagen (u. a. Montageautomaten) mit Sitz 53842 Troisdorf.</t>
+          <t>Familiengeführter Anlagenbauer (Gesellschafter Falch) für Intralogistik, Fördertechnik und Hochregallager in Holz-, Wellpappen- und Reifenindustrie.</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>https://weidmann-maschinenbau.de/ansprechpartner.php | https://weidmann-maschinenbau.de/unternehmen.php (Standort 53842 Troisdorf)</t>
+          <t>https://www.minda.com/de/kontakt/management | https://www.minda.com/de/kontakt/geschaeftsfuehrung</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Dominic Scheumann</t>
+          <t>Dr. Sascha Falkenberg</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer</t>
+          <t>Managing Director / Member of the Board (Geschäftsführer)</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>d.scheumann@wibra-formenbau.de</t>
+          <t>s.falkenberg@minda.com</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>+49 (0) 2351 / 36824-10</t>
+          <t>+49 (0) 5721 / 9789-20</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>WIBRA Formenbau GmbH</t>
+          <t>MINDA Industrieanlagen GmbH</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -3206,44 +3206,44 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Lüdenscheid (Sauerland / Märkischer Kreis)</t>
+          <t>Minden (Ostwestfalen-Lippe)</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>Werkzeug- und Formenbauer in Lüdenscheid (58511) mit eigener Konstruktion und Betriebsleitung; zwei geschäftsführende Gesellschafter.</t>
+          <t>Anlagenbauer für Material- und Fördertechnik in der Wellpappen-, Holzwerkstoff- und Reifenindustrie mit Hauptsitz Minden.</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>https://wibraformenbau.de/kontakt/ | https://wibraformenbau.de/kontakt/ (zweiter Geschäftsführer: 'Sebastian Scholz | Geschäftsführer | Telefon: +49 (0) 23 51 / 36824 12 | E-Mail: s.scholz@wibra-formenbau.de'; Betriebsleiter: 'Jürgen Manz | Betriebsleiter | j.manz@wibra-formenbau.de')</t>
+          <t>https://minda.com/en/contact/general-management | https://minda.com/en/contact/management (Produktionsleitung Minden: 'Dirk Juras | Head of Production | +49 (0) 571 / 3997 - 0 | d.juras@minda.com')</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Rainer Grimm</t>
+          <t>Matthias Droste</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer (Dipl.-Ing. TU)</t>
+          <t>Serviceleitung</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>grimm@fm-control.de</t>
+          <t>m.droste@minda.com</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>+49 3741 1702-0</t>
+          <t>+49 571 3997-540</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>fm control GmbH</t>
+          <t>MINDA Industrieanlagen GmbH</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -3253,24 +3253,24 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Plauen (Sachsen)</t>
+          <t>Minden (OWL)</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Inhabergeführtes Unternehmen für Automatisierungs- und Materialflusssteuerung (Steuerungstechnik, Softwareentwicklung) für Produktions- und Förderanlagen.</t>
+          <t>Bereichsleiter Service des familiengeführten Fördertechnik- und Anlagenbauers; verantwortet Instandhaltung und Serviceorganisation.</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>https://www.fm-control.de/kontakt/</t>
+          <t>https://www.minda.com/de/kontakt/management</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Christoph Dahlmann</t>
+          <t>Diana Reich</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3280,722 +3280,722 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>c.dahlmann@als-arnsberg.de</t>
+          <t>diana.reich@msr-chemnitz.de</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>02932 9306-15</t>
+          <t>+49 371 81495-21</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>A.L.S. Allgemeine Land- und Seespedition GmbH</t>
+          <t>MSR Elektro- und Anlagenbau GmbH</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Maschinenbau &amp; Fertigung</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Arnsberg (Sauerland)</t>
+          <t>Chemnitz (Sachsen)</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>Mittelständische Spedition mit nationalen und internationalen Verkehren, Überseeverkehr, Zollabwicklung und Logistikzentrum. Klare Leitungsstruktur mit vier Prokuristen (Vertrieb, Disposition, Marketing, kaufmännische Logistikleitung).</t>
+          <t>Mittelständischer Elektro- und Anlagenbauer aus Chemnitz mit Projektierung, Schaltanlagenbau und Automatisierung für Industrieanlagen. Zweiter Geschäftsführer: Sven Mehnert (sven.mehnert@msr-chemnitz.de, gleiche Quelle).</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>https://www.als-arnsberg.de/ansprechpartner | https://www.regiomanager.de/suedwestfalen/ranking/mobilitaet-logistik/spedition-und-logistik/hochsauerlandkreis/</t>
+          <t>https://www.msr-chemnitz.de/kontakt/ | https://www.msr-chemnitz.de/ueber-uns/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>René Fröhlich</t>
+          <t>Heiko Müller</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer</t>
+          <t>Geschäftsführer (lt. Impressum vertretungsberechtigt), Technik und Vertrieb</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>r.froehlich@lrp24.de</t>
+          <t>heiko.mueller@mueller-sut.de</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>+49 341 222 8 66 55 (Zentrale)</t>
+          <t>+49 9254 7913</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>ALN Logistik GmbH</t>
+          <t>Müller Maschinen und Anlagen GmbH &amp; Co. KG (MÜLLER Gefrees)</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Maschinenbau &amp; Fertigung</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Leipzig (Sachsen)</t>
+          <t>Gefrees (Bayern, Oberfranken)</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>Spedition für Transport-, Sonder- und Lagerlogistik mit Sitz Brahestraße 10, 04347 Leipzig und Lagerstandorten in Leipzig und Berlin.</t>
+          <t>Inhabergeführter Hersteller von Pressen und Sondermaschinen (C-Gestell-Pressen, Stanzautomaten, CNC-Stanzanlagen) inkl. Kundendienst und Retrofit.</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>https://aln-logistik.de/logistik-experten/ansprechpartner/</t>
+          <t>https://mueller-sut.de/kontakt/ansprechpartner/ | https://mueller-sut.de/impressum/ ('Müller Maschinen und Anlagen GmbH &amp; Co. KG ... Vertreten durch Herr Heiko Müller')</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Hubertus Beumer</t>
+          <t>Johannes Rehm</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer</t>
+          <t>Geschäftsführer / CEO</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>hubertus.beumer@b-logistik.de</t>
+          <t>j.rehm@rehm-group.com</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>+49 2524 911-0 (Zentrale, keine Durchwahl veröffentlicht)</t>
+          <t>+49 7344 9606-0</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>B Logistik GmbH</t>
+          <t>Rehm Thermal Systems GmbH</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Maschinenbau &amp; Fertigung</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Ennigerloh (Münsterland, NRW)</t>
+          <t>Blaubeuren-Seissen (Baden-Württemberg)</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>Mittelständischer, inhabergeführter Kontraktlogistiker mit 65.000 qm Logistikfläche an drei Standorten (u. a. Pharma-Logistik-Centrum, Retail/E-Commerce, Nahrungsmittel). Branchenmix mit hohen Compliance-Anforderungen (Pharma/GDP) und kundenindividuellen Value-Added-Services — klassisches Umfeld für manuelle Prozesse und ERP-/LVS-Integration.</t>
+          <t>Familiengeführter Sondermaschinenbauer für thermische Systemlösungen und Fertigungsanlagen der Elektronik- und Leistungselektronikproduktion.</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>https://www.b-logistik.de/kontakt | https://www.b-logistik.de/ | https://www.b-logistik.de/ueber-uns/unser-team</t>
+          <t>https://www.rehm-group.com/unternehmen.html</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Jan Feldberg</t>
+          <t>Volker Rößner</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer</t>
+          <t>Geschäftsführer, Vertrieb</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>jan.feldberg@btg-feldberg.de</t>
+          <t>v.roessner@roessner-maschinenbau.de</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>+49 (0) 2871 9970 260</t>
+          <t>+49 6631 9622-24</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>BTG Feldberg &amp; Sohn GmbH &amp; Co. KG</t>
+          <t>Rößner Maschinenbau GmbH</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Maschinenbau &amp; Fertigung</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Bocholt (Westmünsterland)</t>
+          <t>Alsfeld (Hessen)</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>Familiengeführte Spedition (Geschäftsführer Jan und Jörg Feldberg) mit Stückgut, Luft- und Seefracht, Logistikzentrum, Umzugslogistik sowie eigenem Projektmanagement und QM.</t>
+          <t>Familiengeführter Maschinenbau- und Lohnfertigungsbetrieb (Schweiß- und Stahlbaugruppen, Brikettierpressen) mit eigener Konstruktion.</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>https://www.btg-feldberg.de/ansprechpartner | https://www.regiomanager.de/ranking/mobilitaet-logistik/spedition-und-logistik/muensterland/</t>
+          <t>https://www.roessner-maschinenbau.de/kontakt/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Mathias Ronneberger</t>
+          <t>Susanne Wolf</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer (Shipping – Chartering &amp; Brokerage), Mitinhaber</t>
+          <t>Geschäftsführende Gesellschafterin</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>ronneberger@balticlloyd.com</t>
+          <t>susanne.wolf@sme-leipzig.de</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>+49 381 666 139 14</t>
+          <t>+49 341 2574 616</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Baltic Lloyd Schiffahrt-Spedition-Logistik GmbH</t>
+          <t>SME Sondermaschinenbau Engelsdorf GmbH</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Maschinenbau &amp; Fertigung</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Rostock (Mecklenburg-Vorpommern)</t>
+          <t>Leipzig (Sachsen)</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>Im Rostocker Überseehafen (Am Skandinavienkai 2-3) ansässige Spedition für Schifffahrt, Hafenumschlag, Lagerung und Landverkehre; seit einer Nachfolgeregelung inhabergeführt durch drei langjährige Mitarbeiter.</t>
+          <t>Familiengeführter Sondermaschinenbauer für Förder-, Handling- und Montagetechnik sowie Roboterzellen (Automotive, Baustoffe, Konsumgüter). Zweiter Geschäftsführender Gesellschafter (Vertrieb): Jan Wolf (jan.wolf@sme-leipzig.de, gleiche Quelle).</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>https://balticlloyd.com/dasteam/ | https://www.mbg-mv.de/rostocker-logistikunternehmen-auf-erfolgskurs-dreifache-nachfolgeregelung-sichert-zukunft</t>
+          <t>https://www.sme-leipzig.de/ | https://www.sme-leipzig.de/industriezweige/automotive/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Ronny Oldag</t>
+          <t>Olaf Clemens</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer (Cargo Handling, Storage), Mitinhaber</t>
+          <t>Geschäftsführender Gesellschafter</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>oldag@balticlloyd.com</t>
+          <t>olaf.clemens@sn-packaging.de</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>+49 381 666 139 12</t>
+          <t>+49 2267 699-0</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Baltic Lloyd Schiffahrt-Spedition-Logistik GmbH</t>
+          <t>SN Maschinenbau GmbH</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Maschinenbau &amp; Fertigung</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Rostock (Mecklenburg-Vorpommern)</t>
+          <t>Wipperfürth (Bergisches Land / Rheinland)</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer mit Zuständigkeit für Umschlag und Lagerung im Rostocker Überseehafen; dritter Geschäftsführer Wolfgang Nuß.</t>
+          <t>Familiengeführter Hersteller von Beutelverpackungsmaschinen (Form-, Füll- und Verschließmaschinen) mit Firmensitz und Entwicklung in Wipperfürth. International tätig über die Marke SN Packaging.</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>https://balticlloyd.com/dasteam/</t>
+          <t>https://sn-maschinenbau.de/service-kontakt/kontakt-sales/beratung-vertrieb | https://sn-maschinenbau.de/unternehmen/ (Zitat: 'An unserem Firmensitz in Wipperfürth entwickeln täglich rund 300 Mitarbeiterinnen und Mitarbeiter führende Beutelverpackungslösung...', 51688 Wipperfürth)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Wolfgang Heidel</t>
+          <t>Roland Mertens</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsleitung</t>
+          <t>Geschäftsleitung Sales (Chief Sales Officer)</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>wolfgang.heidel@bayern-express-spedition.de</t>
+          <t>rmertens@schoellerwerk.de</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>+49 89 329892-10</t>
+          <t>+49 2482 81 129</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Bayern Express Spedition GmbH</t>
+          <t>Schoeller Werk GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Maschinenbau &amp; Fertigung</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Garching bei München, weiterer Standort Pilsting-Ganacker, Bayern</t>
+          <t>Hellenthal (Eifel, NRW)</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>Familiengeführte bayerische Spedition (Familie Heidel) mit Fernverkehr, Nahverkehrsdisposition, Stückgut-/VTL-Systemverkehr und eigener Abwicklung an zwei Standorten.</t>
+          <t>Metallverarbeitende Fertigung: Hersteller längsnahtgeschweißter Edelstahlrohre für Industrie und Automotive. Teil der familiengeführten Schoeller-Gruppe.</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>https://www.bayern-express-spedition.de/mitarbeiter.php</t>
+          <t>https://schoellerwerk.de/kontakt/ | https://www.schoellerwerk.de/en/contact/ (englische Fassung derselben Ansprechpartner-Tabelle: 'Roland Mertens | Chief Sales Officer')</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Christian Messing</t>
+          <t>Arne Strohdiek</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer</t>
+          <t>Bereichsleiter / Vertrieb Maschinenbau</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>c.messing@spedition-messing.de</t>
+          <t>arne.strohdiek@spilker.de</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>02541 9487-10</t>
+          <t>+49 5202 9100-806</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Bernhard Messing GmbH &amp; Co. KG (Spedition Messing)</t>
+          <t>Spilker GmbH</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Maschinenbau &amp; Fertigung</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Coesfeld</t>
+          <t>Steinhagen (Kreis Gütersloh, OWL)</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>Familiengeführte Spedition mit Sammelgut, Fernverkehr, Tourendisposition, eigener Lagerlogistik und Bereich Bio &amp; Frische (Lebensmittellogistik). Mehrere Familienmitglieder (Christian, Andreas, Esther Meßing) im Unternehmen.</t>
+          <t>Familiengeführter Hersteller von Rotationsstanzwerkzeugen, Stanzblechen und eigenem Maschinenbau für die Etiketten- und Verpackungsindustrie.</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>https://www.spedition-messing.de/ansprechpartner | https://www.regiomanager.de/ranking/mobilitaet-logistik/spedition-und-logistik/kreis-coesfeld/</t>
+          <t>https://www.spilker.de/kontakt/ansprechpartner/vertrieb-maschinenbau/ | https://www.spilker.de/kontakt/</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Tim Bönders</t>
+          <t>Mario Taenzler</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführender Gesellschafter (4. Generation)</t>
+          <t>Geschäftsführer</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>tboenders@bk-group.de</t>
+          <t>m.taenzler@tma-sachsen.de</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>nicht öffentlich</t>
+          <t>+49 35795 2891-0</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Bönders GmbH (B+K Group)</t>
+          <t>Taenzler Maschinen- und Anlagenbau GmbH</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Maschinenbau &amp; Fertigung</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Krefeld</t>
+          <t>Laußnitz (Sachsen)</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>Inhabergeführter Logistikdienstleister aus Krefeld (seit über 70 Jahren, 4. Generation) mit Kontraktlogistik, Ersatzteillogistik, Warehousing und Distribution für ausgewählte Schlüsselbranchen.</t>
+          <t>Inhabergeführter Maschinen- und Anlagenbauer mit eigener CNC-Fertigung; Anlagenbau u. a. für die Automobilindustrie sowie Elektrotechnik/SPS und Konstruktion im Haus.</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>https://www.boenders.de/about/management/ | https://www.regiomanager.de/niederrhein/ranking/mobilitaet-logistik/spedition-und-logistik/krefeld/</t>
+          <t>https://tma-sachsen.de/kontakt/ | https://tma-sachsen.de/impressum/ (Impressum: 'Taenzler Maschinen- und Anlagenbau GmbH, Grenzstraße 13, 01936 Laußnitz ... Geschäftsführer: Herr Mario Taenzler')</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Norman Lippe</t>
+          <t>Andreas Sommer</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer</t>
+          <t>Geschäftsführer (Werkzeugmachermeister)</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>norman.lippe@cargotrans.de</t>
+          <t>asommer@oelfke.de</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>+49 2361 3061-0 (Zentrale Recklinghausen)</t>
+          <t>+49 2351 676950</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>CARGOTRANS GmbH &amp; Co. KG</t>
+          <t>Ulrich Oelfke Formenbau GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Maschinenbau &amp; Fertigung</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Recklinghausen (Hauptsitz), Verwaltung Dortmund, NL Hamburg</t>
+          <t>Lüdenscheid (Sauerland / Märkischer Kreis)</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>Mittelständische Spedition im nördlichen Ruhrgebiet mit Road-/Intermodal-Verkehren, Warehousing und Zollservice; vollständige Ansprechpartnerliste inkl. Dispositions- und Lagerleitung öffentlich.</t>
+          <t>Inhabergeführter Werkzeug- und Formenbaubetrieb für Spritzgießwerkzeuge in Lüdenscheid, Kerkhagen 15.</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>https://www.cargotrans.de/kontakt | https://www.regiomanager.de/ranking/mobilitaet-logistik/spedition-und-logistik/dortmund/</t>
+          <t>https://oelfke.de/kontakt/ | https://oelfke.de/impressum/ (Zitat: 'Ulrich Oelfke | Formenbau GmbH &amp; Co. KG | Geschäftsführer | Andreas Sommer | Kerkhagen 15 | 58513 Lüdenscheid') | Weiterer Entscheider: 'Julian Sommer | Geschäftsleitung | Feinwerkmechanikermeister | jsommer@oelfke.de' (https://oelfke.de/kontakt/)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Jens Haverland</t>
+          <t>Ulrich Rotte</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer</t>
+          <t>Geschäftsführender Gesellschafter</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>jhaverland@cargomar.de</t>
+          <t>rotte@ulrich-rotte.de</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>+49 421 5590-10 (Zentrale)</t>
+          <t>+49 5258 9789-0</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Cargomar GmbH Internationale Spedition / Cargomar Air &amp; Sea GmbH</t>
+          <t>Ulrich Rotte Anlagenbau &amp; Fördertechnik GmbH</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Maschinenbau &amp; Fertigung</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Bremen</t>
+          <t>Salzkotten / Kreis Paderborn (Ostwestfalen-Lippe)</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>Inhabergeführte Bremer Spedition mit See-/Luftfracht, Import/Export sowie eigener Lagerlogistik (Teamleitung Lagerlogistik im Haus).</t>
+          <t>1994 gegründetes Familienunternehmen für Anlagenbau und Fördertechnik, u. a. für Holztechnik, technische Laminate und Industrieautomation.</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>https://www.cargomar.de/</t>
+          <t>https://www.ulrich-rotte.de/ueber-uns/ | https://www.ulrich-rotte.de/ueber-uns/ (Zitat: 'Gegründet 1994 von Ulrich und Brigitte Rotte haben wir inzwischen 90 Mitarbeiter und einen Jahresumsatz von 16 Millionen...', 33154 Salzkotten) | Zweiter Entscheider auf derselben Seite: 'Benedikt Rotte | Geschäftsführender Gesellschafter | +49 5258 9789-0 | benedikt.rotte@ulrich-rotte.de'</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Dr. Rimbert J. Kelber</t>
+          <t>Dipl.-Ing. Norbert Felder</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Niederlassungsleitung</t>
+          <t>Geschäftsführer / Konstruktion &amp; Entwicklung</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>rimbert.kelber@koester-hapke-sped.com</t>
+          <t>felder@weidmann-mb.de</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>+49 5132 822-100</t>
+          <t>+49 2241 2014101</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Carl Köster &amp; Louis Hapke GmbH &amp; Co. KG</t>
+          <t>WEIDMANN Maschinenbau GmbH</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Maschinenbau &amp; Fertigung</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Sehnde-Höver bei Hannover, Niedersachsen</t>
+          <t>Troisdorf (Raum Köln/Bonn, Rheinland)</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>Mittelständische, inhabergeführte Spedition seit 1854 mit nationalen/internationalen Stückgutverkehren, Messelogistik und eigener Lagerlogistik (eigene Lagerleitung).</t>
+          <t>Sondermaschinenbauer für automatisierte Produktions- und Montageanlagen (u. a. Montageautomaten) mit Sitz 53842 Troisdorf.</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>https://koester-hapke-sped.com/ansprechpartner/ | https://koester-hapke-sped.com/wir-ueber-uns/ | https://koester-hapke-sped.com/kontakt/</t>
+          <t>https://weidmann-maschinenbau.de/ansprechpartner.php | https://weidmann-maschinenbau.de/unternehmen.php (Standort 53842 Troisdorf)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Andreas Grimmeißen</t>
+          <t>Dominic Scheumann</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>CEO – Geschäftsführer</t>
+          <t>Geschäftsführer</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>andreas.grimmeissen@ewo-logistics.com</t>
+          <t>d.scheumann@wibra-formenbau.de</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>+49 7191 969 93 10</t>
+          <t>+49 (0) 2351 / 36824-10</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>E.W.O Logistics GmbH</t>
+          <t>WIBRA Formenbau GmbH</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Maschinenbau &amp; Fertigung</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Backnang bei Stuttgart (Baden-Württemberg)</t>
+          <t>Lüdenscheid (Sauerland / Märkischer Kreis)</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>Inhabergeführte Speditions- und Logistikgesellschaft im Raum Stuttgart/Backnang, Familienunternehmen (Geschäftsführung, Verkaufs- und Dispositionsleitung sämtlich Familie Grimmeißen).</t>
+          <t>Werkzeug- und Formenbauer in Lüdenscheid (58511) mit eigener Konstruktion und Betriebsleitung; zwei geschäftsführende Gesellschafter.</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>https://www.ewo-logistics.com/ewo-logistics-backnang-stuttgart-badenwuerttemberg-deutschland/</t>
+          <t>https://wibraformenbau.de/kontakt/ | https://wibraformenbau.de/kontakt/ (zweiter Geschäftsführer: 'Sebastian Scholz | Geschäftsführer | Telefon: +49 (0) 23 51 / 36824 12 | E-Mail: s.scholz@wibra-formenbau.de'; Betriebsleiter: 'Jürgen Manz | Betriebsleiter | j.manz@wibra-formenbau.de')</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Doris Grimmeißen</t>
+          <t>Rainer Grimm</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>CEO – Geschäftsführerin</t>
+          <t>Geschäftsführer (Dipl.-Ing. TU)</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>doris.grimmeissen@ewo-logistics.com</t>
+          <t>grimm@fm-control.de</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>+49 7191 969 93 20</t>
+          <t>+49 3741 1702-0</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>E.W.O Logistics GmbH</t>
+          <t>fm control GmbH</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Maschinenbau &amp; Fertigung</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Backnang bei Stuttgart (Baden-Württemberg)</t>
+          <t>Plauen (Sachsen)</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>Zweite Geschäftsführerin des inhabergeführten Logistikunternehmens im Rems-Murr-Kreis.</t>
+          <t>Inhabergeführtes Unternehmen für Automatisierungs- und Materialflusssteuerung (Steuerungstechnik, Softwareentwicklung) für Produktions- und Förderanlagen.</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>https://www.ewo-logistics.com/ewo-logistics-backnang-stuttgart-badenwuerttemberg-deutschland/</t>
+          <t>https://www.fm-control.de/kontakt/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Anja Hollenhorst</t>
+          <t>Stefanie Flaeper</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführerin (lt. Impressum; auf der Website Ansprechpartnerin Kundenservice)</t>
+          <t>Geschäftsführerin Vertrieb/Marketing</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>anja@hti-spedition.de</t>
+          <t>sflaeper@transfluid.de</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>+49 251 74787-0 (Zentrale, Durchwahlen 11-21)</t>
+          <t>+49 2972 9715 10</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>HTI Spedition und Logistik GmbH</t>
+          <t>transfluid Maschinenbau GmbH</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>Logistik &amp; Supply Chain</t>
+          <t>Maschinenbau &amp; Fertigung</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Münster (NRW)</t>
+          <t>Schmallenberg (Sauerland)</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>Familiengeführte Spedition (Familie Hollenhorst) mit Fernverkehr, Luft-/Seefracht inkl. Zollabwicklung, Lager und Status Reglementierter Beauftragter. Zoll-, Fracht- und Dispositionsprozesse mit hohem Dokumentenaufkommen — gutes Feld für Prozessautomatisierung und Systemanbindung.</t>
+          <t>Inhabergeführter Hersteller von Rohrbiege-, Rohrbearbeitungs- und Automationsanlagen; Geschäftsführerin aus der Eigentümerfamilie.</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>https://hti-spedition.de/ | https://hti-spedition.de/impressum/</t>
+          <t>https://www.transfluid.de/unternehmen/vertrieb/leitung | https://www.regiomanager.de/suedwestfalen/ranking/produktion/maschinenbau/suedwestfalen/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Klaus Hüttemann</t>
+          <t>Christoph Dahlmann</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer / geschäftsführender Gesellschafter (2. Generation)</t>
+          <t>Geschäftsführung</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>k.huettemann@huelog.de</t>
+          <t>c.dahlmann@als-arnsberg.de</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>+49 2065 909116</t>
+          <t>02932 9306-15</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>HUETTEMANN Logistik GmbH (HUETTEMANN Group)</t>
+          <t>A.L.S. Allgemeine Land- und Seespedition GmbH</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -4005,24 +4005,24 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Duisburg</t>
+          <t>Arnsberg (Sauerland)</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>Inhabergeführte Logistikgruppe aus Duisburg mit Kontraktlogistik, Lagerlogistik, Hafenumschlag und Transport. Klaus Hüttemann führt die Gruppe in zweiter Generation als geschäftsführender Gesellschafter.</t>
+          <t>Mittelständische Spedition mit nationalen und internationalen Verkehren, Überseeverkehr, Zollabwicklung und Logistikzentrum. Klare Leitungsstruktur mit vier Prokuristen (Vertrieb, Disposition, Marketing, kaufmännische Logistikleitung).</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>https://www.huettemann-logistik.de/unternehmensgruppe/management/ | https://www.regiomanager.de/revier/ranking/mobilitaet-logistik/spedition-und-logistik/duisburg/</t>
+          <t>https://www.als-arnsberg.de/ansprechpartner | https://www.regiomanager.de/suedwestfalen/ranking/mobilitaet-logistik/spedition-und-logistik/hochsauerlandkreis/</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Hanjo Heinen</t>
+          <t>René Fröhlich</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -4032,17 +4032,17 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>hanjo.heinen@heinen-ht.de</t>
+          <t>r.froehlich@lrp24.de</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>nicht öffentlich</t>
+          <t>+49 341 222 8 66 55 (Zentrale)</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Heinen Transport GmbH (Heinen Gruppe: HT, HLS, HHL, HSK, HHV, HG)</t>
+          <t>ALN Logistik GmbH</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -4052,44 +4052,44 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>Meerbusch (Hauptsitz), Logistikzentrum Duisburg</t>
+          <t>Leipzig (Sachsen)</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>Familiengeführte Transport- und Logistikgruppe im Rheinland mit Logistikzentrum in Duisburg, Speditions-, Lager- und Kontraktlogistikgesellschaften. Weitere Entscheider: Pascal Heinen (Prokurist / Leitung Logistik, pascal.heinen@heinen-ht.de), Sabine Heinen (Prokuristin, sabine.heinen@heinen-ht.de).</t>
+          <t>Spedition für Transport-, Sonder- und Lagerlogistik mit Sitz Brahestraße 10, 04347 Leipzig und Lagerstandorten in Leipzig und Berlin.</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>https://www.heinen-transport-gmbh.de/ansprechpartner | https://www.heinen-transport-gmbh.de/impressum</t>
+          <t>https://aln-logistik.de/logistik-experten/ansprechpartner/</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Ludger Henke</t>
+          <t>Hubertus Beumer</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführung</t>
+          <t>Geschäftsführer</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>l.henke@henke-spedition.de</t>
+          <t>hubertus.beumer@b-logistik.de</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>+49 5250 9850-0</t>
+          <t>+49 2524 911-0 (Zentrale, keine Durchwahl veröffentlicht)</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Heinrich Henke Güterfernverkehr und Spedition GmbH &amp; Co.</t>
+          <t>B Logistik GmbH</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -4099,24 +4099,24 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Delbrück (Kreis Paderborn)</t>
+          <t>Ennigerloh (Münsterland, NRW)</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>Familienspedition in dritter Generation mit Fernverkehr, Disposition und Lagerlogistik im Raum Paderborn. Mehrere Familienmitglieder (Ludger, Ludgerus, Regina Henke) im Unternehmen tätig.</t>
+          <t>Mittelständischer, inhabergeführter Kontraktlogistiker mit 65.000 qm Logistikfläche an drei Standorten (u. a. Pharma-Logistik-Centrum, Retail/E-Commerce, Nahrungsmittel). Branchenmix mit hohen Compliance-Anforderungen (Pharma/GDP) und kundenindividuellen Value-Added-Services — klassisches Umfeld für manuelle Prozesse und ERP-/LVS-Integration.</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>https://www.henke-spedition.de/kontakt | https://www.regiomanager.de/ostwestfalen/ranking/mobilitaet-logistik/spedition-und-logistik/kreis-paderborn/</t>
+          <t>https://www.b-logistik.de/kontakt | https://www.b-logistik.de/ | https://www.b-logistik.de/ueber-uns/unser-team</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Bernd Specht</t>
+          <t>Jan Feldberg</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -4126,17 +4126,17 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>b.specht@wichmann-transporte.de</t>
+          <t>jan.feldberg@btg-feldberg.de</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>+49 5481/808-51</t>
+          <t>+49 (0) 2871 9970 260</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Heinrich Wichmann Transporte GmbH</t>
+          <t>BTG Feldberg &amp; Sohn GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -4146,44 +4146,44 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Lengerich (Kreis Steinfurt)</t>
+          <t>Bocholt (Westmünsterland)</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>Mittelständisches Transportunternehmen mit eigener Werkstatt, Disposition und Fuhrparkmanagement im nördlichen Münsterland.</t>
+          <t>Familiengeführte Spedition (Geschäftsführer Jan und Jörg Feldberg) mit Stückgut, Luft- und Seefracht, Logistikzentrum, Umzugslogistik sowie eigenem Projektmanagement und QM.</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>https://www.wichmann-transporte.de/kontakt | https://www.regiomanager.de/muensterland/ranking/mobilitaet-logistik/spedition-und-logistik/kreis-steinfurt/</t>
+          <t>https://www.btg-feldberg.de/ansprechpartner | https://www.regiomanager.de/ranking/mobilitaet-logistik/spedition-und-logistik/muensterland/</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Peter Plank</t>
+          <t>Mathias Ronneberger</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Vorsitzender Geschäftsführer / Inhaber</t>
+          <t>Geschäftsführer (Shipping – Chartering &amp; Brokerage), Mitinhaber</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>peterplank@hellmold-plank.de</t>
+          <t>ronneberger@balticlloyd.com</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>+49 641 95201-16</t>
+          <t>+49 381 666 139 14</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Hellmold &amp; Plank GmbH &amp; Co. KG Spedition</t>
+          <t>Baltic Lloyd Schiffahrt-Spedition-Logistik GmbH</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -4193,44 +4193,44 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Gießen (Europastr. 7+9, 35394), Hessen</t>
+          <t>Rostock (Mecklenburg-Vorpommern)</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>1904 gegründete, inhabergeführte hessische Spedition (seit 1996 im Alleinbesitz der Familie Plank) mit Systemverkehren, Fernverkehr und Lagerlogistik; zweite Generation (Niklas Plank) in der Geschäftsführung.</t>
+          <t>Im Rostocker Überseehafen (Am Skandinavienkai 2-3) ansässige Spedition für Schifffahrt, Hafenumschlag, Lagerung und Landverkehre; seit einer Nachfolgeregelung inhabergeführt durch drei langjährige Mitarbeiter.</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>https://www.hellmold-plank.de/de/kontakt | https://www.hellmold-plank.de/</t>
+          <t>https://balticlloyd.com/dasteam/ | https://www.mbg-mv.de/rostocker-logistikunternehmen-auf-erfolgskurs-dreifache-nachfolgeregelung-sichert-zukunft</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Oliver Hüer</t>
+          <t>Ronny Oldag</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer</t>
+          <t>Geschäftsführer (Cargo Handling, Storage), Mitinhaber</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>oliver@hueer.com</t>
+          <t>oldag@balticlloyd.com</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>0251 87189-130</t>
+          <t>+49 381 666 139 12</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Hüer Transport und Logistik GmbH</t>
+          <t>Baltic Lloyd Schiffahrt-Spedition-Logistik GmbH</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -4240,44 +4240,44 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Münster</t>
+          <t>Rostock (Mecklenburg-Vorpommern)</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>Inhabergeführte Spedition in Münster mit Nahverkehr, Kurierdienst und Logistikdienstleistungen. Familienstruktur: Oliver Hüer (GF) und Patrycja Hüer (Prokuristin).</t>
+          <t>Geschäftsführer mit Zuständigkeit für Umschlag und Lagerung im Rostocker Überseehafen; dritter Geschäftsführer Wolfgang Nuß.</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>https://www.hueer.com/kontakt | https://www.hueer.com/</t>
+          <t>https://balticlloyd.com/dasteam/</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Ingo Kaiser</t>
+          <t>Wolfgang Heidel</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführung (Management)</t>
+          <t>Geschäftsleitung</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>ingo.kaiser@ikg-spedition.de</t>
+          <t>wolfgang.heidel@bayern-express-spedition.de</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>+49 7223 281689-19</t>
+          <t>+49 89 329892-10</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>IKG Spedition GmbH</t>
+          <t>Bayern Express Spedition GmbH</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -4287,24 +4287,24 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Baden-Baden / Sinzheim, Baden-Württemberg</t>
+          <t>Garching bei München, weiterer Standort Pilsting-Ganacker, Bayern</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>Familiengeführte Spedition (Ingo und Kristina Kaiser) mit intermodalen Transporten Richtung Italien/Frankreich/Schweiz, eigenem Lager und Fuhrpark sowie Niederlassung in Busto Arsizio.</t>
+          <t>Familiengeführte bayerische Spedition (Familie Heidel) mit Fernverkehr, Nahverkehrsdisposition, Stückgut-/VTL-Systemverkehr und eigener Abwicklung an zwei Standorten.</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>https://www.ikg-spedition.de/team/ | https://www.ikg-spedition.de/</t>
+          <t>https://www.bayern-express-spedition.de/mitarbeiter.php</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Joachim Berends</t>
+          <t>Christian Messing</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -4314,17 +4314,17 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>j.berends@bentheimer-eisenbahn.de</t>
+          <t>c.messing@spedition-messing.de</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>+49 5921 8034-0</t>
+          <t>02541 9487-10</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Kraftverkehr Emsland GmbH</t>
+          <t>Bernhard Messing GmbH &amp; Co. KG (Spedition Messing)</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -4334,44 +4334,44 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Nordhorn, Niedersachsen</t>
+          <t>Coesfeld</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer der Kraftverkehr Emsland GmbH (Spedition/Logistiklager der Bentheimer Eisenbahn-Gruppe). Hinweis: die auf der Ansprechpartner-Seite genannte E-Mail läuft über die Domain der Muttergesellschaft.</t>
+          <t>Familiengeführte Spedition mit Sammelgut, Fernverkehr, Tourendisposition, eigener Lagerlogistik und Bereich Bio &amp; Frische (Lebensmittellogistik). Mehrere Familienmitglieder (Christian, Andreas, Esther Meßing) im Unternehmen.</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>https://www.kraftverkehr-emsland.de/kontakt/</t>
+          <t>https://www.spedition-messing.de/ansprechpartner | https://www.regiomanager.de/ranking/mobilitaet-logistik/spedition-und-logistik/kreis-coesfeld/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Marco Oppermann</t>
+          <t>Tim Bönders</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Speditionsleitung &amp; Prokurist</t>
+          <t>Geschäftsführender Gesellschafter (4. Generation)</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>marco.oppermann@kraftverkehr-emsland.de</t>
+          <t>tboenders@bk-group.de</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>+49 5921 8034-96</t>
+          <t>nicht öffentlich</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Kraftverkehr Emsland GmbH</t>
+          <t>Bönders GmbH (B+K Group)</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -4381,44 +4381,44 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Nordhorn, Niedersachsen</t>
+          <t>Krefeld</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>Mittelständische Spedition mit Sammelgut, Ladungsverkehren und eigenem Warehousing-Bereich; Prokurist und Speditionsleiter mit Entscheidungsbefugnis über Prozesse/IT-Themen.</t>
+          <t>Inhabergeführter Logistikdienstleister aus Krefeld (seit über 70 Jahren, 4. Generation) mit Kontraktlogistik, Ersatzteillogistik, Warehousing und Distribution für ausgewählte Schlüsselbranchen.</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>https://www.kraftverkehr-emsland.de/kontakt/ | https://www.kraftverkehr-emsland.de/spedition-logistiklager/</t>
+          <t>https://www.boenders.de/about/management/ | https://www.regiomanager.de/niederrhein/ranking/mobilitaet-logistik/spedition-und-logistik/krefeld/</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Lena Milde</t>
+          <t>Norman Lippe</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Standort-/Niederlassungsleitung Magdeburg</t>
+          <t>Geschäftsführer</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>lena.milde@krage-gerloff.de</t>
+          <t>norman.lippe@cargotrans.de</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>+49 39424 951 0 (Zentrale Schwanebeck)</t>
+          <t>+49 2361 3061-0 (Zentrale Recklinghausen)</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Krage &amp; Gerloff Logistik GmbH</t>
+          <t>CARGOTRANS GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -4428,24 +4428,24 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Magdeburg (Sachsen-Anhalt)</t>
+          <t>Recklinghausen (Hauptsitz), Verwaltung Dortmund, NL Hamburg</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>1995 gegründeter Logistikdienstleister mit Hauptsitz Schwanebeck und Logistikstandort Tucheimer Straße 5, 39126 Magdeburg; Lager- und Transportlogistik.</t>
+          <t>Mittelständische Spedition im nördlichen Ruhrgebiet mit Road-/Intermodal-Verkehren, Warehousing und Zollservice; vollständige Ansprechpartnerliste inkl. Dispositions- und Lagerleitung öffentlich.</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>https://www.krage-gerloff.de/magdeburg</t>
+          <t>https://www.cargotrans.de/kontakt | https://www.regiomanager.de/ranking/mobilitaet-logistik/spedition-und-logistik/dortmund/</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Andreas Köhler</t>
+          <t>Jens Haverland</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -4455,17 +4455,17 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>a.koehler@koehler-transport.de</t>
+          <t>jhaverland@cargomar.de</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>+49 221 96640-10</t>
+          <t>+49 421 5590-10 (Zentrale)</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>KÖHLER GmbH &amp; Co. KG</t>
+          <t>Cargomar GmbH Internationale Spedition / Cargomar Air &amp; Sea GmbH</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -4475,44 +4475,44 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Bremen</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>Inhabergeführtes Familienunternehmen in Köln mit Transport, Lager und eigener Werkstatt. Etwas unterhalb der Zielgröße, aber klar mittelständisch und inhabergeführt.</t>
+          <t>Inhabergeführte Bremer Spedition mit See-/Luftfracht, Import/Export sowie eigener Lagerlogistik (Teamleitung Lagerlogistik im Haus).</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>https://www.koehler-transport.com/ansprechpartner | https://www.koehler-transport.com/</t>
+          <t>https://www.cargomar.de/</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Alexander Schwarz</t>
+          <t>Dr. Rimbert J. Kelber</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Business Development Manager &amp; Lager Management</t>
+          <t>Niederlassungsleitung</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>a.schwarz@lkt-thiele.com</t>
+          <t>rimbert.kelber@koester-hapke-sped.com</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>+49 36373 129831-20</t>
+          <t>+49 5132 822-100</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>LOGISTIK KONTOR GmbH (LKT Thiele)</t>
+          <t>Carl Köster &amp; Louis Hapke GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -4522,44 +4522,44 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Buttstädt (Thüringen)</t>
+          <t>Sehnde-Höver bei Hannover, Niedersachsen</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>Verantwortlich für Geschäftsentwicklung und Lagermanagement – Bereichsleiter-Ebene für Lager-/Distributionslogistik bei der Thüringer Spedition.</t>
+          <t>Mittelständische, inhabergeführte Spedition seit 1854 mit nationalen/internationalen Stückgutverkehren, Messelogistik und eigener Lagerlogistik (eigene Lagerleitung).</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>https://www.lkt-thiele.com/unternehmen/team/</t>
+          <t>https://koester-hapke-sped.com/ansprechpartner/ | https://koester-hapke-sped.com/wir-ueber-uns/ | https://koester-hapke-sped.com/kontakt/</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Stephan Voigt</t>
+          <t>Andreas Grimmeißen</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer</t>
+          <t>CEO – Geschäftsführer</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>s.voigt@lkt-thiele.com</t>
+          <t>andreas.grimmeissen@ewo-logistics.com</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>+49 36373 129831-13</t>
+          <t>+49 7191 969 93 10</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>LOGISTIK KONTOR GmbH (LKT Thiele)</t>
+          <t>E.W.O Logistics GmbH</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
@@ -4569,44 +4569,44 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Buttstädt (Thüringen)</t>
+          <t>Backnang bei Stuttgart (Baden-Württemberg)</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>Seit 2004 tätige mittelständische Spedition mit Sitz Vor dem Lohe 5, 99628 Buttstädt und Niederlassung Wiebelsheim; nationale/internationale Transporte, Lagerung, Charterverkehr.</t>
+          <t>Inhabergeführte Speditions- und Logistikgesellschaft im Raum Stuttgart/Backnang, Familienunternehmen (Geschäftsführung, Verkaufs- und Dispositionsleitung sämtlich Familie Grimmeißen).</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>https://www.lkt-thiele.com/unternehmen/team/ | https://www.lkt-thiele.com/</t>
+          <t>https://www.ewo-logistics.com/ewo-logistics-backnang-stuttgart-badenwuerttemberg-deutschland/</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>David Liedhegener</t>
+          <t>Doris Grimmeißen</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführender Gesellschafter</t>
+          <t>CEO – Geschäftsführerin</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>d.liedhegener@liedhegener-logistik.de</t>
+          <t>doris.grimmeissen@ewo-logistics.com</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>02933 - 9 22 22 10</t>
+          <t>+49 7191 969 93 20</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Liedhegener-Logistik GmbH &amp; Co. KG</t>
+          <t>E.W.O Logistics GmbH</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
@@ -4616,44 +4616,44 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Sundern (Sauerland)</t>
+          <t>Backnang bei Stuttgart (Baden-Württemberg)</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>Inhabergeführter Logistikdienstleister mit Transport, Verladung und Lagerlogistik im Sauerland. Familie Liedhegener (David und Sandra Liedhegener) in Geschäftsführung und Verwaltung.</t>
+          <t>Zweite Geschäftsführerin des inhabergeführten Logistikunternehmens im Rems-Murr-Kreis.</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>https://www.liedhegener-logistik.de/kontakt | https://www.regiomanager.de/suedwestfalen/ranking/mobilitaet-logistik/spedition-und-logistik/hochsauerlandkreis/</t>
+          <t>https://www.ewo-logistics.com/ewo-logistics-backnang-stuttgart-badenwuerttemberg-deutschland/</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Jakob Riesen</t>
+          <t>Anja Hollenhorst</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer</t>
+          <t>Geschäftsführerin (lt. Impressum; auf der Website Ansprechpartnerin Kundenservice)</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>j.riesen@mbi-spedition.de</t>
+          <t>anja@hti-spedition.de</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>+49 (521) 93 803 - 0</t>
+          <t>+49 251 74787-0 (Zentrale, Durchwahlen 11-21)</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>MBI Internationale Spedition GmbH</t>
+          <t>HTI Spedition und Logistik GmbH</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
@@ -4663,44 +4663,44 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Bielefeld</t>
+          <t>Münster (NRW)</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>Familiengeführte internationale Spedition mit Kontraktlogistik, Lagerung, Kommissionierung und Zollabwicklung. Zwei Geschäftsführer aus der Familie Riesen (Jakob und Peter Riesen).</t>
+          <t>Familiengeführte Spedition (Familie Hollenhorst) mit Fernverkehr, Luft-/Seefracht inkl. Zollabwicklung, Lager und Status Reglementierter Beauftragter. Zoll-, Fracht- und Dispositionsprozesse mit hohem Dokumentenaufkommen — gutes Feld für Prozessautomatisierung und Systemanbindung.</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>https://www.mbi-spedition.de/unser-team/ | https://www.mbi-spedition.de/</t>
+          <t>https://hti-spedition.de/ | https://hti-spedition.de/impressum/</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Christof Mielke</t>
+          <t>Klaus Hüttemann</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführung</t>
+          <t>Geschäftsführer / geschäftsführender Gesellschafter (2. Generation)</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>mielke@mielke-logistik.de</t>
+          <t>k.huettemann@huelog.de</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>0271 / 37514-0</t>
+          <t>+49 2065 909116</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Mielke Logistik GmbH</t>
+          <t>HUETTEMANN Logistik GmbH (HUETTEMANN Group)</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
@@ -4710,44 +4710,44 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Freudenberg (Siegerland)</t>
+          <t>Duisburg</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>Familiengeführte Spedition mit Schwer-/Spezialtransport, Disposition national und international sowie Lagerstandorten (u. a. Außenlager Netphen). Zweite Generation (Tim Christopher Mielke) bereits in der Geschäftsführung.</t>
+          <t>Inhabergeführte Logistikgruppe aus Duisburg mit Kontraktlogistik, Lagerlogistik, Hafenumschlag und Transport. Klaus Hüttemann führt die Gruppe in zweiter Generation als geschäftsführender Gesellschafter.</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>https://www.mielke-logistik.de/ansprechpartner | https://www.regiomanager.de/suedwestfalen/ranking/mobilitaet-logistik/spedition-und-logistik/kreis-siegen-wittgenstein/</t>
+          <t>https://www.huettemann-logistik.de/unternehmensgruppe/management/ | https://www.regiomanager.de/revier/ranking/mobilitaet-logistik/spedition-und-logistik/duisburg/</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>René Langen</t>
+          <t>Hanjo Heinen</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsleitung</t>
+          <t>Geschäftsführer</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>r.langen@speditionlangen.de</t>
+          <t>hanjo.heinen@heinen-ht.de</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>+49 2166 9539-0</t>
+          <t>nicht öffentlich</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Paul Langen GmbH &amp; Co. KG</t>
+          <t>Heinen Transport GmbH (Heinen Gruppe: HT, HLS, HHL, HSK, HHV, HG)</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -4757,44 +4757,44 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Mönchengladbach</t>
+          <t>Meerbusch (Hauptsitz), Logistikzentrum Duisburg</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>Familienunternehmen seit 1883 mit Spedition, Lagerlogistik und Möbel-/Sperrgutlogistik, europaweite Distribution ab Mönchengladbach.</t>
+          <t>Familiengeführte Transport- und Logistikgruppe im Rheinland mit Logistikzentrum in Duisburg, Speditions-, Lager- und Kontraktlogistikgesellschaften. Weitere Entscheider: Pascal Heinen (Prokurist / Leitung Logistik, pascal.heinen@heinen-ht.de), Sabine Heinen (Prokuristin, sabine.heinen@heinen-ht.de).</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>https://www.speditionlangen.de/kontakt | https://www.regiomanager.de/ranking/mobilitaet-logistik/spedition-und-logistik/moenchengladbach/</t>
+          <t>https://www.heinen-transport-gmbh.de/ansprechpartner | https://www.heinen-transport-gmbh.de/impressum</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Benjamin Peelen</t>
+          <t>Ludger Henke</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer (Peelen Logistik GmbH)</t>
+          <t>Geschäftsführung</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>benjamin.peelen@peelen.de</t>
+          <t>l.henke@henke-spedition.de</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>+49 2843 9597-114 (Peelen Logistik GmbH, Rheinberg)</t>
+          <t>+49 5250 9850-0</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Peelen Transporte GmbH / Peelen Logistik GmbH</t>
+          <t>Heinrich Henke Güterfernverkehr und Spedition GmbH &amp; Co.</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -4804,44 +4804,44 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Duisburg (Betriebshof) / Rheinberg (Logistikzentrum Niederrhein)</t>
+          <t>Delbrück (Kreis Paderborn)</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>Familiengeführte Transport- und Logistikgruppe am Niederrhein mit eigenem Fuhrpark, Warehouse (LZN Rheinberg) und Kontraktlogistik.</t>
+          <t>Familienspedition in dritter Generation mit Fernverkehr, Disposition und Lagerlogistik im Raum Paderborn. Mehrere Familienmitglieder (Ludger, Ludgerus, Regina Henke) im Unternehmen tätig.</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>https://www.peelen.de/kontakt | https://www.regiomanager.de/revier/ranking/mobilitaet-logistik/spedition-und-logistik/duisburg/</t>
+          <t>https://www.henke-spedition.de/kontakt | https://www.regiomanager.de/ostwestfalen/ranking/mobilitaet-logistik/spedition-und-logistik/kreis-paderborn/</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Florian Meyer</t>
+          <t>Bernd Specht</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführung / Logistik- und Lagerleitung</t>
+          <t>Geschäftsführer</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>florian.meyer@rdllogistik.de</t>
+          <t>b.specht@wichmann-transporte.de</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>+49 (0)2151 36806-16</t>
+          <t>+49 5481/808-51</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>RDL Logistik Rheinische Distributions- und Lagerlogistik GmbH</t>
+          <t>Heinrich Wichmann Transporte GmbH</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -4851,44 +4851,44 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Krefeld (Niederrhein, NRW), zweiter Standort Willich</t>
+          <t>Lengerich (Kreis Steinfurt)</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>Inhabergeführter Lager- und Distributionslogistiker am Niederrhein (seit 2000) mit Lagerlogistik, Distribution und Fuhrpark an zwei Standorten. Geschäftsführung leitet operativ Lager und Abrechnung selbst — Digitalisierung von Lagerverwaltung, Disposition und Abrechnung ist unmittelbar chef-relevant.</t>
+          <t>Mittelständisches Transportunternehmen mit eigener Werkstatt, Disposition und Fuhrparkmanagement im nördlichen Münsterland.</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>https://rdllogistik.de/ueber-uns/ | https://rdllogistik.de/ | https://rdllogistik.de/impressum/</t>
+          <t>https://www.wichmann-transporte.de/kontakt | https://www.regiomanager.de/muensterland/ranking/mobilitaet-logistik/spedition-und-logistik/kreis-steinfurt/</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Udo Feldmann</t>
+          <t>Peter Plank</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Leitung Disposition Landmaschinen &amp; Prokurist</t>
+          <t>Vorsitzender Geschäftsführer / Inhaber</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>feldmann@reiling-logistik.de</t>
+          <t>peterplank@hellmold-plank.de</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>05247/9837-14</t>
+          <t>+49 641 95201-16</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Reiling Logistik GmbH &amp; Co. KG</t>
+          <t>Hellmold &amp; Plank GmbH &amp; Co. KG Spedition</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -4898,24 +4898,24 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>Harsewinkel (Kreis Gütersloh)</t>
+          <t>Gießen (Europastr. 7+9, 35394), Hessen</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>Inhabergeführte Logistikgruppe (Geschäftsführer Christian Reiling und Carsten Mannefeld) mit Schüttgut-, Landmaschinen- und Kommunallogistik. Persönliche E-Mail der Geschäftsführer nicht eindeutig belegt, daher Prokurist als Ansprechpartner.</t>
+          <t>1904 gegründete, inhabergeführte hessische Spedition (seit 1996 im Alleinbesitz der Familie Plank) mit Systemverkehren, Fernverkehr und Lagerlogistik; zweite Generation (Niklas Plank) in der Geschäftsführung.</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>https://www.reiling-logistik.de | https://www.regiomanager.de/ostwestfalen/ranking/mobilitaet-logistik/spedition-und-logistik/kreis-guetersloh/</t>
+          <t>https://www.hellmold-plank.de/de/kontakt | https://www.hellmold-plank.de/</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Michael Hoeper</t>
+          <t>Oliver Hüer</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -4925,17 +4925,17 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>hoeper@hoeper-spedition.de</t>
+          <t>oliver@hueer.com</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>02862-418327-10</t>
+          <t>0251 87189-130</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Richard Hoeper GmbH &amp; Co. KG (Hoeper Spedition)</t>
+          <t>Hüer Transport und Logistik GmbH</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -4945,44 +4945,44 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Südlohn-Oeding (Westmünsterland, NRW)</t>
+          <t>Münster</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>Familienunternehmen in zweiter Generation mit Transporten, eigenem Fuhrpark, Lagerlogistik und Palettenmanagement im Westmünsterland. Kleinerer, aber voll ausgebauter Betrieb mit Dispo-, QM- und Projektmanagement-Funktionen; Hinweis: liegt vermutlich unterhalb der 50-Mitarbeiter-Schwelle.</t>
+          <t>Inhabergeführte Spedition in Münster mit Nahverkehr, Kurierdienst und Logistikdienstleistungen. Familienstruktur: Oliver Hüer (GF) und Patrycja Hüer (Prokuristin).</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>https://hoeper-spedition.de/team/ | https://hoeper-spedition.de/ | https://hoeper-spedition.de/impressum/</t>
+          <t>https://www.hueer.com/kontakt | https://www.hueer.com/</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Tanja Meininghaus</t>
+          <t>Ingo Kaiser</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführerin</t>
+          <t>Geschäftsführung (Management)</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>tanja.meininghaus@sitra-spedition.de</t>
+          <t>ingo.kaiser@ikg-spedition.de</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>+49 40 751006-0 (Zentrale)</t>
+          <t>+49 7223 281689-19</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>SITRA Spedition GmbH</t>
+          <t>IKG Spedition GmbH</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
@@ -4992,44 +4992,44 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>Hamburg</t>
+          <t>Baden-Baden / Sinzheim, Baden-Württemberg</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>Inhabergeführte Hamburger Spedition mit nationalen Stückgut-/Ladungsverkehren, internationalem Geschäft und eigener Disposition; bewusst als persönlich erreichbare Alternative zu Konzernen positioniert.</t>
+          <t>Familiengeführte Spedition (Ingo und Kristina Kaiser) mit intermodalen Transporten Richtung Italien/Frankreich/Schweiz, eigenem Lager und Fuhrpark sowie Niederlassung in Busto Arsizio.</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>https://sitra-spedition.de/team/ | https://sitra-spedition.de/</t>
+          <t>https://www.ikg-spedition.de/team/ | https://www.ikg-spedition.de/</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Mike Forker</t>
+          <t>Joachim Berends</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführender Gesellschafter</t>
+          <t>Geschäftsführer</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>forker@sachsenland-gmbh.de</t>
+          <t>j.berends@bentheimer-eisenbahn.de</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>+49 351 799010</t>
+          <t>+49 5921 8034-0</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Sachsenland Transport &amp; Logistik GmbH</t>
+          <t>Kraftverkehr Emsland GmbH</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -5039,44 +5039,44 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Dresden (Sachsen)</t>
+          <t>Nordhorn, Niedersachsen</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>Selbstbeschreibung: 'Wir sind ein mittelständisches, inhabergeführtes Transport- und Logistikunternehmen'. Sitz Magdeburger Straße 58, 01067 Dresden, weitere Standorte Duisburg, Vilnius, Kiew; Transport, Lager, Zoll, Air &amp; Sea.</t>
+          <t>Geschäftsführer der Kraftverkehr Emsland GmbH (Spedition/Logistiklager der Bentheimer Eisenbahn-Gruppe). Hinweis: die auf der Ansprechpartner-Seite genannte E-Mail läuft über die Domain der Muttergesellschaft.</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>https://www.sachsenland-gmbh.de/kontakt-dresden/ | https://www.sachsenland-gmbh.de/</t>
+          <t>https://www.kraftverkehr-emsland.de/kontakt/</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Sandra Aleksanderek</t>
+          <t>Marco Oppermann</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführung</t>
+          <t>Speditionsleitung &amp; Prokurist</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>sandra.aleksanderek@sander-logistics.de</t>
+          <t>marco.oppermann@kraftverkehr-emsland.de</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>+49 40 73354-128</t>
+          <t>+49 5921 8034-96</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>Sander Logistics GmbH</t>
+          <t>Kraftverkehr Emsland GmbH</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -5086,44 +5086,44 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Hamburg (Altenwerder), weitere Standorte Itzehoe und Rostock</t>
+          <t>Nordhorn, Niedersachsen</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>Mittelständisches, familiengeführtes Logistikunternehmen mit Sammelgut, Komplettladungen, Seefracht sowie Lager-, Beschaffungs- und Kontraktlogistik an fünf Standorten.</t>
+          <t>Mittelständische Spedition mit Sammelgut, Ladungsverkehren und eigenem Warehousing-Bereich; Prokurist und Speditionsleiter mit Entscheidungsbefugnis über Prozesse/IT-Themen.</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>https://sander-logistics.de/ihre-ansprechpartner/ | https://sander-logistics.de/kontakt/</t>
+          <t>https://www.kraftverkehr-emsland.de/kontakt/ | https://www.kraftverkehr-emsland.de/spedition-logistiklager/</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Markus Baur</t>
+          <t>Lena Milde</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer / Leiter Finanz- und Lohnbuchhaltung</t>
+          <t>Standort-/Niederlassungsleitung Magdeburg</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>m.baur@spedition-baur.de</t>
+          <t>lena.milde@krage-gerloff.de</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>+49 7371 9515 20</t>
+          <t>+49 39424 951 0 (Zentrale Schwanebeck)</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>Spedition Anton Baur GmbH</t>
+          <t>Krage &amp; Gerloff Logistik GmbH</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
@@ -5133,44 +5133,44 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Ertingen (Baden-Württemberg)</t>
+          <t>Magdeburg (Sachsen-Anhalt)</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>Familiengeführte Spedition in 88521 Ertingen mit Niederlassung Stuttgart (A. Baur Mineralöl-Abfertigungsspedition). Schwerpunkte Fernverkehr, Schüttgut-/Kipper-/Schubbodentransporte, Kran- und Baustofflogistik sowie Mineralöltransporte.</t>
+          <t>1995 gegründeter Logistikdienstleister mit Hauptsitz Schwanebeck und Logistikstandort Tucheimer Straße 5, 39126 Magdeburg; Lager- und Transportlogistik.</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>https://www.spedition-baur.de/team</t>
+          <t>https://www.krage-gerloff.de/magdeburg</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>Thomas Baur</t>
+          <t>Andreas Köhler</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer / Abrechnung Baustoff- und Holztransporte</t>
+          <t>Geschäftsführer</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>t.baur@spedition-baur.de</t>
+          <t>a.koehler@koehler-transport.de</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>+49 7371 9515 10</t>
+          <t>+49 221 96640-10</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>Spedition Anton Baur GmbH</t>
+          <t>KÖHLER GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
@@ -5180,44 +5180,44 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Ertingen (Baden-Württemberg)</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>Zweiter Geschäftsführer des inhabergeführten Familienbetriebs (Zentrale Industriestraße 8, 88521 Ertingen). Zusätzlich Prokuristen Adrian und Tobias Baur im Unternehmen.</t>
+          <t>Inhabergeführtes Familienunternehmen in Köln mit Transport, Lager und eigener Werkstatt. Etwas unterhalb der Zielgröße, aber klar mittelständisch und inhabergeführt.</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>https://www.spedition-baur.de/team</t>
+          <t>https://www.koehler-transport.com/ansprechpartner | https://www.koehler-transport.com/</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Frank Blodt</t>
+          <t>Alexander Schwarz</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer</t>
+          <t>Business Development Manager &amp; Lager Management</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>frankblodt@spedition-blodt.de</t>
+          <t>a.schwarz@lkt-thiele.com</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>+49 6131 25007-0</t>
+          <t>+49 36373 129831-20</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>Spedition Blodt GmbH</t>
+          <t>LOGISTIK KONTOR GmbH (LKT Thiele)</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
@@ -5227,44 +5227,44 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>Mainz, Rheinland-Pfalz</t>
+          <t>Buttstädt (Thüringen)</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>Familiengeführte Spedition in Mainz mit Transport, Lagerlogistik und Projektmanagement; Geschäftsführung und Lagerlogistik liegen in der Familie Blodt.</t>
+          <t>Verantwortlich für Geschäftsentwicklung und Lagermanagement – Bereichsleiter-Ebene für Lager-/Distributionslogistik bei der Thüringer Spedition.</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>https://spedition-blodt.de/unser-team/</t>
+          <t>https://www.lkt-thiele.com/unternehmen/team/</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Miriam Blodt</t>
+          <t>Stephan Voigt</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführerin</t>
+          <t>Geschäftsführer</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>miriamblodt@spedition-blodt.de</t>
+          <t>s.voigt@lkt-thiele.com</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>+49 6131 25007-0</t>
+          <t>+49 36373 129831-13</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>Spedition Blodt GmbH</t>
+          <t>LOGISTIK KONTOR GmbH (LKT Thiele)</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
@@ -5274,44 +5274,44 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Mainz, Rheinland-Pfalz</t>
+          <t>Buttstädt (Thüringen)</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>Zweite Geschäftsführerin des inhabergeführten Mainzer Speditions- und Lagerlogistikbetriebs.</t>
+          <t>Seit 2004 tätige mittelständische Spedition mit Sitz Vor dem Lohe 5, 99628 Buttstädt und Niederlassung Wiebelsheim; nationale/internationale Transporte, Lagerung, Charterverkehr.</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>https://spedition-blodt.de/unser-team/</t>
+          <t>https://www.lkt-thiele.com/unternehmen/team/ | https://www.lkt-thiele.com/</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Bernd Häger</t>
+          <t>David Liedhegener</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer</t>
+          <t>Geschäftsführender Gesellschafter</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>bhaeger@spedition-haeger.de</t>
+          <t>d.liedhegener@liedhegener-logistik.de</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>02904 9740-0</t>
+          <t>02933 - 9 22 22 10</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>Spedition Häger GmbH &amp; Co. KG / Häger Transporte u. Logistik GmbH &amp; Co. KG</t>
+          <t>Liedhegener-Logistik GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
@@ -5321,24 +5321,24 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>Bestwig (Sauerland, NRW)</t>
+          <t>Sundern (Sauerland)</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>Familiengeführte Sauerland-Spedition mit Transport-, Lager- und Kontraktlogistik über zwei Schwestergesellschaften. Zwei-Firmen-Struktur und gewachsene Dispositions-/Lagerprozesse sprechen für manuelle Abläufe mit Digitalisierungs- und Systemintegrationsbedarf.</t>
+          <t>Inhabergeführter Logistikdienstleister mit Transport, Verladung und Lagerlogistik im Sauerland. Familie Liedhegener (David und Sandra Liedhegener) in Geschäftsführung und Verwaltung.</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>https://www.spedition-haeger.de/kontakt/</t>
+          <t>https://www.liedhegener-logistik.de/kontakt | https://www.regiomanager.de/suedwestfalen/ranking/mobilitaet-logistik/spedition-und-logistik/hochsauerlandkreis/</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>Gregor Roes</t>
+          <t>Jakob Riesen</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -5348,17 +5348,17 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>g.roes@spedition-hoevelmann.de</t>
+          <t>j.riesen@mbi-spedition.de</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>+49 2851 962-121</t>
+          <t>+49 (521) 93 803 - 0</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>Spedition Hövelmann GmbH &amp; Co. KG</t>
+          <t>MBI Internationale Spedition GmbH</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
@@ -5368,44 +5368,44 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>Rees (Niederrhein)</t>
+          <t>Bielefeld</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>Familiengeführte Niederrhein-Spedition mit Transport-, Lager- und Kontraktlogistik. Weitere Entscheider: Markus Hövelmann (Gesellschafter, m.hoevelmann@spedition-hoevelmann.de), Ricarda Hövelmann (Gesellschafterin, r.hoevelmann@spedition-hoevelmann.de), Jörg Möllenbeck (Prokurist, j.moellenbeck@spedition-hoevelmann.de).</t>
+          <t>Familiengeführte internationale Spedition mit Kontraktlogistik, Lagerung, Kommissionierung und Zollabwicklung. Zwei Geschäftsführer aus der Familie Riesen (Jakob und Peter Riesen).</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>https://www.spedition-hoevelmann.de/kontakt</t>
+          <t>https://www.mbi-spedition.de/unser-team/ | https://www.mbi-spedition.de/</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Verena Wiechers</t>
+          <t>Christof Mielke</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsleitung</t>
+          <t>Geschäftsführung</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>v.wiechers@wiechers-spedition.de</t>
+          <t>mielke@mielke-logistik.de</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>+49 234 94338-27</t>
+          <t>0271 / 37514-0</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>Spedition Josef Wiechers GmbH (WIECHERS Spedition + Logistik)</t>
+          <t>Mielke Logistik GmbH</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
@@ -5415,44 +5415,44 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Bochum (Hauptsitz), Standort Duisburg</t>
+          <t>Freudenberg (Siegerland)</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>Familiengeführte Spedition aus Bochum mit Standort Duisburg, Schwerpunkt Transport-, Lager- und Distributionslogistik im Ruhrgebiet. Zusätzlicher Ansprechpartner: Markus Koch (Speditionsleitung, Prokurist), m.koch@wiechers-spedition.de.</t>
+          <t>Familiengeführte Spedition mit Schwer-/Spezialtransport, Disposition national und international sowie Lagerstandorten (u. a. Außenlager Netphen). Zweite Generation (Tim Christopher Mielke) bereits in der Geschäftsführung.</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>https://www.wiechers-spedition.de/kontakt | https://www.regiomanager.de/ranking/mobilitaet-logistik/spedition-und-logistik/bochum/</t>
+          <t>https://www.mielke-logistik.de/ansprechpartner | https://www.regiomanager.de/suedwestfalen/ranking/mobilitaet-logistik/spedition-und-logistik/kreis-siegen-wittgenstein/</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>Dr. Christine Kollmannsberger</t>
+          <t>René Langen</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsleitung / Geschäftsführerin</t>
+          <t>Geschäftsleitung</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>C.Kollmannsberger@spedition-kollmannsberger.de</t>
+          <t>r.langen@speditionlangen.de</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>+49 8456 966-212</t>
+          <t>+49 2166 9539-0</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>Spedition Kollmannsberger KG</t>
+          <t>Paul Langen GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
@@ -5462,44 +5462,44 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Großmehring bei Ingolstadt (Bayern)</t>
+          <t>Mönchengladbach</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>Zweite Person der Geschäftsleitung des Familienunternehmens; Dispositionsleitung Helmut Atzmüller ebenfalls mit persönlicher Adresse gelistet.</t>
+          <t>Familienunternehmen seit 1883 mit Spedition, Lagerlogistik und Möbel-/Sperrgutlogistik, europaweite Distribution ab Mönchengladbach.</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>https://www.spedition-kollmannsberger.de/spedition-ansprechpartner</t>
+          <t>https://www.speditionlangen.de/kontakt | https://www.regiomanager.de/ranking/mobilitaet-logistik/spedition-und-logistik/moenchengladbach/</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Ludwig Kollmannsberger</t>
+          <t>Benjamin Peelen</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsleitung / Geschäftsführer</t>
+          <t>Geschäftsführer (Peelen Logistik GmbH)</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>L.Kollmannsberger@spedition-kollmannsberger.de</t>
+          <t>benjamin.peelen@peelen.de</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>+49 8456 966-211</t>
+          <t>+49 2843 9597-114 (Peelen Logistik GmbH, Rheinberg)</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>Spedition Kollmannsberger KG</t>
+          <t>Peelen Transporte GmbH / Peelen Logistik GmbH</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
@@ -5509,44 +5509,44 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Großmehring bei Ingolstadt (Bayern)</t>
+          <t>Duisburg (Betriebshof) / Rheinberg (Logistikzentrum Niederrhein)</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>Familiengeführte Spedition im InTerPark Ingolstadt (Dieselstraße 6, 85098 Großmehring) mit Transport-, Lager- und Distributionslogistik für den Raum Ingolstadt/Oberbayern.</t>
+          <t>Familiengeführte Transport- und Logistikgruppe am Niederrhein mit eigenem Fuhrpark, Warehouse (LZN Rheinberg) und Kontraktlogistik.</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>https://www.spedition-kollmannsberger.de/spedition-ansprechpartner | https://www.spedition-kollmannsberger.de/</t>
+          <t>https://www.peelen.de/kontakt | https://www.regiomanager.de/revier/ranking/mobilitaet-logistik/spedition-und-logistik/duisburg/</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>Jürgen Frömberg</t>
+          <t>Florian Meyer</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer</t>
+          <t>Geschäftsführung / Logistik- und Lagerleitung</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>jFroemberg@spedition-maier.de</t>
+          <t>florian.meyer@rdllogistik.de</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>+49 7731 828-201</t>
+          <t>+49 (0)2151 36806-16</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>Spedition Maier GmbH</t>
+          <t>RDL Logistik Rheinische Distributions- und Lagerlogistik GmbH</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
@@ -5556,44 +5556,44 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>Singen (Hohentwiel), Baden-Württemberg</t>
+          <t>Krefeld (Niederrhein, NRW), zweiter Standort Willich</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>Mittelständische Spedition mit Standorten Singen, Pfullendorf und Ramsen (CH). Sammelgut, Charterverkehr, Zollabwicklung sowie eigene Lagerlogistik mit mehreren Betriebs- und Standortleitern.</t>
+          <t>Inhabergeführter Lager- und Distributionslogistiker am Niederrhein (seit 2000) mit Lagerlogistik, Distribution und Fuhrpark an zwei Standorten. Geschäftsführung leitet operativ Lager und Abrechnung selbst — Digitalisierung von Lagerverwaltung, Disposition und Abrechnung ist unmittelbar chef-relevant.</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>https://www.spedition-maier.de/team/</t>
+          <t>https://rdllogistik.de/ueber-uns/ | https://rdllogistik.de/ | https://rdllogistik.de/impressum/</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Thomas Marizzi</t>
+          <t>Udo Feldmann</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsleitung – Speditionsleitung</t>
+          <t>Leitung Disposition Landmaschinen &amp; Prokurist</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>tMarizzi@spedition-maier.de</t>
+          <t>feldmann@reiling-logistik.de</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>+49 7731 828-188</t>
+          <t>05247/9837-14</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>Spedition Maier GmbH</t>
+          <t>Reiling Logistik GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
@@ -5603,44 +5603,44 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Singen (Hohentwiel), Baden-Württemberg</t>
+          <t>Harsewinkel (Kreis Gütersloh)</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>Mitglied der Geschäftsleitung mit Verantwortung für den Speditionsbereich; kaufmännische Leitung Jochen Sigg (jsigg@spedition-maier.de) ebenfalls auf derselben Seite belegt.</t>
+          <t>Inhabergeführte Logistikgruppe (Geschäftsführer Christian Reiling und Carsten Mannefeld) mit Schüttgut-, Landmaschinen- und Kommunallogistik. Persönliche E-Mail der Geschäftsführer nicht eindeutig belegt, daher Prokurist als Ansprechpartner.</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>https://www.spedition-maier.de/team/</t>
+          <t>https://www.reiling-logistik.de | https://www.regiomanager.de/ostwestfalen/ranking/mobilitaet-logistik/spedition-und-logistik/kreis-guetersloh/</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>Nicole Körtge</t>
+          <t>Michael Hoeper</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Leitung Auftragsmanagement/Logistik</t>
+          <t>Geschäftsführer</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>nicolekoertge@spedition-wagner.net</t>
+          <t>hoeper@hoeper-spedition.de</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>+49 2642 9022922</t>
+          <t>02862-418327-10</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>Spedition Wagner GmbH</t>
+          <t>Richard Hoeper GmbH &amp; Co. KG (Hoeper Spedition)</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
@@ -5650,44 +5650,44 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>Remagen (Am Römerhof 60, 53424), Rheinland-Pfalz</t>
+          <t>Südlohn-Oeding (Westmünsterland, NRW)</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>Familiengeführter Logistikdienstleister mit Kontraktlogistik für die Getränkeindustrie (u. a. Krombacher), Lagerlogistik, Displaybau und eigenem Fuhrpark. Geschäftsführung (Arlt/Gaßner/Kröhl) ohne öffentliche E-Mail – Bereichsleitung Logistik als Entscheidungsträger.</t>
+          <t>Familienunternehmen in zweiter Generation mit Transporten, eigenem Fuhrpark, Lagerlogistik und Palettenmanagement im Westmünsterland. Kleinerer, aber voll ausgebauter Betrieb mit Dispo-, QM- und Projektmanagement-Funktionen; Hinweis: liegt vermutlich unterhalb der 50-Mitarbeiter-Schwelle.</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>https://spedition-wagner.net/unternehmen/team/</t>
+          <t>https://hoeper-spedition.de/team/ | https://hoeper-spedition.de/ | https://hoeper-spedition.de/impressum/</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Matthias Schork</t>
+          <t>Tanja Meininghaus</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer</t>
+          <t>Geschäftsführerin</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>m.schork@wuest.com</t>
+          <t>tanja.meininghaus@sitra-spedition.de</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>+49 9141 8684-140</t>
+          <t>+49 40 751006-0 (Zentrale)</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>Spedition Wüst (Wüst GmbH &amp; Co. KG)</t>
+          <t>SITRA Spedition GmbH</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
@@ -5697,44 +5697,44 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>Weißenburg i. Bay., weiteres Logistikzentrum Ansbach, Bayern</t>
+          <t>Hamburg</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>Mittelständische bayerische Spedition mit Stückgut- und Ladungsverkehren sowie zwei eigenen Logistikzentren (Lagerung, Kommissionierung, Value Added Services).</t>
+          <t>Inhabergeführte Hamburger Spedition mit nationalen Stückgut-/Ladungsverkehren, internationalem Geschäft und eigener Disposition; bewusst als persönlich erreichbare Alternative zu Konzernen positioniert.</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>https://www.wuest.com/kontakt/ | https://www.wuest.com/</t>
+          <t>https://sitra-spedition.de/team/ | https://sitra-spedition.de/</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>Michael Müller</t>
+          <t>Mike Forker</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Logistikleiter</t>
+          <t>Geschäftsführender Gesellschafter</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>m.mueller@wuest.com</t>
+          <t>forker@sachsenland-gmbh.de</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>+49 9141 8684-106</t>
+          <t>+49 351 799010</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>Spedition Wüst (Wüst GmbH &amp; Co. KG)</t>
+          <t>Sachsenland Transport &amp; Logistik GmbH</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
@@ -5744,44 +5744,44 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Weißenburg i. Bay., Bayern</t>
+          <t>Dresden (Sachsen)</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>Verantwortlicher für die Logistikzentren Weißenburg und Ansbach – direkter Entscheider für Lager-/Kontraktlogistikprozesse.</t>
+          <t>Selbstbeschreibung: 'Wir sind ein mittelständisches, inhabergeführtes Transport- und Logistikunternehmen'. Sitz Magdeburger Straße 58, 01067 Dresden, weitere Standorte Duisburg, Vilnius, Kiew; Transport, Lager, Zoll, Air &amp; Sea.</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>https://www.wuest.com/kontakt/</t>
+          <t>https://www.sachsenland-gmbh.de/kontakt-dresden/ | https://www.sachsenland-gmbh.de/</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Bernd Stratkötter</t>
+          <t>Sandra Aleksanderek</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer, Auftragsmanagement &amp; Disposition</t>
+          <t>Geschäftsführung</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>bs@stratkoetter.de</t>
+          <t>sandra.aleksanderek@sander-logistics.de</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>02523 / 9200-12</t>
+          <t>+49 40 73354-128</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>Stratkötter Logistik + Transport GmbH &amp; Co. KG</t>
+          <t>Sander Logistics GmbH</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
@@ -5791,44 +5791,44 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>Wadersloh (Kreis Warendorf)</t>
+          <t>Hamburg (Altenwerder), weitere Standorte Itzehoe und Rostock</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>Familienbetrieb mit drei Geschäftsführern aus der Familie Stratkötter (Werner, Bernd, Thomas), Schwerpunkt Auftragsmanagement, Disposition und Lagerlogistik im Münsterland.</t>
+          <t>Mittelständisches, familiengeführtes Logistikunternehmen mit Sammelgut, Komplettladungen, Seefracht sowie Lager-, Beschaffungs- und Kontraktlogistik an fünf Standorten.</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>https://www.stratkoetter.de/ansprechpartner | https://www.regiomanager.de/muensterland/ranking/mobilitaet-logistik/spedition-und-logistik/kreis-warendorf/</t>
+          <t>https://sander-logistics.de/ihre-ansprechpartner/ | https://sander-logistics.de/kontakt/</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>Ralf Greinert</t>
+          <t>Markus Baur</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer</t>
+          <t>Geschäftsführer / Leiter Finanz- und Lohnbuchhaltung</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>ralf.greinert@teamlogistic.de</t>
+          <t>m.baur@spedition-baur.de</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>+49 2602 1309-0 (Zentrale)</t>
+          <t>+49 7371 9515 20</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>TEAM Logistic GmbH &amp; Co. KG</t>
+          <t>Spedition Anton Baur GmbH</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
@@ -5838,44 +5838,44 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>Montabaur (Westerwaldstr. 2a, 56410), Rheinland-Pfalz</t>
+          <t>Ertingen (Baden-Württemberg)</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>Familiengeführte Spedition im Westerwald (Familie Greinert) mit eigener Disposition, Werkstatt und Verwaltung; Transporte national/international.</t>
+          <t>Familiengeführte Spedition in 88521 Ertingen mit Niederlassung Stuttgart (A. Baur Mineralöl-Abfertigungsspedition). Schwerpunkte Fernverkehr, Schüttgut-/Kipper-/Schubbodentransporte, Kran- und Baustofflogistik sowie Mineralöltransporte.</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>https://teamlogistic.de/ansprechpartner/ | https://teamlogistic.de/impressum/</t>
+          <t>https://www.spedition-baur.de/team</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Uwe Diel</t>
+          <t>Thomas Baur</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer</t>
+          <t>Geschäftsführer / Abrechnung Baustoff- und Holztransporte</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>uwe.diel@teamlogistic.de</t>
+          <t>t.baur@spedition-baur.de</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>+49 2602 1309-0 (Zentrale)</t>
+          <t>+49 7371 9515 10</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>TEAM Logistic GmbH &amp; Co. KG</t>
+          <t>Spedition Anton Baur GmbH</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
@@ -5885,44 +5885,44 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>Montabaur, Rheinland-Pfalz</t>
+          <t>Ertingen (Baden-Württemberg)</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>Zweiter Geschäftsführer der Team Logistic GmbH &amp; Co. KG, mittelständische Spedition mit eigenem Fuhrpark.</t>
+          <t>Zweiter Geschäftsführer des inhabergeführten Familienbetriebs (Zentrale Industriestraße 8, 88521 Ertingen). Zusätzlich Prokuristen Adrian und Tobias Baur im Unternehmen.</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>https://teamlogistic.de/ansprechpartner/</t>
+          <t>https://www.spedition-baur.de/team</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>Manuel Keller</t>
+          <t>Frank Blodt</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Bereichsleiter / Mitglied der Geschäftsleitung</t>
+          <t>Geschäftsführer</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Manuel.Keller@teamlog.de</t>
+          <t>frankblodt@spedition-blodt.de</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>+49 6021 1507-121</t>
+          <t>+49 6131 25007-0</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>TEAMLOG (Team Log GmbH &amp; Co. KG)</t>
+          <t>Spedition Blodt GmbH</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
@@ -5932,44 +5932,44 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>Aschaffenburg (Bayern)</t>
+          <t>Mainz, Rheinland-Pfalz</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>Inhabergeführter Kontrakt- und Lagerlogistiker mit Zentrale Germanenstraße 30, 63741 Aschaffenburg und 15 Standorten im Rhein-Main-Gebiet.</t>
+          <t>Familiengeführte Spedition in Mainz mit Transport, Lagerlogistik und Projektmanagement; Geschäftsführung und Lagerlogistik liegen in der Familie Blodt.</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>https://teamlog.de/kontakt/ | https://teamlog.de/</t>
+          <t>https://spedition-blodt.de/unser-team/</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>Theodor Schulz</t>
+          <t>Miriam Blodt</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer (Disposition &amp; Kundenbetreuung)</t>
+          <t>Geschäftsführerin</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>ts@schulz-spedition.de</t>
+          <t>miriamblodt@spedition-blodt.de</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>+49 251 26333-211</t>
+          <t>+49 6131 25007-0</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>Theodor Schulz GmbH &amp; Co. KG (Schulz Spedition)</t>
+          <t>Spedition Blodt GmbH</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
@@ -5979,44 +5979,44 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>Münster (NRW)</t>
+          <t>Mainz, Rheinland-Pfalz</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>Inhabergeführte Münsteraner Spedition mit Transport, Lagerung/Lagerverwaltung, Palettenmanagement und Abrechnung als eigene Abteilungen. Geschäftsführung sitzt selbst in der Disposition — kurze Entscheidungswege, viele manuell getriebene Dispo- und Abrechnungsprozesse als Digitalisierungsansatz.</t>
+          <t>Zweite Geschäftsführerin des inhabergeführten Mainzer Speditions- und Lagerlogistikbetriebs.</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>https://www.schulz-spedition.de/ | https://www.schulz-spedition.de/#unternehmen</t>
+          <t>https://spedition-blodt.de/unser-team/</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>Christian Vetten</t>
+          <t>Bernd Häger</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer (Ansprechpartner Transporte/Lagerlogistik)</t>
+          <t>Geschäftsführer</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>christian.vetten@vetten-gruppe.de</t>
+          <t>bhaeger@spedition-haeger.de</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>02162 5302-379</t>
+          <t>02904 9740-0</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>Vetten Gruppe (Gebr. Vetten GmbH &amp; Co. KG)</t>
+          <t>Spedition Häger GmbH &amp; Co. KG / Häger Transporte u. Logistik GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
@@ -6026,24 +6026,24 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>Mönchengladbach (Niederrhein, NRW)</t>
+          <t>Bestwig (Sauerland, NRW)</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>Familienbetrieb seit 1931 mit Transport, Lagerlogistik, Textil- und Kontraktlogistik auf &gt;100.000 qm Lagerfläche. Gewachsene Gruppenstruktur mit mehreren Standorten, Variantenvielfalt (Textilaufbereitung, Kontraktlogistik) und vorhandener Logistik-IT (ecovium/SPEDION im Einsatz) — viel Potenzial für Prozessdigitalisierung und Schnittstellen-/ERP-Themen.</t>
+          <t>Familiengeführte Sauerland-Spedition mit Transport-, Lager- und Kontraktlogistik über zwei Schwestergesellschaften. Zwei-Firmen-Struktur und gewachsene Dispositions-/Lagerprozesse sprechen für manuelle Abläufe mit Digitalisierungs- und Systemintegrationsbedarf.</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>https://vetten-gruppe.de/kontakt/ | https://vetten-gruppe.de/ | https://vetten-gruppe.de/impressum/ | https://vetten-gruppe.de/die-vetten-gruppe/</t>
+          <t>https://www.spedition-haeger.de/kontakt/</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>Dirk Schröder</t>
+          <t>Gregor Roes</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -6053,17 +6053,17 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>dirk.schroeder@westfalia-intralog.com</t>
+          <t>g.roes@spedition-hoevelmann.de</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>+49 (0) 5221 - 1809 - 690</t>
+          <t>+49 2851 962-121</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>WESTFALIA intralog GmbH</t>
+          <t>Spedition Hövelmann GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
@@ -6073,44 +6073,44 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Herford (OWL)</t>
+          <t>Rees (Niederrhein)</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>Kontraktlogistiker mit Standorten in Herford und Bremerhaven, Schwerpunkt Lager- und Value-Added-Services für Industriekunden.</t>
+          <t>Familiengeführte Niederrhein-Spedition mit Transport-, Lager- und Kontraktlogistik. Weitere Entscheider: Markus Hövelmann (Gesellschafter, m.hoevelmann@spedition-hoevelmann.de), Ricarda Hövelmann (Gesellschafterin, r.hoevelmann@spedition-hoevelmann.de), Jörg Möllenbeck (Prokurist, j.moellenbeck@spedition-hoevelmann.de).</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>https://www.westfalia-intralog.de/kontakt | https://www.regiomanager.de/ostwestfalen-lippe/ranking/mobilitaet-logistik/spedition-und-logistik/kreis-herford/</t>
+          <t>https://www.spedition-hoevelmann.de/kontakt</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>Andreas Koch</t>
+          <t>Verena Wiechers</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer</t>
+          <t>Geschäftsleitung</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>a.koch@eckhardt-logistik.de</t>
+          <t>v.wiechers@wiechers-spedition.de</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>+49 711 80000-0 (Zentrale)</t>
+          <t>+49 234 94338-27</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>Walter Eckhardt GmbH Spedition + Logistik</t>
+          <t>Spedition Josef Wiechers GmbH (WIECHERS Spedition + Logistik)</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
@@ -6120,44 +6120,44 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>Korntal-Münchingen (Raum Stuttgart), Baden-Württemberg</t>
+          <t>Bochum (Hauptsitz), Standort Duisburg</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>Inhabergeführte Spedition seit 1987 mit Stückgut, Gefahrgut- und Pflanzentransporten sowie eigenem Lager-/Kommissionierzentrum (seit 2019). Eigene Bereiche für Umschlag, Lagerlogistik und Disposition.</t>
+          <t>Familiengeführte Spedition aus Bochum mit Standort Duisburg, Schwerpunkt Transport-, Lager- und Distributionslogistik im Ruhrgebiet. Zusätzlicher Ansprechpartner: Markus Koch (Speditionsleitung, Prokurist), m.koch@wiechers-spedition.de.</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>https://eckhardt-logistik.de/kontakt/ansprechpartner | https://eckhardt-logistik.de/</t>
+          <t>https://www.wiechers-spedition.de/kontakt | https://www.regiomanager.de/ranking/mobilitaet-logistik/spedition-und-logistik/bochum/</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>Marc Eckhardt</t>
+          <t>Dr. Christine Kollmannsberger</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Gesellschafter (Inhaberfamilie)</t>
+          <t>Geschäftsleitung / Geschäftsführerin</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>m.eckhardt@eckhardt-logistik.de</t>
+          <t>C.Kollmannsberger@spedition-kollmannsberger.de</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>+49 711 80000-0 (Zentrale)</t>
+          <t>+49 8456 966-212</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>Walter Eckhardt GmbH Spedition + Logistik</t>
+          <t>Spedition Kollmannsberger KG</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
@@ -6167,44 +6167,44 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>Korntal-Münchingen (Raum Stuttgart), Baden-Württemberg</t>
+          <t>Großmehring bei Ingolstadt (Bayern)</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>Gesellschafter und Namensträger des familiengeführten Speditions- und Logistikunternehmens; zweiter Entscheidungsträger neben der Geschäftsführung.</t>
+          <t>Zweite Person der Geschäftsleitung des Familienunternehmens; Dispositionsleitung Helmut Atzmüller ebenfalls mit persönlicher Adresse gelistet.</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>https://eckhardt-logistik.de/kontakt/ansprechpartner | https://eckhardt-logistik.de/</t>
+          <t>https://www.spedition-kollmannsberger.de/spedition-ansprechpartner</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>Dirk Valerius</t>
+          <t>Ludwig Kollmannsberger</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführender Gesellschafter</t>
+          <t>Geschäftsleitung / Geschäftsführer</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>d.valerius@werneke.de</t>
+          <t>L.Kollmannsberger@spedition-kollmannsberger.de</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>02922 / 8060 - 260</t>
+          <t>+49 8456 966-211</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>Werneke Logistic GmbH &amp; Co. KG</t>
+          <t>Spedition Kollmannsberger KG</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
@@ -6214,24 +6214,24 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>Werl (Kreis Soest / Südwestfalen)</t>
+          <t>Großmehring bei Ingolstadt (Bayern)</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>Inhabergeführter Logistikdienstleister mit Stückgut, Sammelgut, Charterverkehr und vier Lagerstandorten (Kontraktlogistik). Familie Werneke weiterhin im Unternehmen aktiv.</t>
+          <t>Familiengeführte Spedition im InTerPark Ingolstadt (Dieselstraße 6, 85098 Großmehring) mit Transport-, Lager- und Distributionslogistik für den Raum Ingolstadt/Oberbayern.</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>https://www.werneke.de/ansprechpartner | https://www.regiomanager.de/suedwestfalen/ranking/mobilitaet-logistik/spedition-und-logistik/kreis-soest/</t>
+          <t>https://www.spedition-kollmannsberger.de/spedition-ansprechpartner | https://www.spedition-kollmannsberger.de/</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>Jörg Küpper</t>
+          <t>Jürgen Frömberg</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -6241,17 +6241,17 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>j.kuepper@d-log.de</t>
+          <t>jFroemberg@spedition-maier.de</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>+49 201 2897960</t>
+          <t>+49 7731 828-201</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>d-log GmbH</t>
+          <t>Spedition Maier GmbH</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
@@ -6261,682 +6261,682 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>Essen</t>
+          <t>Singen (Hohentwiel), Baden-Württemberg</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>Inhabergeführter Logistikdienstleister aus Essen (Schacht Neu-Cöln) mit Transport-, Lager- und Distributionslogistik im Ruhrgebiet.</t>
+          <t>Mittelständische Spedition mit Standorten Singen, Pfullendorf und Ramsen (CH). Sammelgut, Charterverkehr, Zollabwicklung sowie eigene Lagerlogistik mit mehreren Betriebs- und Standortleitern.</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>https://www.d-log.de/impressum | https://www.regiomanager.de/ranking/mobilitaet-logistik/spedition-und-logistik/essen/</t>
+          <t>https://www.spedition-maier.de/team/</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>Johan Bogaerts</t>
+          <t>Thomas Marizzi</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer</t>
+          <t>Geschäftsleitung – Speditionsleitung</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>johan.bogaerts@arichemie.com</t>
+          <t>tMarizzi@spedition-maier.de</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>+49 6198 5912-0 (Zentrale; keine persönliche Durchwahl veröffentlicht)</t>
+          <t>+49 7731 828-188</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>ARICHEMIE GmbH</t>
+          <t>Spedition Maier GmbH</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>Chemie &amp; Prozessindustrie</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Eppstein-Bremthal (Hessen)</t>
+          <t>Singen (Hohentwiel), Baden-Württemberg</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>Inhabergeführte Füllstoff- und Farbenfabrik, entwickelt und produziert Pigment-Präparationen ausschließlich für B2B-Kunden. Mitglied bei HessenChemie.</t>
+          <t>Mitglied der Geschäftsleitung mit Verantwortung für den Speditionsbereich; kaufmännische Leitung Jochen Sigg (jsigg@spedition-maier.de) ebenfalls auf derselben Seite belegt.</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>https://arichemie.com/de/arichemie/kontakt/ | https://www.arichemie.com | https://www.hessenchemie.de/mitgliedsunternehmen</t>
+          <t>https://www.spedition-maier.de/team/</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>Adem Baygin</t>
+          <t>Nicole Körtge</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Prokurist, Leitung Vertrieb</t>
+          <t>Leitung Auftragsmanagement/Logistik</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>a.baygin@astorplast.de</t>
+          <t>nicolekoertge@spedition-wagner.net</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>+49 7172 303-47</t>
+          <t>+49 2642 9022922</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>ASTORPLAST Klebetechnik GmbH</t>
+          <t>Spedition Wagner GmbH</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>Chemie &amp; Prozessindustrie</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>Alfdorf (Baden-Württemberg)</t>
+          <t>Remagen (Am Römerhof 60, 53424), Rheinland-Pfalz</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>Hersteller von Klebebändern und Klebelösungen, u. a. für Luft- und Winddichtung sowie Profiltechnik; Mitglied im Industrieverband Klebstoffe.</t>
+          <t>Familiengeführter Logistikdienstleister mit Kontraktlogistik für die Getränkeindustrie (u. a. Krombacher), Lagerlogistik, Displaybau und eigenem Fuhrpark. Geschäftsführung (Arlt/Gaßner/Kröhl) ohne öffentliche E-Mail – Bereichsleitung Logistik als Entscheidungsträger.</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>https://www.astorplast.de/kontakt | https://www.klebstoffe.com/mitglieder/</t>
+          <t>https://spedition-wagner.net/unternehmen/team/</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>Roland Albrecht</t>
+          <t>Matthias Schork</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>Prokurist, Produktionsleitung</t>
+          <t>Geschäftsführer</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>r.albrecht@aurora-kunststoffe.de</t>
+          <t>m.schork@wuest.com</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>+49 7942 9142-49</t>
+          <t>+49 9141 8684-140</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>AURORA Kunststoffe GmbH</t>
+          <t>Spedition Wüst (Wüst GmbH &amp; Co. KG)</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>Chemie &amp; Prozessindustrie</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Neuenstein (Baden-Württemberg)</t>
+          <t>Weißenburg i. Bay., weiteres Logistikzentrum Ansbach, Bayern</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>Mittelständischer Compoundeur für technische Kunststoff-Compounds und hochwertige Rezyklate mit eigener Extrusion.</t>
+          <t>Mittelständische bayerische Spedition mit Stückgut- und Ladungsverkehren sowie zwei eigenen Logistikzentren (Lagerung, Kommissionierung, Value Added Services).</t>
         </is>
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>https://www.aurora-kunststoffe.de/ansprechpartner</t>
+          <t>https://www.wuest.com/kontakt/ | https://www.wuest.com/</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>Thomas Rätzsch</t>
+          <t>Michael Müller</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsleitung</t>
+          <t>Logistikleiter</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>t.raetzsch@aurora-kunststoffe.de</t>
+          <t>m.mueller@wuest.com</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>+49 7942 9142-0</t>
+          <t>+49 9141 8684-106</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>AURORA Kunststoffe GmbH</t>
+          <t>Spedition Wüst (Wüst GmbH &amp; Co. KG)</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>Chemie &amp; Prozessindustrie</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>Neuenstein (Baden-Württemberg)</t>
+          <t>Weißenburg i. Bay., Bayern</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>Mittelständischer Compoundeur für technische Kunststoff-Compounds und hochwertige Rezyklate mit eigener Extrusion.</t>
+          <t>Verantwortlicher für die Logistikzentren Weißenburg und Ansbach – direkter Entscheider für Lager-/Kontraktlogistikprozesse.</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>https://www.aurora-kunststoffe.de/ansprechpartner | https://www.aurora-kunststoffe.de/kontakt/</t>
+          <t>https://www.wuest.com/kontakt/</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>Senol Topcu</t>
+          <t>Bernd Stratkötter</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer</t>
+          <t>Geschäftsführer, Auftragsmanagement &amp; Disposition</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>s.topcu@chemopur.info</t>
+          <t>bs@stratkoetter.de</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>+49 2323 98797-0</t>
+          <t>02523 / 9200-12</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>CHEMOPUR H. Brand GmbH</t>
+          <t>Stratkötter Logistik + Transport GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>Chemie &amp; Prozessindustrie</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>Herne (Baukauer Str. 125, 44653 Herne)</t>
+          <t>Wadersloh (Kreis Warendorf)</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>Mittelständischer Hersteller von Polyurethan- und Reaktionsharzsystemen sowie Beschichtungs-/Bauchemieprodukten mit eigener Anwendungstechnik und F&amp;E.</t>
+          <t>Familienbetrieb mit drei Geschäftsführern aus der Familie Stratkötter (Werner, Bernd, Thomas), Schwerpunkt Auftragsmanagement, Disposition und Lagerlogistik im Münsterland.</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>https://chemopur.de/kontakt/ | https://chemopur.de/impressum/</t>
+          <t>https://www.stratkoetter.de/ansprechpartner | https://www.regiomanager.de/muensterland/ranking/mobilitaet-logistik/spedition-und-logistik/kreis-warendorf/</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>Martin Polczyk</t>
+          <t>Ralf Greinert</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Managing Director / CEO</t>
+          <t>Geschäftsführer</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>polczyk@cofermin.de</t>
+          <t>ralf.greinert@teamlogistic.de</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>+49 201 43878-35</t>
+          <t>+49 2602 1309-0 (Zentrale)</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>COFERMIN Group / Cofermin Chemicals GmbH &amp; Co. KG</t>
+          <t>TEAM Logistic GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>Chemie &amp; Prozessindustrie</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>Essen</t>
+          <t>Montabaur (Westerwaldstr. 2a, 56410), Rheinland-Pfalz</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>Inhabergeführte Essener Gruppe für Chemikalien- und Mineralstoffhandel, Feuerfest und chemische Spezialitäten mit mehreren Produktions- und Handelsgesellschaften.</t>
+          <t>Familiengeführte Spedition im Westerwald (Familie Greinert) mit eigener Disposition, Werkstatt und Verwaltung; Transporte national/international.</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>https://cofermin.de/ansprechpartner/</t>
+          <t>https://teamlogistic.de/ansprechpartner/ | https://teamlogistic.de/impressum/</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>Franco Menchetti</t>
+          <t>Uwe Diel</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>Vertriebsleiter &amp; Prokurist</t>
+          <t>Geschäftsführer</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>Franco.Menchetti@cta-gmbh.de</t>
+          <t>uwe.diel@teamlogistic.de</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>+49 7141 299916-148</t>
+          <t>+49 2602 1309-0 (Zentrale)</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>CTA GmbH</t>
+          <t>TEAM Logistic GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>Chemie &amp; Prozessindustrie</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>Ludwigsburg (Baden-Württemberg)</t>
+          <t>Montabaur, Rheinland-Pfalz</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>Lohnabfüller und Lohnfertiger für chemisch-technische Produkte (Flüssigkeiten, Aerosole, Sets) inkl. Standort in den USA.</t>
+          <t>Zweiter Geschäftsführer der Team Logistic GmbH &amp; Co. KG, mittelständische Spedition mit eigenem Fuhrpark.</t>
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>https://www.cta-gmbh.de/kontakt/ | https://www.cta-gmbh.de/lohnabfuellung-in-den-usa-ihre-ansprechpartner/</t>
+          <t>https://teamlogistic.de/ansprechpartner/</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>Hans-Dieter Worch</t>
+          <t>Manuel Keller</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer</t>
+          <t>Bereichsleiter / Mitglied der Geschäftsleitung</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>hans-dieter.worch@cta-gmbh.de</t>
+          <t>Manuel.Keller@teamlog.de</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>+49 7141 299916-0 (Zentrale; keine persönliche Durchwahl veröffentlicht)</t>
+          <t>+49 6021 1507-121</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>CTA GmbH</t>
+          <t>TEAMLOG (Team Log GmbH &amp; Co. KG)</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>Chemie &amp; Prozessindustrie</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>Ludwigsburg (Baden-Württemberg)</t>
+          <t>Aschaffenburg (Bayern)</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>Lohnabfüller und Lohnfertiger für chemisch-technische Produkte (Flüssigkeiten, Aerosole, Sets) inkl. Standort in den USA.</t>
+          <t>Inhabergeführter Kontrakt- und Lagerlogistiker mit Zentrale Germanenstraße 30, 63741 Aschaffenburg und 15 Standorten im Rhein-Main-Gebiet.</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>https://www.cta-gmbh.de/lohnabfuellung-in-den-usa-ihre-ansprechpartner/ | https://www.cta-gmbh.de/kontakt/ (dort: 'Hans-Dieter Worch Geschäftsführer')</t>
+          <t>https://teamlog.de/kontakt/ | https://teamlog.de/</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>Benjamin Wrobel</t>
+          <t>Theodor Schulz</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>COO (Chief Operating Officer)</t>
+          <t>Geschäftsführer (Disposition &amp; Kundenbetreuung)</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>b.wrobel@wocklum.de</t>
+          <t>ts@schulz-spedition.de</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>+49 2375 925 291</t>
+          <t>+49 251 26333-211</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>Chemische Fabrik Wocklum (Wocklum Chemie)</t>
+          <t>Theodor Schulz GmbH &amp; Co. KG (Schulz Spedition)</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>Chemie &amp; Prozessindustrie</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>Balve (Sauerland/Westfalen)</t>
+          <t>Münster (NRW)</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>Familiengeführte Chemiegruppe mit Lohnfertigung/Contract Manufacturing, Bulk-Handel sowie Recycling und Entsorgung chemischer Produkte. Geschäftsführer laut Seite: Gero Hertin (nur Sammeladresse geschaeftsfuehrung@wocklum-gruppe.de).</t>
+          <t>Inhabergeführte Münsteraner Spedition mit Transport, Lagerung/Lagerverwaltung, Palettenmanagement und Abrechnung als eigene Abteilungen. Geschäftsführung sitzt selbst in der Disposition — kurze Entscheidungswege, viele manuell getriebene Dispo- und Abrechnungsprozesse als Digitalisierungsansatz.</t>
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>https://wocklum-chemie.de/kontakt/</t>
+          <t>https://www.schulz-spedition.de/ | https://www.schulz-spedition.de/#unternehmen</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>Julian Cirkel</t>
+          <t>Christian Vetten</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer (Managing Director), Inhaberfamilie</t>
+          <t>Geschäftsführer (Ansprechpartner Transporte/Lagerlogistik)</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>julian.cirkel@cirkel.de</t>
+          <t>christian.vetten@vetten-gruppe.de</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>+49 2364 938124</t>
+          <t>02162 5302-379</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>Cirkel GmbH &amp; Co. KG</t>
+          <t>Vetten Gruppe (Gebr. Vetten GmbH &amp; Co. KG)</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>Chemie &amp; Prozessindustrie</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>Haltern am See (Werk Wickede, Standort Emsdetten)</t>
+          <t>Mönchengladbach (Niederrhein, NRW)</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>Familiengeführter Hersteller mineralischer Bau- und Prozessstoffe (Baustoffe, multifunktionale Mineralien) mit mehreren Produktionsstandorten in NRW.</t>
+          <t>Familienbetrieb seit 1931 mit Transport, Lagerlogistik, Textil- und Kontraktlogistik auf &gt;100.000 qm Lagerfläche. Gewachsene Gruppenstruktur mit mehreren Standorten, Variantenvielfalt (Textilaufbereitung, Kontraktlogistik) und vorhandener Logistik-IT (ecovium/SPEDION im Einsatz) — viel Potenzial für Prozessdigitalisierung und Schnittstellen-/ERP-Themen.</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>https://www.cirkel.de/kontakt</t>
+          <t>https://vetten-gruppe.de/kontakt/ | https://vetten-gruppe.de/ | https://vetten-gruppe.de/impressum/ | https://vetten-gruppe.de/die-vetten-gruppe/</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>Dr. Sabrina Mondrzyk</t>
+          <t>Dirk Schröder</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>Kaufmännische Leitung</t>
+          <t>Geschäftsführer</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>sabrina.mondrzyk@dhc-solvent.de</t>
+          <t>dirk.schroeder@westfalia-intralog.com</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>+49 208 9940-161</t>
+          <t>+49 (0) 5221 - 1809 - 690</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>DHC Solvent Chemie GmbH</t>
+          <t>WESTFALIA intralog GmbH</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>Chemie &amp; Prozessindustrie</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>Mülheim an der Ruhr</t>
+          <t>Herford (OWL)</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>Hersteller und Aufbereiter von Lösemitteln und Lösemittelrecycling für Lack-, Klebstoff- und Prozessindustrie. Geschäftsführer laut Impressum: Thomas Schreiber, Michaela Hodyas (nur info@-Adresse veröffentlicht).</t>
+          <t>Kontraktlogistiker mit Standorten in Herford und Bremerhaven, Schwerpunkt Lager- und Value-Added-Services für Industriekunden.</t>
         </is>
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>https://dhc-solvent.de/vertrieb/ | https://dhc-solvent.de/impressum/</t>
+          <t>https://www.westfalia-intralog.de/kontakt | https://www.regiomanager.de/ostwestfalen-lippe/ranking/mobilitaet-logistik/spedition-und-logistik/kreis-herford/</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>Dimitri Peters</t>
+          <t>Andreas Koch</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Werksleiter (Produktion)</t>
+          <t>Geschäftsführer</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>d.peters@dr-demuth.com</t>
+          <t>a.koch@eckhardt-logistik.de</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>+49 5551 9794-36</t>
+          <t>+49 711 80000-0 (Zentrale)</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>Dr. Demuth Derisol Lackfarben GmbH &amp; Co. KG</t>
+          <t>Walter Eckhardt GmbH Spedition + Logistik</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>Chemie &amp; Prozessindustrie</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>Raum Northeim (Niedersachsen)</t>
+          <t>Korntal-Münchingen (Raum Stuttgart), Baden-Württemberg</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>Seit über 60 Jahren Hersteller von Lackfarben und Beschichtungen 'Made in Germany'; eigene Produktion mit Werksleitung und Labor.</t>
+          <t>Inhabergeführte Spedition seit 1987 mit Stückgut, Gefahrgut- und Pflanzentransporten sowie eigenem Lager-/Kommissionierzentrum (seit 2019). Eigene Bereiche für Umschlag, Lagerlogistik und Disposition.</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>https://www.dr-demuth.com/das-team</t>
+          <t>https://eckhardt-logistik.de/kontakt/ansprechpartner | https://eckhardt-logistik.de/</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>Ludwig Haring</t>
+          <t>Marc Eckhardt</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführung</t>
+          <t>Gesellschafter (Inhaberfamilie)</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>l.haring@dr-demuth.com</t>
+          <t>m.eckhardt@eckhardt-logistik.de</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>+49 5551 9794-10</t>
+          <t>+49 711 80000-0 (Zentrale)</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>Dr. Demuth Derisol Lackfarben GmbH &amp; Co. KG</t>
+          <t>Walter Eckhardt GmbH Spedition + Logistik</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>Chemie &amp; Prozessindustrie</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>Raum Northeim (Niedersachsen)</t>
+          <t>Korntal-Münchingen (Raum Stuttgart), Baden-Württemberg</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>Seit über 60 Jahren Hersteller von Lackfarben und Beschichtungen 'Made in Germany'; eigene Produktion mit Werksleitung und Labor.</t>
+          <t>Gesellschafter und Namensträger des familiengeführten Speditions- und Logistikunternehmens; zweiter Entscheidungsträger neben der Geschäftsführung.</t>
         </is>
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>https://www.dr-demuth.com/das-team | https://www.dr-demuth.com/das-team (Zitat: 'Unser Team von rund 60 Mitarbeitern')</t>
+          <t>https://eckhardt-logistik.de/kontakt/ansprechpartner | https://eckhardt-logistik.de/</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>Olaf Fresdorf</t>
+          <t>Dirk Valerius</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Leitung Produktion sowie Leitung Beratung und Verkauf</t>
+          <t>Geschäftsführender Gesellschafter</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>fresdorf@eurotech-kunststofftechnik.de</t>
+          <t>d.valerius@werneke.de</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>+49 208 6209220</t>
+          <t>02922 / 8060 - 260</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>Eurotech Kunststofftechnik GmbH</t>
+          <t>Werneke Logistic GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>Chemie &amp; Prozessindustrie</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>Oberhausen (Otto-Roelen-Straße 1, 46147)</t>
+          <t>Werl (Kreis Soest / Südwestfalen)</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>Kunststoffverarbeitender Betrieb im Ruhrgebiet (Halbzeuge, Zuschnitt, Fertigteile) mit eigener Produktion und technischer Beratung.</t>
+          <t>Inhabergeführter Logistikdienstleister mit Stückgut, Sammelgut, Charterverkehr und vier Lagerstandorten (Kontraktlogistik). Familie Werneke weiterhin im Unternehmen aktiv.</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>https://www.eurotech.nrw/unternehmen</t>
+          <t>https://www.werneke.de/ansprechpartner | https://www.regiomanager.de/suedwestfalen/ranking/mobilitaet-logistik/spedition-und-logistik/kreis-soest/</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>Gerd Kleemeyer</t>
+          <t>Jörg Küpper</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
@@ -6946,64 +6946,64 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>gerd.kleemeyer@gera-chemie.de</t>
+          <t>j.kuepper@d-log.de</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>+49 208 802080</t>
+          <t>+49 201 2897960</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>GERA Chemie GmbH</t>
+          <t>d-log GmbH</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>Chemie &amp; Prozessindustrie</t>
+          <t>Logistik &amp; Supply Chain</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>Mülheim an der Ruhr</t>
+          <t>Essen</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>Inhabergeführter Hersteller/Konfektionierer chemischer Spezialitäten mit eigener Produktion und Labor im Ruhrgebiet.</t>
+          <t>Inhabergeführter Logistikdienstleister aus Essen (Schacht Neu-Cöln) mit Transport-, Lager- und Distributionslogistik im Ruhrgebiet.</t>
         </is>
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>https://www.gera-chemie.de/team/</t>
+          <t>https://www.d-log.de/impressum | https://www.regiomanager.de/ranking/mobilitaet-logistik/spedition-und-logistik/essen/</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>Rainer Hähnle</t>
+          <t>Johan Bogaerts</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Einkaufsleiter</t>
+          <t>Geschäftsführer</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>rainer.haehnle@haering.de</t>
+          <t>johan.bogaerts@arichemie.com</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>+49 7130 4702-70</t>
+          <t>+49 6198 5912-0 (Zentrale; keine persönliche Durchwahl veröffentlicht)</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>HAERING GmbH</t>
+          <t>ARICHEMIE GmbH</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
@@ -7013,44 +7013,44 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>Untergruppenbach-Unterheinriet (Baden-Württemberg)</t>
+          <t>Eppstein-Bremthal (Hessen)</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>Seit rund 140 Jahren mittelständischer Hersteller von Farben, Lacken und Bautenschutzprodukten mit eigenem Farbstudio und Auslieferungslager.</t>
+          <t>Inhabergeführte Füllstoff- und Farbenfabrik, entwickelt und produziert Pigment-Präparationen ausschließlich für B2B-Kunden. Mitglied bei HessenChemie.</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>https://www.haering.de/kontakt | https://www.haering.de/unternehmen (Zitat: '100 Mitarbeiter') | https://www.haering-lacke.de/kontakt</t>
+          <t>https://arichemie.com/de/arichemie/kontakt/ | https://www.arichemie.com | https://www.hessenchemie.de/mitgliedsunternehmen</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>Sergey Krasnikov</t>
+          <t>Adem Baygin</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>EDV-Leiter (IT)</t>
+          <t>Prokurist, Leitung Vertrieb</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>sergey.krasnikov@haering.de</t>
+          <t>a.baygin@astorplast.de</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>+49 7130 4702-32</t>
+          <t>+49 7172 303-47</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>HAERING GmbH</t>
+          <t>ASTORPLAST Klebetechnik GmbH</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
@@ -7060,44 +7060,44 @@
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>Untergruppenbach-Unterheinriet (Baden-Württemberg)</t>
+          <t>Alfdorf (Baden-Württemberg)</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>Seit rund 140 Jahren mittelständischer Hersteller von Farben, Lacken und Bautenschutzprodukten mit eigenem Farbstudio und Auslieferungslager.</t>
+          <t>Hersteller von Klebebändern und Klebelösungen, u. a. für Luft- und Winddichtung sowie Profiltechnik; Mitglied im Industrieverband Klebstoffe.</t>
         </is>
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>https://www.haering.de/kontakt</t>
+          <t>https://www.astorplast.de/kontakt | https://www.klebstoffe.com/mitglieder/</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>Daniel Neubner</t>
+          <t>Roland Albrecht</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Managing Director (Geschäftsführer)</t>
+          <t>Prokurist, Produktionsleitung</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>dn@harke.com</t>
+          <t>r.albrecht@aurora-kunststoffe.de</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>+49 208 3069-1050</t>
+          <t>+49 7942 9142-49</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>HARKE GROUP / HARKE Chemicals GmbH</t>
+          <t>AURORA Kunststoffe GmbH</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
@@ -7107,44 +7107,44 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>Mülheim an der Ruhr</t>
+          <t>Neuenstein (Baden-Württemberg)</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>Inhabergeführte Unternehmensgruppe für Spezialchemikalien, Distribution, Lohnabfüllung/CoPacking und Eigenprodukte (u.a. SOLUBLON). Sitz Xantener Straße 1, Mülheim an der Ruhr.</t>
+          <t>Mittelständischer Compoundeur für technische Kunststoff-Compounds und hochwertige Rezyklate mit eigener Extrusion.</t>
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>https://www.harke.com/contact/ | https://www.harke.com/harke-group/about-us/</t>
+          <t>https://www.aurora-kunststoffe.de/ansprechpartner</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>Benjamin Hille</t>
+          <t>Thomas Rätzsch</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>Leiter Logistik</t>
+          <t>Geschäftsleitung</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>benjamin.hille@harold-scholz.de</t>
+          <t>t.raetzsch@aurora-kunststoffe.de</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>+49 2361 98880</t>
+          <t>+49 7942 9142-0</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>Harold Scholz &amp; Co. GmbH (Scholz Farbpigmente)</t>
+          <t>AURORA Kunststoffe GmbH</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr">
@@ -7154,44 +7154,44 @@
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>Recklinghausen (Suderwich)</t>
+          <t>Neuenstein (Baden-Württemberg)</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>Familiengeführter Hersteller von Farbpigmenten und Pigmentpräparationen für Bau, Farbe &amp; Lack sowie Kunststoff, mit Tochtergesellschaften in AT, CH und BeNeLux.</t>
+          <t>Mittelständischer Compoundeur für technische Kunststoff-Compounds und hochwertige Rezyklate mit eigener Extrusion.</t>
         </is>
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>https://www.harold-scholz.de/uber-uns/unser-team | https://www.harold-scholz.de/impressum</t>
+          <t>https://www.aurora-kunststoffe.de/ansprechpartner | https://www.aurora-kunststoffe.de/kontakt/</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>Dirk Ruppmann</t>
+          <t>Senol Topcu</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Betriebsleitung / Prokurist</t>
+          <t>Geschäftsführer</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>dirkruppmann@kapp-chemie.com</t>
+          <t>s.topcu@chemopur.info</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>+49 6772 9311-250</t>
+          <t>+49 2323 98797-0</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>KAPP-CHEMIE GmbH &amp; Co. KG</t>
+          <t>CHEMOPUR H. Brand GmbH</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
@@ -7201,44 +7201,44 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>Miehlen (Rheinland-Pfalz)</t>
+          <t>Herne (Baukauer Str. 125, 44653 Herne)</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>Mittelständischer Spezialchemie-Hersteller (u. a. Farbstoffe, technische Chemikalien, Lohnfertigung). Gehört zur familiengeführten STOCKMEIER-Gruppe.</t>
+          <t>Mittelständischer Hersteller von Polyurethan- und Reaktionsharzsystemen sowie Beschichtungs-/Bauchemieprodukten mit eigener Anwendungstechnik und F&amp;E.</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>https://www.stockmeier.com/de/kapp-chemie/kontakt/ | https://www.kapp-chemie.de/de/kapp-chemie/kontakt/</t>
+          <t>https://chemopur.de/kontakt/ | https://chemopur.de/impressum/</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>Hendrik Breiden</t>
+          <t>Martin Polczyk</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>Leitung Einkauf/Logistik</t>
+          <t>Managing Director / CEO</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>hendrikbreiden@kapp-chemie.com</t>
+          <t>polczyk@cofermin.de</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>+49 6772 9311-150</t>
+          <t>+49 201 43878-35</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>KAPP-CHEMIE GmbH &amp; Co. KG</t>
+          <t>COFERMIN Group / Cofermin Chemicals GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr">
@@ -7248,44 +7248,44 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>Miehlen (Rheinland-Pfalz)</t>
+          <t>Essen</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>Mittelständischer Spezialchemie-Hersteller (u. a. Farbstoffe, technische Chemikalien, Lohnfertigung). Gehört zur familiengeführten STOCKMEIER-Gruppe.</t>
+          <t>Inhabergeführte Essener Gruppe für Chemikalien- und Mineralstoffhandel, Feuerfest und chemische Spezialitäten mit mehreren Produktions- und Handelsgesellschaften.</t>
         </is>
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>https://www.stockmeier.com/de/kapp-chemie/kontakt/ | https://www.kapp-chemie.de/de/kapp-chemie/kontakt/</t>
+          <t>https://cofermin.de/ansprechpartner/</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>Marco Hermann</t>
+          <t>Franco Menchetti</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer</t>
+          <t>Vertriebsleiter &amp; Prokurist</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>marcohermann@kapp-chemie.com</t>
+          <t>Franco.Menchetti@cta-gmbh.de</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>+49 6772 9311-360</t>
+          <t>+49 7141 299916-148</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>KAPP-CHEMIE GmbH &amp; Co. KG</t>
+          <t>CTA GmbH</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr">
@@ -7295,44 +7295,44 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>Miehlen (Rheinland-Pfalz)</t>
+          <t>Ludwigsburg (Baden-Württemberg)</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>Mittelständischer Spezialchemie-Hersteller (u. a. Farbstoffe, technische Chemikalien, Lohnfertigung). Gehört zur familiengeführten STOCKMEIER-Gruppe.</t>
+          <t>Lohnabfüller und Lohnfertiger für chemisch-technische Produkte (Flüssigkeiten, Aerosole, Sets) inkl. Standort in den USA.</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>https://www.stockmeier.com/de/kapp-chemie/kontakt/ | https://www.kapp-chemie.de/de/kapp-chemie/kontakt/</t>
+          <t>https://www.cta-gmbh.de/kontakt/ | https://www.cta-gmbh.de/lohnabfuellung-in-den-usa-ihre-ansprechpartner/</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>Jochen Obermeier</t>
+          <t>Hans-Dieter Worch</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>CEO / Geschäftsleitung (Inhaberfamilie)</t>
+          <t>Geschäftsführer</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>jochen.obermeier@obermeier.de</t>
+          <t>hans-dieter.worch@cta-gmbh.de</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>+49 2751 524-0</t>
+          <t>+49 7141 299916-0 (Zentrale; keine persönliche Durchwahl veröffentlicht)</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>Kurt Obermeier GmbH &amp; Co. KG</t>
+          <t>CTA GmbH</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr">
@@ -7342,44 +7342,44 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>Bad Berleburg (Wittgenstein/Westfalen)</t>
+          <t>Ludwigsburg (Baden-Württemberg)</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>Familienunternehmen der Spezialchemie: Silikone, Trennmittel, Metallbearbeitungs- und Spezialchemikalien mit eigenem Vertrieb und Anwendungstechnik/F&amp;E.</t>
+          <t>Lohnabfüller und Lohnfertiger für chemisch-technische Produkte (Flüssigkeiten, Aerosole, Sets) inkl. Standort in den USA.</t>
         </is>
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>https://www.obermeier.de/kontakt/ansprechpartner/</t>
+          <t>https://www.cta-gmbh.de/lohnabfuellung-in-den-usa-ihre-ansprechpartner/ | https://www.cta-gmbh.de/kontakt/ (dort: 'Hans-Dieter Worch Geschäftsführer')</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>Tobias Adamczyk</t>
+          <t>Benjamin Wrobel</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Manager</t>
+          <t>COO (Chief Operating Officer)</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>tobias.adamczyk@orontec.com</t>
+          <t>b.wrobel@wocklum.de</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>+49 202 52746318</t>
+          <t>+49 2375 925 291</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>ORONTEC GmbH &amp; Co. KG</t>
+          <t>Chemische Fabrik Wocklum (Wocklum Chemie)</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr">
@@ -7389,44 +7389,44 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Dortmund (Hauptsitz), Niederlassung Wuppertal</t>
+          <t>Balve (Sauerland/Westfalen)</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>Mittelständischer Anbieter chemisch-technischer Spezialprodukte und Prozesschemikalien für Industrieanwendungen mit internationalen Partnerstandorten.</t>
+          <t>Familiengeführte Chemiegruppe mit Lohnfertigung/Contract Manufacturing, Bulk-Handel sowie Recycling und Entsorgung chemischer Produkte. Geschäftsführer laut Seite: Gero Hertin (nur Sammeladresse geschaeftsfuehrung@wocklum-gruppe.de).</t>
         </is>
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>https://orontec.com/kontakt/ | https://orontec.com/unternehmen/standorte/</t>
+          <t>https://wocklum-chemie.de/kontakt/</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>Marko Sonnemann</t>
+          <t>Julian Cirkel</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer</t>
+          <t>Geschäftsführer (Managing Director), Inhaberfamilie</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>ms@pentacarbon.de</t>
+          <t>julian.cirkel@cirkel.de</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>+49 2364 89979-70</t>
+          <t>+49 2364 938124</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>PentaCarbon GmbH</t>
+          <t>Cirkel GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr">
@@ -7436,44 +7436,44 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>Haltern am See</t>
+          <t>Haltern am See (Werk Wickede, Standort Emsdetten)</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>Inhabergeführter Spezialist für Kohlenstoff-/Graphitprodukte und technische Rohstoffe für die Prozessindustrie mit eigener Materialwirtschaft und Standorten in Polen und der Ukraine.</t>
+          <t>Familiengeführter Hersteller mineralischer Bau- und Prozessstoffe (Baustoffe, multifunktionale Mineralien) mit mehreren Produktionsstandorten in NRW.</t>
         </is>
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>https://www.pentacarbon.de/unternehmen/</t>
+          <t>https://www.cirkel.de/kontakt</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>Oliver Sentek</t>
+          <t>Dr. Sabrina Mondrzyk</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Geschäftsführer</t>
+          <t>Kaufmännische Leitung</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>sentek@technifol.de</t>
+          <t>sabrina.mondrzyk@dhc-solvent.de</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>+49 2368 87962-22</t>
+          <t>+49 208 9940-161</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>Technifol Verpackungsfolien GmbH</t>
+          <t>DHC Solvent Chemie GmbH</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
@@ -7483,69 +7483,774 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>Oer-Erkenschwick (Karlstr. 1, 45739)</t>
+          <t>Mülheim an der Ruhr</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>Anbieter von Kunststoff-Verpackungsfolien und Verpackungsmaschinen inkl. eigenem Service; zweiter Geschäftsführer Manuel Zielke (zielke@technifol.de).</t>
+          <t>Hersteller und Aufbereiter von Lösemitteln und Lösemittelrecycling für Lack-, Klebstoff- und Prozessindustrie. Geschäftsführer laut Impressum: Thomas Schreiber, Michaela Hodyas (nur info@-Adresse veröffentlicht).</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>https://technifol.de/ansprechpartner/</t>
+          <t>https://dhc-solvent.de/vertrieb/ | https://dhc-solvent.de/impressum/</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>Dimitri Peters</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>Werksleiter (Produktion)</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>d.peters@dr-demuth.com</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>+49 5551 9794-36</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Demuth Derisol Lackfarben GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>Chemie &amp; Prozessindustrie</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>Raum Northeim (Niedersachsen)</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>Seit über 60 Jahren Hersteller von Lackfarben und Beschichtungen 'Made in Germany'; eigene Produktion mit Werksleitung und Labor.</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dr-demuth.com/das-team</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>Ludwig Haring</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführung</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>l.haring@dr-demuth.com</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>+49 5551 9794-10</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Demuth Derisol Lackfarben GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>Chemie &amp; Prozessindustrie</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>Raum Northeim (Niedersachsen)</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>Seit über 60 Jahren Hersteller von Lackfarben und Beschichtungen 'Made in Germany'; eigene Produktion mit Werksleitung und Labor.</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dr-demuth.com/das-team | https://www.dr-demuth.com/das-team (Zitat: 'Unser Team von rund 60 Mitarbeitern')</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>Olaf Fresdorf</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>Leitung Produktion sowie Leitung Beratung und Verkauf</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>fresdorf@eurotech-kunststofftechnik.de</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>+49 208 6209220</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>Eurotech Kunststofftechnik GmbH</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>Chemie &amp; Prozessindustrie</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>Oberhausen (Otto-Roelen-Straße 1, 46147)</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>Kunststoffverarbeitender Betrieb im Ruhrgebiet (Halbzeuge, Zuschnitt, Fertigteile) mit eigener Produktion und technischer Beratung.</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>https://www.eurotech.nrw/unternehmen</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>Gerd Kleemeyer</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführer</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>gerd.kleemeyer@gera-chemie.de</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>+49 208 802080</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>GERA Chemie GmbH</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>Chemie &amp; Prozessindustrie</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>Mülheim an der Ruhr</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>Inhabergeführter Hersteller/Konfektionierer chemischer Spezialitäten mit eigener Produktion und Labor im Ruhrgebiet.</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gera-chemie.de/team/</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>Rainer Hähnle</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>Einkaufsleiter</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>rainer.haehnle@haering.de</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>+49 7130 4702-70</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>HAERING GmbH</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>Chemie &amp; Prozessindustrie</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>Untergruppenbach-Unterheinriet (Baden-Württemberg)</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>Seit rund 140 Jahren mittelständischer Hersteller von Farben, Lacken und Bautenschutzprodukten mit eigenem Farbstudio und Auslieferungslager.</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>https://www.haering.de/kontakt | https://www.haering.de/unternehmen (Zitat: '100 Mitarbeiter') | https://www.haering-lacke.de/kontakt</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>Sergey Krasnikov</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>EDV-Leiter (IT)</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>sergey.krasnikov@haering.de</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>+49 7130 4702-32</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>HAERING GmbH</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>Chemie &amp; Prozessindustrie</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>Untergruppenbach-Unterheinriet (Baden-Württemberg)</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>Seit rund 140 Jahren mittelständischer Hersteller von Farben, Lacken und Bautenschutzprodukten mit eigenem Farbstudio und Auslieferungslager.</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t>https://www.haering.de/kontakt</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>Daniel Neubner</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director (Geschäftsführer)</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>dn@harke.com</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>+49 208 3069-1050</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>HARKE GROUP / HARKE Chemicals GmbH</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>Chemie &amp; Prozessindustrie</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>Mülheim an der Ruhr</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>Inhabergeführte Unternehmensgruppe für Spezialchemikalien, Distribution, Lohnabfüllung/CoPacking und Eigenprodukte (u.a. SOLUBLON). Sitz Xantener Straße 1, Mülheim an der Ruhr.</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>https://www.harke.com/contact/ | https://www.harke.com/harke-group/about-us/</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>Benjamin Hille</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>Leiter Logistik</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>benjamin.hille@harold-scholz.de</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>+49 2361 98880</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>Harold Scholz &amp; Co. GmbH (Scholz Farbpigmente)</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>Chemie &amp; Prozessindustrie</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>Recklinghausen (Suderwich)</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>Familiengeführter Hersteller von Farbpigmenten und Pigmentpräparationen für Bau, Farbe &amp; Lack sowie Kunststoff, mit Tochtergesellschaften in AT, CH und BeNeLux.</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>https://www.harold-scholz.de/uber-uns/unser-team | https://www.harold-scholz.de/impressum</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>Dirk Ruppmann</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>Betriebsleitung / Prokurist</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>dirkruppmann@kapp-chemie.com</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>+49 6772 9311-250</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>KAPP-CHEMIE GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>Chemie &amp; Prozessindustrie</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>Miehlen (Rheinland-Pfalz)</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>Mittelständischer Spezialchemie-Hersteller (u. a. Farbstoffe, technische Chemikalien, Lohnfertigung). Gehört zur familiengeführten STOCKMEIER-Gruppe.</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>https://www.stockmeier.com/de/kapp-chemie/kontakt/ | https://www.kapp-chemie.de/de/kapp-chemie/kontakt/</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>Hendrik Breiden</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>Leitung Einkauf/Logistik</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>hendrikbreiden@kapp-chemie.com</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>+49 6772 9311-150</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>KAPP-CHEMIE GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>Chemie &amp; Prozessindustrie</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>Miehlen (Rheinland-Pfalz)</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>Mittelständischer Spezialchemie-Hersteller (u. a. Farbstoffe, technische Chemikalien, Lohnfertigung). Gehört zur familiengeführten STOCKMEIER-Gruppe.</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>https://www.stockmeier.com/de/kapp-chemie/kontakt/ | https://www.kapp-chemie.de/de/kapp-chemie/kontakt/</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>Marco Hermann</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführer</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>marcohermann@kapp-chemie.com</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>+49 6772 9311-360</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>KAPP-CHEMIE GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>Chemie &amp; Prozessindustrie</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>Miehlen (Rheinland-Pfalz)</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>Mittelständischer Spezialchemie-Hersteller (u. a. Farbstoffe, technische Chemikalien, Lohnfertigung). Gehört zur familiengeführten STOCKMEIER-Gruppe.</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>https://www.stockmeier.com/de/kapp-chemie/kontakt/ | https://www.kapp-chemie.de/de/kapp-chemie/kontakt/</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>Jochen Obermeier</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>CEO / Geschäftsleitung (Inhaberfamilie)</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>jochen.obermeier@obermeier.de</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>+49 2751 524-0</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>Kurt Obermeier GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>Chemie &amp; Prozessindustrie</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>Bad Berleburg (Wittgenstein/Westfalen)</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>Familienunternehmen der Spezialchemie: Silikone, Trennmittel, Metallbearbeitungs- und Spezialchemikalien mit eigenem Vertrieb und Anwendungstechnik/F&amp;E.</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="inlineStr">
+        <is>
+          <t>https://www.obermeier.de/kontakt/ansprechpartner/</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>Tobias Adamczyk</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Manager</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>tobias.adamczyk@orontec.com</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>+49 202 52746318</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>ORONTEC GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>Chemie &amp; Prozessindustrie</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>Dortmund (Hauptsitz), Niederlassung Wuppertal</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>Mittelständischer Anbieter chemisch-technischer Spezialprodukte und Prozesschemikalien für Industrieanwendungen mit internationalen Partnerstandorten.</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="inlineStr">
+        <is>
+          <t>https://orontec.com/kontakt/ | https://orontec.com/unternehmen/standorte/</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>Marko Sonnemann</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführer</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>ms@pentacarbon.de</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>+49 2364 89979-70</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>PentaCarbon GmbH</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>Chemie &amp; Prozessindustrie</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>Haltern am See</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>Inhabergeführter Spezialist für Kohlenstoff-/Graphitprodukte und technische Rohstoffe für die Prozessindustrie mit eigener Materialwirtschaft und Standorten in Polen und der Ukraine.</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>https://www.pentacarbon.de/unternehmen/</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>Oliver Sentek</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>Geschäftsführer</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>sentek@technifol.de</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>+49 2368 87962-22</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>Technifol Verpackungsfolien GmbH</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>Chemie &amp; Prozessindustrie</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>Oer-Erkenschwick (Karlstr. 1, 45739)</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>Anbieter von Kunststoff-Verpackungsfolien und Verpackungsmaschinen inkl. eigenem Service; zweiter Geschäftsführer Manuel Zielke (zielke@technifol.de).</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>https://technifol.de/ansprechpartner/</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
           <t>Michael Stache</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
+      <c r="B166" s="2" t="inlineStr">
         <is>
           <t>Geschäftsführender Gesellschafter</t>
         </is>
       </c>
-      <c r="C151" s="2" t="inlineStr">
+      <c r="C166" s="2" t="inlineStr">
         <is>
           <t>michael.stache@wigol.de</t>
         </is>
       </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="D166" s="2" t="inlineStr">
         <is>
           <t>+49 6241 4141-0 (Zentrale; keine persönliche Durchwahl veröffentlicht)</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E166" s="2" t="inlineStr">
         <is>
           <t>WIGOL W. Stache GmbH</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F166" s="2" t="inlineStr">
         <is>
           <t>Chemie &amp; Prozessindustrie</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr">
+      <c r="G166" s="2" t="inlineStr">
         <is>
           <t>Worms (Rheinland-Pfalz)</t>
         </is>
       </c>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="H166" s="2" t="inlineStr">
         <is>
           <t>Familiengeführter Hersteller von Reinigungs- und Prozesschemie für Lebensmittel-/Getränke-, Pharma-, Kosmetikindustrie sowie Oberflächentechnik und Industriereinigung.</t>
         </is>
       </c>
-      <c r="I151" s="2" t="inlineStr">
+      <c r="I166" s="2" t="inlineStr">
         <is>
           <t>https://www.wigol.de/de/kontakt</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I151"/>
+  <autoFilter ref="A1:I166"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7601,10 +8306,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="C3" t="n">
-        <v>105</v>
+        <v>163</v>
       </c>
     </row>
     <row r="4">
@@ -7640,10 +8345,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="C6" t="n">
-        <v>392</v>
+        <v>450</v>
       </c>
     </row>
   </sheetData>
@@ -7657,7 +8362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D393"/>
+  <dimension ref="A1:D451"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -16312,6 +17017,1282 @@
         </is>
       </c>
     </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>Wemhöner Surface Technologies GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Herford</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>Auf Homepage, /kontakt und /ueber-uns/vertrieb nur info@-Adressen bzw. E-Mails ausländischer Handelsvertreter – keine persönliche Adresse eines deutschen Entscheiders</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>KOLBUS GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>Rahden</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>Kontaktseite listet nur Regional Sales Manager / Area Service Manager, keine Geschäftsführung oder Bereichsleitung Produktion/IT/Logistik</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>Gebrüder Lödige Maschinenbau GmbH</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Paderborn</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>Nur eine persönliche Adresse (Backoffice Sales Frankreich), kein Entscheidungsträger</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>Achenbach Buschhüttten GmbH</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Kreuztal</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>Kontaktseite ausschließlich Funktionspostfächer (einkauf@, personal@, sales@, fertigung@)</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>HAVER &amp; BOECKER OHG</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Oelde</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>Persönliche Adressen vorhanden, aber nur Geschäftsbereichs-/Vertriebsansprechpartner ohne Leitungstitel; Gruppe zudem &gt;1000 MA</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>Herbert Kannegiesser GmbH</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Vlotho</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>Website liefert nur Splash-/Weiterleitungsseite (14 KB), keine Team- oder Ansprechpartnerseite crawlbar</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>DENIOS SE</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Bad Oeynhausen</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>Nur Personalreferent:innen (HR) mit persönlicher Adresse, keine Zielrolle</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>MENNEKES Elektrotechnik GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Kirchhundem</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>Persönliche Adressen nur von Presse-/Marketing-Mitarbeitenden</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>EJOT SE &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Bad Laasphe</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>Persönliche Adressen ausschließlich Recruiting/Ausbildung</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>SCHÄFER Werke GmbH</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Neunkirchen (Siegerland)</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>Einzige persönliche Adresse ist der Leiter Personalwesen – keine Zielrolle</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>BOGE KOMPRESSOREN Otto Boge GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>Bielefeld</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>Einzige persönliche Adresse ist Leiter Marketing (Pressekontakt), keine Zielrolle</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>Bernhard Hohage GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>Kierspe</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>Kontaktseite listet nur Teamleiter Vertrieb und Key-Account-Manager, keine Geschäftsführung</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>Dango &amp; Dienenthal Maschinenbau GmbH</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Siegen</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>Ansprechpartnerseite enthält nur Auslandsvertretungen (UK/USA) und career@</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>SKS metaplast Scheffer-Klute GmbH</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Sundern</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>Persönliche Adresse nur für Praktikumsanfragen; übrige Kontakte sind Auslandsvertriebe</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>Isringhausen (isringhausen.com)</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>Lemgo</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>Domain gehört einem gleichnamigen US-Autohaus – Fehltreffer, keine Relevanz</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>technotrans SE</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>Sassenberg</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>Börsennotierte SE, kein familien-/inhabergeführtes Unternehmen (Ausschlusskriterium Konzern)</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>Paul Craemer GmbH</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>Herzebrock-Clarholz</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>Persönliche Adressen nur in der Routing-Konfiguration des Kontaktformulars, ohne Namens-/Positionszuordnung auf der Seite</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>JÖST GmbH + Co. KG</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Dülmen</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>Persönliche Adressen nur von Verkaufsingenieuren an auswärtigen Standorten, keine Leitungsfunktion</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>OBO Bettermann Holding GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Menden</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>Nur Funktionspostfächer (info@, digital@); zudem Konzerngröße</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>TRILUX GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>Arnsberg</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>Nur Funktionspostfächer (lms@, career@)</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>ERCO GmbH</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Lüdenscheid</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>Nur Hinweisgebersystem-Adresse (speakup@), keine Personenkontakte</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>Hueck-Gruppe</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Lüdenscheid</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>Persönliche Adresse nur im Personalwesen-Kontext, Bewerbungen an jobs@</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>SIEGENIA-AUBI KG</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Siegen</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>Nur eine persönliche Adresse ohne Namens-/Positionskontext im HTML</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>Spaleck GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Bocholt</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>Ansprechpartnerseite (960 KB) enthält keine E-Mail-Adressen, nur Formular</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>ELHA-MASCHINENBAU Liemke KG</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Hövelhof</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>Team- und Kontaktseite ohne E-Mail-Adressen</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>Remmert GmbH</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>Löhne</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>Nur Funktionspostfächer (info@, sales@, hotline@)</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>Sollich KG</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Bad Salzuflen</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>Persönliche Adressen nur bei Auslandsvertretungen</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>ROSE Systemtechnik GmbH</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>Porta Westfalica</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>Kontaktseiten national/international ohne persönliche E-Mail-Adressen</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>Börger GmbH</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Borken</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>Keine persönlichen E-Mail-Adressen auf Kontakt-/Unternehmensseiten</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>L.B. Bohle Maschinen + Verfahren GmbH</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Ennigerloh</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>Nur inquiry@ sowie eine Adresse der indischen Tochter</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>Wilhelm Severt Maschinenbau GmbH</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Vreden</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>Keine persönlichen E-Mail-Adressen auffindbar</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>Othmerding Maschinenbau GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Ascheberg-Davensberg</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>Keine persönlichen E-Mail-Adressen auffindbar</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>Strothmann Machines &amp; Handling GmbH</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Schloß Holte-Stukenbrock</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>Keine persönlichen E-Mail-Adressen auffindbar</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>Venjakob Maschinenbau GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>Rheda-Wiedenbrück</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>Keine persönlichen E-Mail-Adressen auffindbar</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>KRACHT GmbH</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Werdohl</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>Persönliche Adressen nur im Karrierebereich (Recruiting)</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>Klemm Bohrtechnik GmbH</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Drolshagen</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>Keine persönlichen E-Mail-Adressen auffindbar</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>Rickmeier GmbH</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Balve</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>E-Mail-Adressen base64-verschleiert und nur Funktionspostfächer (products-a@, products-e@)</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>HST Systemtechnik GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>Meschede</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>Keine persönlichen E-Mail-Adressen auffindbar</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>Ohrmann GmbH</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>Möhnesee</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>Keine persönlichen E-Mail-Adressen auffindbar</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>OPS-Ingersoll Funkenerosion GmbH</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Burbach</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>Keine persönlichen E-Mail-Adressen auffindbar</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>Gräbener Maschinentechnik GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>Netphen</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>Keine persönlichen E-Mail-Adressen auffindbar</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>Pekrun Getriebebau GmbH</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Iserlohn</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>Keine persönlichen E-Mail-Adressen auffindbar</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>Paul Köster GmbH</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>Medebach</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>Keine persönlichen E-Mail-Adressen auffindbar</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>Bilsing Automation GmbH</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>Attendorn</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>Keine persönlichen E-Mail-Adressen auffindbar</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>Krampe Werkzeuge GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Arnsberg</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>Keine persönlichen E-Mail-Adressen auffindbar</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>Garthe &amp; Stoltenhoff GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>Arnsberg</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>Keine persönlichen E-Mail-Adressen auffindbar</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>saritec GmbH</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Lüdenscheid</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>Keine persönlichen E-Mail-Adressen auffindbar</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>Arning Edelstahl &amp; Sondermaschinenbau GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>Münsterland</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>Keine persönlichen E-Mail-Adressen auffindbar</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>KMB Maschinenbau</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>OWL</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>Keine persönlichen E-Mail-Adressen auffindbar</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>BELU GmbH</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>Bielefeld</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>Keine persönlichen E-Mail-Adressen auffindbar</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>TEKAWE GmbH</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>OWL</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>Keine persönlichen E-Mail-Adressen auffindbar</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>Becker Sonder-Maschinenbau GmbH</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>OWL</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>Keine persönlichen E-Mail-Adressen auffindbar</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>AVENTUS GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>Warendorf</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>Nur Funktionspostfächer (info@, hotline@, purchasing@, ana@)</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>KORDEL Antriebstechnik GmbH</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>Dülmen</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>Nur Länder-Funktionspostfächer (china@, france@, usa@)</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>MGK Maschinenbau / ihs Industrie Handling + Fördertechnik GmbH</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>Freudenberg u.a.</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>Keine persönlichen E-Mail-Adressen auffindbar</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>Metzen Industries GmbH (Standorte außerhalb der Zielregion)</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>Hamburg/Bitburg/Sonsbeck</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>Nur der Standort Beckum liegt in der Zielregion; übrige Entscheider außerhalb NRW-Zielraum</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>Hanning &amp; Kahl GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>Oerlinghausen</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>Website nicht crawlbar (nur 1,7 KB Shell), keine Inhalte abrufbar</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>Böcker AG / Möller Werke / Dürkopp Fördertechnik / BSG Sondermaschinenbau / HKS Konstruktion</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>Werne / Bielefeld</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>Maschinenbau &amp; Fertigung</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>HTTP-Fehler bzw. nicht erreichbar, auch mit Browser-User-Agent</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
